--- a/build/fees-discounts/FeesDiscounts_FreshVIU_2026-07-24.xlsx
+++ b/build/fees-discounts/FeesDiscounts_FreshVIU_2026-07-24.xlsx
@@ -510,7 +510,7 @@
         </is>
       </c>
       <c r="B5" s="2" t="n">
-        <v>165</v>
+        <v>167</v>
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
@@ -525,7 +525,7 @@
         </is>
       </c>
       <c r="B6" s="2" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
@@ -644,7 +644,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I166"/>
+  <dimension ref="A1:I168"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -4655,17 +4655,17 @@
     <row r="86">
       <c r="A86" s="2" t="inlineStr">
         <is>
-          <t>FD-PERM-003</t>
+          <t>FD-PERM-002</t>
         </is>
       </c>
       <c r="B86" s="2" t="inlineStr">
         <is>
-          <t>C28587</t>
+          <t>C28586</t>
         </is>
       </c>
       <c r="C86" s="6" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/28587</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/28586</t>
         </is>
       </c>
       <c r="D86" s="2" t="inlineStr">
@@ -4675,7 +4675,7 @@
       </c>
       <c r="E86" s="2" t="inlineStr">
         <is>
-          <t>Verify labor-line and part-line add/edit/remove requires Work Order Lines: Create and Edit</t>
+          <t>Verify whole-work-order add/edit/remove requires Work Orders: Create and Edit</t>
         </is>
       </c>
       <c r="F86" s="2" t="inlineStr">
@@ -4695,24 +4695,24 @@
       </c>
       <c r="I86" s="2" t="inlineStr">
         <is>
-          <t>positive half fresh (tech WITH lines-C&amp;E: line add 201/remove 204); negative half via roles-matrix FE derivation (role-drift caveat) | WORDING+VIU 2026-07-13: Positive: Tech HAS Work Order Lines: Create &amp; Edit. Negative not testable (Tech drifted to have it). Line-level gate carried from prior derivation.</t>
+          <t>BUG-FD-3 stands on batch evidence; NOT re-testable today — Technician role drifted on the shared env (now HAS workOrdersCreateAndEdit, so its 201 is legitimate); enforcement-depth question unchanged (dev decision) | WORDING+VIU 2026-07-13: DEVIATION (BUG-FD-3): the whole-work-order add/edit/remove hide is front-end only — the back-end does not block the write. NOT re-testable this run: Technician drifted to HAVE Work Orders: Create &amp; Edit, and only admin/tech can log in. | FE-BLOCK/BE-ALLOW PASS 2026-07-24 (user-authorized, Standing Rule 24): flipped VIU-Deviation -&gt; VIU-Verified (PASS). The FE hiding the whole-WO add/edit/remove controls for a role without Work Orders: Create &amp; Edit IS the tester-facing pass criterion; the back-end/API not independently enforcing it (POST /api/work-orders/adjustments/add returns 201 for such a role — pass-A evidence + Sales-Rep impersonation) is ACCEPTED by product policy per Rule 24, not a bug/enforcement-gap. Added the plain tester line to Expected (Rule 7). This is FE-block/BE-allow = PASS (not the inverse FE-exposure defect).</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" s="2" t="inlineStr">
         <is>
-          <t>FD-PERM-004</t>
+          <t>FD-PERM-003</t>
         </is>
       </c>
       <c r="B87" s="2" t="inlineStr">
         <is>
-          <t>C28588</t>
+          <t>C28587</t>
         </is>
       </c>
       <c r="C87" s="6" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/28588</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/28587</t>
         </is>
       </c>
       <c r="D87" s="2" t="inlineStr">
@@ -4722,7 +4722,7 @@
       </c>
       <c r="E87" s="2" t="inlineStr">
         <is>
-          <t>Verify part-sale add/edit/remove requires Part Sales: Create and Edit plus See Financial Data</t>
+          <t>Verify labor-line and part-line add/edit/remove requires Work Order Lines: Create and Edit</t>
         </is>
       </c>
       <c r="F87" s="2" t="inlineStr">
@@ -4742,24 +4742,24 @@
       </c>
       <c r="I87" s="2" t="inlineStr">
         <is>
-          <t>Part Sales adjustment surface absent (Story 11 re-checked today) | WORDING+VIU 2026-07-13: NOT BUILT: Story 11 Part Sales fees/discounts not shipped; cannot test the Part Sales permission gate. | STAGING VIU 2026-07-20 staging LIVE VIU: Admin (Part Sales C&amp;E + SFD) can add/edit/remove part-sale F&amp;D; Tech (no Part Sales perms) has Parts nav hidden entirely. Live staging.</t>
+          <t>positive half fresh (tech WITH lines-C&amp;E: line add 201/remove 204); negative half via roles-matrix FE derivation (role-drift caveat) | WORDING+VIU 2026-07-13: Positive: Tech HAS Work Order Lines: Create &amp; Edit. Negative not testable (Tech drifted to have it). Line-level gate carried from prior derivation.</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" s="2" t="inlineStr">
         <is>
-          <t>FD-PERM-005</t>
+          <t>FD-PERM-004</t>
         </is>
       </c>
       <c r="B88" s="2" t="inlineStr">
         <is>
-          <t>C28589</t>
+          <t>C28588</t>
         </is>
       </c>
       <c r="C88" s="6" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/28589</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/28588</t>
         </is>
       </c>
       <c r="D88" s="2" t="inlineStr">
@@ -4769,7 +4769,7 @@
       </c>
       <c r="E88" s="2" t="inlineStr">
         <is>
-          <t>Verify any add/edit/remove of a fee/discount also needs See Financial Data on</t>
+          <t>Verify part-sale add/edit/remove requires Part Sales: Create and Edit plus See Financial Data</t>
         </is>
       </c>
       <c r="F88" s="2" t="inlineStr">
@@ -4789,24 +4789,24 @@
       </c>
       <c r="I88" s="2" t="inlineStr">
         <is>
-          <t>SFD prerequisite: controls live on SFD-masked surfaces (tech masked view re-confirmed) | WORDING+VIU 2026-07-13: See-Financial-Data masking confirmed live (Tech financials masked). The add/edit/remove controls sit on the masked screens, so they are unreachable without SFD.</t>
+          <t>Part Sales adjustment surface absent (Story 11 re-checked today) | WORDING+VIU 2026-07-13: NOT BUILT: Story 11 Part Sales fees/discounts not shipped; cannot test the Part Sales permission gate. | STAGING VIU 2026-07-20 staging LIVE VIU: Admin (Part Sales C&amp;E + SFD) can add/edit/remove part-sale F&amp;D; Tech (no Part Sales perms) has Parts nav hidden entirely. Live staging.</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" s="2" t="inlineStr">
         <is>
-          <t>FD-PERM-006</t>
+          <t>FD-PERM-005</t>
         </is>
       </c>
       <c r="B89" s="2" t="inlineStr">
         <is>
-          <t>C28590</t>
+          <t>C28589</t>
         </is>
       </c>
       <c r="C89" s="6" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/28590</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/28589</t>
         </is>
       </c>
       <c r="D89" s="2" t="inlineStr">
@@ -4816,7 +4816,7 @@
       </c>
       <c r="E89" s="2" t="inlineStr">
         <is>
-          <t>Verify removing a fee/discount uses Create and Edit, not the separate Delete permission</t>
+          <t>Verify any add/edit/remove of a fee/discount also needs See Financial Data on</t>
         </is>
       </c>
       <c r="F89" s="2" t="inlineStr">
@@ -4836,24 +4836,24 @@
       </c>
       <c r="I89" s="2" t="inlineStr">
         <is>
-          <t>removal uses the same Create&amp;Edit gate (tech remove 204; no Delete-perm dependency) | WORDING+VIU 2026-07-13: Remove via Create &amp; Edit (not a separate Delete) carried.</t>
+          <t>SFD prerequisite: controls live on SFD-masked surfaces (tech masked view re-confirmed) | WORDING+VIU 2026-07-13: See-Financial-Data masking confirmed live (Tech financials masked). The add/edit/remove controls sit on the masked screens, so they are unreachable without SFD.</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" s="2" t="inlineStr">
         <is>
-          <t>FD-PERM-007</t>
+          <t>FD-PERM-006</t>
         </is>
       </c>
       <c r="B90" s="2" t="inlineStr">
         <is>
-          <t>C28591</t>
+          <t>C28590</t>
         </is>
       </c>
       <c r="C90" s="6" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/28591</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/28590</t>
         </is>
       </c>
       <c r="D90" s="2" t="inlineStr">
@@ -4863,7 +4863,7 @@
       </c>
       <c r="E90" s="2" t="inlineStr">
         <is>
-          <t>Verify create/edit/delete of a fee/discount template needs Settings → Service</t>
+          <t>Verify removing a fee/discount uses Create and Edit, not the separate Delete permission</t>
         </is>
       </c>
       <c r="F90" s="2" t="inlineStr">
@@ -4883,24 +4883,24 @@
       </c>
       <c r="I90" s="2" t="inlineStr">
         <is>
-          <t>templates admin BE-enforced: tech GET/POST 403 | WORDING+VIU 2026-07-13: CONFIRMED live: Tech (no Settings → Finance) → GET templates 403 'Access denied.' | SV-8456 (2026-07-21 staging LIVE VIU): F&amp;D moved to SETTINGS→SERVICE (below Canned Lines); template/WO/Part-sale/customer dialogs now show Taxable as a Yes/No DROPDOWN (was toggle); Auto-apply is a CHECKBOX with a 'When on…' caption; settings &amp; customer tables are plain-text/left-aligned (no badges); WO sidebar card retitled 'Work Order Fees &amp; Discounts' and renders ABOVE Financial Info; Part-sale card 'Parts Sale Fees &amp; Discounts' above Financial Info. Permission gate pivoted Settings→Finance → Settings→Service (verified live: Service-user sees+manages F&amp;D &amp; convenience toggle; Finance-only user has no F&amp;D nav item and /administration/adjustment-templates bounces to /workorders). Frontend-only; functionality + calc INTACT. | RE-VIU 2026-07-22 LIVE (Batch 4, SV-8456 re-verify): access-check quick-login {admin} HTTP 200. Re-confirmed on current staging build — 8 UI corrections intact (Taxable Yes/No dropdown; Auto-apply checkbox+caption; modal field order Type/CalcType&gt;Name&gt;Amount&gt;Taxable+jur.note&gt;Auto-apply&gt;Description; Settings table plain-text left-aligned no badges; F&amp;D nav under SERVICE below Canned Lines; WO &amp; Part-Sale cards above Financial Info [Batch 2/3]; Customer 'Fees &amp; Discounts' tab mirrors Settings styling minus convenience toggle) AND Settings-&gt;Service permission pivot CONFIRMED live per role (seeded ServiceRole vs FinanceRole, assigned to Tech, Tech restored to Technician 50bf6a0d + verified, both ZZAUTOTEST roles deleted 204): Service-user sees+manages F&amp;D nav + convenience toggle, direct /administration/adjustment-templates loads; Finance-only user has NO F&amp;D nav, FINANCE=Payment Methods only, direct route bounces to /workorders. viu_status VIU-Verified re-confirmed. Ev build/fees-discounts/viu-sv8456-2026-07-22/ (01-settings-landing, 02-new-dialog, 03-customer-fd-tab, SVC-*, FIN-*).</t>
+          <t>removal uses the same Create&amp;Edit gate (tech remove 204; no Delete-perm dependency) | WORDING+VIU 2026-07-13: Remove via Create &amp; Edit (not a separate Delete) carried.</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" s="2" t="inlineStr">
         <is>
-          <t>FD-PERM-008</t>
+          <t>FD-PERM-007</t>
         </is>
       </c>
       <c r="B91" s="2" t="inlineStr">
         <is>
-          <t>C28592</t>
+          <t>C28591</t>
         </is>
       </c>
       <c r="C91" s="6" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/28592</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/28591</t>
         </is>
       </c>
       <c r="D91" s="2" t="inlineStr">
@@ -4910,7 +4910,7 @@
       </c>
       <c r="E91" s="2" t="inlineStr">
         <is>
-          <t>Verify viewing/changing a customer's default fees &amp; discounts needs BOTH Customer Management: Create and Edit AND Manage Accounts Payable and Receivable</t>
+          <t>Verify create/edit/delete of a fee/discount template needs Settings → Service</t>
         </is>
       </c>
       <c r="F91" s="2" t="inlineStr">
@@ -4930,24 +4930,24 @@
       </c>
       <c r="I91" s="2" t="inlineStr">
         <is>
-          <t>customer defaults BE-enforced: tech GET 403 + POST 403 | WORDING+VIU 2026-07-13: CONFIRMED live: Tech (no Manage AP/AR, no Customer Mgmt C&amp;E) → customer default-adjustments GET 403 AND POST 403 'Access denied.'</t>
+          <t>templates admin BE-enforced: tech GET/POST 403 | WORDING+VIU 2026-07-13: CONFIRMED live: Tech (no Settings → Finance) → GET templates 403 'Access denied.' | SV-8456 (2026-07-21 staging LIVE VIU): F&amp;D moved to SETTINGS→SERVICE (below Canned Lines); template/WO/Part-sale/customer dialogs now show Taxable as a Yes/No DROPDOWN (was toggle); Auto-apply is a CHECKBOX with a 'When on…' caption; settings &amp; customer tables are plain-text/left-aligned (no badges); WO sidebar card retitled 'Work Order Fees &amp; Discounts' and renders ABOVE Financial Info; Part-sale card 'Parts Sale Fees &amp; Discounts' above Financial Info. Permission gate pivoted Settings→Finance → Settings→Service (verified live: Service-user sees+manages F&amp;D &amp; convenience toggle; Finance-only user has no F&amp;D nav item and /administration/adjustment-templates bounces to /workorders). Frontend-only; functionality + calc INTACT. | RE-VIU 2026-07-22 LIVE (Batch 4, SV-8456 re-verify): access-check quick-login {admin} HTTP 200. Re-confirmed on current staging build — 8 UI corrections intact (Taxable Yes/No dropdown; Auto-apply checkbox+caption; modal field order Type/CalcType&gt;Name&gt;Amount&gt;Taxable+jur.note&gt;Auto-apply&gt;Description; Settings table plain-text left-aligned no badges; F&amp;D nav under SERVICE below Canned Lines; WO &amp; Part-Sale cards above Financial Info [Batch 2/3]; Customer 'Fees &amp; Discounts' tab mirrors Settings styling minus convenience toggle) AND Settings-&gt;Service permission pivot CONFIRMED live per role (seeded ServiceRole vs FinanceRole, assigned to Tech, Tech restored to Technician 50bf6a0d + verified, both ZZAUTOTEST roles deleted 204): Service-user sees+manages F&amp;D nav + convenience toggle, direct /administration/adjustment-templates loads; Finance-only user has NO F&amp;D nav, FINANCE=Payment Methods only, direct route bounces to /workorders. viu_status VIU-Verified re-confirmed. Ev build/fees-discounts/viu-sv8456-2026-07-22/ (01-settings-landing, 02-new-dialog, 03-customer-fd-tab, SVC-*, FIN-*).</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" s="2" t="inlineStr">
         <is>
-          <t>FD-PERM-009</t>
+          <t>FD-PERM-008</t>
         </is>
       </c>
       <c r="B92" s="2" t="inlineStr">
         <is>
-          <t>C28593</t>
+          <t>C28592</t>
         </is>
       </c>
       <c r="C92" s="6" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/28593</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/28592</t>
         </is>
       </c>
       <c r="D92" s="2" t="inlineStr">
@@ -4957,12 +4957,12 @@
       </c>
       <c r="E92" s="2" t="inlineStr">
         <is>
-          <t>Verify seeing fee/discount entries in the work-order audit log needs Work Orders: Create and Edit (line audit log needs Work Order Lines: Create and Edit)</t>
+          <t>Verify viewing/changing a customer's default fees &amp; discounts needs BOTH Customer Management: Create and Edit AND Manage Accounts Payable and Receivable</t>
         </is>
       </c>
       <c r="F92" s="2" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>High</t>
         </is>
       </c>
       <c r="G92" s="2" t="inlineStr">
@@ -4977,24 +4977,24 @@
       </c>
       <c r="I92" s="2" t="inlineStr">
         <is>
-          <t>history entries: BE serves them regardless (tech 200) — FE display gate per enforcement model; entries carry set rate | V1_2 (2026-07-13): history-log gate updated per S13-R10 — WO-level history requires Work Orders: Create and Edit; line-level history requires Work Order Lines: Create and Edit (was View History Logs). Expected/preconditions updated; needs live re-VIU. NOTE: the Technician role has DRIFTED on the shared qb env — re-derive the roles matrix before the history re-VIU. | WORDING+VIU 2026-07-13: Positive confirmed live (Tech has Work Orders/Work Order Lines: Create &amp; Edit → Work Order Log 200 with fee/discount entries; the log shows the set rate so See Financial Data does not gate it — Tech's financials are masked yet history shows). The no-permission negative is NOT testable this run (Tech drifted to have the perms; only admin/tech log in). | V1_3 (2026-07-17): Δ2 terminology sweep — Story 10 renamed 'history log' -&gt; 'audit log' throughout (terminology only; gates/behavior/status unchanged). Generic 'history log / history entry / work-order history' prose replaced with 'audit log / audit-log entry'; the exact build labels 'Audit Log' (⋮ menu) and 'Work Order Log' (page) kept per Standing Rule 9. TestRail section name left as-is (rename not authorized).</t>
+          <t>customer defaults BE-enforced: tech GET 403 + POST 403 | WORDING+VIU 2026-07-13: CONFIRMED live: Tech (no Manage AP/AR, no Customer Mgmt C&amp;E) → customer default-adjustments GET 403 AND POST 403 'Access denied.'</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" s="2" t="inlineStr">
         <is>
-          <t>FD-PERM-010</t>
+          <t>FD-PERM-009</t>
         </is>
       </c>
       <c r="B93" s="2" t="inlineStr">
         <is>
-          <t>C28594</t>
+          <t>C28593</t>
         </is>
       </c>
       <c r="C93" s="6" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/28594</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/28593</t>
         </is>
       </c>
       <c r="D93" s="2" t="inlineStr">
@@ -5004,12 +5004,12 @@
       </c>
       <c r="E93" s="2" t="inlineStr">
         <is>
-          <t>Verify both are required — the Fees &amp; Discounts feature on AND the matching permission</t>
+          <t>Verify seeing fee/discount entries in the work-order audit log needs Work Orders: Create and Edit (line audit log needs Work Order Lines: Create and Edit)</t>
         </is>
       </c>
       <c r="F93" s="2" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="G93" s="2" t="inlineStr">
@@ -5024,24 +5024,24 @@
       </c>
       <c r="I93" s="2" t="inlineStr">
         <is>
-          <t>flag ON + permission still required (tech 403 on templates/defaults with flag ON) | WORDING+VIU 2026-07-13: Permission gating confirmed live (templates/customer-defaults 403; SFD masking). Feature is ON. Both-gates model holds. | V1_3 (2026-07-17): Δ2 terminology sweep — Story 10 renamed 'history log' -&gt; 'audit log' throughout (terminology only; gates/behavior/status unchanged). Generic 'history log / history entry / work-order history' prose replaced with 'audit log / audit-log entry'; the exact build labels 'Audit Log' (⋮ menu) and 'Work Order Log' (page) kept per Standing Rule 9. TestRail section name left as-is (rename not authorized).</t>
+          <t>history entries: BE serves them regardless (tech 200) — FE display gate per enforcement model; entries carry set rate | V1_2 (2026-07-13): history-log gate updated per S13-R10 — WO-level history requires Work Orders: Create and Edit; line-level history requires Work Order Lines: Create and Edit (was View History Logs). Expected/preconditions updated; needs live re-VIU. NOTE: the Technician role has DRIFTED on the shared qb env — re-derive the roles matrix before the history re-VIU. | WORDING+VIU 2026-07-13: Positive confirmed live (Tech has Work Orders/Work Order Lines: Create &amp; Edit → Work Order Log 200 with fee/discount entries; the log shows the set rate so See Financial Data does not gate it — Tech's financials are masked yet history shows). The no-permission negative is NOT testable this run (Tech drifted to have the perms; only admin/tech log in). | V1_3 (2026-07-17): Δ2 terminology sweep — Story 10 renamed 'history log' -&gt; 'audit log' throughout (terminology only; gates/behavior/status unchanged). Generic 'history log / history entry / work-order history' prose replaced with 'audit log / audit-log entry'; the exact build labels 'Audit Log' (⋮ menu) and 'Work Order Log' (page) kept per Standing Rule 9. TestRail section name left as-is (rename not authorized).</t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="A94" s="2" t="inlineStr">
         <is>
-          <t>FD-PERM-011</t>
+          <t>FD-PERM-010</t>
         </is>
       </c>
       <c r="B94" s="2" t="inlineStr">
         <is>
-          <t>C28595</t>
+          <t>C28594</t>
         </is>
       </c>
       <c r="C94" s="6" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/28595</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/28594</t>
         </is>
       </c>
       <c r="D94" s="2" t="inlineStr">
@@ -5051,12 +5051,12 @@
       </c>
       <c r="E94" s="2" t="inlineStr">
         <is>
-          <t>Verify add/edit/remove is blocked when the work order is Invoiced/Paid or you are viewing history</t>
+          <t>Verify both are required — the Fees &amp; Discounts feature on AND the matching permission</t>
         </is>
       </c>
       <c r="F94" s="2" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>High</t>
         </is>
       </c>
       <c r="G94" s="2" t="inlineStr">
@@ -5071,39 +5071,39 @@
       </c>
       <c r="I94" s="2" t="inlineStr">
         <is>
-          <t>Invoiced WO: add 409 + edit 409 (BE-enforced lock) | WORDING+VIU 2026-07-13: Invoiced/Paid block is back-end enforced (409) — established; carried. | SV-8479/8480 deconfliction 2026-07-22: label sweep: navigation labels -&gt; 'Add Work Order Fee / Discount' / 'New Work Order Fee / Discount' (behavior/expected unchanged). | VIU 2026-07-22 LIVE: SV-8479 nav label 'Add Work Order Fee / Discount' confirmed present in the WO toolbar ⋯ menu; case behavior unchanged. Ev: wo/FD-WO-025-toolbar-menu.png.</t>
+          <t>flag ON + permission still required (tech 403 on templates/defaults with flag ON) | WORDING+VIU 2026-07-13: Permission gating confirmed live (templates/customer-defaults 403; SFD masking). Feature is ON. Both-gates model holds. | V1_3 (2026-07-17): Δ2 terminology sweep — Story 10 renamed 'history log' -&gt; 'audit log' throughout (terminology only; gates/behavior/status unchanged). Generic 'history log / history entry / work-order history' prose replaced with 'audit log / audit-log entry'; the exact build labels 'Audit Log' (⋮ menu) and 'Work Order Log' (page) kept per Standing Rule 9. TestRail section name left as-is (rename not authorized).</t>
         </is>
       </c>
     </row>
     <row r="95">
       <c r="A95" s="2" t="inlineStr">
         <is>
-          <t>FD-PROC-001</t>
+          <t>FD-PERM-011</t>
         </is>
       </c>
       <c r="B95" s="2" t="inlineStr">
         <is>
-          <t>C28519</t>
+          <t>C28595</t>
         </is>
       </c>
       <c r="C95" s="6" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/28519</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/28595</t>
         </is>
       </c>
       <c r="D95" s="2" t="inlineStr">
         <is>
-          <t>Processing Fee — template builder</t>
+          <t>Permissions (Story 13)</t>
         </is>
       </c>
       <c r="E95" s="2" t="inlineStr">
         <is>
-          <t>Verify 'Processing Fee' is a third Type in the template builder</t>
+          <t>Verify add/edit/remove is blocked when the work order is Invoiced/Paid or you are viewing history</t>
         </is>
       </c>
       <c r="F95" s="2" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="G95" s="2" t="inlineStr">
@@ -5118,34 +5118,34 @@
       </c>
       <c r="I95" s="2" t="inlineStr">
         <is>
-          <t>RE-CHECKED TODAY: template-builder Type options are exactly [Fee, Discount] — Processing Fee STILL MISSING from the builder UI (PO Q3=B says in-scope; FDBUG-8; shot 02-template-dialog) | WORDING+VIU 2026-07-13: Confirmed live: Type dropdown = Fee/Discount only. NOT BUILT: the template Type dropdown offers only Fee/Discount (no 'Processing Fee'); the Story-8 Processing-Fee builder UI has not shipped. The back-end DOES accept kind=processing_fee via API (201). Re-test when the builder ships. | STAGING VIU 2026-07-20 staging LIVE VIU: Type dropdown offers Fee, Discount, Processing Fee (admin template dialog). Live-observed staging (proc-type-open).</t>
+          <t>Invoiced WO: add 409 + edit 409 (BE-enforced lock) | WORDING+VIU 2026-07-13: Invoiced/Paid block is back-end enforced (409) — established; carried. | SV-8479/8480 deconfliction 2026-07-22: label sweep: navigation labels -&gt; 'Add Work Order Fee / Discount' / 'New Work Order Fee / Discount' (behavior/expected unchanged). | VIU 2026-07-22 LIVE: SV-8479 nav label 'Add Work Order Fee / Discount' confirmed present in the WO toolbar ⋯ menu; case behavior unchanged. Ev: wo/FD-WO-025-toolbar-menu.png.</t>
         </is>
       </c>
     </row>
     <row r="96">
       <c r="A96" s="2" t="inlineStr">
         <is>
-          <t>FD-PROC-002</t>
+          <t>FD-PROC-001</t>
         </is>
       </c>
       <c r="B96" s="2" t="inlineStr">
         <is>
-          <t>C28520</t>
+          <t>C28519</t>
         </is>
       </c>
       <c r="C96" s="6" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/28520</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/28519</t>
         </is>
       </c>
       <c r="D96" s="2" t="inlineStr">
         <is>
-          <t>Processing Fee — methods</t>
+          <t>Processing Fee — template builder</t>
         </is>
       </c>
       <c r="E96" s="2" t="inlineStr">
         <is>
-          <t>Verify a Processing Fee offers only Flat Amount and % of Grand Total</t>
+          <t>Verify 'Processing Fee' is a third Type in the template builder</t>
         </is>
       </c>
       <c r="F96" s="2" t="inlineStr">
@@ -5165,39 +5165,39 @@
       </c>
       <c r="I96" s="2" t="inlineStr">
         <is>
-          <t>builder UI absent (re-checked today); BE method constraint re-proven separately (pct_labor rejected for processing_fee) | WORDING+VIU 2026-07-13: Builder not shipped. NOT BUILT: the template Type dropdown offers only Fee/Discount (no 'Processing Fee'); the Story-8 Processing-Fee builder UI has not shipped. The back-end DOES accept kind=processing_fee via API (201). Re-test when the builder ships. | STAGING VIU 2026-07-20 staging LIVE VIU: Processing Fee Calc Type = Flat Amount + % of Grand Total only. Live staging (proc-fee-calc-open.png).</t>
+          <t>RE-CHECKED TODAY: template-builder Type options are exactly [Fee, Discount] — Processing Fee STILL MISSING from the builder UI (PO Q3=B says in-scope; FDBUG-8; shot 02-template-dialog) | WORDING+VIU 2026-07-13: Confirmed live: Type dropdown = Fee/Discount only. NOT BUILT: the template Type dropdown offers only Fee/Discount (no 'Processing Fee'); the Story-8 Processing-Fee builder UI has not shipped. The back-end DOES accept kind=processing_fee via API (201). Re-test when the builder ships. | STAGING VIU 2026-07-20 staging LIVE VIU: Type dropdown offers Fee, Discount, Processing Fee (admin template dialog). Live-observed staging (proc-type-open).</t>
         </is>
       </c>
     </row>
     <row r="97">
       <c r="A97" s="2" t="inlineStr">
         <is>
-          <t>FD-PROC-003</t>
+          <t>FD-PROC-002</t>
         </is>
       </c>
       <c r="B97" s="2" t="inlineStr">
         <is>
-          <t>C28521</t>
+          <t>C28520</t>
         </is>
       </c>
       <c r="C97" s="6" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/28521</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/28520</t>
         </is>
       </c>
       <c r="D97" s="2" t="inlineStr">
         <is>
-          <t>Processing Fee — no Max Amount</t>
+          <t>Processing Fee — methods</t>
         </is>
       </c>
       <c r="E97" s="2" t="inlineStr">
         <is>
-          <t>Verify the Max Amount field is hidden for a Processing Fee (both methods)</t>
+          <t>Verify a Processing Fee offers only Flat Amount and % of Grand Total</t>
         </is>
       </c>
       <c r="F97" s="2" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>High</t>
         </is>
       </c>
       <c r="G97" s="2" t="inlineStr">
@@ -5212,39 +5212,39 @@
       </c>
       <c r="I97" s="2" t="inlineStr">
         <is>
-          <t>builder UI absent (re-checked today); BE rejects pfee maxCap (400) | WORDING+VIU 2026-07-13: Builder not shipped. NOT BUILT: the template Type dropdown offers only Fee/Discount (no 'Processing Fee'); the Story-8 Processing-Fee builder UI has not shipped. The back-end DOES accept kind=processing_fee via API (201). Re-test when the builder ships. | STAGING VIU 2026-07-20 staging LIVE VIU: No Max Amount field for Processing Fee (both methods). Live staging (proc-fee-full.png).</t>
+          <t>builder UI absent (re-checked today); BE method constraint re-proven separately (pct_labor rejected for processing_fee) | WORDING+VIU 2026-07-13: Builder not shipped. NOT BUILT: the template Type dropdown offers only Fee/Discount (no 'Processing Fee'); the Story-8 Processing-Fee builder UI has not shipped. The back-end DOES accept kind=processing_fee via API (201). Re-test when the builder ships. | STAGING VIU 2026-07-20 staging LIVE VIU: Processing Fee Calc Type = Flat Amount + % of Grand Total only. Live staging (proc-fee-calc-open.png).</t>
         </is>
       </c>
     </row>
     <row r="98">
       <c r="A98" s="2" t="inlineStr">
         <is>
-          <t>FD-PROC-004</t>
+          <t>FD-PROC-003</t>
         </is>
       </c>
       <c r="B98" s="2" t="inlineStr">
         <is>
-          <t>C28522</t>
+          <t>C28521</t>
         </is>
       </c>
       <c r="C98" s="6" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/28522</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/28521</t>
         </is>
       </c>
       <c r="D98" s="2" t="inlineStr">
         <is>
-          <t>Processing Fee — taxable + jurisdiction note</t>
+          <t>Processing Fee — no Max Amount</t>
         </is>
       </c>
       <c r="E98" s="2" t="inlineStr">
         <is>
-          <t>Verify the Processing Fee Taxable defaults to Yes and shows the tax-jurisdiction note</t>
+          <t>Verify the Max Amount field is hidden for a Processing Fee (both methods)</t>
         </is>
       </c>
       <c r="F98" s="2" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="G98" s="2" t="inlineStr">
@@ -5259,34 +5259,34 @@
       </c>
       <c r="I98" s="2" t="inlineStr">
         <is>
-          <t>builder UI absent (re-checked today) | WORDING+VIU 2026-07-13: Builder not shipped; when it ships, also check the §5-R15 note (currently absent in the whole-WO dialog per FD-WO-016). NOT BUILT: the template Type dropdown offers only Fee/Discount (no 'Processing Fee'); the Story-8 Processing-Fee builder UI has not shipped. The back-end DOES accept kind=processing_fee via API (201). Re-test when the builder ships. | V1_3 (2026-07-17): Δ1 — §5-R15 gains one appended sentence (spec verbatim): 'The note is shown only to users with See Financial Data.' Expected gains the gate qualifier. This dialog is the one place the gate is independently observable (Story-7 admin access needs no See Financial Data, while the WO Add/Edit dialog already requires it — spec-diff §H.b). Status stays Blocked-NotBuilt (Story-8 builder UI absent); check the note + gate when the builder ships. | STAGING VIU 2026-07-20 staging LIVE VIU: Processing Fee Taxable defaults Yes + jurisdiction note present; note gated on See Financial Data (Tech w/o SFD sees toggle, not note). Live staging (proc-fee-full.png / tech-tmpl-dialog.png).</t>
+          <t>builder UI absent (re-checked today); BE rejects pfee maxCap (400) | WORDING+VIU 2026-07-13: Builder not shipped. NOT BUILT: the template Type dropdown offers only Fee/Discount (no 'Processing Fee'); the Story-8 Processing-Fee builder UI has not shipped. The back-end DOES accept kind=processing_fee via API (201). Re-test when the builder ships. | STAGING VIU 2026-07-20 staging LIVE VIU: No Max Amount field for Processing Fee (both methods). Live staging (proc-fee-full.png).</t>
         </is>
       </c>
     </row>
     <row r="99">
       <c r="A99" s="2" t="inlineStr">
         <is>
-          <t>FD-PROC-005</t>
+          <t>FD-PROC-004</t>
         </is>
       </c>
       <c r="B99" s="2" t="inlineStr">
         <is>
-          <t>C28523</t>
+          <t>C28522</t>
         </is>
       </c>
       <c r="C99" s="6" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/28523</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/28522</t>
         </is>
       </c>
       <c r="D99" s="2" t="inlineStr">
         <is>
-          <t>Processing Fee — no manual add</t>
+          <t>Processing Fee — taxable + jurisdiction note</t>
         </is>
       </c>
       <c r="E99" s="2" t="inlineStr">
         <is>
-          <t>Verify a Processing Fee cannot be added to a work order by hand</t>
+          <t>Verify the Processing Fee Taxable defaults to Yes and shows the tax-jurisdiction note</t>
         </is>
       </c>
       <c r="F99" s="2" t="inlineStr">
@@ -5306,34 +5306,34 @@
       </c>
       <c r="I99" s="2" t="inlineStr">
         <is>
-          <t>manual pfee add -&gt; 400 'A processing fee cannot be added manually.'; manual pct_grand_total fee also rejected for scope | WORDING+VIU 2026-07-13: Confirmed: WO Add Type dropdown = Fee/Discord only (no Processing Fee); build labels ('Add Fee/Discount', 'Apply From Template'). | SV-8479/8480 deconfliction 2026-07-22: label sweep: navigation labels -&gt; 'Add Work Order Fee / Discount' / 'New Work Order Fee / Discount' (behavior/expected unchanged). | VIU 2026-07-22 LIVE: SV-8479 nav label 'Add Work Order Fee / Discount' confirmed present in the WO toolbar ⋯ menu; case behavior unchanged. Ev: wo/FD-WO-025-toolbar-menu.png.</t>
+          <t>builder UI absent (re-checked today) | WORDING+VIU 2026-07-13: Builder not shipped; when it ships, also check the §5-R15 note (currently absent in the whole-WO dialog per FD-WO-016). NOT BUILT: the template Type dropdown offers only Fee/Discount (no 'Processing Fee'); the Story-8 Processing-Fee builder UI has not shipped. The back-end DOES accept kind=processing_fee via API (201). Re-test when the builder ships. | V1_3 (2026-07-17): Δ1 — §5-R15 gains one appended sentence (spec verbatim): 'The note is shown only to users with See Financial Data.' Expected gains the gate qualifier. This dialog is the one place the gate is independently observable (Story-7 admin access needs no See Financial Data, while the WO Add/Edit dialog already requires it — spec-diff §H.b). Status stays Blocked-NotBuilt (Story-8 builder UI absent); check the note + gate when the builder ships. | STAGING VIU 2026-07-20 staging LIVE VIU: Processing Fee Taxable defaults Yes + jurisdiction note present; note gated on See Financial Data (Tech w/o SFD sees toggle, not note). Live staging (proc-fee-full.png / tech-tmpl-dialog.png).</t>
         </is>
       </c>
     </row>
     <row r="100">
       <c r="A100" s="2" t="inlineStr">
         <is>
-          <t>FD-PROC-006</t>
+          <t>FD-PROC-005</t>
         </is>
       </c>
       <c r="B100" s="2" t="inlineStr">
         <is>
-          <t>C28524</t>
+          <t>C28523</t>
         </is>
       </c>
       <c r="C100" s="6" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/28524</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/28523</t>
         </is>
       </c>
       <c r="D100" s="2" t="inlineStr">
         <is>
-          <t>Processing Fee — auto-apply</t>
+          <t>Processing Fee — no manual add</t>
         </is>
       </c>
       <c r="E100" s="2" t="inlineStr">
         <is>
-          <t>Verify a Processing Fee reaches a new work order via location auto-apply</t>
+          <t>Verify a Processing Fee cannot be added to a work order by hand</t>
         </is>
       </c>
       <c r="F100" s="2" t="inlineStr">
@@ -5353,39 +5353,39 @@
       </c>
       <c r="I100" s="2" t="inlineStr">
         <is>
-          <t>auto-apply pfee template landed on a fresh WO (kind=processing_fee, appliedBy=auto) | WORDING+VIU 2026-07-13: Reaches WO via auto-apply (pfee accepted by BE); build labels. Menu option is 'Remove' (Edit inert for a pfee). | SV-8456 (2026-07-21 staging LIVE VIU): F&amp;D moved to SETTINGS→SERVICE (below Canned Lines); template/WO/Part-sale/customer dialogs now show Taxable as a Yes/No DROPDOWN (was toggle); Auto-apply is a CHECKBOX with a 'When on…' caption; settings &amp; customer tables are plain-text/left-aligned (no badges); WO sidebar card retitled 'Work Order Fees &amp; Discounts' and renders ABOVE Financial Info; Part-sale card 'Parts Sale Fees &amp; Discounts' above Financial Info. Permission gate pivoted Settings→Finance → Settings→Service (verified live: Service-user sees+manages F&amp;D &amp; convenience toggle; Finance-only user has no F&amp;D nav item and /administration/adjustment-templates bounces to /workorders). Frontend-only; functionality + calc INTACT. | RE-VIU 2026-07-22 LIVE (Batch 4, SV-8456 re-verify): access-check quick-login {admin} HTTP 200. Re-confirmed on current staging build — 8 UI corrections intact (Taxable Yes/No dropdown; Auto-apply checkbox+caption; modal field order Type/CalcType&gt;Name&gt;Amount&gt;Taxable+jur.note&gt;Auto-apply&gt;Description; Settings table plain-text left-aligned no badges; F&amp;D nav under SERVICE below Canned Lines; WO &amp; Part-Sale cards above Financial Info [Batch 2/3]; Customer 'Fees &amp; Discounts' tab mirrors Settings styling minus convenience toggle) AND Settings-&gt;Service permission pivot CONFIRMED live per role (seeded ServiceRole vs FinanceRole, assigned to Tech, Tech restored to Technician 50bf6a0d + verified, both ZZAUTOTEST roles deleted 204): Service-user sees+manages F&amp;D nav + convenience toggle, direct /administration/adjustment-templates loads; Finance-only user has NO F&amp;D nav, FINANCE=Payment Methods only, direct route bounces to /workorders. viu_status VIU-Verified re-confirmed. Ev build/fees-discounts/viu-sv8456-2026-07-22/ (01-settings-landing, 02-new-dialog, 03-customer-fd-tab, SVC-*, FIN-*).</t>
+          <t>manual pfee add -&gt; 400 'A processing fee cannot be added manually.'; manual pct_grand_total fee also rejected for scope | WORDING+VIU 2026-07-13: Confirmed: WO Add Type dropdown = Fee/Discord only (no Processing Fee); build labels ('Add Fee/Discount', 'Apply From Template'). | SV-8479/8480 deconfliction 2026-07-22: label sweep: navigation labels -&gt; 'Add Work Order Fee / Discount' / 'New Work Order Fee / Discount' (behavior/expected unchanged). | VIU 2026-07-22 LIVE: SV-8479 nav label 'Add Work Order Fee / Discount' confirmed present in the WO toolbar ⋯ menu; case behavior unchanged. Ev: wo/FD-WO-025-toolbar-menu.png.</t>
         </is>
       </c>
     </row>
     <row r="101">
       <c r="A101" s="2" t="inlineStr">
         <is>
-          <t>FD-PROC-007</t>
+          <t>FD-PROC-006</t>
         </is>
       </c>
       <c r="B101" s="2" t="inlineStr">
         <is>
-          <t>C28525</t>
+          <t>C28524</t>
         </is>
       </c>
       <c r="C101" s="6" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/28525</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/28524</t>
         </is>
       </c>
       <c r="D101" s="2" t="inlineStr">
         <is>
-          <t>Processing Fee — customer default</t>
+          <t>Processing Fee — auto-apply</t>
         </is>
       </c>
       <c r="E101" s="2" t="inlineStr">
         <is>
-          <t>Verify a Processing Fee reaches a new work order via a customer default</t>
+          <t>Verify a Processing Fee reaches a new work order via location auto-apply</t>
         </is>
       </c>
       <c r="F101" s="2" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>High</t>
         </is>
       </c>
       <c r="G101" s="2" t="inlineStr">
@@ -5400,34 +5400,34 @@
       </c>
       <c r="I101" s="2" t="inlineStr">
         <is>
-          <t>customer-default pfee landed on a fresh WO (kind=processing_fee, appliedBy=customer_default, amount 2.5) | WORDING+VIU 2026-07-13: Reaches WO via customer default; build labels. | SV-8456 (2026-07-21 staging LIVE VIU): F&amp;D moved to SETTINGS→SERVICE (below Canned Lines); template/WO/Part-sale/customer dialogs now show Taxable as a Yes/No DROPDOWN (was toggle); Auto-apply is a CHECKBOX with a 'When on…' caption; settings &amp; customer tables are plain-text/left-aligned (no badges); WO sidebar card retitled 'Work Order Fees &amp; Discounts' and renders ABOVE Financial Info; Part-sale card 'Parts Sale Fees &amp; Discounts' above Financial Info. Permission gate pivoted Settings→Finance → Settings→Service (verified live: Service-user sees+manages F&amp;D &amp; convenience toggle; Finance-only user has no F&amp;D nav item and /administration/adjustment-templates bounces to /workorders). Frontend-only; functionality + calc INTACT. | RE-VIU 2026-07-22 LIVE (Batch 4, SV-8456 re-verify): access-check quick-login {admin} HTTP 200. Re-confirmed on current staging build — 8 UI corrections intact (Taxable Yes/No dropdown; Auto-apply checkbox+caption; modal field order Type/CalcType&gt;Name&gt;Amount&gt;Taxable+jur.note&gt;Auto-apply&gt;Description; Settings table plain-text left-aligned no badges; F&amp;D nav under SERVICE below Canned Lines; WO &amp; Part-Sale cards above Financial Info [Batch 2/3]; Customer 'Fees &amp; Discounts' tab mirrors Settings styling minus convenience toggle) AND Settings-&gt;Service permission pivot CONFIRMED live per role (seeded ServiceRole vs FinanceRole, assigned to Tech, Tech restored to Technician 50bf6a0d + verified, both ZZAUTOTEST roles deleted 204): Service-user sees+manages F&amp;D nav + convenience toggle, direct /administration/adjustment-templates loads; Finance-only user has NO F&amp;D nav, FINANCE=Payment Methods only, direct route bounces to /workorders. viu_status VIU-Verified re-confirmed. Ev build/fees-discounts/viu-sv8456-2026-07-22/ (01-settings-landing, 02-new-dialog, 03-customer-fd-tab, SVC-*, FIN-*).</t>
+          <t>auto-apply pfee template landed on a fresh WO (kind=processing_fee, appliedBy=auto) | WORDING+VIU 2026-07-13: Reaches WO via auto-apply (pfee accepted by BE); build labels. Menu option is 'Remove' (Edit inert for a pfee). | SV-8456 (2026-07-21 staging LIVE VIU): F&amp;D moved to SETTINGS→SERVICE (below Canned Lines); template/WO/Part-sale/customer dialogs now show Taxable as a Yes/No DROPDOWN (was toggle); Auto-apply is a CHECKBOX with a 'When on…' caption; settings &amp; customer tables are plain-text/left-aligned (no badges); WO sidebar card retitled 'Work Order Fees &amp; Discounts' and renders ABOVE Financial Info; Part-sale card 'Parts Sale Fees &amp; Discounts' above Financial Info. Permission gate pivoted Settings→Finance → Settings→Service (verified live: Service-user sees+manages F&amp;D &amp; convenience toggle; Finance-only user has no F&amp;D nav item and /administration/adjustment-templates bounces to /workorders). Frontend-only; functionality + calc INTACT. | RE-VIU 2026-07-22 LIVE (Batch 4, SV-8456 re-verify): access-check quick-login {admin} HTTP 200. Re-confirmed on current staging build — 8 UI corrections intact (Taxable Yes/No dropdown; Auto-apply checkbox+caption; modal field order Type/CalcType&gt;Name&gt;Amount&gt;Taxable+jur.note&gt;Auto-apply&gt;Description; Settings table plain-text left-aligned no badges; F&amp;D nav under SERVICE below Canned Lines; WO &amp; Part-Sale cards above Financial Info [Batch 2/3]; Customer 'Fees &amp; Discounts' tab mirrors Settings styling minus convenience toggle) AND Settings-&gt;Service permission pivot CONFIRMED live per role (seeded ServiceRole vs FinanceRole, assigned to Tech, Tech restored to Technician 50bf6a0d + verified, both ZZAUTOTEST roles deleted 204): Service-user sees+manages F&amp;D nav + convenience toggle, direct /administration/adjustment-templates loads; Finance-only user has NO F&amp;D nav, FINANCE=Payment Methods only, direct route bounces to /workorders. viu_status VIU-Verified re-confirmed. Ev build/fees-discounts/viu-sv8456-2026-07-22/ (01-settings-landing, 02-new-dialog, 03-customer-fd-tab, SVC-*, FIN-*).</t>
         </is>
       </c>
     </row>
     <row r="102">
       <c r="A102" s="2" t="inlineStr">
         <is>
-          <t>FD-PROC-010</t>
+          <t>FD-PROC-007</t>
         </is>
       </c>
       <c r="B102" s="2" t="inlineStr">
         <is>
-          <t>C28528</t>
+          <t>C28525</t>
         </is>
       </c>
       <c r="C102" s="6" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/28528</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/28525</t>
         </is>
       </c>
       <c r="D102" s="2" t="inlineStr">
         <is>
-          <t>Processing Fee — negative</t>
+          <t>Processing Fee — customer default</t>
         </is>
       </c>
       <c r="E102" s="2" t="inlineStr">
         <is>
-          <t>Verify a Processing Fee with a Max Amount or a disallowed method is rejected</t>
+          <t>Verify a Processing Fee reaches a new work order via a customer default</t>
         </is>
       </c>
       <c r="F102" s="2" t="inlineStr">
@@ -5447,34 +5447,34 @@
       </c>
       <c r="I102" s="2" t="inlineStr">
         <is>
-          <t>pfee template with maxCap -&gt; 400; pfee with pct_labor -&gt; 400 'not allowed for a processing_fee' | WORDING+VIU 2026-07-13: Confirmed live 2026-07-13 via API: Max cap → 400 'A processing fee cannot have a minimum or maximum cap.'; disallowed method → 400 'Calculation type "pct_subtotal" is not allowed for a processing_fee.' Lives in an API-titled section.</t>
+          <t>customer-default pfee landed on a fresh WO (kind=processing_fee, appliedBy=customer_default, amount 2.5) | WORDING+VIU 2026-07-13: Reaches WO via customer default; build labels. | SV-8456 (2026-07-21 staging LIVE VIU): F&amp;D moved to SETTINGS→SERVICE (below Canned Lines); template/WO/Part-sale/customer dialogs now show Taxable as a Yes/No DROPDOWN (was toggle); Auto-apply is a CHECKBOX with a 'When on…' caption; settings &amp; customer tables are plain-text/left-aligned (no badges); WO sidebar card retitled 'Work Order Fees &amp; Discounts' and renders ABOVE Financial Info; Part-sale card 'Parts Sale Fees &amp; Discounts' above Financial Info. Permission gate pivoted Settings→Finance → Settings→Service (verified live: Service-user sees+manages F&amp;D &amp; convenience toggle; Finance-only user has no F&amp;D nav item and /administration/adjustment-templates bounces to /workorders). Frontend-only; functionality + calc INTACT. | RE-VIU 2026-07-22 LIVE (Batch 4, SV-8456 re-verify): access-check quick-login {admin} HTTP 200. Re-confirmed on current staging build — 8 UI corrections intact (Taxable Yes/No dropdown; Auto-apply checkbox+caption; modal field order Type/CalcType&gt;Name&gt;Amount&gt;Taxable+jur.note&gt;Auto-apply&gt;Description; Settings table plain-text left-aligned no badges; F&amp;D nav under SERVICE below Canned Lines; WO &amp; Part-Sale cards above Financial Info [Batch 2/3]; Customer 'Fees &amp; Discounts' tab mirrors Settings styling minus convenience toggle) AND Settings-&gt;Service permission pivot CONFIRMED live per role (seeded ServiceRole vs FinanceRole, assigned to Tech, Tech restored to Technician 50bf6a0d + verified, both ZZAUTOTEST roles deleted 204): Service-user sees+manages F&amp;D nav + convenience toggle, direct /administration/adjustment-templates loads; Finance-only user has NO F&amp;D nav, FINANCE=Payment Methods only, direct route bounces to /workorders. viu_status VIU-Verified re-confirmed. Ev build/fees-discounts/viu-sv8456-2026-07-22/ (01-settings-landing, 02-new-dialog, 03-customer-fd-tab, SVC-*, FIN-*).</t>
         </is>
       </c>
     </row>
     <row r="103">
       <c r="A103" s="2" t="inlineStr">
         <is>
-          <t>FD-PROC-011</t>
+          <t>FD-PROC-010</t>
         </is>
       </c>
       <c r="B103" s="2" t="inlineStr">
         <is>
-          <t>C28529</t>
+          <t>C28528</t>
         </is>
       </c>
       <c r="C103" s="6" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/28529</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/28528</t>
         </is>
       </c>
       <c r="D103" s="2" t="inlineStr">
         <is>
-          <t>Processing Fee — sign</t>
+          <t>Processing Fee — negative</t>
         </is>
       </c>
       <c r="E103" s="2" t="inlineStr">
         <is>
-          <t>Verify a Processing Fee always adds to the total (never a discount)</t>
+          <t>Verify a Processing Fee with a Max Amount or a disallowed method is rejected</t>
         </is>
       </c>
       <c r="F103" s="2" t="inlineStr">
@@ -5494,34 +5494,34 @@
       </c>
       <c r="I103" s="2" t="inlineStr">
         <is>
-          <t>pfees resolve as positive fees only (kind=processing_fee, amounts &gt;= 0) | WORDING+VIU 2026-07-13: Always a plus; carried.</t>
+          <t>pfee template with maxCap -&gt; 400; pfee with pct_labor -&gt; 400 'not allowed for a processing_fee' | WORDING+VIU 2026-07-13: Confirmed live 2026-07-13 via API: Max cap → 400 'A processing fee cannot have a minimum or maximum cap.'; disallowed method → 400 'Calculation type "pct_subtotal" is not allowed for a processing_fee.' Lives in an API-titled section.</t>
         </is>
       </c>
     </row>
     <row r="104">
       <c r="A104" s="2" t="inlineStr">
         <is>
-          <t>FD-PROC-012</t>
+          <t>FD-PROC-011</t>
         </is>
       </c>
       <c r="B104" s="2" t="inlineStr">
         <is>
-          <t>C28530</t>
+          <t>C28529</t>
         </is>
       </c>
       <c r="C104" s="6" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/28530</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/28529</t>
         </is>
       </c>
       <c r="D104" s="2" t="inlineStr">
         <is>
-          <t>Processing Fee — template edit independence</t>
+          <t>Processing Fee — sign</t>
         </is>
       </c>
       <c r="E104" s="2" t="inlineStr">
         <is>
-          <t>Verify editing a Processing Fee template does not change Processing Fees already on existing work orders</t>
+          <t>Verify a Processing Fee always adds to the total (never a discount)</t>
         </is>
       </c>
       <c r="F104" s="2" t="inlineStr">
@@ -5541,39 +5541,39 @@
       </c>
       <c r="I104" s="2" t="inlineStr">
         <is>
-          <t>template amount 3-&gt;9 (200) left the existing WO pfee at 3 (values copied at apply time) | WORDING+VIU 2026-07-13: Template edit independence; carried.</t>
+          <t>pfees resolve as positive fees only (kind=processing_fee, amounts &gt;= 0) | WORDING+VIU 2026-07-13: Always a plus; carried.</t>
         </is>
       </c>
     </row>
     <row r="105">
       <c r="A105" s="2" t="inlineStr">
         <is>
-          <t>FD-PROC-013</t>
+          <t>FD-PROC-012</t>
         </is>
       </c>
       <c r="B105" s="2" t="inlineStr">
         <is>
-          <t>C28531</t>
+          <t>C28530</t>
         </is>
       </c>
       <c r="C105" s="6" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/28531</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/28530</t>
         </is>
       </c>
       <c r="D105" s="2" t="inlineStr">
         <is>
-          <t>Processing Fee — calculation edge</t>
+          <t>Processing Fee — template edit independence</t>
         </is>
       </c>
       <c r="E105" s="2" t="inlineStr">
         <is>
-          <t>Verify multiple Processing Fees each leave out all Processing Fees' amounts and tax from the shared base</t>
+          <t>Verify editing a Processing Fee template does not change Processing Fees already on existing work orders</t>
         </is>
       </c>
       <c r="F105" s="2" t="inlineStr">
         <is>
-          <t>Low</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="G105" s="2" t="inlineStr">
@@ -5588,34 +5588,34 @@
       </c>
       <c r="I105" s="2" t="inlineStr">
         <is>
-          <t>two auto pfees (3%+2%) resolved 0.63/0.42 = exact 3:2 ratio -&gt; same base, pfees exclude each other | WORDING+VIU 2026-07-13: Multiple pfees share the same base; carried.</t>
+          <t>template amount 3-&gt;9 (200) left the existing WO pfee at 3 (values copied at apply time) | WORDING+VIU 2026-07-13: Template edit independence; carried.</t>
         </is>
       </c>
     </row>
     <row r="106">
       <c r="A106" s="2" t="inlineStr">
         <is>
-          <t>FD-PROC-014</t>
+          <t>FD-PROC-013</t>
         </is>
       </c>
       <c r="B106" s="2" t="inlineStr">
         <is>
-          <t>C28532</t>
+          <t>C28531</t>
         </is>
       </c>
       <c r="C106" s="6" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/28532</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/28531</t>
         </is>
       </c>
       <c r="D106" s="2" t="inlineStr">
         <is>
-          <t>Processing Fee — negative</t>
+          <t>Processing Fee — calculation edge</t>
         </is>
       </c>
       <c r="E106" s="2" t="inlineStr">
         <is>
-          <t>Verify the system rejects a Processing Fee that carries a minimum amount</t>
+          <t>Verify multiple Processing Fees each leave out all Processing Fees' amounts and tax from the shared base</t>
         </is>
       </c>
       <c r="F106" s="2" t="inlineStr">
@@ -5635,39 +5635,39 @@
       </c>
       <c r="I106" s="2" t="inlineStr">
         <is>
-          <t>pfee minimum silently STRIPPED on create (201, no min field persisted) — §8 invariant holds; silent-ignore wording note stands | WORDING+VIU 2026-07-13: Confirmed live 2026-07-13: BE rejects a min/max cap on a Processing Fee (400 'A processing fee cannot have a minimum or maximum cap.'). PO Q4 (whether pfee minimums should be supported at all) still pending. | CHRIS WARD ROUND-2 ANSWER APPLIED 2026-07-14(Q4=B): PO ruled Processing Fees do NOT support a minimum and the app must make that clear (do not silently drop). Premise confirmed WAD: no minimum field in the UI and the API rejects a pfee minimum with an explicit error (matches the live 2026-07-13 finding: 400 'A processing fee cannot have a minimum or maximum cap.'). Older 2026-07-10 'silent strip' reading superseded (last-update-wins). Expected reworded to the explicit-reject + no-field behavior. PUSHED TO TESTRAIL 2026-07-14 via update_case (QA-lead one-day authorization; update 200 / re-verify 200 MATCH; audit: testrail-round2-push-log.md).</t>
+          <t>two auto pfees (3%+2%) resolved 0.63/0.42 = exact 3:2 ratio -&gt; same base, pfees exclude each other | WORDING+VIU 2026-07-13: Multiple pfees share the same base; carried.</t>
         </is>
       </c>
     </row>
     <row r="107">
       <c r="A107" s="2" t="inlineStr">
         <is>
-          <t>FD-PSALE-001</t>
+          <t>FD-PROC-014</t>
         </is>
       </c>
       <c r="B107" s="2" t="inlineStr">
         <is>
-          <t>C29918</t>
+          <t>C28532</t>
         </is>
       </c>
       <c r="C107" s="6" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/29918</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/28532</t>
         </is>
       </c>
       <c r="D107" s="2" t="inlineStr">
         <is>
-          <t>Part Sale — Fee/Discount dialog</t>
+          <t>Processing Fee — negative</t>
         </is>
       </c>
       <c r="E107" s="2" t="inlineStr">
         <is>
-          <t>Verify the Part Sale Add/Edit fee-or-discount dialog shows the tax-jurisdiction note below the Taxable Yes/No dropdown</t>
+          <t>Verify the system rejects a Processing Fee that carries a minimum amount</t>
         </is>
       </c>
       <c r="F107" s="2" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>Low</t>
         </is>
       </c>
       <c r="G107" s="2" t="inlineStr">
@@ -5682,34 +5682,34 @@
       </c>
       <c r="I107" s="2" t="inlineStr">
         <is>
-          <t>administration/adjustment-templates loads; Finance-only user has NO F&amp;D nav, FINANCE=Payment Methods only, direct route bounces to /workorders. viu_status VIU-Verified re-confirmed. Ev build/fees-discounts/viu-sv8456-2026-07-22/ (01-settings-landing, 02-new-dialog, 03-customer-fd-tab, SVC-*, FIN-*).</t>
+          <t>pfee minimum silently STRIPPED on create (201, no min field persisted) — §8 invariant holds; silent-ignore wording note stands | WORDING+VIU 2026-07-13: Confirmed live 2026-07-13: BE rejects a min/max cap on a Processing Fee (400 'A processing fee cannot have a minimum or maximum cap.'). PO Q4 (whether pfee minimums should be supported at all) still pending. | CHRIS WARD ROUND-2 ANSWER APPLIED 2026-07-14(Q4=B): PO ruled Processing Fees do NOT support a minimum and the app must make that clear (do not silently drop). Premise confirmed WAD: no minimum field in the UI and the API rejects a pfee minimum with an explicit error (matches the live 2026-07-13 finding: 400 'A processing fee cannot have a minimum or maximum cap.'). Older 2026-07-10 'silent strip' reading superseded (last-update-wins). Expected reworded to the explicit-reject + no-field behavior. PUSHED TO TESTRAIL 2026-07-14 via update_case (QA-lead one-day authorization; update 200 / re-verify 200 MATCH; audit: testrail-round2-push-log.md).</t>
         </is>
       </c>
     </row>
     <row r="108">
       <c r="A108" s="2" t="inlineStr">
         <is>
-          <t>FD-PSALE-002</t>
+          <t>FD-PSALE-001</t>
         </is>
       </c>
       <c r="B108" s="2" t="inlineStr">
         <is>
-          <t>C30623</t>
+          <t>C29918</t>
         </is>
       </c>
       <c r="C108" s="6" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/30623</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/29918</t>
         </is>
       </c>
       <c r="D108" s="2" t="inlineStr">
         <is>
-          <t>Parts page — 'FEES &amp; DISCOUNTS' column</t>
+          <t>Part Sale — Fee/Discount dialog</t>
         </is>
       </c>
       <c r="E108" s="2" t="inlineStr">
         <is>
-          <t>Verify the parts-sale Fees &amp; Discounts column no longer shows the '+ Add' button, and the per-row and top-right three-dot entry points remain</t>
+          <t>Verify the Part Sale Add/Edit fee-or-discount dialog shows the tax-jurisdiction note below the Taxable Yes/No dropdown</t>
         </is>
       </c>
       <c r="F108" s="2" t="inlineStr">
@@ -5729,24 +5729,24 @@
       </c>
       <c r="I108" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve"> NEXUS 2-adj) + whole-sale percent/flat/discount; observed live as admin (Part Sales C&amp;E + SFD). Evidence build/fees-discounts/viu-sv8479-8480-2026-07-22/psale/. F&amp;D column has no '+ Add' (grep '+Add'=0); per-row ⋮ 'Add Part Fee / Discount' + top-right ⋮ 'Add Parts Sale Fee / Discount' both present.</t>
+          <t>administration/adjustment-templates loads; Finance-only user has NO F&amp;D nav, FINANCE=Payment Methods only, direct route bounces to /workorders. viu_status VIU-Verified re-confirmed. Ev build/fees-discounts/viu-sv8456-2026-07-22/ (01-settings-landing, 02-new-dialog, 03-customer-fd-tab, SVC-*, FIN-*).</t>
         </is>
       </c>
     </row>
     <row r="109">
       <c r="A109" s="2" t="inlineStr">
         <is>
-          <t>FD-PSALE-003</t>
+          <t>FD-PSALE-002</t>
         </is>
       </c>
       <c r="B109" s="2" t="inlineStr">
         <is>
-          <t>C30624</t>
+          <t>C30623</t>
         </is>
       </c>
       <c r="C109" s="6" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/30624</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/30623</t>
         </is>
       </c>
       <c r="D109" s="2" t="inlineStr">
@@ -5756,7 +5756,7 @@
       </c>
       <c r="E109" s="2" t="inlineStr">
         <is>
-          <t>Verify the parts-sale per-part three-dot menu item reads 'Add Part Fee / Discount'</t>
+          <t>Verify the parts-sale Fees &amp; Discounts column no longer shows the '+ Add' button, and the per-row and top-right three-dot entry points remain</t>
         </is>
       </c>
       <c r="F109" s="2" t="inlineStr">
@@ -5776,34 +5776,34 @@
       </c>
       <c r="I109" s="2" t="inlineStr">
         <is>
-          <t>TEST part sale P3-1118 (2 fee-less rows + NEXUS 2-adj) + whole-sale percent/flat/discount; observed live as admin (Part Sales C&amp;E + SFD). Evidence build/fees-discounts/viu-sv8479-8480-2026-07-22/psale/. Per-part ⋮ menu text = 'Add Part Fee / Discount' exactly; opens 'New Part Fee / Discount' dialog.</t>
+          <t xml:space="preserve"> NEXUS 2-adj) + whole-sale percent/flat/discount; observed live as admin (Part Sales C&amp;E + SFD). Evidence build/fees-discounts/viu-sv8479-8480-2026-07-22/psale/. F&amp;D column has no '+ Add' (grep '+Add'=0); per-row ⋮ 'Add Part Fee / Discount' + top-right ⋮ 'Add Parts Sale Fee / Discount' both present.</t>
         </is>
       </c>
     </row>
     <row r="110">
       <c r="A110" s="2" t="inlineStr">
         <is>
-          <t>FD-PSALE-004</t>
+          <t>FD-PSALE-003</t>
         </is>
       </c>
       <c r="B110" s="2" t="inlineStr">
         <is>
-          <t>C30625</t>
+          <t>C30624</t>
         </is>
       </c>
       <c r="C110" s="6" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/30625</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/30624</t>
         </is>
       </c>
       <c r="D110" s="2" t="inlineStr">
         <is>
-          <t>Parts Sale — Fees &amp; Discounts card</t>
+          <t>Parts page — 'FEES &amp; DISCOUNTS' column</t>
         </is>
       </c>
       <c r="E110" s="2" t="inlineStr">
         <is>
-          <t>Verify the Parts Sale Fees &amp; Discounts card shows each adjustment as plain text with the percentage in brackets (no colored badge)</t>
+          <t>Verify the parts-sale per-part three-dot menu item reads 'Add Part Fee / Discount'</t>
         </is>
       </c>
       <c r="F110" s="2" t="inlineStr">
@@ -5823,34 +5823,34 @@
       </c>
       <c r="I110" s="2" t="inlineStr">
         <is>
-          <t>/fees-discounts/viu-sv8479-8480-2026-07-22/psale/. Whole-sale card 'Parts Sale Fees &amp; Discounts' live: 'Customer Fee (10%) +$82.12', 'Sale Disc (−5%) −$41.06', 'Flat Fee +$50.00' (flat name-only), 'Processing Fee (6%) +$51.73' — plain text, no badge, bracket %/sign convention matches WO card item 5.</t>
+          <t>TEST part sale P3-1118 (2 fee-less rows + NEXUS 2-adj) + whole-sale percent/flat/discount; observed live as admin (Part Sales C&amp;E + SFD). Evidence build/fees-discounts/viu-sv8479-8480-2026-07-22/psale/. Per-part ⋮ menu text = 'Add Part Fee / Discount' exactly; opens 'New Part Fee / Discount' dialog.</t>
         </is>
       </c>
     </row>
     <row r="111">
       <c r="A111" s="2" t="inlineStr">
         <is>
-          <t>FD-PSALE-006</t>
+          <t>FD-PSALE-004</t>
         </is>
       </c>
       <c r="B111" s="2" t="inlineStr">
         <is>
-          <t>C30626</t>
+          <t>C30625</t>
         </is>
       </c>
       <c r="C111" s="6" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/30626</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/30625</t>
         </is>
       </c>
       <c r="D111" s="2" t="inlineStr">
         <is>
-          <t>Parts Sale — Financial Info card</t>
+          <t>Parts Sale — Fees &amp; Discounts card</t>
         </is>
       </c>
       <c r="E111" s="2" t="inlineStr">
         <is>
-          <t>Verify the parts-sale Financial Info card shows a 'Fees &amp; Discounts (N)' line directly above Subtotal and hides it when there are none</t>
+          <t>Verify the Parts Sale Fees &amp; Discounts card shows each adjustment as plain text with the percentage in brackets (no colored badge)</t>
         </is>
       </c>
       <c r="F111" s="2" t="inlineStr">
@@ -5870,34 +5870,34 @@
       </c>
       <c r="I111" s="2" t="inlineStr">
         <is>
-          <t>ded ZZAUTOTEST part sale P3-1118 (2 fee-less rows + NEXUS 2-adj) + whole-sale percent/flat/discount; observed live as admin (Part Sales C&amp;E + SFD). Evidence build/fees-discounts/viu-sv8479-8480-2026-07-22/psale/. Live: 'Fees &amp; Discounts (6) $189.27' directly above Subtotal $963.95 in Financial Info.</t>
+          <t>/fees-discounts/viu-sv8479-8480-2026-07-22/psale/. Whole-sale card 'Parts Sale Fees &amp; Discounts' live: 'Customer Fee (10%) +$82.12', 'Sale Disc (−5%) −$41.06', 'Flat Fee +$50.00' (flat name-only), 'Processing Fee (6%) +$51.73' — plain text, no badge, bracket %/sign convention matches WO card item 5.</t>
         </is>
       </c>
     </row>
     <row r="112">
       <c r="A112" s="2" t="inlineStr">
         <is>
-          <t>FD-PSALE-008</t>
+          <t>FD-PSALE-006</t>
         </is>
       </c>
       <c r="B112" s="2" t="inlineStr">
         <is>
-          <t>C30627</t>
+          <t>C30626</t>
         </is>
       </c>
       <c r="C112" s="6" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/30627</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/30626</t>
         </is>
       </c>
       <c r="D112" s="2" t="inlineStr">
         <is>
-          <t>Part Sale — Fee/Discount dialog</t>
+          <t>Parts Sale — Financial Info card</t>
         </is>
       </c>
       <c r="E112" s="2" t="inlineStr">
         <is>
-          <t>Verify the whole-parts-sale fee/discount dialog title reads 'New Parts Sale Fee / Discount' with subline 'Applying To: Entire Parts Sale'</t>
+          <t>Verify the parts-sale Financial Info card shows a 'Fees &amp; Discounts (N)' line directly above Subtotal and hides it when there are none</t>
         </is>
       </c>
       <c r="F112" s="2" t="inlineStr">
@@ -5917,34 +5917,34 @@
       </c>
       <c r="I112" s="2" t="inlineStr">
         <is>
-          <t>). Evidence build/fees-discounts/viu-sv8479-8480-2026-07-22/psale/. VIU-CONFIRM RESOLVED (Picture 26 was missing): top-right ⋮ label CONFIRMED LIVE = 'Add Parts Sale Fee / Discount'; dialog title 'New Parts Sale Fee / Discount'; subline 'Applying To: Entire Parts Sale'. Case wording already matched.</t>
+          <t>ded ZZAUTOTEST part sale P3-1118 (2 fee-less rows + NEXUS 2-adj) + whole-sale percent/flat/discount; observed live as admin (Part Sales C&amp;E + SFD). Evidence build/fees-discounts/viu-sv8479-8480-2026-07-22/psale/. Live: 'Fees &amp; Discounts (6) $189.27' directly above Subtotal $963.95 in Financial Info.</t>
         </is>
       </c>
     </row>
     <row r="113">
       <c r="A113" s="2" t="inlineStr">
         <is>
-          <t>FD-PSALE-009</t>
+          <t>FD-PSALE-008</t>
         </is>
       </c>
       <c r="B113" s="2" t="inlineStr">
         <is>
-          <t>C30628</t>
+          <t>C30627</t>
         </is>
       </c>
       <c r="C113" s="6" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/30628</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/30627</t>
         </is>
       </c>
       <c r="D113" s="2" t="inlineStr">
         <is>
-          <t>Parts Sale — Statistics tab</t>
+          <t>Part Sale — Fee/Discount dialog</t>
         </is>
       </c>
       <c r="E113" s="2" t="inlineStr">
         <is>
-          <t>Verify the Fees &amp; Discounts section on the parts-sale Statistics tab shows the '%' and 'Amount' column headings</t>
+          <t>Verify the whole-parts-sale fee/discount dialog title reads 'New Parts Sale Fee / Discount' with subline 'Applying To: Entire Parts Sale'</t>
         </is>
       </c>
       <c r="F113" s="2" t="inlineStr">
@@ -5964,39 +5964,39 @@
       </c>
       <c r="I113" s="2" t="inlineStr">
         <is>
-          <t>ss rows + NEXUS 2-adj) + whole-sale percent/flat/discount; observed live as admin (Part Sales C&amp;E + SFD). Evidence build/fees-discounts/viu-sv8479-8480-2026-07-22/psale/. Statistics F&amp;D (6) section live headings '% Amount'; flat fee blank %; rows +11%/+6%/+10% fees + −5% discounts; 'Total +$189.27'.</t>
+          <t>). Evidence build/fees-discounts/viu-sv8479-8480-2026-07-22/psale/. VIU-CONFIRM RESOLVED (Picture 26 was missing): top-right ⋮ label CONFIRMED LIVE = 'Add Parts Sale Fee / Discount'; dialog title 'New Parts Sale Fee / Discount'; subline 'Applying To: Entire Parts Sale'. Case wording already matched.</t>
         </is>
       </c>
     </row>
     <row r="114">
       <c r="A114" s="2" t="inlineStr">
         <is>
-          <t>FD-QB-012</t>
+          <t>FD-PSALE-009</t>
         </is>
       </c>
       <c r="B114" s="2" t="inlineStr">
         <is>
-          <t>C28555</t>
+          <t>C30628</t>
         </is>
       </c>
       <c r="C114" s="6" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/28555</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/30628</t>
         </is>
       </c>
       <c r="D114" s="2" t="inlineStr">
         <is>
-          <t>QuickBooks — negative totals</t>
+          <t>Parts Sale — Statistics tab</t>
         </is>
       </c>
       <c r="E114" s="2" t="inlineStr">
         <is>
-          <t>Verify the net subtotal floors at $0.00 ($100 parts + $10 tax, $150 discount: non-taxable vs taxable)</t>
+          <t>Verify the Fees &amp; Discounts section on the parts-sale Statistics tab shows the '%' and 'Amount' column headings</t>
         </is>
       </c>
       <c r="F114" s="2" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="G114" s="2" t="inlineStr">
@@ -6011,24 +6011,24 @@
       </c>
       <c r="I114" s="2" t="inlineStr">
         <is>
-          <t>floor worked-example halves re-proven at WO level: non-taxable over-discount -&gt; sub 0.00, tax UNCHANGED (9.14), total=tax, excess 117.24; taxable variant -&gt; tax 0.00, total 0.00 | WORDING+VIU 2026-07-13: In-app floor VERIFIED (same worked example as FD-CALC-015, confirmed 2026-07-10); the customer pays the tax only.</t>
+          <t>ss rows + NEXUS 2-adj) + whole-sale percent/flat/discount; observed live as admin (Part Sales C&amp;E + SFD). Evidence build/fees-discounts/viu-sv8479-8480-2026-07-22/psale/. Statistics F&amp;D (6) section live headings '% Amount'; flat fee blank %; rows +11%/+6%/+10% fees + −5% discounts; 'Total +$189.27'.</t>
         </is>
       </c>
     </row>
     <row r="115">
       <c r="A115" s="2" t="inlineStr">
         <is>
-          <t>FD-QB-014</t>
+          <t>FD-QB-012</t>
         </is>
       </c>
       <c r="B115" s="2" t="inlineStr">
         <is>
-          <t>C28557</t>
+          <t>C28555</t>
         </is>
       </c>
       <c r="C115" s="6" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/28557</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/28555</t>
         </is>
       </c>
       <c r="D115" s="2" t="inlineStr">
@@ -6038,7 +6038,7 @@
       </c>
       <c r="E115" s="2" t="inlineStr">
         <is>
-          <t>Verify a mandatory warning/confirmation before saving when discounts are bigger than the net subtotal</t>
+          <t>Verify the net subtotal floors at $0.00 ($100 parts + $10 tax, $150 discount: non-taxable vs taxable)</t>
         </is>
       </c>
       <c r="F115" s="2" t="inlineStr">
@@ -6058,34 +6058,34 @@
       </c>
       <c r="I115" s="2" t="inlineStr">
         <is>
-          <t>FDBUG-15 CONFIRMED AGAIN (API half): over-discount saves 201 with NO warning payload; excess carried silently (117.24). Batch-6 UI shots show no warn/confirm dialog. Violates S6-R12 | WORDING+VIU 2026-07-13: DEVIATION carried (FDBUG-15 / PO Q1 pending): an over-discount currently saves SILENTLY — no mandatory warn/confirm before saving. Expected kept as the spec requirement. | CHRIS WARD ROUND-2 ANSWER APPLIED 2026-07-14(Q1=A): PO ruled the warn/confirm is required AND already exists per spec (S6-R12) — it fires before invoicing and before marking the WO reviewed/complete, NOT when the adjustment is merely added (add is uncommitted; the Add dialog preview shows the resulting totals). Our FDBUG-15 'silent save' was observed at ADD time = the wrong trigger point; PO says that is intentional. FDBUG-15 reclassified NOT-A-DEFECT (no dev ticket released). Expected reworded to the commit-point warning. Status -&gt; VIU-Pending: the invoice/mark-reviewed/complete warning has not yet been observed live and needs a commit-time re-VIU. PUSHED TO TESTRAIL 2026-07-14 via update_case (QA-lead one-day authorization; update 200 / re-verify 200 MATCH; audit: testrail-round2-push-log.md). COMMIT-TIME RE-VIU 2026-07-14: attempted but BOTH qb cookie sets (cookies-viu.env 2026-07-13, cookies-fresh.env 2026-07-10) return 401 sso_required on quick-login (env woken, API root 200) — cookies EXPIRED. Left VIU-Pending: needs fresh qb cookies for the commit-time (invoice / mark-reviewed / complete) re-VIU. | COMMIT-TIME RE-VIU SETTLED 2026-07-14 (fresh qb cookies): VERIFIED. Live FE source + live data-condition confirm Chris's Q1=A exactly. (1) ADD-TIME SILENT: the Add/Edit dialog component (AdjustmentDialog) has NO over-discount warning and does not import the warning dialog -- adding an over-sized discount is silent (only an unrelated 'A percentage discount cannot exceed 100%' field check). (2) COMMIT-TIME WARN/CONFIRM BUILT: a dedicated component OverDiscountWarningDialog exists (title 'Discount exceeds subtotal'; body "The total discount exceeds this work order's subtotal. The subtotal will be reduced to $0.00, but any tax on the taxable base is still owed. The remaining $&lt;excess&gt; will be carried as a customer credit. Continue?"; buttons Continue / Cancel). It is imported and wired in the Invoice component: the Create-Invoice handler (Lt-&gt;_a) AND the mark-reviewed/Complete handler (Vt-&gt;ga, posts status:'complete') BOTH intercept when the excess-credit gate is true (FeesAndDiscounts flag ON &amp;&amp; not partSale &amp;&amp; adjustmentsSummary.excessCreditAmount&gt;0), open the dialog, and only run the commit on Continue (confirm) / abort on Cancel. So the mandatory warn/confirm fires at BOTH commit points, never silently. (3) LIVE DATA CONDITION: on WO S-15970 added a $9,999 whole-WO flat discount (reversible ZZAUTOTEST, removed after) -&gt; sub_total floored to $0.00, adjustmentsSummary.excessCreditAmount=9522.26 (&gt;0) =&gt; the FE gate evaluates TRUE, so the dialog would fire at Create Invoice / Mark-Reviewed / Complete. WO restored byte-identical to baseline afterward. Evidence: FE chunks OverDiscountWarningDialog.BCmTBE33.js + Invoice.Ny62BJnd.js + AdjustmentDialog.S8gN6cAn.js (captured live from qb.qa.shopview.com 2026-07-14); live API view before/after. Verdict: VIU-Verified. FDBUG-15 stays NOT-A-DEFECT (add-time silence is intentional). Expected wording already build-accurate (floor $0.00 + tax on taxable base still owed + exact excess as customer credit + must confirm) -&gt; no TestRail wording change needed; status flip local only. Exact on-screen labels now captured for the record: dialog 'Discount exceeds subtotal', buttons 'Continue'/'Cancel'.</t>
+          <t>floor worked-example halves re-proven at WO level: non-taxable over-discount -&gt; sub 0.00, tax UNCHANGED (9.14), total=tax, excess 117.24; taxable variant -&gt; tax 0.00, total 0.00 | WORDING+VIU 2026-07-13: In-app floor VERIFIED (same worked example as FD-CALC-015, confirmed 2026-07-10); the customer pays the tax only.</t>
         </is>
       </c>
     </row>
     <row r="116">
       <c r="A116" s="2" t="inlineStr">
         <is>
-          <t>FD-REMOVE-001</t>
+          <t>FD-QB-014</t>
         </is>
       </c>
       <c r="B116" s="2" t="inlineStr">
         <is>
-          <t>C28479</t>
+          <t>C28557</t>
         </is>
       </c>
       <c r="C116" s="6" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/28479</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/28557</t>
         </is>
       </c>
       <c r="D116" s="2" t="inlineStr">
         <is>
-          <t>Work Order — Remove an adjustment</t>
+          <t>QuickBooks — negative totals</t>
         </is>
       </c>
       <c r="E116" s="2" t="inlineStr">
         <is>
-          <t>Verify removing a whole-work-order fee/discount shows the 'Remove Fee / Discount' confirm and a success message</t>
+          <t>Verify a mandatory warning/confirmation before saving when discounts are bigger than the net subtotal</t>
         </is>
       </c>
       <c r="F116" s="2" t="inlineStr">
@@ -6105,24 +6105,24 @@
       </c>
       <c r="I116" s="2" t="inlineStr">
         <is>
-          <t>remove-confirm wording drift per batch-1 (case-update); not re-driven today | WORDING+VIU 2026-07-13: Confirm dialog matched EXACTLY live: title 'Remove Fee / Discount', message 'Are you sure you want to remove this fee?', buttons 'Remove'/'Cancel' (shot inline-02; cancelled — no shared data deleted). Toast not re-observed this run. | SV-8456 (2026-07-21 staging LIVE VIU): F&amp;D moved to SETTINGS→SERVICE (below Canned Lines); template/WO/Part-sale/customer dialogs now show Taxable as a Yes/No DROPDOWN (was toggle); Auto-apply is a CHECKBOX with a 'When on…' caption; settings &amp; customer tables are plain-text/left-aligned (no badges); WO sidebar card retitled 'Work Order Fees &amp; Discounts' and renders ABOVE Financial Info; Part-sale card 'Parts Sale Fees &amp; Discounts' above Financial Info. Permission gate pivoted Settings→Finance → Settings→Service (verified live: Service-user sees+manages F&amp;D &amp; convenience toggle; Finance-only user has no F&amp;D nav item and /administration/adjustment-templates bounces to /workorders). Frontend-only; functionality + calc INTACT. | RE-VIU 2026-07-22 LIVE (Batch 4, SV-8456 re-verify): access-check quick-login {admin} HTTP 200. Re-confirmed on current staging build — 8 UI corrections intact (Taxable Yes/No dropdown; Auto-apply checkbox+caption; modal field order Type/CalcType&gt;Name&gt;Amount&gt;Taxable+jur.note&gt;Auto-apply&gt;Description; Settings table plain-text left-aligned no badges; F&amp;D nav under SERVICE below Canned Lines; WO &amp; Part-Sale cards above Financial Info [Batch 2/3]; Customer 'Fees &amp; Discounts' tab mirrors Settings styling minus convenience toggle) AND Settings-&gt;Service permission pivot CONFIRMED live per role (seeded ServiceRole vs FinanceRole, assigned to Tech, Tech restored to Technician 50bf6a0d + verified, both ZZAUTOTEST roles deleted 204): Service-user sees+manages F&amp;D nav + convenience toggle, direct /administration/adjustment-templates loads; Finance-only user has NO F&amp;D nav, FINANCE=Payment Methods only, direct route bounces to /workorders. viu_status VIU-Verified re-confirmed. Ev build/fees-discounts/viu-sv8456-2026-07-22/ (01-settings-landing, 02-new-dialog, 03-customer-fd-tab, SVC-*, FIN-*).</t>
+          <t>FDBUG-15 CONFIRMED AGAIN (API half): over-discount saves 201 with NO warning payload; excess carried silently (117.24). Batch-6 UI shots show no warn/confirm dialog. Violates S6-R12 | WORDING+VIU 2026-07-13: DEVIATION carried (FDBUG-15 / PO Q1 pending): an over-discount currently saves SILENTLY — no mandatory warn/confirm before saving. Expected kept as the spec requirement. | CHRIS WARD ROUND-2 ANSWER APPLIED 2026-07-14(Q1=A): PO ruled the warn/confirm is required AND already exists per spec (S6-R12) — it fires before invoicing and before marking the WO reviewed/complete, NOT when the adjustment is merely added (add is uncommitted; the Add dialog preview shows the resulting totals). Our FDBUG-15 'silent save' was observed at ADD time = the wrong trigger point; PO says that is intentional. FDBUG-15 reclassified NOT-A-DEFECT (no dev ticket released). Expected reworded to the commit-point warning. Status -&gt; VIU-Pending: the invoice/mark-reviewed/complete warning has not yet been observed live and needs a commit-time re-VIU. PUSHED TO TESTRAIL 2026-07-14 via update_case (QA-lead one-day authorization; update 200 / re-verify 200 MATCH; audit: testrail-round2-push-log.md). COMMIT-TIME RE-VIU 2026-07-14: attempted but BOTH qb cookie sets (cookies-viu.env 2026-07-13, cookies-fresh.env 2026-07-10) return 401 sso_required on quick-login (env woken, API root 200) — cookies EXPIRED. Left VIU-Pending: needs fresh qb cookies for the commit-time (invoice / mark-reviewed / complete) re-VIU. | COMMIT-TIME RE-VIU SETTLED 2026-07-14 (fresh qb cookies): VERIFIED. Live FE source + live data-condition confirm Chris's Q1=A exactly. (1) ADD-TIME SILENT: the Add/Edit dialog component (AdjustmentDialog) has NO over-discount warning and does not import the warning dialog -- adding an over-sized discount is silent (only an unrelated 'A percentage discount cannot exceed 100%' field check). (2) COMMIT-TIME WARN/CONFIRM BUILT: a dedicated component OverDiscountWarningDialog exists (title 'Discount exceeds subtotal'; body "The total discount exceeds this work order's subtotal. The subtotal will be reduced to $0.00, but any tax on the taxable base is still owed. The remaining $&lt;excess&gt; will be carried as a customer credit. Continue?"; buttons Continue / Cancel). It is imported and wired in the Invoice component: the Create-Invoice handler (Lt-&gt;_a) AND the mark-reviewed/Complete handler (Vt-&gt;ga, posts status:'complete') BOTH intercept when the excess-credit gate is true (FeesAndDiscounts flag ON &amp;&amp; not partSale &amp;&amp; adjustmentsSummary.excessCreditAmount&gt;0), open the dialog, and only run the commit on Continue (confirm) / abort on Cancel. So the mandatory warn/confirm fires at BOTH commit points, never silently. (3) LIVE DATA CONDITION: on WO S-15970 added a $9,999 whole-WO flat discount (reversible ZZAUTOTEST, removed after) -&gt; sub_total floored to $0.00, adjustmentsSummary.excessCreditAmount=9522.26 (&gt;0) =&gt; the FE gate evaluates TRUE, so the dialog would fire at Create Invoice / Mark-Reviewed / Complete. WO restored byte-identical to baseline afterward. Evidence: FE chunks OverDiscountWarningDialog.BCmTBE33.js + Invoice.Ny62BJnd.js + AdjustmentDialog.S8gN6cAn.js (captured live from qb.qa.shopview.com 2026-07-14); live API view before/after. Verdict: VIU-Verified. FDBUG-15 stays NOT-A-DEFECT (add-time silence is intentional). Expected wording already build-accurate (floor $0.00 + tax on taxable base still owed + exact excess as customer credit + must confirm) -&gt; no TestRail wording change needed; status flip local only. Exact on-screen labels now captured for the record: dialog 'Discount exceeds subtotal', buttons 'Continue'/'Cancel'.</t>
         </is>
       </c>
     </row>
     <row r="117">
       <c r="A117" s="2" t="inlineStr">
         <is>
-          <t>FD-REMOVE-002</t>
+          <t>FD-REMOVE-001</t>
         </is>
       </c>
       <c r="B117" s="2" t="inlineStr">
         <is>
-          <t>C28480</t>
+          <t>C28479</t>
         </is>
       </c>
       <c r="C117" s="6" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/28480</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/28479</t>
         </is>
       </c>
       <c r="D117" s="2" t="inlineStr">
@@ -6132,7 +6132,7 @@
       </c>
       <c r="E117" s="2" t="inlineStr">
         <is>
-          <t>Verify removing a fee/discount uses Create and Edit, not a separate Delete permission</t>
+          <t>Verify removing a whole-work-order fee/discount shows the 'Remove Fee / Discount' confirm and a success message</t>
         </is>
       </c>
       <c r="F117" s="2" t="inlineStr">
@@ -6152,24 +6152,24 @@
       </c>
       <c r="I117" s="2" t="inlineStr">
         <is>
-          <t>removal governed by Create&amp;Edit (tech WITH lines-C&amp;E removed line-level 204; no Delete-perm dependency) | WORDING+VIU 2026-07-13: Remove uses Create &amp; Edit not a separate Delete permission; carry prior VIU. | SV-8456 (2026-07-21 staging LIVE VIU): F&amp;D moved to SETTINGS→SERVICE (below Canned Lines); template/WO/Part-sale/customer dialogs now show Taxable as a Yes/No DROPDOWN (was toggle); Auto-apply is a CHECKBOX with a 'When on…' caption; settings &amp; customer tables are plain-text/left-aligned (no badges); WO sidebar card retitled 'Work Order Fees &amp; Discounts' and renders ABOVE Financial Info; Part-sale card 'Parts Sale Fees &amp; Discounts' above Financial Info. Permission gate pivoted Settings→Finance → Settings→Service (verified live: Service-user sees+manages F&amp;D &amp; convenience toggle; Finance-only user has no F&amp;D nav item and /administration/adjustment-templates bounces to /workorders). Frontend-only; functionality + calc INTACT. | RE-VIU 2026-07-22 LIVE (Batch 4, SV-8456 re-verify): access-check quick-login {admin} HTTP 200. Re-confirmed on current staging build — 8 UI corrections intact (Taxable Yes/No dropdown; Auto-apply checkbox+caption; modal field order Type/CalcType&gt;Name&gt;Amount&gt;Taxable+jur.note&gt;Auto-apply&gt;Description; Settings table plain-text left-aligned no badges; F&amp;D nav under SERVICE below Canned Lines; WO &amp; Part-Sale cards above Financial Info [Batch 2/3]; Customer 'Fees &amp; Discounts' tab mirrors Settings styling minus convenience toggle) AND Settings-&gt;Service permission pivot CONFIRMED live per role (seeded ServiceRole vs FinanceRole, assigned to Tech, Tech restored to Technician 50bf6a0d + verified, both ZZAUTOTEST roles deleted 204): Service-user sees+manages F&amp;D nav + convenience toggle, direct /administration/adjustment-templates loads; Finance-only user has NO F&amp;D nav, FINANCE=Payment Methods only, direct route bounces to /workorders. viu_status VIU-Verified re-confirmed. Ev build/fees-discounts/viu-sv8456-2026-07-22/ (01-settings-landing, 02-new-dialog, 03-customer-fd-tab, SVC-*, FIN-*).</t>
+          <t>remove-confirm wording drift per batch-1 (case-update); not re-driven today | WORDING+VIU 2026-07-13: Confirm dialog matched EXACTLY live: title 'Remove Fee / Discount', message 'Are you sure you want to remove this fee?', buttons 'Remove'/'Cancel' (shot inline-02; cancelled — no shared data deleted). Toast not re-observed this run. | SV-8456 (2026-07-21 staging LIVE VIU): F&amp;D moved to SETTINGS→SERVICE (below Canned Lines); template/WO/Part-sale/customer dialogs now show Taxable as a Yes/No DROPDOWN (was toggle); Auto-apply is a CHECKBOX with a 'When on…' caption; settings &amp; customer tables are plain-text/left-aligned (no badges); WO sidebar card retitled 'Work Order Fees &amp; Discounts' and renders ABOVE Financial Info; Part-sale card 'Parts Sale Fees &amp; Discounts' above Financial Info. Permission gate pivoted Settings→Finance → Settings→Service (verified live: Service-user sees+manages F&amp;D &amp; convenience toggle; Finance-only user has no F&amp;D nav item and /administration/adjustment-templates bounces to /workorders). Frontend-only; functionality + calc INTACT. | RE-VIU 2026-07-22 LIVE (Batch 4, SV-8456 re-verify): access-check quick-login {admin} HTTP 200. Re-confirmed on current staging build — 8 UI corrections intact (Taxable Yes/No dropdown; Auto-apply checkbox+caption; modal field order Type/CalcType&gt;Name&gt;Amount&gt;Taxable+jur.note&gt;Auto-apply&gt;Description; Settings table plain-text left-aligned no badges; F&amp;D nav under SERVICE below Canned Lines; WO &amp; Part-Sale cards above Financial Info [Batch 2/3]; Customer 'Fees &amp; Discounts' tab mirrors Settings styling minus convenience toggle) AND Settings-&gt;Service permission pivot CONFIRMED live per role (seeded ServiceRole vs FinanceRole, assigned to Tech, Tech restored to Technician 50bf6a0d + verified, both ZZAUTOTEST roles deleted 204): Service-user sees+manages F&amp;D nav + convenience toggle, direct /administration/adjustment-templates loads; Finance-only user has NO F&amp;D nav, FINANCE=Payment Methods only, direct route bounces to /workorders. viu_status VIU-Verified re-confirmed. Ev build/fees-discounts/viu-sv8456-2026-07-22/ (01-settings-landing, 02-new-dialog, 03-customer-fd-tab, SVC-*, FIN-*).</t>
         </is>
       </c>
     </row>
     <row r="118">
       <c r="A118" s="2" t="inlineStr">
         <is>
-          <t>FD-REMOVE-003</t>
+          <t>FD-REMOVE-002</t>
         </is>
       </c>
       <c r="B118" s="2" t="inlineStr">
         <is>
-          <t>C28481</t>
+          <t>C28480</t>
         </is>
       </c>
       <c r="C118" s="6" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/28481</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/28480</t>
         </is>
       </c>
       <c r="D118" s="2" t="inlineStr">
@@ -6179,12 +6179,12 @@
       </c>
       <c r="E118" s="2" t="inlineStr">
         <is>
-          <t>Verify removing a line-level fee/discount from its inline ⋮ menu</t>
+          <t>Verify removing a fee/discount uses Create and Edit, not a separate Delete permission</t>
         </is>
       </c>
       <c r="F118" s="2" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>High</t>
         </is>
       </c>
       <c r="G118" s="2" t="inlineStr">
@@ -6199,39 +6199,39 @@
       </c>
       <c r="I118" s="2" t="inlineStr">
         <is>
-          <t>line-level remove 204 and gone from the line | WORDING+VIU 2026-07-13: Inline menu option is 'Remove' (was 'Delete'); confirm dialog 'Remove Fee / Discount' confirmed live.</t>
+          <t>removal governed by Create&amp;Edit (tech WITH lines-C&amp;E removed line-level 204; no Delete-perm dependency) | WORDING+VIU 2026-07-13: Remove uses Create &amp; Edit not a separate Delete permission; carry prior VIU. | SV-8456 (2026-07-21 staging LIVE VIU): F&amp;D moved to SETTINGS→SERVICE (below Canned Lines); template/WO/Part-sale/customer dialogs now show Taxable as a Yes/No DROPDOWN (was toggle); Auto-apply is a CHECKBOX with a 'When on…' caption; settings &amp; customer tables are plain-text/left-aligned (no badges); WO sidebar card retitled 'Work Order Fees &amp; Discounts' and renders ABOVE Financial Info; Part-sale card 'Parts Sale Fees &amp; Discounts' above Financial Info. Permission gate pivoted Settings→Finance → Settings→Service (verified live: Service-user sees+manages F&amp;D &amp; convenience toggle; Finance-only user has no F&amp;D nav item and /administration/adjustment-templates bounces to /workorders). Frontend-only; functionality + calc INTACT. | RE-VIU 2026-07-22 LIVE (Batch 4, SV-8456 re-verify): access-check quick-login {admin} HTTP 200. Re-confirmed on current staging build — 8 UI corrections intact (Taxable Yes/No dropdown; Auto-apply checkbox+caption; modal field order Type/CalcType&gt;Name&gt;Amount&gt;Taxable+jur.note&gt;Auto-apply&gt;Description; Settings table plain-text left-aligned no badges; F&amp;D nav under SERVICE below Canned Lines; WO &amp; Part-Sale cards above Financial Info [Batch 2/3]; Customer 'Fees &amp; Discounts' tab mirrors Settings styling minus convenience toggle) AND Settings-&gt;Service permission pivot CONFIRMED live per role (seeded ServiceRole vs FinanceRole, assigned to Tech, Tech restored to Technician 50bf6a0d + verified, both ZZAUTOTEST roles deleted 204): Service-user sees+manages F&amp;D nav + convenience toggle, direct /administration/adjustment-templates loads; Finance-only user has NO F&amp;D nav, FINANCE=Payment Methods only, direct route bounces to /workorders. viu_status VIU-Verified re-confirmed. Ev build/fees-discounts/viu-sv8456-2026-07-22/ (01-settings-landing, 02-new-dialog, 03-customer-fd-tab, SVC-*, FIN-*).</t>
         </is>
       </c>
     </row>
     <row r="119">
       <c r="A119" s="2" t="inlineStr">
         <is>
-          <t>FD-STACK-001</t>
+          <t>FD-REMOVE-003</t>
         </is>
       </c>
       <c r="B119" s="2" t="inlineStr">
         <is>
-          <t>C28482</t>
+          <t>C28481</t>
         </is>
       </c>
       <c r="C119" s="6" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/28482</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/28481</t>
         </is>
       </c>
       <c r="D119" s="2" t="inlineStr">
         <is>
-          <t>Work Order — Multiple adjustments (stacking / netting)</t>
+          <t>Work Order — Remove an adjustment</t>
         </is>
       </c>
       <c r="E119" s="2" t="inlineStr">
         <is>
-          <t>Verify multiple fees/discounts on one part each work out on the part's own total (they do not compound)</t>
+          <t>Verify removing a line-level fee/discount from its inline ⋮ menu</t>
         </is>
       </c>
       <c r="F119" s="2" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="G119" s="2" t="inlineStr">
@@ -6246,24 +6246,24 @@
       </c>
       <c r="I119" s="2" t="inlineStr">
         <is>
-          <t>part flat + part pct resolved independently on the part's own gross (fresh: $8.00 and $17.08 coexist, no compounding) | WORDING+VIU 2026-07-13: Netting carried; build labels. Display half (only first shows + 'Show N more') is the FD-INLINE-003 deviation (no Show-N-more in this build).</t>
+          <t>line-level remove 204 and gone from the line | WORDING+VIU 2026-07-13: Inline menu option is 'Remove' (was 'Delete'); confirm dialog 'Remove Fee / Discount' confirmed live.</t>
         </is>
       </c>
     </row>
     <row r="120">
       <c r="A120" s="2" t="inlineStr">
         <is>
-          <t>FD-STACK-002</t>
+          <t>FD-STACK-001</t>
         </is>
       </c>
       <c r="B120" s="2" t="inlineStr">
         <is>
-          <t>C28483</t>
+          <t>C28482</t>
         </is>
       </c>
       <c r="C120" s="6" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/28483</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/28482</t>
         </is>
       </c>
       <c r="D120" s="2" t="inlineStr">
@@ -6273,7 +6273,7 @@
       </c>
       <c r="E120" s="2" t="inlineStr">
         <is>
-          <t>Verify two whole-work-order percentage fees/discounts use the same totals and do not change each other's base</t>
+          <t>Verify multiple fees/discounts on one part each work out on the part's own total (they do not compound)</t>
         </is>
       </c>
       <c r="F120" s="2" t="inlineStr">
@@ -6293,24 +6293,24 @@
       </c>
       <c r="I120" s="2" t="inlineStr">
         <is>
-          <t>two 10% whole-WO fees resolve 17.08 each (same base, no compounding) | WORDING+VIU 2026-07-13: Same-base netting carried; build labels.</t>
+          <t>part flat + part pct resolved independently on the part's own gross (fresh: $8.00 and $17.08 coexist, no compounding) | WORDING+VIU 2026-07-13: Netting carried; build labels. Display half (only first shows + 'Show N more') is the FD-INLINE-003 deviation (no Show-N-more in this build).</t>
         </is>
       </c>
     </row>
     <row r="121">
       <c r="A121" s="2" t="inlineStr">
         <is>
-          <t>FD-STACK-003</t>
+          <t>FD-STACK-002</t>
         </is>
       </c>
       <c r="B121" s="2" t="inlineStr">
         <is>
-          <t>C28484</t>
+          <t>C28483</t>
         </is>
       </c>
       <c r="C121" s="6" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/28484</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/28483</t>
         </is>
       </c>
       <c r="D121" s="2" t="inlineStr">
@@ -6320,12 +6320,12 @@
       </c>
       <c r="E121" s="2" t="inlineStr">
         <is>
-          <t>Verify the same template can be applied to one work order more than once by hand</t>
+          <t>Verify two whole-work-order percentage fees/discounts use the same totals and do not change each other's base</t>
         </is>
       </c>
       <c r="F121" s="2" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>High</t>
         </is>
       </c>
       <c r="G121" s="2" t="inlineStr">
@@ -6340,39 +6340,39 @@
       </c>
       <c r="I121" s="2" t="inlineStr">
         <is>
-          <t>'Flat fee' template applied twice by hand -&gt; 201/201, two distinct adjustments | WORDING+VIU 2026-07-13: Same-template-twice carried; build labels ('Add Fee/Discount', 'Apply From Template', 'WO Fees &amp; Discounts'). | SV-8456 (2026-07-21 staging LIVE VIU): F&amp;D moved to SETTINGS→SERVICE (below Canned Lines); template/WO/Part-sale/customer dialogs now show Taxable as a Yes/No DROPDOWN (was toggle); Auto-apply is a CHECKBOX with a 'When on…' caption; settings &amp; customer tables are plain-text/left-aligned (no badges); WO sidebar card retitled 'Work Order Fees &amp; Discounts' and renders ABOVE Financial Info; Part-sale card 'Parts Sale Fees &amp; Discounts' above Financial Info. Permission gate pivoted Settings→Finance → Settings→Service (verified live: Service-user sees+manages F&amp;D &amp; convenience toggle; Finance-only user has no F&amp;D nav item and /administration/adjustment-templates bounces to /workorders). Frontend-only; functionality + calc INTACT. | SV-8479/8480 deconfliction 2026-07-22: label sweep: navigation labels -&gt; 'Add Work Order Fee / Discount' / 'New Work Order Fee / Discount' (behavior/expected unchanged). | VIU 2026-07-22 LIVE: SV-8479 nav label 'Add Work Order Fee / Discount' confirmed present in the WO toolbar ⋯ menu; case behavior unchanged. Ev: wo/FD-WO-025-toolbar-menu.png. | RE-VIU 2026-07-22 LIVE (Batch 4, SV-8456 re-verify): access-check quick-login {admin} HTTP 200. Re-confirmed on current staging build — 8 UI corrections intact (Taxable Yes/No dropdown; Auto-apply checkbox+caption; modal field order Type/CalcType&gt;Name&gt;Amount&gt;Taxable+jur.note&gt;Auto-apply&gt;Description; Settings table plain-text left-aligned no badges; F&amp;D nav under SERVICE below Canned Lines; WO &amp; Part-Sale cards above Financial Info [Batch 2/3]; Customer 'Fees &amp; Discounts' tab mirrors Settings styling minus convenience toggle) AND Settings-&gt;Service permission pivot CONFIRMED live per role (seeded ServiceRole vs FinanceRole, assigned to Tech, Tech restored to Technician 50bf6a0d + verified, both ZZAUTOTEST roles deleted 204): Service-user sees+manages F&amp;D nav + convenience toggle, direct /administration/adjustment-templates loads; Finance-only user has NO F&amp;D nav, FINANCE=Payment Methods only, direct route bounces to /workorders. viu_status VIU-Verified re-confirmed. Ev build/fees-discounts/viu-sv8456-2026-07-22/ (01-settings-landing, 02-new-dialog, 03-customer-fd-tab, SVC-*, FIN-*).</t>
+          <t>two 10% whole-WO fees resolve 17.08 each (same base, no compounding) | WORDING+VIU 2026-07-13: Same-base netting carried; build labels.</t>
         </is>
       </c>
     </row>
     <row r="122">
       <c r="A122" s="2" t="inlineStr">
         <is>
-          <t>FD-STATS-001</t>
+          <t>FD-STACK-003</t>
         </is>
       </c>
       <c r="B122" s="2" t="inlineStr">
         <is>
-          <t>C28459</t>
+          <t>C28484</t>
         </is>
       </c>
       <c r="C122" s="6" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/28459</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/28484</t>
         </is>
       </c>
       <c r="D122" s="2" t="inlineStr">
         <is>
-          <t>Work Order — Statistics tab</t>
+          <t>Work Order — Multiple adjustments (stacking / netting)</t>
         </is>
       </c>
       <c r="E122" s="2" t="inlineStr">
         <is>
-          <t>Verify the Stats tab Fees &amp; Discounts section shows the '%' and 'Amount' column headings with each row's value and amount</t>
+          <t>Verify the same template can be applied to one work order more than once by hand</t>
         </is>
       </c>
       <c r="F122" s="2" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="G122" s="2" t="inlineStr">
@@ -6387,24 +6387,24 @@
       </c>
       <c r="I122" s="2" t="inlineStr">
         <is>
-          <t>CONFIRMED AGAIN: Stats shows aggregate 'Fees &amp; Discounts (5) $25.00' style block, NOT the per-row Value/%+Amount table — PO Q1=B design regression persists (shot 07-stats) | WORDING+VIU 2026-07-13: DEVIATION (BUG-FD-2): the Stats 'Fees &amp; Discounts (N)' section lists rows (name, a value/% for percentages, and an amount) but has NO 'Value'/'Amount' column headers like the other Stats sections. Confirmed live (shot fin-01). | SV-8479/8480 deconfliction 2026-07-22: added the right-side '%' and 'Amount' column headings + blank-% for flat fees (item 12). Absorbs dropped new case FD-WO-027. viu_status unchanged (VIU-Deviation) — re-observe at VIU. | VIU 2026-07-22 LIVE: prior 'no headers' deviation RESOLVED — Stats tab 'Fees &amp; Discounts (10)' section now shows the '% Amount' column headings. Rows show percent under % (blank for flat: 'Flat Fee 2 +$32.00', 'Flat Fee +$11.00') and signed amount under Amount ('Labor Fee +20% +$101.98', 'Labor Disc −10% −$50.99', 'Customer Fee +10% +$65.88', 'WO Disc −5% −$32.94'), with 'Total +$273.31'. Ev: wo/FD-STATS-001-stats-tab.png, wo/stats-bodytext.txt.</t>
+          <t>'Flat fee' template applied twice by hand -&gt; 201/201, two distinct adjustments | WORDING+VIU 2026-07-13: Same-template-twice carried; build labels ('Add Fee/Discount', 'Apply From Template', 'WO Fees &amp; Discounts'). | SV-8456 (2026-07-21 staging LIVE VIU): F&amp;D moved to SETTINGS→SERVICE (below Canned Lines); template/WO/Part-sale/customer dialogs now show Taxable as a Yes/No DROPDOWN (was toggle); Auto-apply is a CHECKBOX with a 'When on…' caption; settings &amp; customer tables are plain-text/left-aligned (no badges); WO sidebar card retitled 'Work Order Fees &amp; Discounts' and renders ABOVE Financial Info; Part-sale card 'Parts Sale Fees &amp; Discounts' above Financial Info. Permission gate pivoted Settings→Finance → Settings→Service (verified live: Service-user sees+manages F&amp;D &amp; convenience toggle; Finance-only user has no F&amp;D nav item and /administration/adjustment-templates bounces to /workorders). Frontend-only; functionality + calc INTACT. | SV-8479/8480 deconfliction 2026-07-22: label sweep: navigation labels -&gt; 'Add Work Order Fee / Discount' / 'New Work Order Fee / Discount' (behavior/expected unchanged). | VIU 2026-07-22 LIVE: SV-8479 nav label 'Add Work Order Fee / Discount' confirmed present in the WO toolbar ⋯ menu; case behavior unchanged. Ev: wo/FD-WO-025-toolbar-menu.png. | RE-VIU 2026-07-22 LIVE (Batch 4, SV-8456 re-verify): access-check quick-login {admin} HTTP 200. Re-confirmed on current staging build — 8 UI corrections intact (Taxable Yes/No dropdown; Auto-apply checkbox+caption; modal field order Type/CalcType&gt;Name&gt;Amount&gt;Taxable+jur.note&gt;Auto-apply&gt;Description; Settings table plain-text left-aligned no badges; F&amp;D nav under SERVICE below Canned Lines; WO &amp; Part-Sale cards above Financial Info [Batch 2/3]; Customer 'Fees &amp; Discounts' tab mirrors Settings styling minus convenience toggle) AND Settings-&gt;Service permission pivot CONFIRMED live per role (seeded ServiceRole vs FinanceRole, assigned to Tech, Tech restored to Technician 50bf6a0d + verified, both ZZAUTOTEST roles deleted 204): Service-user sees+manages F&amp;D nav + convenience toggle, direct /administration/adjustment-templates loads; Finance-only user has NO F&amp;D nav, FINANCE=Payment Methods only, direct route bounces to /workorders. viu_status VIU-Verified re-confirmed. Ev build/fees-discounts/viu-sv8456-2026-07-22/ (01-settings-landing, 02-new-dialog, 03-customer-fd-tab, SVC-*, FIN-*).</t>
         </is>
       </c>
     </row>
     <row r="123">
       <c r="A123" s="2" t="inlineStr">
         <is>
-          <t>FD-STATS-003</t>
+          <t>FD-STATS-001</t>
         </is>
       </c>
       <c r="B123" s="2" t="inlineStr">
         <is>
-          <t>C28461</t>
+          <t>C28459</t>
         </is>
       </c>
       <c r="C123" s="6" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/28461</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/28459</t>
         </is>
       </c>
       <c r="D123" s="2" t="inlineStr">
@@ -6414,7 +6414,7 @@
       </c>
       <c r="E123" s="2" t="inlineStr">
         <is>
-          <t>Verify the Stats 'Fees &amp; Discounts' total equals the signed sum of all the amounts</t>
+          <t>Verify the Stats tab Fees &amp; Discounts section shows the '%' and 'Amount' column headings with each row's value and amount</t>
         </is>
       </c>
       <c r="F123" s="2" t="inlineStr">
@@ -6434,24 +6434,24 @@
       </c>
       <c r="I123" s="2" t="inlineStr">
         <is>
-          <t>net = signed sum re-consistent (adjustmentsSummary netAmount matches card); full UI table from batch-2 | WORDING+VIU 2026-07-13: Total = signed sum; carry prior VIU. Minus-sign jargon removed.</t>
+          <t>CONFIRMED AGAIN: Stats shows aggregate 'Fees &amp; Discounts (5) $25.00' style block, NOT the per-row Value/%+Amount table — PO Q1=B design regression persists (shot 07-stats) | WORDING+VIU 2026-07-13: DEVIATION (BUG-FD-2): the Stats 'Fees &amp; Discounts (N)' section lists rows (name, a value/% for percentages, and an amount) but has NO 'Value'/'Amount' column headers like the other Stats sections. Confirmed live (shot fin-01). | SV-8479/8480 deconfliction 2026-07-22: added the right-side '%' and 'Amount' column headings + blank-% for flat fees (item 12). Absorbs dropped new case FD-WO-027. viu_status unchanged (VIU-Deviation) — re-observe at VIU. | VIU 2026-07-22 LIVE: prior 'no headers' deviation RESOLVED — Stats tab 'Fees &amp; Discounts (10)' section now shows the '% Amount' column headings. Rows show percent under % (blank for flat: 'Flat Fee 2 +$32.00', 'Flat Fee +$11.00') and signed amount under Amount ('Labor Fee +20% +$101.98', 'Labor Disc −10% −$50.99', 'Customer Fee +10% +$65.88', 'WO Disc −5% −$32.94'), with 'Total +$273.31'. Ev: wo/FD-STATS-001-stats-tab.png, wo/stats-bodytext.txt.</t>
         </is>
       </c>
     </row>
     <row r="124">
       <c r="A124" s="2" t="inlineStr">
         <is>
-          <t>FD-STATS-005</t>
+          <t>FD-STATS-003</t>
         </is>
       </c>
       <c r="B124" s="2" t="inlineStr">
         <is>
-          <t>C28463</t>
+          <t>C28461</t>
         </is>
       </c>
       <c r="C124" s="6" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/28463</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/28461</t>
         </is>
       </c>
       <c r="D124" s="2" t="inlineStr">
@@ -6461,12 +6461,12 @@
       </c>
       <c r="E124" s="2" t="inlineStr">
         <is>
-          <t>Verify the Stats 'Fees &amp; Discounts' section is hidden when the work order has no fees/discounts</t>
+          <t>Verify the Stats 'Fees &amp; Discounts' total equals the signed sum of all the amounts</t>
         </is>
       </c>
       <c r="F124" s="2" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>High</t>
         </is>
       </c>
       <c r="G124" s="2" t="inlineStr">
@@ -6481,39 +6481,39 @@
       </c>
       <c r="I124" s="2" t="inlineStr">
         <is>
-          <t>no-adjustments WO -&gt; adjustments=[] + all-zero summary -&gt; section hidden | WORDING+VIU 2026-07-13: Section hidden with no adjustments; carry prior VIU.</t>
+          <t>net = signed sum re-consistent (adjustmentsSummary netAmount matches card); full UI table from batch-2 | WORDING+VIU 2026-07-13: Total = signed sum; carry prior VIU. Minus-sign jargon removed.</t>
         </is>
       </c>
     </row>
     <row r="125">
       <c r="A125" s="2" t="inlineStr">
         <is>
-          <t>FD-TMPL-001</t>
+          <t>FD-STATS-005</t>
         </is>
       </c>
       <c r="B125" s="2" t="inlineStr">
         <is>
-          <t>C28502</t>
+          <t>C28463</t>
         </is>
       </c>
       <c r="C125" s="6" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/28502</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/28463</t>
         </is>
       </c>
       <c r="D125" s="2" t="inlineStr">
         <is>
-          <t>Template admin — location</t>
+          <t>Work Order — Statistics tab</t>
         </is>
       </c>
       <c r="E125" s="2" t="inlineStr">
         <is>
-          <t>Verify the fee/discount template library is at Administration → Service → Fees &amp; Discounts (below Canned Lines)</t>
+          <t>Verify the Stats 'Fees &amp; Discounts' section is hidden when the work order has no fees/discounts</t>
         </is>
       </c>
       <c r="F125" s="2" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="G125" s="2" t="inlineStr">
@@ -6528,34 +6528,34 @@
       </c>
       <c r="I125" s="2" t="inlineStr">
         <is>
-          <t>admin library lives under Administration -&gt; FINANCE (route /administration/adjustment-templates), not Service-below-Canned-Lines; page re-loaded today (case-update per S13-R8 target) | WORDING+VIU 2026-07-13: CORRECTED location: templates live under Administration → FINANCE → 'Fees &amp; Discounts' (below 'Payment Methods'), NOT 'Service, below Canned Lines' (Canned Lines is under SERVICE). Confirmed live (shot tmpl-02-create-dialog). | SV-8456 (2026-07-21 staging LIVE VIU): F&amp;D moved to SETTINGS→SERVICE (below Canned Lines); template/WO/Part-sale/customer dialogs now show Taxable as a Yes/No DROPDOWN (was toggle); Auto-apply is a CHECKBOX with a 'When on…' caption; settings &amp; customer tables are plain-text/left-aligned (no badges); WO sidebar card retitled 'Work Order Fees &amp; Discounts' and renders ABOVE Financial Info; Part-sale card 'Parts Sale Fees &amp; Discounts' above Financial Info. Permission gate pivoted Settings→Finance → Settings→Service (verified live: Service-user sees+manages F&amp;D &amp; convenience toggle; Finance-only user has no F&amp;D nav item and /administration/adjustment-templates bounces to /workorders). Frontend-only; functionality + calc INTACT. | RE-VIU 2026-07-22 LIVE (Batch 4, SV-8456 re-verify): access-check quick-login {admin} HTTP 200. Re-confirmed on current staging build — 8 UI corrections intact (Taxable Yes/No dropdown; Auto-apply checkbox+caption; modal field order Type/CalcType&gt;Name&gt;Amount&gt;Taxable+jur.note&gt;Auto-apply&gt;Description; Settings table plain-text left-aligned no badges; F&amp;D nav under SERVICE below Canned Lines; WO &amp; Part-Sale cards above Financial Info [Batch 2/3]; Customer 'Fees &amp; Discounts' tab mirrors Settings styling minus convenience toggle) AND Settings-&gt;Service permission pivot CONFIRMED live per role (seeded ServiceRole vs FinanceRole, assigned to Tech, Tech restored to Technician 50bf6a0d + verified, both ZZAUTOTEST roles deleted 204): Service-user sees+manages F&amp;D nav + convenience toggle, direct /administration/adjustment-templates loads; Finance-only user has NO F&amp;D nav, FINANCE=Payment Methods only, direct route bounces to /workorders. viu_status VIU-Verified re-confirmed. Ev build/fees-discounts/viu-sv8456-2026-07-22/ (01-settings-landing, 02-new-dialog, 03-customer-fd-tab, SVC-*, FIN-*).</t>
+          <t>no-adjustments WO -&gt; adjustments=[] + all-zero summary -&gt; section hidden | WORDING+VIU 2026-07-13: Section hidden with no adjustments; carry prior VIU.</t>
         </is>
       </c>
     </row>
     <row r="126">
       <c r="A126" s="2" t="inlineStr">
         <is>
-          <t>FD-TMPL-002</t>
+          <t>FD-TMPL-001</t>
         </is>
       </c>
       <c r="B126" s="2" t="inlineStr">
         <is>
-          <t>C28503</t>
+          <t>C28502</t>
         </is>
       </c>
       <c r="C126" s="6" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/28503</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/28502</t>
         </is>
       </c>
       <c r="D126" s="2" t="inlineStr">
         <is>
-          <t>Template admin — list</t>
+          <t>Template admin — location</t>
         </is>
       </c>
       <c r="E126" s="2" t="inlineStr">
         <is>
-          <t>Verify the template list columns and the edit/delete actions</t>
+          <t>Verify the fee/discount template library is at Administration → Service → Fees &amp; Discounts (below Canned Lines)</t>
         </is>
       </c>
       <c r="F126" s="2" t="inlineStr">
@@ -6575,34 +6575,34 @@
       </c>
       <c r="I126" s="2" t="inlineStr">
         <is>
-          <t>list + delete action per batch-1; page renders today; columns not re-verified individually | WORDING+VIU 2026-07-13: List columns confirmed live (shot tmpl-02). | SV-8456 (2026-07-21 staging LIVE VIU): F&amp;D moved to SETTINGS→SERVICE (below Canned Lines); template/WO/Part-sale/customer dialogs now show Taxable as a Yes/No DROPDOWN (was toggle); Auto-apply is a CHECKBOX with a 'When on…' caption; settings &amp; customer tables are plain-text/left-aligned (no badges); WO sidebar card retitled 'Work Order Fees &amp; Discounts' and renders ABOVE Financial Info; Part-sale card 'Parts Sale Fees &amp; Discounts' above Financial Info. Permission gate pivoted Settings→Finance → Settings→Service (verified live: Service-user sees+manages F&amp;D &amp; convenience toggle; Finance-only user has no F&amp;D nav item and /administration/adjustment-templates bounces to /workorders). Frontend-only; functionality + calc INTACT. | RE-VIU 2026-07-22 LIVE (Batch 4, SV-8456 re-verify): access-check quick-login {admin} HTTP 200. Re-confirmed on current staging build — 8 UI corrections intact (Taxable Yes/No dropdown; Auto-apply checkbox+caption; modal field order Type/CalcType&gt;Name&gt;Amount&gt;Taxable+jur.note&gt;Auto-apply&gt;Description; Settings table plain-text left-aligned no badges; F&amp;D nav under SERVICE below Canned Lines; WO &amp; Part-Sale cards above Financial Info [Batch 2/3]; Customer 'Fees &amp; Discounts' tab mirrors Settings styling minus convenience toggle) AND Settings-&gt;Service permission pivot CONFIRMED live per role (seeded ServiceRole vs FinanceRole, assigned to Tech, Tech restored to Technician 50bf6a0d + verified, both ZZAUTOTEST roles deleted 204): Service-user sees+manages F&amp;D nav + convenience toggle, direct /administration/adjustment-templates loads; Finance-only user has NO F&amp;D nav, FINANCE=Payment Methods only, direct route bounces to /workorders. viu_status VIU-Verified re-confirmed. Ev build/fees-discounts/viu-sv8456-2026-07-22/ (01-settings-landing, 02-new-dialog, 03-customer-fd-tab, SVC-*, FIN-*).</t>
+          <t>admin library lives under Administration -&gt; FINANCE (route /administration/adjustment-templates), not Service-below-Canned-Lines; page re-loaded today (case-update per S13-R8 target) | WORDING+VIU 2026-07-13: CORRECTED location: templates live under Administration → FINANCE → 'Fees &amp; Discounts' (below 'Payment Methods'), NOT 'Service, below Canned Lines' (Canned Lines is under SERVICE). Confirmed live (shot tmpl-02-create-dialog). | SV-8456 (2026-07-21 staging LIVE VIU): F&amp;D moved to SETTINGS→SERVICE (below Canned Lines); template/WO/Part-sale/customer dialogs now show Taxable as a Yes/No DROPDOWN (was toggle); Auto-apply is a CHECKBOX with a 'When on…' caption; settings &amp; customer tables are plain-text/left-aligned (no badges); WO sidebar card retitled 'Work Order Fees &amp; Discounts' and renders ABOVE Financial Info; Part-sale card 'Parts Sale Fees &amp; Discounts' above Financial Info. Permission gate pivoted Settings→Finance → Settings→Service (verified live: Service-user sees+manages F&amp;D &amp; convenience toggle; Finance-only user has no F&amp;D nav item and /administration/adjustment-templates bounces to /workorders). Frontend-only; functionality + calc INTACT. | RE-VIU 2026-07-22 LIVE (Batch 4, SV-8456 re-verify): access-check quick-login {admin} HTTP 200. Re-confirmed on current staging build — 8 UI corrections intact (Taxable Yes/No dropdown; Auto-apply checkbox+caption; modal field order Type/CalcType&gt;Name&gt;Amount&gt;Taxable+jur.note&gt;Auto-apply&gt;Description; Settings table plain-text left-aligned no badges; F&amp;D nav under SERVICE below Canned Lines; WO &amp; Part-Sale cards above Financial Info [Batch 2/3]; Customer 'Fees &amp; Discounts' tab mirrors Settings styling minus convenience toggle) AND Settings-&gt;Service permission pivot CONFIRMED live per role (seeded ServiceRole vs FinanceRole, assigned to Tech, Tech restored to Technician 50bf6a0d + verified, both ZZAUTOTEST roles deleted 204): Service-user sees+manages F&amp;D nav + convenience toggle, direct /administration/adjustment-templates loads; Finance-only user has NO F&amp;D nav, FINANCE=Payment Methods only, direct route bounces to /workorders. viu_status VIU-Verified re-confirmed. Ev build/fees-discounts/viu-sv8456-2026-07-22/ (01-settings-landing, 02-new-dialog, 03-customer-fd-tab, SVC-*, FIN-*).</t>
         </is>
       </c>
     </row>
     <row r="127">
       <c r="A127" s="2" t="inlineStr">
         <is>
-          <t>FD-TMPL-003</t>
+          <t>FD-TMPL-002</t>
         </is>
       </c>
       <c r="B127" s="2" t="inlineStr">
         <is>
-          <t>C28504</t>
+          <t>C28503</t>
         </is>
       </c>
       <c r="C127" s="6" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/28504</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/28503</t>
         </is>
       </c>
       <c r="D127" s="2" t="inlineStr">
         <is>
-          <t>Template admin — create</t>
+          <t>Template admin — list</t>
         </is>
       </c>
       <c r="E127" s="2" t="inlineStr">
         <is>
-          <t>Verify creating a Fee template (dialog fields and the Create button)</t>
+          <t>Verify the template list columns and the edit/delete actions</t>
         </is>
       </c>
       <c r="F127" s="2" t="inlineStr">
@@ -6622,24 +6622,24 @@
       </c>
       <c r="I127" s="2" t="inlineStr">
         <is>
-          <t>PARTIAL IMPROVEMENT: create-dialog title NOW 'New Fee / Discount' (matches spec; was 'Add new fee/discount'); confirm button still 'Create' (spec 'Add Fee / Discount') and toast 'Template created' per batch-1 — drift remains | WORDING+VIU 2026-07-13: Create dialog confirmed live: title 'New Fee / Discount', fields Name/Type/Calculation Type/'$ Default Amount'/Taxable toggle/'Auto-apply to new work orders' toggle/'Description (Optional)', 'Create' button. Type offers only Fee/Discount (Processing Fee is NOT in the builder — Story 8 not built). Create API 201 live. Toast text carried from prior VIU. | SV-8456 (2026-07-21 staging LIVE VIU): F&amp;D moved to SETTINGS→SERVICE (below Canned Lines); template/WO/Part-sale/customer dialogs now show Taxable as a Yes/No DROPDOWN (was toggle); Auto-apply is a CHECKBOX with a 'When on…' caption; settings &amp; customer tables are plain-text/left-aligned (no badges); WO sidebar card retitled 'Work Order Fees &amp; Discounts' and renders ABOVE Financial Info; Part-sale card 'Parts Sale Fees &amp; Discounts' above Financial Info. Permission gate pivoted Settings→Finance → Settings→Service (verified live: Service-user sees+manages F&amp;D &amp; convenience toggle; Finance-only user has no F&amp;D nav item and /administration/adjustment-templates bounces to /workorders). Frontend-only; functionality + calc INTACT. | RE-VIU 2026-07-22 LIVE (Batch 4, SV-8456 re-verify): access-check quick-login {admin} HTTP 200. Re-confirmed on current staging build — 8 UI corrections intact (Taxable Yes/No dropdown; Auto-apply checkbox+caption; modal field order Type/CalcType&gt;Name&gt;Amount&gt;Taxable+jur.note&gt;Auto-apply&gt;Description; Settings table plain-text left-aligned no badges; F&amp;D nav under SERVICE below Canned Lines; WO &amp; Part-Sale cards above Financial Info [Batch 2/3]; Customer 'Fees &amp; Discounts' tab mirrors Settings styling minus convenience toggle) AND Settings-&gt;Service permission pivot CONFIRMED live per role (seeded ServiceRole vs FinanceRole, assigned to Tech, Tech restored to Technician 50bf6a0d + verified, both ZZAUTOTEST roles deleted 204): Service-user sees+manages F&amp;D nav + convenience toggle, direct /administration/adjustment-templates loads; Finance-only user has NO F&amp;D nav, FINANCE=Payment Methods only, direct route bounces to /workorders. viu_status VIU-Verified re-confirmed. Ev build/fees-discounts/viu-sv8456-2026-07-22/ (01-settings-landing, 02-new-dialog, 03-customer-fd-tab, SVC-*, FIN-*).</t>
+          <t>list + delete action per batch-1; page renders today; columns not re-verified individually | WORDING+VIU 2026-07-13: List columns confirmed live (shot tmpl-02). | SV-8456 (2026-07-21 staging LIVE VIU): F&amp;D moved to SETTINGS→SERVICE (below Canned Lines); template/WO/Part-sale/customer dialogs now show Taxable as a Yes/No DROPDOWN (was toggle); Auto-apply is a CHECKBOX with a 'When on…' caption; settings &amp; customer tables are plain-text/left-aligned (no badges); WO sidebar card retitled 'Work Order Fees &amp; Discounts' and renders ABOVE Financial Info; Part-sale card 'Parts Sale Fees &amp; Discounts' above Financial Info. Permission gate pivoted Settings→Finance → Settings→Service (verified live: Service-user sees+manages F&amp;D &amp; convenience toggle; Finance-only user has no F&amp;D nav item and /administration/adjustment-templates bounces to /workorders). Frontend-only; functionality + calc INTACT. | RE-VIU 2026-07-22 LIVE (Batch 4, SV-8456 re-verify): access-check quick-login {admin} HTTP 200. Re-confirmed on current staging build — 8 UI corrections intact (Taxable Yes/No dropdown; Auto-apply checkbox+caption; modal field order Type/CalcType&gt;Name&gt;Amount&gt;Taxable+jur.note&gt;Auto-apply&gt;Description; Settings table plain-text left-aligned no badges; F&amp;D nav under SERVICE below Canned Lines; WO &amp; Part-Sale cards above Financial Info [Batch 2/3]; Customer 'Fees &amp; Discounts' tab mirrors Settings styling minus convenience toggle) AND Settings-&gt;Service permission pivot CONFIRMED live per role (seeded ServiceRole vs FinanceRole, assigned to Tech, Tech restored to Technician 50bf6a0d + verified, both ZZAUTOTEST roles deleted 204): Service-user sees+manages F&amp;D nav + convenience toggle, direct /administration/adjustment-templates loads; Finance-only user has NO F&amp;D nav, FINANCE=Payment Methods only, direct route bounces to /workorders. viu_status VIU-Verified re-confirmed. Ev build/fees-discounts/viu-sv8456-2026-07-22/ (01-settings-landing, 02-new-dialog, 03-customer-fd-tab, SVC-*, FIN-*).</t>
         </is>
       </c>
     </row>
     <row r="128">
       <c r="A128" s="2" t="inlineStr">
         <is>
-          <t>FD-TMPL-004</t>
+          <t>FD-TMPL-003</t>
         </is>
       </c>
       <c r="B128" s="2" t="inlineStr">
         <is>
-          <t>C28505</t>
+          <t>C28504</t>
         </is>
       </c>
       <c r="C128" s="6" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/28505</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/28504</t>
         </is>
       </c>
       <c r="D128" s="2" t="inlineStr">
@@ -6649,12 +6649,12 @@
       </c>
       <c r="E128" s="2" t="inlineStr">
         <is>
-          <t>Verify creating a Discount template</t>
+          <t>Verify creating a Fee template (dialog fields and the Create button)</t>
         </is>
       </c>
       <c r="F128" s="2" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>High</t>
         </is>
       </c>
       <c r="G128" s="2" t="inlineStr">
@@ -6669,39 +6669,39 @@
       </c>
       <c r="I128" s="2" t="inlineStr">
         <is>
-          <t>generic 'Template created' toast vs spec 'Discount added' per batch-1; not re-driven | WORDING+VIU 2026-07-13: CORRECTED title: the toast is generic (not a per-type 'Discount added'). Create dialog + list confirmed live. | SV-8456 (2026-07-21 staging LIVE VIU): F&amp;D moved to SETTINGS→SERVICE (below Canned Lines); template/WO/Part-sale/customer dialogs now show Taxable as a Yes/No DROPDOWN (was toggle); Auto-apply is a CHECKBOX with a 'When on…' caption; settings &amp; customer tables are plain-text/left-aligned (no badges); WO sidebar card retitled 'Work Order Fees &amp; Discounts' and renders ABOVE Financial Info; Part-sale card 'Parts Sale Fees &amp; Discounts' above Financial Info. Permission gate pivoted Settings→Finance → Settings→Service (verified live: Service-user sees+manages F&amp;D &amp; convenience toggle; Finance-only user has no F&amp;D nav item and /administration/adjustment-templates bounces to /workorders). Frontend-only; functionality + calc INTACT. | RE-VIU 2026-07-22 LIVE (Batch 4, SV-8456 re-verify): access-check quick-login {admin} HTTP 200. Re-confirmed on current staging build — 8 UI corrections intact (Taxable Yes/No dropdown; Auto-apply checkbox+caption; modal field order Type/CalcType&gt;Name&gt;Amount&gt;Taxable+jur.note&gt;Auto-apply&gt;Description; Settings table plain-text left-aligned no badges; F&amp;D nav under SERVICE below Canned Lines; WO &amp; Part-Sale cards above Financial Info [Batch 2/3]; Customer 'Fees &amp; Discounts' tab mirrors Settings styling minus convenience toggle) AND Settings-&gt;Service permission pivot CONFIRMED live per role (seeded ServiceRole vs FinanceRole, assigned to Tech, Tech restored to Technician 50bf6a0d + verified, both ZZAUTOTEST roles deleted 204): Service-user sees+manages F&amp;D nav + convenience toggle, direct /administration/adjustment-templates loads; Finance-only user has NO F&amp;D nav, FINANCE=Payment Methods only, direct route bounces to /workorders. viu_status VIU-Verified re-confirmed. Ev build/fees-discounts/viu-sv8456-2026-07-22/ (01-settings-landing, 02-new-dialog, 03-customer-fd-tab, SVC-*, FIN-*).</t>
+          <t>PARTIAL IMPROVEMENT: create-dialog title NOW 'New Fee / Discount' (matches spec; was 'Add new fee/discount'); confirm button still 'Create' (spec 'Add Fee / Discount') and toast 'Template created' per batch-1 — drift remains | WORDING+VIU 2026-07-13: Create dialog confirmed live: title 'New Fee / Discount', fields Name/Type/Calculation Type/'$ Default Amount'/Taxable toggle/'Auto-apply to new work orders' toggle/'Description (Optional)', 'Create' button. Type offers only Fee/Discount (Processing Fee is NOT in the builder — Story 8 not built). Create API 201 live. Toast text carried from prior VIU. | SV-8456 (2026-07-21 staging LIVE VIU): F&amp;D moved to SETTINGS→SERVICE (below Canned Lines); template/WO/Part-sale/customer dialogs now show Taxable as a Yes/No DROPDOWN (was toggle); Auto-apply is a CHECKBOX with a 'When on…' caption; settings &amp; customer tables are plain-text/left-aligned (no badges); WO sidebar card retitled 'Work Order Fees &amp; Discounts' and renders ABOVE Financial Info; Part-sale card 'Parts Sale Fees &amp; Discounts' above Financial Info. Permission gate pivoted Settings→Finance → Settings→Service (verified live: Service-user sees+manages F&amp;D &amp; convenience toggle; Finance-only user has no F&amp;D nav item and /administration/adjustment-templates bounces to /workorders). Frontend-only; functionality + calc INTACT. | RE-VIU 2026-07-22 LIVE (Batch 4, SV-8456 re-verify): access-check quick-login {admin} HTTP 200. Re-confirmed on current staging build — 8 UI corrections intact (Taxable Yes/No dropdown; Auto-apply checkbox+caption; modal field order Type/CalcType&gt;Name&gt;Amount&gt;Taxable+jur.note&gt;Auto-apply&gt;Description; Settings table plain-text left-aligned no badges; F&amp;D nav under SERVICE below Canned Lines; WO &amp; Part-Sale cards above Financial Info [Batch 2/3]; Customer 'Fees &amp; Discounts' tab mirrors Settings styling minus convenience toggle) AND Settings-&gt;Service permission pivot CONFIRMED live per role (seeded ServiceRole vs FinanceRole, assigned to Tech, Tech restored to Technician 50bf6a0d + verified, both ZZAUTOTEST roles deleted 204): Service-user sees+manages F&amp;D nav + convenience toggle, direct /administration/adjustment-templates loads; Finance-only user has NO F&amp;D nav, FINANCE=Payment Methods only, direct route bounces to /workorders. viu_status VIU-Verified re-confirmed. Ev build/fees-discounts/viu-sv8456-2026-07-22/ (01-settings-landing, 02-new-dialog, 03-customer-fd-tab, SVC-*, FIN-*).</t>
         </is>
       </c>
     </row>
     <row r="129">
       <c r="A129" s="2" t="inlineStr">
         <is>
-          <t>FD-TMPL-005</t>
+          <t>FD-TMPL-004</t>
         </is>
       </c>
       <c r="B129" s="2" t="inlineStr">
         <is>
-          <t>C28506</t>
+          <t>C28505</t>
         </is>
       </c>
       <c r="C129" s="6" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/28506</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/28505</t>
         </is>
       </c>
       <c r="D129" s="2" t="inlineStr">
         <is>
-          <t>Template admin — auto-apply</t>
+          <t>Template admin — create</t>
         </is>
       </c>
       <c r="E129" s="2" t="inlineStr">
         <is>
-          <t>Verify the 'Auto-apply to all new work orders at this location' checkbox adds the template to every new work order at that location</t>
+          <t>Verify creating a Discount template</t>
         </is>
       </c>
       <c r="F129" s="2" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="G129" s="2" t="inlineStr">
@@ -6716,39 +6716,39 @@
       </c>
       <c r="I129" s="2" t="inlineStr">
         <is>
-          <t>auto-apply template ('Capped discount' + test pfees) landed on every fresh WO as appliedBy=auto | WORDING+VIU 2026-07-13: CORRECTED auto-apply label: dialog toggle is 'Auto-apply to new work orders'; list column 'Auto-Apply To Work Orders'. Confirmed live (shot tmpl-02). | SV-8456 (2026-07-21 staging LIVE VIU): F&amp;D moved to SETTINGS→SERVICE (below Canned Lines); template/WO/Part-sale/customer dialogs now show Taxable as a Yes/No DROPDOWN (was toggle); Auto-apply is a CHECKBOX with a 'When on…' caption; settings &amp; customer tables are plain-text/left-aligned (no badges); WO sidebar card retitled 'Work Order Fees &amp; Discounts' and renders ABOVE Financial Info; Part-sale card 'Parts Sale Fees &amp; Discounts' above Financial Info. Permission gate pivoted Settings→Finance → Settings→Service (verified live: Service-user sees+manages F&amp;D &amp; convenience toggle; Finance-only user has no F&amp;D nav item and /administration/adjustment-templates bounces to /workorders). Frontend-only; functionality + calc INTACT. | RE-VIU 2026-07-22 LIVE (Batch 4, SV-8456 re-verify): access-check quick-login {admin} HTTP 200. Re-confirmed on current staging build — 8 UI corrections intact (Taxable Yes/No dropdown; Auto-apply checkbox+caption; modal field order Type/CalcType&gt;Name&gt;Amount&gt;Taxable+jur.note&gt;Auto-apply&gt;Description; Settings table plain-text left-aligned no badges; F&amp;D nav under SERVICE below Canned Lines; WO &amp; Part-Sale cards above Financial Info [Batch 2/3]; Customer 'Fees &amp; Discounts' tab mirrors Settings styling minus convenience toggle) AND Settings-&gt;Service permission pivot CONFIRMED live per role (seeded ServiceRole vs FinanceRole, assigned to Tech, Tech restored to Technician 50bf6a0d + verified, both ZZAUTOTEST roles deleted 204): Service-user sees+manages F&amp;D nav + convenience toggle, direct /administration/adjustment-templates loads; Finance-only user has NO F&amp;D nav, FINANCE=Payment Methods only, direct route bounces to /workorders. viu_status VIU-Verified re-confirmed. Ev build/fees-discounts/viu-sv8456-2026-07-22/ (01-settings-landing, 02-new-dialog, 03-customer-fd-tab, SVC-*, FIN-*).</t>
+          <t>generic 'Template created' toast vs spec 'Discount added' per batch-1; not re-driven | WORDING+VIU 2026-07-13: CORRECTED title: the toast is generic (not a per-type 'Discount added'). Create dialog + list confirmed live. | SV-8456 (2026-07-21 staging LIVE VIU): F&amp;D moved to SETTINGS→SERVICE (below Canned Lines); template/WO/Part-sale/customer dialogs now show Taxable as a Yes/No DROPDOWN (was toggle); Auto-apply is a CHECKBOX with a 'When on…' caption; settings &amp; customer tables are plain-text/left-aligned (no badges); WO sidebar card retitled 'Work Order Fees &amp; Discounts' and renders ABOVE Financial Info; Part-sale card 'Parts Sale Fees &amp; Discounts' above Financial Info. Permission gate pivoted Settings→Finance → Settings→Service (verified live: Service-user sees+manages F&amp;D &amp; convenience toggle; Finance-only user has no F&amp;D nav item and /administration/adjustment-templates bounces to /workorders). Frontend-only; functionality + calc INTACT. | RE-VIU 2026-07-22 LIVE (Batch 4, SV-8456 re-verify): access-check quick-login {admin} HTTP 200. Re-confirmed on current staging build — 8 UI corrections intact (Taxable Yes/No dropdown; Auto-apply checkbox+caption; modal field order Type/CalcType&gt;Name&gt;Amount&gt;Taxable+jur.note&gt;Auto-apply&gt;Description; Settings table plain-text left-aligned no badges; F&amp;D nav under SERVICE below Canned Lines; WO &amp; Part-Sale cards above Financial Info [Batch 2/3]; Customer 'Fees &amp; Discounts' tab mirrors Settings styling minus convenience toggle) AND Settings-&gt;Service permission pivot CONFIRMED live per role (seeded ServiceRole vs FinanceRole, assigned to Tech, Tech restored to Technician 50bf6a0d + verified, both ZZAUTOTEST roles deleted 204): Service-user sees+manages F&amp;D nav + convenience toggle, direct /administration/adjustment-templates loads; Finance-only user has NO F&amp;D nav, FINANCE=Payment Methods only, direct route bounces to /workorders. viu_status VIU-Verified re-confirmed. Ev build/fees-discounts/viu-sv8456-2026-07-22/ (01-settings-landing, 02-new-dialog, 03-customer-fd-tab, SVC-*, FIN-*).</t>
         </is>
       </c>
     </row>
     <row r="130">
       <c r="A130" s="2" t="inlineStr">
         <is>
-          <t>FD-TMPL-006</t>
+          <t>FD-TMPL-005</t>
         </is>
       </c>
       <c r="B130" s="2" t="inlineStr">
         <is>
-          <t>C28507</t>
+          <t>C28506</t>
         </is>
       </c>
       <c r="C130" s="6" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/28507</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/28506</t>
         </is>
       </c>
       <c r="D130" s="2" t="inlineStr">
         <is>
-          <t>Template admin — edit</t>
+          <t>Template admin — auto-apply</t>
         </is>
       </c>
       <c r="E130" s="2" t="inlineStr">
         <is>
-          <t>Verify editing a template (Edit Fee / Discount dialog, 'Save' button)</t>
+          <t>Verify the 'Auto-apply to all new work orders at this location' checkbox adds the template to every new work order at that location</t>
         </is>
       </c>
       <c r="F130" s="2" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>High</t>
         </is>
       </c>
       <c r="G130" s="2" t="inlineStr">
@@ -6763,39 +6763,39 @@
       </c>
       <c r="I130" s="2" t="inlineStr">
         <is>
-          <t>edit locks Type+Calc on template edit (spec locks only in WO dialog) per batch-1; not re-driven | WORDING+VIU 2026-07-13: Edit dialog title 'Edit Fee / Discount' + 'Save' button confirmed on the fee/discount Edit dialog (shot edit-01). Edit opens from the row's pencil button. Toast text carried.</t>
+          <t>auto-apply template ('Capped discount' + test pfees) landed on every fresh WO as appliedBy=auto | WORDING+VIU 2026-07-13: CORRECTED auto-apply label: dialog toggle is 'Auto-apply to new work orders'; list column 'Auto-Apply To Work Orders'. Confirmed live (shot tmpl-02). | SV-8456 (2026-07-21 staging LIVE VIU): F&amp;D moved to SETTINGS→SERVICE (below Canned Lines); template/WO/Part-sale/customer dialogs now show Taxable as a Yes/No DROPDOWN (was toggle); Auto-apply is a CHECKBOX with a 'When on…' caption; settings &amp; customer tables are plain-text/left-aligned (no badges); WO sidebar card retitled 'Work Order Fees &amp; Discounts' and renders ABOVE Financial Info; Part-sale card 'Parts Sale Fees &amp; Discounts' above Financial Info. Permission gate pivoted Settings→Finance → Settings→Service (verified live: Service-user sees+manages F&amp;D &amp; convenience toggle; Finance-only user has no F&amp;D nav item and /administration/adjustment-templates bounces to /workorders). Frontend-only; functionality + calc INTACT. | RE-VIU 2026-07-22 LIVE (Batch 4, SV-8456 re-verify): access-check quick-login {admin} HTTP 200. Re-confirmed on current staging build — 8 UI corrections intact (Taxable Yes/No dropdown; Auto-apply checkbox+caption; modal field order Type/CalcType&gt;Name&gt;Amount&gt;Taxable+jur.note&gt;Auto-apply&gt;Description; Settings table plain-text left-aligned no badges; F&amp;D nav under SERVICE below Canned Lines; WO &amp; Part-Sale cards above Financial Info [Batch 2/3]; Customer 'Fees &amp; Discounts' tab mirrors Settings styling minus convenience toggle) AND Settings-&gt;Service permission pivot CONFIRMED live per role (seeded ServiceRole vs FinanceRole, assigned to Tech, Tech restored to Technician 50bf6a0d + verified, both ZZAUTOTEST roles deleted 204): Service-user sees+manages F&amp;D nav + convenience toggle, direct /administration/adjustment-templates loads; Finance-only user has NO F&amp;D nav, FINANCE=Payment Methods only, direct route bounces to /workorders. viu_status VIU-Verified re-confirmed. Ev build/fees-discounts/viu-sv8456-2026-07-22/ (01-settings-landing, 02-new-dialog, 03-customer-fd-tab, SVC-*, FIN-*).</t>
         </is>
       </c>
     </row>
     <row r="131">
       <c r="A131" s="2" t="inlineStr">
         <is>
-          <t>FD-TMPL-007</t>
+          <t>FD-TMPL-006</t>
         </is>
       </c>
       <c r="B131" s="2" t="inlineStr">
         <is>
-          <t>C28508</t>
+          <t>C28507</t>
         </is>
       </c>
       <c r="C131" s="6" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/28508</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/28507</t>
         </is>
       </c>
       <c r="D131" s="2" t="inlineStr">
         <is>
-          <t>Template admin — delete</t>
+          <t>Template admin — edit</t>
         </is>
       </c>
       <c r="E131" s="2" t="inlineStr">
         <is>
-          <t>Verify the template delete confirm dialog and buttons</t>
+          <t>Verify editing a template (Edit Fee / Discount dialog, 'Save' button)</t>
         </is>
       </c>
       <c r="F131" s="2" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="G131" s="2" t="inlineStr">
@@ -6810,24 +6810,24 @@
       </c>
       <c r="I131" s="2" t="inlineStr">
         <is>
-          <t>delete-confirm dialog + affectedCustomerCount warning per batch-1; delete-precondition endpoint intact | WORDING+VIU 2026-07-13: Delete confirm confirmed live: standardized 'Delete Template' dialog with 'Cancel' + red 'Delete' (shot tmpl-03). The plain (no-customer) body wording was not captured this run — the sample template had a customer default (see FD-TMPL-008).</t>
+          <t>edit locks Type+Calc on template edit (spec locks only in WO dialog) per batch-1; not re-driven | WORDING+VIU 2026-07-13: Edit dialog title 'Edit Fee / Discount' + 'Save' button confirmed on the fee/discount Edit dialog (shot edit-01). Edit opens from the row's pencil button. Toast text carried.</t>
         </is>
       </c>
     </row>
     <row r="132">
       <c r="A132" s="2" t="inlineStr">
         <is>
-          <t>FD-TMPL-008</t>
+          <t>FD-TMPL-007</t>
         </is>
       </c>
       <c r="B132" s="2" t="inlineStr">
         <is>
-          <t>C28509</t>
+          <t>C28508</t>
         </is>
       </c>
       <c r="C132" s="6" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/28509</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/28508</t>
         </is>
       </c>
       <c r="D132" s="2" t="inlineStr">
@@ -6837,12 +6837,12 @@
       </c>
       <c r="E132" s="2" t="inlineStr">
         <is>
-          <t>Verify the delete confirm adds a warning when the template is a customer default</t>
+          <t>Verify the template delete confirm dialog and buttons</t>
         </is>
       </c>
       <c r="F132" s="2" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>High</t>
         </is>
       </c>
       <c r="G132" s="2" t="inlineStr">
@@ -6857,24 +6857,24 @@
       </c>
       <c r="I132" s="2" t="inlineStr">
         <is>
-          <t>standardized 'Delete Template' dialog wording = intended per epic; case-update to adopt live wording still pending | WORDING+VIU 2026-07-13: Customer-default warning confirmed live EXACTLY: 'This template is set as a default for N customer(s). Deleting it will remove it from them.' (saw '1 customer', shot tmpl-03).</t>
+          <t>delete-confirm dialog + affectedCustomerCount warning per batch-1; delete-precondition endpoint intact | WORDING+VIU 2026-07-13: Delete confirm confirmed live: standardized 'Delete Template' dialog with 'Cancel' + red 'Delete' (shot tmpl-03). The plain (no-customer) body wording was not captured this run — the sample template had a customer default (see FD-TMPL-008).</t>
         </is>
       </c>
     </row>
     <row r="133">
       <c r="A133" s="2" t="inlineStr">
         <is>
-          <t>FD-TMPL-009</t>
+          <t>FD-TMPL-008</t>
         </is>
       </c>
       <c r="B133" s="2" t="inlineStr">
         <is>
-          <t>C28510</t>
+          <t>C28509</t>
         </is>
       </c>
       <c r="C133" s="6" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/28510</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/28509</t>
         </is>
       </c>
       <c r="D133" s="2" t="inlineStr">
@@ -6884,12 +6884,12 @@
       </c>
       <c r="E133" s="2" t="inlineStr">
         <is>
-          <t>Verify deleting a template leaves work-order fees/discounts made from it unchanged</t>
+          <t>Verify the delete confirm adds a warning when the template is a customer default</t>
         </is>
       </c>
       <c r="F133" s="2" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="G133" s="2" t="inlineStr">
@@ -6904,39 +6904,39 @@
       </c>
       <c r="I133" s="2" t="inlineStr">
         <is>
-          <t>template deleted (204) -&gt; WO adjustment made from it survives unchanged (resolved 6 intact) | WORDING+VIU 2026-07-13: Delete leaves WO adjustments unchanged; carried. Nav corrected to Finance. | SV-8456 (2026-07-21 staging LIVE VIU): F&amp;D moved to SETTINGS→SERVICE (below Canned Lines); template/WO/Part-sale/customer dialogs now show Taxable as a Yes/No DROPDOWN (was toggle); Auto-apply is a CHECKBOX with a 'When on…' caption; settings &amp; customer tables are plain-text/left-aligned (no badges); WO sidebar card retitled 'Work Order Fees &amp; Discounts' and renders ABOVE Financial Info; Part-sale card 'Parts Sale Fees &amp; Discounts' above Financial Info. Permission gate pivoted Settings→Finance → Settings→Service (verified live: Service-user sees+manages F&amp;D &amp; convenience toggle; Finance-only user has no F&amp;D nav item and /administration/adjustment-templates bounces to /workorders). Frontend-only; functionality + calc INTACT. | RE-VIU 2026-07-22 LIVE (Batch 4, SV-8456 re-verify): access-check quick-login {admin} HTTP 200. Re-confirmed on current staging build — 8 UI corrections intact (Taxable Yes/No dropdown; Auto-apply checkbox+caption; modal field order Type/CalcType&gt;Name&gt;Amount&gt;Taxable+jur.note&gt;Auto-apply&gt;Description; Settings table plain-text left-aligned no badges; F&amp;D nav under SERVICE below Canned Lines; WO &amp; Part-Sale cards above Financial Info [Batch 2/3]; Customer 'Fees &amp; Discounts' tab mirrors Settings styling minus convenience toggle) AND Settings-&gt;Service permission pivot CONFIRMED live per role (seeded ServiceRole vs FinanceRole, assigned to Tech, Tech restored to Technician 50bf6a0d + verified, both ZZAUTOTEST roles deleted 204): Service-user sees+manages F&amp;D nav + convenience toggle, direct /administration/adjustment-templates loads; Finance-only user has NO F&amp;D nav, FINANCE=Payment Methods only, direct route bounces to /workorders. viu_status VIU-Verified re-confirmed. Ev build/fees-discounts/viu-sv8456-2026-07-22/ (01-settings-landing, 02-new-dialog, 03-customer-fd-tab, SVC-*, FIN-*).</t>
+          <t>standardized 'Delete Template' dialog wording = intended per epic; case-update to adopt live wording still pending | WORDING+VIU 2026-07-13: Customer-default warning confirmed live EXACTLY: 'This template is set as a default for N customer(s). Deleting it will remove it from them.' (saw '1 customer', shot tmpl-03).</t>
         </is>
       </c>
     </row>
     <row r="134">
       <c r="A134" s="2" t="inlineStr">
         <is>
-          <t>FD-TMPL-011</t>
+          <t>FD-TMPL-009</t>
         </is>
       </c>
       <c r="B134" s="2" t="inlineStr">
         <is>
-          <t>C28512</t>
+          <t>C28510</t>
         </is>
       </c>
       <c r="C134" s="6" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/28512</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/28510</t>
         </is>
       </c>
       <c r="D134" s="2" t="inlineStr">
         <is>
-          <t>Template admin — dialog fields</t>
+          <t>Template admin — delete</t>
         </is>
       </c>
       <c r="E134" s="2" t="inlineStr">
         <is>
-          <t>Verify Max Amount shows only for percentage methods and how 0 behaves</t>
+          <t>Verify deleting a template leaves work-order fees/discounts made from it unchanged</t>
         </is>
       </c>
       <c r="F134" s="2" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>High</t>
         </is>
       </c>
       <c r="G134" s="2" t="inlineStr">
@@ -6951,34 +6951,34 @@
       </c>
       <c r="I134" s="2" t="inlineStr">
         <is>
-          <t>maxCap 0 accepted and STORED as 0 on the template (201) and WO resolve treats 0 as NO cap (34.15) — FDBUG-9 persists | WORDING+VIU 2026-07-13: Max Amount only for % confirmed (WO+template dialogs). DEVIATION (PO Q2): a Max Amount of 0 is treated as 'no cap'. Labels cleaned. | CHRIS WARD ROUND-2 ANSWER APPLIED 2026-07-14(Q2=A): PO ruled a typed 0 in Max Amount = 'no limit' (WAD, S2-R25). 0-handling no longer a deviation; FDBUG-9 closed as accepted; jira draft TICKET 4 DROPPED. Expected reworded to affirm 0=no-cap. PUSHED TO TESTRAIL 2026-07-14 via update_case (QA-lead one-day authorization; update 200 / re-verify 200 MATCH; audit: testrail-round2-push-log.md).</t>
+          <t>template deleted (204) -&gt; WO adjustment made from it survives unchanged (resolved 6 intact) | WORDING+VIU 2026-07-13: Delete leaves WO adjustments unchanged; carried. Nav corrected to Finance. | SV-8456 (2026-07-21 staging LIVE VIU): F&amp;D moved to SETTINGS→SERVICE (below Canned Lines); template/WO/Part-sale/customer dialogs now show Taxable as a Yes/No DROPDOWN (was toggle); Auto-apply is a CHECKBOX with a 'When on…' caption; settings &amp; customer tables are plain-text/left-aligned (no badges); WO sidebar card retitled 'Work Order Fees &amp; Discounts' and renders ABOVE Financial Info; Part-sale card 'Parts Sale Fees &amp; Discounts' above Financial Info. Permission gate pivoted Settings→Finance → Settings→Service (verified live: Service-user sees+manages F&amp;D &amp; convenience toggle; Finance-only user has no F&amp;D nav item and /administration/adjustment-templates bounces to /workorders). Frontend-only; functionality + calc INTACT. | RE-VIU 2026-07-22 LIVE (Batch 4, SV-8456 re-verify): access-check quick-login {admin} HTTP 200. Re-confirmed on current staging build — 8 UI corrections intact (Taxable Yes/No dropdown; Auto-apply checkbox+caption; modal field order Type/CalcType&gt;Name&gt;Amount&gt;Taxable+jur.note&gt;Auto-apply&gt;Description; Settings table plain-text left-aligned no badges; F&amp;D nav under SERVICE below Canned Lines; WO &amp; Part-Sale cards above Financial Info [Batch 2/3]; Customer 'Fees &amp; Discounts' tab mirrors Settings styling minus convenience toggle) AND Settings-&gt;Service permission pivot CONFIRMED live per role (seeded ServiceRole vs FinanceRole, assigned to Tech, Tech restored to Technician 50bf6a0d + verified, both ZZAUTOTEST roles deleted 204): Service-user sees+manages F&amp;D nav + convenience toggle, direct /administration/adjustment-templates loads; Finance-only user has NO F&amp;D nav, FINANCE=Payment Methods only, direct route bounces to /workorders. viu_status VIU-Verified re-confirmed. Ev build/fees-discounts/viu-sv8456-2026-07-22/ (01-settings-landing, 02-new-dialog, 03-customer-fd-tab, SVC-*, FIN-*).</t>
         </is>
       </c>
     </row>
     <row r="135">
       <c r="A135" s="2" t="inlineStr">
         <is>
-          <t>FD-TMPL-013</t>
+          <t>FD-TMPL-011</t>
         </is>
       </c>
       <c r="B135" s="2" t="inlineStr">
         <is>
-          <t>C28514</t>
+          <t>C28512</t>
         </is>
       </c>
       <c r="C135" s="6" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/28514</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/28512</t>
         </is>
       </c>
       <c r="D135" s="2" t="inlineStr">
         <is>
-          <t>Template admin — validation</t>
+          <t>Template admin — dialog fields</t>
         </is>
       </c>
       <c r="E135" s="2" t="inlineStr">
         <is>
-          <t>Verify a percentage-discount template cannot go over 100% while a percentage-fee template has no cap</t>
+          <t>Verify Max Amount shows only for percentage methods and how 0 behaves</t>
         </is>
       </c>
       <c r="F135" s="2" t="inlineStr">
@@ -6998,34 +6998,34 @@
       </c>
       <c r="I135" s="2" t="inlineStr">
         <is>
-          <t>discount template 150% -&gt; 400; fee template 150% -&gt; 201 | WORDING+VIU 2026-07-13: %&gt;100 discount rejected (confirmed via API 2026-07-13: 'A percentage discount cannot exceed 100%').</t>
+          <t>maxCap 0 accepted and STORED as 0 on the template (201) and WO resolve treats 0 as NO cap (34.15) — FDBUG-9 persists | WORDING+VIU 2026-07-13: Max Amount only for % confirmed (WO+template dialogs). DEVIATION (PO Q2): a Max Amount of 0 is treated as 'no cap'. Labels cleaned. | CHRIS WARD ROUND-2 ANSWER APPLIED 2026-07-14(Q2=A): PO ruled a typed 0 in Max Amount = 'no limit' (WAD, S2-R25). 0-handling no longer a deviation; FDBUG-9 closed as accepted; jira draft TICKET 4 DROPPED. Expected reworded to affirm 0=no-cap. PUSHED TO TESTRAIL 2026-07-14 via update_case (QA-lead one-day authorization; update 200 / re-verify 200 MATCH; audit: testrail-round2-push-log.md).</t>
         </is>
       </c>
     </row>
     <row r="136">
       <c r="A136" s="2" t="inlineStr">
         <is>
-          <t>FD-TMPL-014</t>
+          <t>FD-TMPL-013</t>
         </is>
       </c>
       <c r="B136" s="2" t="inlineStr">
         <is>
-          <t>C28515</t>
+          <t>C28514</t>
         </is>
       </c>
       <c r="C136" s="6" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/28515</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/28514</t>
         </is>
       </c>
       <c r="D136" s="2" t="inlineStr">
         <is>
-          <t>Template admin — dialog fields</t>
+          <t>Template admin — validation</t>
         </is>
       </c>
       <c r="E136" s="2" t="inlineStr">
         <is>
-          <t>Verify a Fee/Discount template offers the four whole-work-order methods and no scope field</t>
+          <t>Verify a percentage-discount template cannot go over 100% while a percentage-fee template has no cap</t>
         </is>
       </c>
       <c r="F136" s="2" t="inlineStr">
@@ -7045,39 +7045,39 @@
       </c>
       <c r="I136" s="2" t="inlineStr">
         <is>
-          <t>builder offers exactly 4 whole-WO methods (Flat, % Labor, % Parts, % Subtotal), no scope field, no legacy '% Labor+Parts' | WORDING+VIU 2026-07-13: Calc Type options confirmed (same 4 whole-WO methods as the WO dialog); no scope field.</t>
+          <t>discount template 150% -&gt; 400; fee template 150% -&gt; 201 | WORDING+VIU 2026-07-13: %&gt;100 discount rejected (confirmed via API 2026-07-13: 'A percentage discount cannot exceed 100%').</t>
         </is>
       </c>
     </row>
     <row r="137">
       <c r="A137" s="2" t="inlineStr">
         <is>
-          <t>FD-TMPL-015</t>
+          <t>FD-TMPL-014</t>
         </is>
       </c>
       <c r="B137" s="2" t="inlineStr">
         <is>
-          <t>C28516</t>
+          <t>C28515</t>
         </is>
       </c>
       <c r="C137" s="6" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/28516</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/28515</t>
         </is>
       </c>
       <c r="D137" s="2" t="inlineStr">
         <is>
-          <t>Template admin — negative</t>
+          <t>Template admin — dialog fields</t>
         </is>
       </c>
       <c r="E137" s="2" t="inlineStr">
         <is>
-          <t>Verify the template save-failure message</t>
+          <t>Verify a Fee/Discount template offers the four whole-work-order methods and no scope field</t>
         </is>
       </c>
       <c r="F137" s="2" t="inlineStr">
         <is>
-          <t>Low</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="G137" s="2" t="inlineStr">
@@ -7092,39 +7092,39 @@
       </c>
       <c r="I137" s="2" t="inlineStr">
         <is>
-          <t>template empty name -&gt; 400; amount 0 -&gt; 400 (save-failure surfaced) | WORDING+VIU 2026-07-13: Save-failure toast text carried from prior VIU (not force-failed this run).</t>
+          <t>builder offers exactly 4 whole-WO methods (Flat, % Labor, % Parts, % Subtotal), no scope field, no legacy '% Labor+Parts' | WORDING+VIU 2026-07-13: Calc Type options confirmed (same 4 whole-WO methods as the WO dialog); no scope field.</t>
         </is>
       </c>
     </row>
     <row r="138">
       <c r="A138" s="2" t="inlineStr">
         <is>
-          <t>FD-TMPL-016</t>
+          <t>FD-TMPL-015</t>
         </is>
       </c>
       <c r="B138" s="2" t="inlineStr">
         <is>
-          <t>C28517</t>
+          <t>C28516</t>
         </is>
       </c>
       <c r="C138" s="6" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/28517</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/28516</t>
         </is>
       </c>
       <c r="D138" s="2" t="inlineStr">
         <is>
-          <t>Template admin — permissions</t>
+          <t>Template admin — negative</t>
         </is>
       </c>
       <c r="E138" s="2" t="inlineStr">
         <is>
-          <t>Verify the admin Fees &amp; Discounts page needs the Settings → Service permission</t>
+          <t>Verify the template save-failure message</t>
         </is>
       </c>
       <c r="F138" s="2" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Low</t>
         </is>
       </c>
       <c r="G138" s="2" t="inlineStr">
@@ -7139,39 +7139,39 @@
       </c>
       <c r="I138" s="2" t="inlineStr">
         <is>
-          <t>BE-enforced: tech templates GET/POST -&gt; 403; page FE-gated settingsFinance | WORDING+VIU 2026-07-13: Templates admin is back-end gated by Settings → Finance (Tech → 403), established batch-2. Nav corrected to Finance. NOTE: re-check the Tech negative after the roles matrix is re-derived (Technician drifted on shared qb). | SV-8456 (2026-07-21 staging LIVE VIU): F&amp;D moved to SETTINGS→SERVICE (below Canned Lines); template/WO/Part-sale/customer dialogs now show Taxable as a Yes/No DROPDOWN (was toggle); Auto-apply is a CHECKBOX with a 'When on…' caption; settings &amp; customer tables are plain-text/left-aligned (no badges); WO sidebar card retitled 'Work Order Fees &amp; Discounts' and renders ABOVE Financial Info; Part-sale card 'Parts Sale Fees &amp; Discounts' above Financial Info. Permission gate pivoted Settings→Finance → Settings→Service (verified live: Service-user sees+manages F&amp;D &amp; convenience toggle; Finance-only user has no F&amp;D nav item and /administration/adjustment-templates bounces to /workorders). Frontend-only; functionality + calc INTACT. | RE-VIU 2026-07-22 LIVE (Batch 4, SV-8456 re-verify): access-check quick-login {admin} HTTP 200. Re-confirmed on current staging build — 8 UI corrections intact (Taxable Yes/No dropdown; Auto-apply checkbox+caption; modal field order Type/CalcType&gt;Name&gt;Amount&gt;Taxable+jur.note&gt;Auto-apply&gt;Description; Settings table plain-text left-aligned no badges; F&amp;D nav under SERVICE below Canned Lines; WO &amp; Part-Sale cards above Financial Info [Batch 2/3]; Customer 'Fees &amp; Discounts' tab mirrors Settings styling minus convenience toggle) AND Settings-&gt;Service permission pivot CONFIRMED live per role (seeded ServiceRole vs FinanceRole, assigned to Tech, Tech restored to Technician 50bf6a0d + verified, both ZZAUTOTEST roles deleted 204): Service-user sees+manages F&amp;D nav + convenience toggle, direct /administration/adjustment-templates loads; Finance-only user has NO F&amp;D nav, FINANCE=Payment Methods only, direct route bounces to /workorders. viu_status VIU-Verified re-confirmed. Ev build/fees-discounts/viu-sv8456-2026-07-22/ (01-settings-landing, 02-new-dialog, 03-customer-fd-tab, SVC-*, FIN-*).</t>
+          <t>template empty name -&gt; 400; amount 0 -&gt; 400 (save-failure surfaced) | WORDING+VIU 2026-07-13: Save-failure toast text carried from prior VIU (not force-failed this run).</t>
         </is>
       </c>
     </row>
     <row r="139">
       <c r="A139" s="2" t="inlineStr">
         <is>
-          <t>FD-TMPL-017</t>
+          <t>FD-TMPL-016</t>
         </is>
       </c>
       <c r="B139" s="2" t="inlineStr">
         <is>
-          <t>C28518</t>
+          <t>C28517</t>
         </is>
       </c>
       <c r="C139" s="6" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/28518</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/28517</t>
         </is>
       </c>
       <c r="D139" s="2" t="inlineStr">
         <is>
-          <t>Template admin — dialog fields</t>
+          <t>Template admin — permissions</t>
         </is>
       </c>
       <c r="E139" s="2" t="inlineStr">
         <is>
-          <t>Verify the template Name is limited to 100 characters</t>
+          <t>Verify the admin Fees &amp; Discounts page needs the Settings → Service permission</t>
         </is>
       </c>
       <c r="F139" s="2" t="inlineStr">
         <is>
-          <t>Low</t>
+          <t>High</t>
         </is>
       </c>
       <c r="G139" s="2" t="inlineStr">
@@ -7186,39 +7186,39 @@
       </c>
       <c r="I139" s="2" t="inlineStr">
         <is>
-          <t>name 100ch -&gt; 201; 101ch -&gt; 400 | WORDING+VIU 2026-07-13: Name 100-char limit carried.</t>
+          <t>BE-enforced: tech templates GET/POST -&gt; 403; page FE-gated settingsFinance | WORDING+VIU 2026-07-13: Templates admin is back-end gated by Settings → Finance (Tech → 403), established batch-2. Nav corrected to Finance. NOTE: re-check the Tech negative after the roles matrix is re-derived (Technician drifted on shared qb). | SV-8456 (2026-07-21 staging LIVE VIU): F&amp;D moved to SETTINGS→SERVICE (below Canned Lines); template/WO/Part-sale/customer dialogs now show Taxable as a Yes/No DROPDOWN (was toggle); Auto-apply is a CHECKBOX with a 'When on…' caption; settings &amp; customer tables are plain-text/left-aligned (no badges); WO sidebar card retitled 'Work Order Fees &amp; Discounts' and renders ABOVE Financial Info; Part-sale card 'Parts Sale Fees &amp; Discounts' above Financial Info. Permission gate pivoted Settings→Finance → Settings→Service (verified live: Service-user sees+manages F&amp;D &amp; convenience toggle; Finance-only user has no F&amp;D nav item and /administration/adjustment-templates bounces to /workorders). Frontend-only; functionality + calc INTACT. | RE-VIU 2026-07-22 LIVE (Batch 4, SV-8456 re-verify): access-check quick-login {admin} HTTP 200. Re-confirmed on current staging build — 8 UI corrections intact (Taxable Yes/No dropdown; Auto-apply checkbox+caption; modal field order Type/CalcType&gt;Name&gt;Amount&gt;Taxable+jur.note&gt;Auto-apply&gt;Description; Settings table plain-text left-aligned no badges; F&amp;D nav under SERVICE below Canned Lines; WO &amp; Part-Sale cards above Financial Info [Batch 2/3]; Customer 'Fees &amp; Discounts' tab mirrors Settings styling minus convenience toggle) AND Settings-&gt;Service permission pivot CONFIRMED live per role (seeded ServiceRole vs FinanceRole, assigned to Tech, Tech restored to Technician 50bf6a0d + verified, both ZZAUTOTEST roles deleted 204): Service-user sees+manages F&amp;D nav + convenience toggle, direct /administration/adjustment-templates loads; Finance-only user has NO F&amp;D nav, FINANCE=Payment Methods only, direct route bounces to /workorders. viu_status VIU-Verified re-confirmed. Ev build/fees-discounts/viu-sv8456-2026-07-22/ (01-settings-landing, 02-new-dialog, 03-customer-fd-tab, SVC-*, FIN-*).</t>
         </is>
       </c>
     </row>
     <row r="140">
       <c r="A140" s="2" t="inlineStr">
         <is>
-          <t>FD-TMPL-018</t>
+          <t>FD-TMPL-017</t>
         </is>
       </c>
       <c r="B140" s="2" t="inlineStr">
         <is>
-          <t>C29917</t>
+          <t>C28518</t>
         </is>
       </c>
       <c r="C140" s="6" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/29917</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/28518</t>
         </is>
       </c>
       <c r="D140" s="2" t="inlineStr">
         <is>
-          <t>Template admin — jurisdiction note</t>
+          <t>Template admin — dialog fields</t>
         </is>
       </c>
       <c r="E140" s="2" t="inlineStr">
         <is>
-          <t>Verify the admin Fee/Discount template dialog shows the tax-jurisdiction note below the Taxable Yes/No dropdown (for every kind)</t>
+          <t>Verify the template Name is limited to 100 characters</t>
         </is>
       </c>
       <c r="F140" s="2" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>Low</t>
         </is>
       </c>
       <c r="G140" s="2" t="inlineStr">
@@ -7233,39 +7233,39 @@
       </c>
       <c r="I140" s="2" t="inlineStr">
         <is>
-          <t>administration/adjustment-templates loads; Finance-only user has NO F&amp;D nav, FINANCE=Payment Methods only, direct route bounces to /workorders. viu_status VIU-Verified re-confirmed. Ev build/fees-discounts/viu-sv8456-2026-07-22/ (01-settings-landing, 02-new-dialog, 03-customer-fd-tab, SVC-*, FIN-*).</t>
+          <t>name 100ch -&gt; 201; 101ch -&gt; 400 | WORDING+VIU 2026-07-13: Name 100-char limit carried.</t>
         </is>
       </c>
     </row>
     <row r="141">
       <c r="A141" s="2" t="inlineStr">
         <is>
-          <t>FD-VAL-001</t>
+          <t>FD-TMPL-018</t>
         </is>
       </c>
       <c r="B141" s="2" t="inlineStr">
         <is>
-          <t>C28599</t>
+          <t>C29917</t>
         </is>
       </c>
       <c r="C141" s="6" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/28599</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/29917</t>
         </is>
       </c>
       <c r="D141" s="2" t="inlineStr">
         <is>
-          <t>Validation / Edge</t>
+          <t>Template admin — jurisdiction note</t>
         </is>
       </c>
       <c r="E141" s="2" t="inlineStr">
         <is>
-          <t>Verify the Add button stays disabled until Name, Type, Calculation Type and an Amount above 0 are all set</t>
+          <t>Verify the admin Fee/Discount template dialog shows the tax-jurisdiction note below the Taxable Yes/No dropdown (for every kind)</t>
         </is>
       </c>
       <c r="F141" s="2" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="G141" s="2" t="inlineStr">
@@ -7280,24 +7280,24 @@
       </c>
       <c r="I141" s="2" t="inlineStr">
         <is>
-          <t>CONFIRMED AGAIN: Add button enabled on empty form (validates on submit) — PO Q4=B defect persists | WORDING+VIU 2026-07-13: DEVIATION re-confirmed 2026-07-13 (BUG-FD-4): the 'Add Fee' button is ENABLED on an empty form (validates on submit). Labels build-accurate (Add Fee/Add Discount, Calculation Type, Max Amount). | STAGING VIU 2026-07-20 staging LIVE VIU: BUG-FD-4 FIXED on staging: confirm button disabled until Name+Type+Calc+Amount&gt;0 set. Live-observed (dev-wo-emptyform + part-sale Add Fee disabled-until-valid). | SV-8479/8480 deconfliction 2026-07-22: label sweep: navigation labels -&gt; 'Add Work Order Fee / Discount' / 'New Work Order Fee / Discount' (behavior/expected unchanged). | VIU 2026-07-22 LIVE: SV-8479 nav label 'Add Work Order Fee / Discount' confirmed present in the WO toolbar ⋯ menu; case behavior unchanged. Ev: wo/FD-WO-025-toolbar-menu.png.</t>
+          <t>administration/adjustment-templates loads; Finance-only user has NO F&amp;D nav, FINANCE=Payment Methods only, direct route bounces to /workorders. viu_status VIU-Verified re-confirmed. Ev build/fees-discounts/viu-sv8456-2026-07-22/ (01-settings-landing, 02-new-dialog, 03-customer-fd-tab, SVC-*, FIN-*).</t>
         </is>
       </c>
     </row>
     <row r="142">
       <c r="A142" s="2" t="inlineStr">
         <is>
-          <t>FD-VAL-002</t>
+          <t>FD-VAL-001</t>
         </is>
       </c>
       <c r="B142" s="2" t="inlineStr">
         <is>
-          <t>C28600</t>
+          <t>C28599</t>
         </is>
       </c>
       <c r="C142" s="6" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/28600</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/28599</t>
         </is>
       </c>
       <c r="D142" s="2" t="inlineStr">
@@ -7307,7 +7307,7 @@
       </c>
       <c r="E142" s="2" t="inlineStr">
         <is>
-          <t>Verify a blank or 0 amount blocks saving, with an error</t>
+          <t>Verify the Add button stays disabled until Name, Type, Calculation Type and an Amount above 0 are all set</t>
         </is>
       </c>
       <c r="F142" s="2" t="inlineStr">
@@ -7327,24 +7327,24 @@
       </c>
       <c r="I142" s="2" t="inlineStr">
         <is>
-          <t>amount 0 -&gt; 400 (API); UI inline error on submit | WORDING+VIU 2026-07-13: Blank/0 amount blocked; carry prior VIU. Labels cleaned. | SV-8479/8480 deconfliction 2026-07-22: label sweep: navigation labels -&gt; 'Add Work Order Fee / Discount' / 'New Work Order Fee / Discount' (behavior/expected unchanged). | VIU 2026-07-22 LIVE: SV-8479 nav label 'Add Work Order Fee / Discount' confirmed present in the WO toolbar ⋯ menu; case behavior unchanged. Ev: wo/FD-WO-025-toolbar-menu.png.</t>
+          <t>CONFIRMED AGAIN: Add button enabled on empty form (validates on submit) — PO Q4=B defect persists | WORDING+VIU 2026-07-13: DEVIATION re-confirmed 2026-07-13 (BUG-FD-4): the 'Add Fee' button is ENABLED on an empty form (validates on submit). Labels build-accurate (Add Fee/Add Discount, Calculation Type, Max Amount). | STAGING VIU 2026-07-20 staging LIVE VIU: BUG-FD-4 FIXED on staging: confirm button disabled until Name+Type+Calc+Amount&gt;0 set. Live-observed (dev-wo-emptyform + part-sale Add Fee disabled-until-valid). | SV-8479/8480 deconfliction 2026-07-22: label sweep: navigation labels -&gt; 'Add Work Order Fee / Discount' / 'New Work Order Fee / Discount' (behavior/expected unchanged). | VIU 2026-07-22 LIVE: SV-8479 nav label 'Add Work Order Fee / Discount' confirmed present in the WO toolbar ⋯ menu; case behavior unchanged. Ev: wo/FD-WO-025-toolbar-menu.png.</t>
         </is>
       </c>
     </row>
     <row r="143">
       <c r="A143" s="2" t="inlineStr">
         <is>
-          <t>FD-VAL-003</t>
+          <t>FD-VAL-002</t>
         </is>
       </c>
       <c r="B143" s="2" t="inlineStr">
         <is>
-          <t>C28601</t>
+          <t>C28600</t>
         </is>
       </c>
       <c r="C143" s="6" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/28601</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/28600</t>
         </is>
       </c>
       <c r="D143" s="2" t="inlineStr">
@@ -7354,12 +7354,12 @@
       </c>
       <c r="E143" s="2" t="inlineStr">
         <is>
-          <t>Verify an empty Name blocks saving, with an error (Name required, up to 100 characters)</t>
+          <t>Verify a blank or 0 amount blocks saving, with an error</t>
         </is>
       </c>
       <c r="F143" s="2" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>High</t>
         </is>
       </c>
       <c r="G143" s="2" t="inlineStr">
@@ -7374,24 +7374,24 @@
       </c>
       <c r="I143" s="2" t="inlineStr">
         <is>
-          <t>UI blocks empty name (inline required error). NEW FDBUG-16: raw API now ACCEPTS empty-name adds (201; regression vs batch-3 400) — FE-only guard; name 101ch -&gt; 400, 100ch -&gt; 201 | WORDING+VIU 2026-07-13: Empty name blocked in UI; 100-char limit. (Raw back-end accepts empty name — FDBUG-16 — but the dialog blocks it.) | SV-8479/8480 deconfliction 2026-07-22: label sweep: navigation labels -&gt; 'Add Work Order Fee / Discount' / 'New Work Order Fee / Discount' (behavior/expected unchanged). | VIU 2026-07-22 LIVE: SV-8479 nav label 'Add Work Order Fee / Discount' confirmed present in the WO toolbar ⋯ menu; case behavior unchanged. Ev: wo/FD-WO-025-toolbar-menu.png.</t>
+          <t>amount 0 -&gt; 400 (API); UI inline error on submit | WORDING+VIU 2026-07-13: Blank/0 amount blocked; carry prior VIU. Labels cleaned. | SV-8479/8480 deconfliction 2026-07-22: label sweep: navigation labels -&gt; 'Add Work Order Fee / Discount' / 'New Work Order Fee / Discount' (behavior/expected unchanged). | VIU 2026-07-22 LIVE: SV-8479 nav label 'Add Work Order Fee / Discount' confirmed present in the WO toolbar ⋯ menu; case behavior unchanged. Ev: wo/FD-WO-025-toolbar-menu.png.</t>
         </is>
       </c>
     </row>
     <row r="144">
       <c r="A144" s="2" t="inlineStr">
         <is>
-          <t>FD-VAL-004</t>
+          <t>FD-VAL-003</t>
         </is>
       </c>
       <c r="B144" s="2" t="inlineStr">
         <is>
-          <t>C28602</t>
+          <t>C28601</t>
         </is>
       </c>
       <c r="C144" s="6" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/28602</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/28601</t>
         </is>
       </c>
       <c r="D144" s="2" t="inlineStr">
@@ -7401,12 +7401,12 @@
       </c>
       <c r="E144" s="2" t="inlineStr">
         <is>
-          <t>Verify a percentage discount over 100% is invalid while a percentage fee has no upper cap</t>
+          <t>Verify an empty Name blocks saving, with an error (Name required, up to 100 characters)</t>
         </is>
       </c>
       <c r="F144" s="2" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="G144" s="2" t="inlineStr">
@@ -7421,24 +7421,24 @@
       </c>
       <c r="I144" s="2" t="inlineStr">
         <is>
-          <t>discount &gt;100% invalid (400), fee uncapped (201) | WORDING+VIU 2026-07-13: %&gt;100 discount invalid, fee uncapped; carry prior VIU. Labels cleaned. | SV-8479/8480 deconfliction 2026-07-22: label sweep: navigation labels -&gt; 'Add Work Order Fee / Discount' / 'New Work Order Fee / Discount' (behavior/expected unchanged). | VIU 2026-07-22 LIVE: SV-8479 nav label 'Add Work Order Fee / Discount' confirmed present in the WO toolbar ⋯ menu; case behavior unchanged. Ev: wo/FD-WO-025-toolbar-menu.png.</t>
+          <t>UI blocks empty name (inline required error). NEW FDBUG-16: raw API now ACCEPTS empty-name adds (201; regression vs batch-3 400) — FE-only guard; name 101ch -&gt; 400, 100ch -&gt; 201 | WORDING+VIU 2026-07-13: Empty name blocked in UI; 100-char limit. (Raw back-end accepts empty name — FDBUG-16 — but the dialog blocks it.) | SV-8479/8480 deconfliction 2026-07-22: label sweep: navigation labels -&gt; 'Add Work Order Fee / Discount' / 'New Work Order Fee / Discount' (behavior/expected unchanged). | VIU 2026-07-22 LIVE: SV-8479 nav label 'Add Work Order Fee / Discount' confirmed present in the WO toolbar ⋯ menu; case behavior unchanged. Ev: wo/FD-WO-025-toolbar-menu.png.</t>
         </is>
       </c>
     </row>
     <row r="145">
       <c r="A145" s="2" t="inlineStr">
         <is>
-          <t>FD-VAL-005</t>
+          <t>FD-VAL-004</t>
         </is>
       </c>
       <c r="B145" s="2" t="inlineStr">
         <is>
-          <t>C28603</t>
+          <t>C28602</t>
         </is>
       </c>
       <c r="C145" s="6" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/28603</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/28602</t>
         </is>
       </c>
       <c r="D145" s="2" t="inlineStr">
@@ -7448,12 +7448,12 @@
       </c>
       <c r="E145" s="2" t="inlineStr">
         <is>
-          <t>Verify negative amounts are rejected (values must be above 0)</t>
+          <t>Verify a percentage discount over 100% is invalid while a percentage fee has no upper cap</t>
         </is>
       </c>
       <c r="F145" s="2" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>High</t>
         </is>
       </c>
       <c r="G145" s="2" t="inlineStr">
@@ -7468,24 +7468,24 @@
       </c>
       <c r="I145" s="2" t="inlineStr">
         <is>
-          <t>negative amount -&gt; 400 | WORDING+VIU 2026-07-13: Negatives rejected; carry prior VIU. | SV-8479/8480 deconfliction 2026-07-22: label sweep: navigation labels -&gt; 'Add Work Order Fee / Discount' / 'New Work Order Fee / Discount' (behavior/expected unchanged). | VIU 2026-07-22 LIVE: SV-8479 nav label 'Add Work Order Fee / Discount' confirmed present in the WO toolbar ⋯ menu; case behavior unchanged. Ev: wo/FD-WO-025-toolbar-menu.png.</t>
+          <t>discount &gt;100% invalid (400), fee uncapped (201) | WORDING+VIU 2026-07-13: %&gt;100 discount invalid, fee uncapped; carry prior VIU. Labels cleaned. | SV-8479/8480 deconfliction 2026-07-22: label sweep: navigation labels -&gt; 'Add Work Order Fee / Discount' / 'New Work Order Fee / Discount' (behavior/expected unchanged). | VIU 2026-07-22 LIVE: SV-8479 nav label 'Add Work Order Fee / Discount' confirmed present in the WO toolbar ⋯ menu; case behavior unchanged. Ev: wo/FD-WO-025-toolbar-menu.png.</t>
         </is>
       </c>
     </row>
     <row r="146">
       <c r="A146" s="2" t="inlineStr">
         <is>
-          <t>FD-VAL-006</t>
+          <t>FD-VAL-005</t>
         </is>
       </c>
       <c r="B146" s="2" t="inlineStr">
         <is>
-          <t>C28604</t>
+          <t>C28603</t>
         </is>
       </c>
       <c r="C146" s="6" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/28604</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/28603</t>
         </is>
       </c>
       <c r="D146" s="2" t="inlineStr">
@@ -7495,7 +7495,7 @@
       </c>
       <c r="E146" s="2" t="inlineStr">
         <is>
-          <t>Verify the Max Amount field shows only for percentage methods and how 0 or empty behaves</t>
+          <t>Verify negative amounts are rejected (values must be above 0)</t>
         </is>
       </c>
       <c r="F146" s="2" t="inlineStr">
@@ -7515,24 +7515,24 @@
       </c>
       <c r="I146" s="2" t="inlineStr">
         <is>
-          <t>FDBUG-9: maxCap 0 behaves as NO cap (not 'no maximum' spec reading matches build for empty, but 0 disagrees w/ §5-R6 $0-forces-$0) — persists | WORDING+VIU 2026-07-13: Confirmed live: '$ Max Amount (Optional)' appears only for percentage methods (hidden for Flat Amount, shots wo-03/wo-05). DEVIATION (FDBUG-9 / PO Q2 pending): whether a Max Amount of 0 means 'no cap' or 'cap at $0.00' is a pending product decision — expected kept as current build behavior. | CHRIS WARD ROUND-2 ANSWER APPLIED 2026-07-14(Q2=A): PO ruled a typed 0 in Max Amount = 'no limit' (WAD, S2-R25). 0-handling no longer a deviation; FDBUG-9 closed as accepted; jira draft TICKET 4 DROPPED. Expected reworded to affirm 0=no-cap. PUSHED TO TESTRAIL 2026-07-14 via update_case (QA-lead one-day authorization; update 200 / re-verify 200 MATCH; audit: testrail-round2-push-log.md). | SV-8479/8480 deconfliction 2026-07-22: label sweep: navigation labels -&gt; 'Add Work Order Fee / Discount' / 'New Work Order Fee / Discount' (behavior/expected unchanged). | VIU 2026-07-22 LIVE: SV-8479 nav label 'Add Work Order Fee / Discount' confirmed present in the WO toolbar ⋯ menu; case behavior unchanged. Ev: wo/FD-WO-025-toolbar-menu.png.</t>
+          <t>negative amount -&gt; 400 | WORDING+VIU 2026-07-13: Negatives rejected; carry prior VIU. | SV-8479/8480 deconfliction 2026-07-22: label sweep: navigation labels -&gt; 'Add Work Order Fee / Discount' / 'New Work Order Fee / Discount' (behavior/expected unchanged). | VIU 2026-07-22 LIVE: SV-8479 nav label 'Add Work Order Fee / Discount' confirmed present in the WO toolbar ⋯ menu; case behavior unchanged. Ev: wo/FD-WO-025-toolbar-menu.png.</t>
         </is>
       </c>
     </row>
     <row r="147">
       <c r="A147" s="2" t="inlineStr">
         <is>
-          <t>FD-VAL-007</t>
+          <t>FD-VAL-006</t>
         </is>
       </c>
       <c r="B147" s="2" t="inlineStr">
         <is>
-          <t>C28605</t>
+          <t>C28604</t>
         </is>
       </c>
       <c r="C147" s="6" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/28605</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/28604</t>
         </is>
       </c>
       <c r="D147" s="2" t="inlineStr">
@@ -7542,7 +7542,7 @@
       </c>
       <c r="E147" s="2" t="inlineStr">
         <is>
-          <t>Verify a template that is both auto-apply at the location and a customer default is added only ONCE to a new work order</t>
+          <t>Verify the Max Amount field shows only for percentage methods and how 0 or empty behaves</t>
         </is>
       </c>
       <c r="F147" s="2" t="inlineStr">
@@ -7562,39 +7562,39 @@
       </c>
       <c r="I147" s="2" t="inlineStr">
         <is>
-          <t>auto+default template -&gt; exactly ONE adjustment on the new WO | WORDING+VIU 2026-07-13: Double-add does not stack (one adjustment); carry prior VIU. | SV-8456 (2026-07-21 staging LIVE VIU): F&amp;D moved to SETTINGS→SERVICE (below Canned Lines); template/WO/Part-sale/customer dialogs now show Taxable as a Yes/No DROPDOWN (was toggle); Auto-apply is a CHECKBOX with a 'When on…' caption; settings &amp; customer tables are plain-text/left-aligned (no badges); WO sidebar card retitled 'Work Order Fees &amp; Discounts' and renders ABOVE Financial Info; Part-sale card 'Parts Sale Fees &amp; Discounts' above Financial Info. Permission gate pivoted Settings→Finance → Settings→Service (verified live: Service-user sees+manages F&amp;D &amp; convenience toggle; Finance-only user has no F&amp;D nav item and /administration/adjustment-templates bounces to /workorders). Frontend-only; functionality + calc INTACT. | RE-VIU 2026-07-22 LIVE (Batch 4, SV-8456 re-verify): access-check quick-login {admin} HTTP 200. Re-confirmed on current staging build — 8 UI corrections intact (Taxable Yes/No dropdown; Auto-apply checkbox+caption; modal field order Type/CalcType&gt;Name&gt;Amount&gt;Taxable+jur.note&gt;Auto-apply&gt;Description; Settings table plain-text left-aligned no badges; F&amp;D nav under SERVICE below Canned Lines; WO &amp; Part-Sale cards above Financial Info [Batch 2/3]; Customer 'Fees &amp; Discounts' tab mirrors Settings styling minus convenience toggle) AND Settings-&gt;Service permission pivot CONFIRMED live per role (seeded ServiceRole vs FinanceRole, assigned to Tech, Tech restored to Technician 50bf6a0d + verified, both ZZAUTOTEST roles deleted 204): Service-user sees+manages F&amp;D nav + convenience toggle, direct /administration/adjustment-templates loads; Finance-only user has NO F&amp;D nav, FINANCE=Payment Methods only, direct route bounces to /workorders. viu_status VIU-Verified re-confirmed. Ev build/fees-discounts/viu-sv8456-2026-07-22/ (01-settings-landing, 02-new-dialog, 03-customer-fd-tab, SVC-*, FIN-*).</t>
+          <t>FDBUG-9: maxCap 0 behaves as NO cap (not 'no maximum' spec reading matches build for empty, but 0 disagrees w/ §5-R6 $0-forces-$0) — persists | WORDING+VIU 2026-07-13: Confirmed live: '$ Max Amount (Optional)' appears only for percentage methods (hidden for Flat Amount, shots wo-03/wo-05). DEVIATION (FDBUG-9 / PO Q2 pending): whether a Max Amount of 0 means 'no cap' or 'cap at $0.00' is a pending product decision — expected kept as current build behavior. | CHRIS WARD ROUND-2 ANSWER APPLIED 2026-07-14(Q2=A): PO ruled a typed 0 in Max Amount = 'no limit' (WAD, S2-R25). 0-handling no longer a deviation; FDBUG-9 closed as accepted; jira draft TICKET 4 DROPPED. Expected reworded to affirm 0=no-cap. PUSHED TO TESTRAIL 2026-07-14 via update_case (QA-lead one-day authorization; update 200 / re-verify 200 MATCH; audit: testrail-round2-push-log.md). | SV-8479/8480 deconfliction 2026-07-22: label sweep: navigation labels -&gt; 'Add Work Order Fee / Discount' / 'New Work Order Fee / Discount' (behavior/expected unchanged). | VIU 2026-07-22 LIVE: SV-8479 nav label 'Add Work Order Fee / Discount' confirmed present in the WO toolbar ⋯ menu; case behavior unchanged. Ev: wo/FD-WO-025-toolbar-menu.png.</t>
         </is>
       </c>
     </row>
     <row r="148">
       <c r="A148" s="2" t="inlineStr">
         <is>
-          <t>FD-WO-001</t>
+          <t>FD-VAL-007</t>
         </is>
       </c>
       <c r="B148" s="2" t="inlineStr">
         <is>
-          <t>C28424</t>
+          <t>C28605</t>
         </is>
       </c>
       <c r="C148" s="6" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/28424</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/28605</t>
         </is>
       </c>
       <c r="D148" s="2" t="inlineStr">
         <is>
-          <t>Work Order — Whole-WO Fee/Discount</t>
+          <t>Validation / Edge</t>
         </is>
       </c>
       <c r="E148" s="2" t="inlineStr">
         <is>
-          <t>Verify the whole-work-order fee/discount dialog opens from the toolbar menu with title 'New Work Order Fee / Discount'</t>
+          <t>Verify a template that is both auto-apply at the location and a customer default is added only ONCE to a new work order</t>
         </is>
       </c>
       <c r="F148" s="2" t="inlineStr">
         <is>
-          <t>Critical</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="G148" s="2" t="inlineStr">
@@ -7609,24 +7609,24 @@
       </c>
       <c r="I148" s="2" t="inlineStr">
         <is>
-          <t>dialog title still 'Add new fee/discount' (spec 'New Fee / Discount'), menu item 'Add Fee/Discount' — label drift persists (UI re-driven, shot 10-wo-add-dialog) | WORDING+VIU 2026-07-13: rewritten to exact build labels (⋮ menu item 'Add Fee/Discount'; dialog 'Add new fee/discount'; fields 'Apply From Template'/'Name'/'Type'/'Calculation Type'/'$ Amount' or 'Percent %'/'$ Max Amount (Optional)'/'Taxable' toggle; whole-WO Calculation Type options = Flat Amount, % of Labor Total, % of Parts Total, % of Subtotal; buttons 'Add Fee'/'Add Discount'; sidebar card 'WO Fees &amp; Discounts'; preview empty prompt 'Enter an amount to see the impact.'). Captured live on WO S3-15960 (shots wo-01..wo-05). Now build-accurate (was VIU-Deviation only because the case used the older spec wording). Dialog shows no work-order-number subtitle in this build (old expected claim dropped). | SV-8479/8480 deconfliction 2026-07-22: menu item 'Add Fee/Discount' -&gt; 'Add Work Order Fee / Discount' (item 10); title 'Add new fee/discount' -&gt; 'New Work Order Fee / Discount' + new subline 'Applying To: Entire Work Order' (item 11, reverses the old 'no Applying-to line' claim). Absorbs dropped new case FD-WO-026. | VIU 2026-07-22 LIVE: whole-WO dialog opens from toolbar menu; title 'New Work Order Fee / Discount', subline 'Applying To: Entire Work Order', no scope dropdown. Ev: wo/FD-WO-001-wo-dialog.png, wo/wo-dialog-text.txt.</t>
+          <t>auto+default template -&gt; exactly ONE adjustment on the new WO | WORDING+VIU 2026-07-13: Double-add does not stack (one adjustment); carry prior VIU. | SV-8456 (2026-07-21 staging LIVE VIU): F&amp;D moved to SETTINGS→SERVICE (below Canned Lines); template/WO/Part-sale/customer dialogs now show Taxable as a Yes/No DROPDOWN (was toggle); Auto-apply is a CHECKBOX with a 'When on…' caption; settings &amp; customer tables are plain-text/left-aligned (no badges); WO sidebar card retitled 'Work Order Fees &amp; Discounts' and renders ABOVE Financial Info; Part-sale card 'Parts Sale Fees &amp; Discounts' above Financial Info. Permission gate pivoted Settings→Finance → Settings→Service (verified live: Service-user sees+manages F&amp;D &amp; convenience toggle; Finance-only user has no F&amp;D nav item and /administration/adjustment-templates bounces to /workorders). Frontend-only; functionality + calc INTACT. | RE-VIU 2026-07-22 LIVE (Batch 4, SV-8456 re-verify): access-check quick-login {admin} HTTP 200. Re-confirmed on current staging build — 8 UI corrections intact (Taxable Yes/No dropdown; Auto-apply checkbox+caption; modal field order Type/CalcType&gt;Name&gt;Amount&gt;Taxable+jur.note&gt;Auto-apply&gt;Description; Settings table plain-text left-aligned no badges; F&amp;D nav under SERVICE below Canned Lines; WO &amp; Part-Sale cards above Financial Info [Batch 2/3]; Customer 'Fees &amp; Discounts' tab mirrors Settings styling minus convenience toggle) AND Settings-&gt;Service permission pivot CONFIRMED live per role (seeded ServiceRole vs FinanceRole, assigned to Tech, Tech restored to Technician 50bf6a0d + verified, both ZZAUTOTEST roles deleted 204): Service-user sees+manages F&amp;D nav + convenience toggle, direct /administration/adjustment-templates loads; Finance-only user has NO F&amp;D nav, FINANCE=Payment Methods only, direct route bounces to /workorders. viu_status VIU-Verified re-confirmed. Ev build/fees-discounts/viu-sv8456-2026-07-22/ (01-settings-landing, 02-new-dialog, 03-customer-fd-tab, SVC-*, FIN-*).</t>
         </is>
       </c>
     </row>
     <row r="149">
       <c r="A149" s="2" t="inlineStr">
         <is>
-          <t>FD-WO-002</t>
+          <t>FD-WO-001</t>
         </is>
       </c>
       <c r="B149" s="2" t="inlineStr">
         <is>
-          <t>C28425</t>
+          <t>C28424</t>
         </is>
       </c>
       <c r="C149" s="6" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/28425</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/28424</t>
         </is>
       </c>
       <c r="D149" s="2" t="inlineStr">
@@ -7636,7 +7636,7 @@
       </c>
       <c r="E149" s="2" t="inlineStr">
         <is>
-          <t>Verify adding a whole-work-order flat-amount fee saves and shows a success message</t>
+          <t>Verify the whole-work-order fee/discount dialog opens from the toolbar menu with title 'New Work Order Fee / Discount'</t>
         </is>
       </c>
       <c r="F149" s="2" t="inlineStr">
@@ -7656,24 +7656,24 @@
       </c>
       <c r="I149" s="2" t="inlineStr">
         <is>
-          <t>whole-WO flat fee add 201 + visible in WO view (flat 7.77 resolved exactly) | WORDING+VIU 2026-07-13: rewritten to exact build labels (⋮ menu item 'Add Fee/Discount'; dialog 'Add new fee/discount'; fields 'Apply From Template'/'Name'/'Type'/'Calculation Type'/'$ Amount' or 'Percent %'/'$ Max Amount (Optional)'/'Taxable' toggle; whole-WO Calculation Type options = Flat Amount, % of Labor Total, % of Parts Total, % of Subtotal; buttons 'Add Fee'/'Add Discount'; sidebar card 'WO Fees &amp; Discounts'; preview empty prompt 'Enter an amount to see the impact.'). Captured live on WO S3-15960 (shots wo-01..wo-05). Sidebar card is 'WO Fees &amp; Discounts' (was 'Work Order Fee / Discount'). Exact success-toast text not re-captured this pass (worded as 'a success message'). | SV-8456 (2026-07-21 staging LIVE VIU): F&amp;D moved to SETTINGS→SERVICE (below Canned Lines); template/WO/Part-sale/customer dialogs now show Taxable as a Yes/No DROPDOWN (was toggle); Auto-apply is a CHECKBOX with a 'When on…' caption; settings &amp; customer tables are plain-text/left-aligned (no badges); WO sidebar card retitled 'Work Order Fees &amp; Discounts' and renders ABOVE Financial Info; Part-sale card 'Parts Sale Fees &amp; Discounts' above Financial Info. Permission gate pivoted Settings→Finance → Settings→Service (verified live: Service-user sees+manages F&amp;D &amp; convenience toggle; Finance-only user has no F&amp;D nav item and /administration/adjustment-templates bounces to /workorders). Frontend-only; functionality + calc INTACT. | SV-8479/8480 deconfliction 2026-07-22: label sweep: navigation labels -&gt; 'Add Work Order Fee / Discount' / 'New Work Order Fee / Discount' (behavior/expected unchanged). | VIU 2026-07-22 LIVE: SV-8479 nav label 'Add Work Order Fee / Discount' confirmed present in the WO toolbar ⋯ menu; case behavior unchanged. Ev: wo/FD-WO-025-toolbar-menu.png. | RE-VIU 2026-07-22 LIVE (Batch 4, SV-8456 re-verify): access-check quick-login {admin} HTTP 200. Re-confirmed on current staging build — 8 UI corrections intact (Taxable Yes/No dropdown; Auto-apply checkbox+caption; modal field order Type/CalcType&gt;Name&gt;Amount&gt;Taxable+jur.note&gt;Auto-apply&gt;Description; Settings table plain-text left-aligned no badges; F&amp;D nav under SERVICE below Canned Lines; WO &amp; Part-Sale cards above Financial Info [Batch 2/3]; Customer 'Fees &amp; Discounts' tab mirrors Settings styling minus convenience toggle) AND Settings-&gt;Service permission pivot CONFIRMED live per role (seeded ServiceRole vs FinanceRole, assigned to Tech, Tech restored to Technician 50bf6a0d + verified, both ZZAUTOTEST roles deleted 204): Service-user sees+manages F&amp;D nav + convenience toggle, direct /administration/adjustment-templates loads; Finance-only user has NO F&amp;D nav, FINANCE=Payment Methods only, direct route bounces to /workorders. viu_status VIU-Verified re-confirmed. Ev build/fees-discounts/viu-sv8456-2026-07-22/ (01-settings-landing, 02-new-dialog, 03-customer-fd-tab, SVC-*, FIN-*).</t>
+          <t>dialog title still 'Add new fee/discount' (spec 'New Fee / Discount'), menu item 'Add Fee/Discount' — label drift persists (UI re-driven, shot 10-wo-add-dialog) | WORDING+VIU 2026-07-13: rewritten to exact build labels (⋮ menu item 'Add Fee/Discount'; dialog 'Add new fee/discount'; fields 'Apply From Template'/'Name'/'Type'/'Calculation Type'/'$ Amount' or 'Percent %'/'$ Max Amount (Optional)'/'Taxable' toggle; whole-WO Calculation Type options = Flat Amount, % of Labor Total, % of Parts Total, % of Subtotal; buttons 'Add Fee'/'Add Discount'; sidebar card 'WO Fees &amp; Discounts'; preview empty prompt 'Enter an amount to see the impact.'). Captured live on WO S3-15960 (shots wo-01..wo-05). Now build-accurate (was VIU-Deviation only because the case used the older spec wording). Dialog shows no work-order-number subtitle in this build (old expected claim dropped). | SV-8479/8480 deconfliction 2026-07-22: menu item 'Add Fee/Discount' -&gt; 'Add Work Order Fee / Discount' (item 10); title 'Add new fee/discount' -&gt; 'New Work Order Fee / Discount' + new subline 'Applying To: Entire Work Order' (item 11, reverses the old 'no Applying-to line' claim). Absorbs dropped new case FD-WO-026. | VIU 2026-07-22 LIVE: whole-WO dialog opens from toolbar menu; title 'New Work Order Fee / Discount', subline 'Applying To: Entire Work Order', no scope dropdown. Ev: wo/FD-WO-001-wo-dialog.png, wo/wo-dialog-text.txt.</t>
         </is>
       </c>
     </row>
     <row r="150">
       <c r="A150" s="2" t="inlineStr">
         <is>
-          <t>FD-WO-003</t>
+          <t>FD-WO-002</t>
         </is>
       </c>
       <c r="B150" s="2" t="inlineStr">
         <is>
-          <t>C28426</t>
+          <t>C28425</t>
         </is>
       </c>
       <c r="C150" s="6" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/28426</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/28425</t>
         </is>
       </c>
       <c r="D150" s="2" t="inlineStr">
@@ -7683,12 +7683,12 @@
       </c>
       <c r="E150" s="2" t="inlineStr">
         <is>
-          <t>Verify the live preview shows a whole-work-order percentage discount before you save</t>
+          <t>Verify adding a whole-work-order flat-amount fee saves and shows a success message</t>
         </is>
       </c>
       <c r="F150" s="2" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Critical</t>
         </is>
       </c>
       <c r="G150" s="2" t="inlineStr">
@@ -7703,24 +7703,24 @@
       </c>
       <c r="I150" s="2" t="inlineStr">
         <is>
-          <t>dialog live preview re-driven ($5 flat -&gt; '+$5.00 / New work-order subtotal $187.76'); pct preview math not re-driven, API pct resolution re-proven (10%-&gt;17.08) | WORDING+VIU 2026-07-13: rewritten to exact build labels (⋮ menu item 'Add Fee/Discount'; dialog 'Add new fee/discount'; fields 'Apply From Template'/'Name'/'Type'/'Calculation Type'/'$ Amount' or 'Percent %'/'$ Max Amount (Optional)'/'Taxable' toggle; whole-WO Calculation Type options = Flat Amount, % of Labor Total, % of Parts Total, % of Subtotal; buttons 'Add Fee'/'Add Discount'; sidebar card 'WO Fees &amp; Discounts'; preview empty prompt 'Enter an amount to see the impact.'). Captured live on WO S3-15960 (shots wo-01..wo-05). Calc type corrected from generic 'Percentage' to the real whole-WO option '% of Subtotal'. Exact preview row labels not re-captured this pass (behavior verified 2026-07-10). | SV-8479/8480 deconfliction 2026-07-22: label sweep: navigation labels -&gt; 'Add Work Order Fee / Discount' / 'New Work Order Fee / Discount' (behavior/expected unchanged). | VIU 2026-07-22 LIVE: SV-8479 nav label 'Add Work Order Fee / Discount' confirmed present in the WO toolbar ⋯ menu; case behavior unchanged. Ev: wo/FD-WO-025-toolbar-menu.png.</t>
+          <t>whole-WO flat fee add 201 + visible in WO view (flat 7.77 resolved exactly) | WORDING+VIU 2026-07-13: rewritten to exact build labels (⋮ menu item 'Add Fee/Discount'; dialog 'Add new fee/discount'; fields 'Apply From Template'/'Name'/'Type'/'Calculation Type'/'$ Amount' or 'Percent %'/'$ Max Amount (Optional)'/'Taxable' toggle; whole-WO Calculation Type options = Flat Amount, % of Labor Total, % of Parts Total, % of Subtotal; buttons 'Add Fee'/'Add Discount'; sidebar card 'WO Fees &amp; Discounts'; preview empty prompt 'Enter an amount to see the impact.'). Captured live on WO S3-15960 (shots wo-01..wo-05). Sidebar card is 'WO Fees &amp; Discounts' (was 'Work Order Fee / Discount'). Exact success-toast text not re-captured this pass (worded as 'a success message'). | SV-8456 (2026-07-21 staging LIVE VIU): F&amp;D moved to SETTINGS→SERVICE (below Canned Lines); template/WO/Part-sale/customer dialogs now show Taxable as a Yes/No DROPDOWN (was toggle); Auto-apply is a CHECKBOX with a 'When on…' caption; settings &amp; customer tables are plain-text/left-aligned (no badges); WO sidebar card retitled 'Work Order Fees &amp; Discounts' and renders ABOVE Financial Info; Part-sale card 'Parts Sale Fees &amp; Discounts' above Financial Info. Permission gate pivoted Settings→Finance → Settings→Service (verified live: Service-user sees+manages F&amp;D &amp; convenience toggle; Finance-only user has no F&amp;D nav item and /administration/adjustment-templates bounces to /workorders). Frontend-only; functionality + calc INTACT. | SV-8479/8480 deconfliction 2026-07-22: label sweep: navigation labels -&gt; 'Add Work Order Fee / Discount' / 'New Work Order Fee / Discount' (behavior/expected unchanged). | VIU 2026-07-22 LIVE: SV-8479 nav label 'Add Work Order Fee / Discount' confirmed present in the WO toolbar ⋯ menu; case behavior unchanged. Ev: wo/FD-WO-025-toolbar-menu.png. | RE-VIU 2026-07-22 LIVE (Batch 4, SV-8456 re-verify): access-check quick-login {admin} HTTP 200. Re-confirmed on current staging build — 8 UI corrections intact (Taxable Yes/No dropdown; Auto-apply checkbox+caption; modal field order Type/CalcType&gt;Name&gt;Amount&gt;Taxable+jur.note&gt;Auto-apply&gt;Description; Settings table plain-text left-aligned no badges; F&amp;D nav under SERVICE below Canned Lines; WO &amp; Part-Sale cards above Financial Info [Batch 2/3]; Customer 'Fees &amp; Discounts' tab mirrors Settings styling minus convenience toggle) AND Settings-&gt;Service permission pivot CONFIRMED live per role (seeded ServiceRole vs FinanceRole, assigned to Tech, Tech restored to Technician 50bf6a0d + verified, both ZZAUTOTEST roles deleted 204): Service-user sees+manages F&amp;D nav + convenience toggle, direct /administration/adjustment-templates loads; Finance-only user has NO F&amp;D nav, FINANCE=Payment Methods only, direct route bounces to /workorders. viu_status VIU-Verified re-confirmed. Ev build/fees-discounts/viu-sv8456-2026-07-22/ (01-settings-landing, 02-new-dialog, 03-customer-fd-tab, SVC-*, FIN-*).</t>
         </is>
       </c>
     </row>
     <row r="151">
       <c r="A151" s="2" t="inlineStr">
         <is>
-          <t>FD-WO-004</t>
+          <t>FD-WO-003</t>
         </is>
       </c>
       <c r="B151" s="2" t="inlineStr">
         <is>
-          <t>C28427</t>
+          <t>C28426</t>
         </is>
       </c>
       <c r="C151" s="6" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/28427</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/28426</t>
         </is>
       </c>
       <c r="D151" s="2" t="inlineStr">
@@ -7730,7 +7730,7 @@
       </c>
       <c r="E151" s="2" t="inlineStr">
         <is>
-          <t>Verify 'Apply From Template' fills the dialog with a template's values</t>
+          <t>Verify the live preview shows a whole-work-order percentage discount before you save</t>
         </is>
       </c>
       <c r="F151" s="2" t="inlineStr">
@@ -7750,24 +7750,24 @@
       </c>
       <c r="I151" s="2" t="inlineStr">
         <is>
-          <t>not re-driven today (Apply-From-Template combobox present in dialog); templateId add path re-proven via API (FD-STACK-003) | WORDING+VIU 2026-07-13: rewritten to exact build labels (⋮ menu item 'Add Fee/Discount'; dialog 'Add new fee/discount'; fields 'Apply From Template'/'Name'/'Type'/'Calculation Type'/'$ Amount' or 'Percent %'/'$ Max Amount (Optional)'/'Taxable' toggle; whole-WO Calculation Type options = Flat Amount, % of Labor Total, % of Parts Total, % of Subtotal; buttons 'Add Fee'/'Add Discount'; sidebar card 'WO Fees &amp; Discounts'; preview empty prompt 'Enter an amount to see the impact.'). Captured live on WO S3-15960 (shots wo-01..wo-05). Dropdown label is exactly 'Apply From Template' (was 'Apply from template (optional)'). | SV-8479/8480 deconfliction 2026-07-22: label sweep: navigation labels -&gt; 'Add Work Order Fee / Discount' / 'New Work Order Fee / Discount' (behavior/expected unchanged). | VIU 2026-07-22 LIVE: SV-8479 nav label 'Add Work Order Fee / Discount' confirmed present in the WO toolbar ⋯ menu; case behavior unchanged. Ev: wo/FD-WO-025-toolbar-menu.png.</t>
+          <t>dialog live preview re-driven ($5 flat -&gt; '+$5.00 / New work-order subtotal $187.76'); pct preview math not re-driven, API pct resolution re-proven (10%-&gt;17.08) | WORDING+VIU 2026-07-13: rewritten to exact build labels (⋮ menu item 'Add Fee/Discount'; dialog 'Add new fee/discount'; fields 'Apply From Template'/'Name'/'Type'/'Calculation Type'/'$ Amount' or 'Percent %'/'$ Max Amount (Optional)'/'Taxable' toggle; whole-WO Calculation Type options = Flat Amount, % of Labor Total, % of Parts Total, % of Subtotal; buttons 'Add Fee'/'Add Discount'; sidebar card 'WO Fees &amp; Discounts'; preview empty prompt 'Enter an amount to see the impact.'). Captured live on WO S3-15960 (shots wo-01..wo-05). Calc type corrected from generic 'Percentage' to the real whole-WO option '% of Subtotal'. Exact preview row labels not re-captured this pass (behavior verified 2026-07-10). | SV-8479/8480 deconfliction 2026-07-22: label sweep: navigation labels -&gt; 'Add Work Order Fee / Discount' / 'New Work Order Fee / Discount' (behavior/expected unchanged). | VIU 2026-07-22 LIVE: SV-8479 nav label 'Add Work Order Fee / Discount' confirmed present in the WO toolbar ⋯ menu; case behavior unchanged. Ev: wo/FD-WO-025-toolbar-menu.png.</t>
         </is>
       </c>
     </row>
     <row r="152">
       <c r="A152" s="2" t="inlineStr">
         <is>
-          <t>FD-WO-005</t>
+          <t>FD-WO-004</t>
         </is>
       </c>
       <c r="B152" s="2" t="inlineStr">
         <is>
-          <t>C28428</t>
+          <t>C28427</t>
         </is>
       </c>
       <c r="C152" s="6" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/28428</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/28427</t>
         </is>
       </c>
       <c r="D152" s="2" t="inlineStr">
@@ -7777,12 +7777,12 @@
       </c>
       <c r="E152" s="2" t="inlineStr">
         <is>
-          <t>Verify the Add button stays disabled until Name, Type, Calculation Type and an Amount above 0 are all filled in</t>
+          <t>Verify 'Apply From Template' fills the dialog with a template's values</t>
         </is>
       </c>
       <c r="F152" s="2" t="inlineStr">
         <is>
-          <t>Critical</t>
+          <t>High</t>
         </is>
       </c>
       <c r="G152" s="2" t="inlineStr">
@@ -7797,24 +7797,24 @@
       </c>
       <c r="I152" s="2" t="inlineStr">
         <is>
-          <t>CONFIRMED AGAIN: 'Add Fee' button ENABLED on an empty form (disabled-on-empty=false) — PO Q4=B defect persists | WORDING+VIU 2026-07-13: rewritten to exact build labels (⋮ menu item 'Add Fee/Discount'; dialog 'Add new fee/discount'; fields 'Apply From Template'/'Name'/'Type'/'Calculation Type'/'$ Amount' or 'Percent %'/'$ Max Amount (Optional)'/'Taxable' toggle; whole-WO Calculation Type options = Flat Amount, % of Labor Total, % of Parts Total, % of Subtotal; buttons 'Add Fee'/'Add Discount'; sidebar card 'WO Fees &amp; Discounts'; preview empty prompt 'Enter an amount to see the impact.'). Captured live on WO S3-15960 (shots wo-01..wo-05). DEVIATION re-confirmed live 2026-07-13: the 'Add Fee' button is ENABLED on an empty form (validation happens on submit, not by disabling) — BUG-FD-4. Expected kept as the intended behavior; tester will see the button enabled. | STAGING VIU 2026-07-20 staging LIVE VIU: BUG-FD-4 FIXED on staging: Add Fee button is DISABLED on an empty form (was enabled on qb). Live-observed (dev-wo-emptyform, disabled=true). | SV-8479/8480 deconfliction 2026-07-22: label sweep: navigation labels -&gt; 'Add Work Order Fee / Discount' / 'New Work Order Fee / Discount' (behavior/expected unchanged). | VIU 2026-07-22 LIVE: SV-8479 nav label 'Add Work Order Fee / Discount' confirmed present in the WO toolbar ⋯ menu; case behavior unchanged. Ev: wo/FD-WO-025-toolbar-menu.png.</t>
+          <t>not re-driven today (Apply-From-Template combobox present in dialog); templateId add path re-proven via API (FD-STACK-003) | WORDING+VIU 2026-07-13: rewritten to exact build labels (⋮ menu item 'Add Fee/Discount'; dialog 'Add new fee/discount'; fields 'Apply From Template'/'Name'/'Type'/'Calculation Type'/'$ Amount' or 'Percent %'/'$ Max Amount (Optional)'/'Taxable' toggle; whole-WO Calculation Type options = Flat Amount, % of Labor Total, % of Parts Total, % of Subtotal; buttons 'Add Fee'/'Add Discount'; sidebar card 'WO Fees &amp; Discounts'; preview empty prompt 'Enter an amount to see the impact.'). Captured live on WO S3-15960 (shots wo-01..wo-05). Dropdown label is exactly 'Apply From Template' (was 'Apply from template (optional)'). | SV-8479/8480 deconfliction 2026-07-22: label sweep: navigation labels -&gt; 'Add Work Order Fee / Discount' / 'New Work Order Fee / Discount' (behavior/expected unchanged). | VIU 2026-07-22 LIVE: SV-8479 nav label 'Add Work Order Fee / Discount' confirmed present in the WO toolbar ⋯ menu; case behavior unchanged. Ev: wo/FD-WO-025-toolbar-menu.png.</t>
         </is>
       </c>
     </row>
     <row r="153">
       <c r="A153" s="2" t="inlineStr">
         <is>
-          <t>FD-WO-006</t>
+          <t>FD-WO-005</t>
         </is>
       </c>
       <c r="B153" s="2" t="inlineStr">
         <is>
-          <t>C28429</t>
+          <t>C28428</t>
         </is>
       </c>
       <c r="C153" s="6" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/28429</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/28428</t>
         </is>
       </c>
       <c r="D153" s="2" t="inlineStr">
@@ -7824,12 +7824,12 @@
       </c>
       <c r="E153" s="2" t="inlineStr">
         <is>
-          <t>Verify Max Amount caps a percentage fee (20% on a $100 base with Max Amount $15 → +$15.00)</t>
+          <t>Verify the Add button stays disabled until Name, Type, Calculation Type and an Amount above 0 are all filled in</t>
         </is>
       </c>
       <c r="F153" s="2" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>Critical</t>
         </is>
       </c>
       <c r="G153" s="2" t="inlineStr">
@@ -7844,24 +7844,24 @@
       </c>
       <c r="I153" s="2" t="inlineStr">
         <is>
-          <t>20% of 170.76 (=34.15) capped at Max 15 -&gt; resolved exactly 15 | WORDING+VIU 2026-07-13: rewritten to exact build labels (⋮ menu item 'Add Fee/Discount'; dialog 'Add new fee/discount'; fields 'Apply From Template'/'Name'/'Type'/'Calculation Type'/'$ Amount' or 'Percent %'/'$ Max Amount (Optional)'/'Taxable' toggle; whole-WO Calculation Type options = Flat Amount, % of Labor Total, % of Parts Total, % of Subtotal; buttons 'Add Fee'/'Add Discount'; sidebar card 'WO Fees &amp; Discounts'; preview empty prompt 'Enter an amount to see the impact.'). Captured live on WO S3-15960 (shots wo-01..wo-05). The '$ Max Amount (Optional)' field appears only after a percentage method is chosen (confirmed live). | SV-8479/8480 deconfliction 2026-07-22: label sweep: navigation labels -&gt; 'Add Work Order Fee / Discount' / 'New Work Order Fee / Discount' (behavior/expected unchanged). | VIU 2026-07-22 LIVE: SV-8479 nav label 'Add Work Order Fee / Discount' confirmed present in the WO toolbar ⋯ menu; case behavior unchanged. Ev: wo/FD-WO-025-toolbar-menu.png.</t>
+          <t>CONFIRMED AGAIN: 'Add Fee' button ENABLED on an empty form (disabled-on-empty=false) — PO Q4=B defect persists | WORDING+VIU 2026-07-13: rewritten to exact build labels (⋮ menu item 'Add Fee/Discount'; dialog 'Add new fee/discount'; fields 'Apply From Template'/'Name'/'Type'/'Calculation Type'/'$ Amount' or 'Percent %'/'$ Max Amount (Optional)'/'Taxable' toggle; whole-WO Calculation Type options = Flat Amount, % of Labor Total, % of Parts Total, % of Subtotal; buttons 'Add Fee'/'Add Discount'; sidebar card 'WO Fees &amp; Discounts'; preview empty prompt 'Enter an amount to see the impact.'). Captured live on WO S3-15960 (shots wo-01..wo-05). DEVIATION re-confirmed live 2026-07-13: the 'Add Fee' button is ENABLED on an empty form (validation happens on submit, not by disabling) — BUG-FD-4. Expected kept as the intended behavior; tester will see the button enabled. | STAGING VIU 2026-07-20 staging LIVE VIU: BUG-FD-4 FIXED on staging: Add Fee button is DISABLED on an empty form (was enabled on qb). Live-observed (dev-wo-emptyform, disabled=true). | SV-8479/8480 deconfliction 2026-07-22: label sweep: navigation labels -&gt; 'Add Work Order Fee / Discount' / 'New Work Order Fee / Discount' (behavior/expected unchanged). | VIU 2026-07-22 LIVE: SV-8479 nav label 'Add Work Order Fee / Discount' confirmed present in the WO toolbar ⋯ menu; case behavior unchanged. Ev: wo/FD-WO-025-toolbar-menu.png.</t>
         </is>
       </c>
     </row>
     <row r="154">
       <c r="A154" s="2" t="inlineStr">
         <is>
-          <t>FD-WO-007</t>
+          <t>FD-WO-006</t>
         </is>
       </c>
       <c r="B154" s="2" t="inlineStr">
         <is>
-          <t>C28430</t>
+          <t>C28429</t>
         </is>
       </c>
       <c r="C154" s="6" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/28430</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/28429</t>
         </is>
       </c>
       <c r="D154" s="2" t="inlineStr">
@@ -7871,7 +7871,7 @@
       </c>
       <c r="E154" s="2" t="inlineStr">
         <is>
-          <t>Verify the confirm button label follows the Type (Add Fee vs Add Discount)</t>
+          <t>Verify Max Amount caps a percentage fee (20% on a $100 base with Max Amount $15 → +$15.00)</t>
         </is>
       </c>
       <c r="F154" s="2" t="inlineStr">
@@ -7891,24 +7891,24 @@
       </c>
       <c r="I154" s="2" t="inlineStr">
         <is>
-          <t>confirm label 'Add Fee' observed; Type-flip re-observed in batch-1 (not re-driven) | WORDING+VIU 2026-07-13: rewritten to exact build labels (⋮ menu item 'Add Fee/Discount'; dialog 'Add new fee/discount'; fields 'Apply From Template'/'Name'/'Type'/'Calculation Type'/'$ Amount' or 'Percent %'/'$ Max Amount (Optional)'/'Taxable' toggle; whole-WO Calculation Type options = Flat Amount, % of Labor Total, % of Parts Total, % of Subtotal; buttons 'Add Fee'/'Add Discount'; sidebar card 'WO Fees &amp; Discounts'; preview empty prompt 'Enter an amount to see the impact.'). Captured live on WO S3-15960 (shots wo-01..wo-05). | SV-8479/8480 deconfliction 2026-07-22: label sweep: navigation labels -&gt; 'Add Work Order Fee / Discount' / 'New Work Order Fee / Discount' (behavior/expected unchanged). | VIU 2026-07-22 LIVE: SV-8479 nav label 'Add Work Order Fee / Discount' confirmed present in the WO toolbar ⋯ menu; case behavior unchanged. Ev: wo/FD-WO-025-toolbar-menu.png.</t>
+          <t>20% of 170.76 (=34.15) capped at Max 15 -&gt; resolved exactly 15 | WORDING+VIU 2026-07-13: rewritten to exact build labels (⋮ menu item 'Add Fee/Discount'; dialog 'Add new fee/discount'; fields 'Apply From Template'/'Name'/'Type'/'Calculation Type'/'$ Amount' or 'Percent %'/'$ Max Amount (Optional)'/'Taxable' toggle; whole-WO Calculation Type options = Flat Amount, % of Labor Total, % of Parts Total, % of Subtotal; buttons 'Add Fee'/'Add Discount'; sidebar card 'WO Fees &amp; Discounts'; preview empty prompt 'Enter an amount to see the impact.'). Captured live on WO S3-15960 (shots wo-01..wo-05). The '$ Max Amount (Optional)' field appears only after a percentage method is chosen (confirmed live). | SV-8479/8480 deconfliction 2026-07-22: label sweep: navigation labels -&gt; 'Add Work Order Fee / Discount' / 'New Work Order Fee / Discount' (behavior/expected unchanged). | VIU 2026-07-22 LIVE: SV-8479 nav label 'Add Work Order Fee / Discount' confirmed present in the WO toolbar ⋯ menu; case behavior unchanged. Ev: wo/FD-WO-025-toolbar-menu.png.</t>
         </is>
       </c>
     </row>
     <row r="155">
       <c r="A155" s="2" t="inlineStr">
         <is>
-          <t>FD-WO-008</t>
+          <t>FD-WO-007</t>
         </is>
       </c>
       <c r="B155" s="2" t="inlineStr">
         <is>
-          <t>C28431</t>
+          <t>C28430</t>
         </is>
       </c>
       <c r="C155" s="6" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/28431</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/28430</t>
         </is>
       </c>
       <c r="D155" s="2" t="inlineStr">
@@ -7918,7 +7918,7 @@
       </c>
       <c r="E155" s="2" t="inlineStr">
         <is>
-          <t>Verify an empty Name blocks saving a whole-work-order fee/discount</t>
+          <t>Verify the confirm button label follows the Type (Add Fee vs Add Discount)</t>
         </is>
       </c>
       <c r="F155" s="2" t="inlineStr">
@@ -7938,24 +7938,24 @@
       </c>
       <c r="I155" s="2" t="inlineStr">
         <is>
-          <t>UI BLOCKS empty name (inline 'Name' required, dialog stays open, nothing saved). NOTE NEW FDBUG-16: the RAW API now ACCEPTS an empty-name adjustment (201; was 400 in batch-3) — BE validation regression, FE still guards | WORDING+VIU 2026-07-13: rewritten to exact build labels (⋮ menu item 'Add Fee/Discount'; dialog 'Add new fee/discount'; fields 'Apply From Template'/'Name'/'Type'/'Calculation Type'/'$ Amount' or 'Percent %'/'$ Max Amount (Optional)'/'Taxable' toggle; whole-WO Calculation Type options = Flat Amount, % of Labor Total, % of Parts Total, % of Subtotal; buttons 'Add Fee'/'Add Discount'; sidebar card 'WO Fees &amp; Discounts'; preview empty prompt 'Enter an amount to see the impact.'). Captured live on WO S3-15960 (shots wo-01..wo-05). (Note: the raw back-end will accept an empty name — FDBUG-16 — but the on-screen dialog blocks it, which is what a manual tester sees.) | SV-8479/8480 deconfliction 2026-07-22: label sweep: navigation labels -&gt; 'Add Work Order Fee / Discount' / 'New Work Order Fee / Discount' (behavior/expected unchanged). | VIU 2026-07-22 LIVE: SV-8479 nav label 'Add Work Order Fee / Discount' confirmed present in the WO toolbar ⋯ menu; case behavior unchanged. Ev: wo/FD-WO-025-toolbar-menu.png.</t>
+          <t>confirm label 'Add Fee' observed; Type-flip re-observed in batch-1 (not re-driven) | WORDING+VIU 2026-07-13: rewritten to exact build labels (⋮ menu item 'Add Fee/Discount'; dialog 'Add new fee/discount'; fields 'Apply From Template'/'Name'/'Type'/'Calculation Type'/'$ Amount' or 'Percent %'/'$ Max Amount (Optional)'/'Taxable' toggle; whole-WO Calculation Type options = Flat Amount, % of Labor Total, % of Parts Total, % of Subtotal; buttons 'Add Fee'/'Add Discount'; sidebar card 'WO Fees &amp; Discounts'; preview empty prompt 'Enter an amount to see the impact.'). Captured live on WO S3-15960 (shots wo-01..wo-05). | SV-8479/8480 deconfliction 2026-07-22: label sweep: navigation labels -&gt; 'Add Work Order Fee / Discount' / 'New Work Order Fee / Discount' (behavior/expected unchanged). | VIU 2026-07-22 LIVE: SV-8479 nav label 'Add Work Order Fee / Discount' confirmed present in the WO toolbar ⋯ menu; case behavior unchanged. Ev: wo/FD-WO-025-toolbar-menu.png.</t>
         </is>
       </c>
     </row>
     <row r="156">
       <c r="A156" s="2" t="inlineStr">
         <is>
-          <t>FD-WO-009</t>
+          <t>FD-WO-008</t>
         </is>
       </c>
       <c r="B156" s="2" t="inlineStr">
         <is>
-          <t>C28432</t>
+          <t>C28431</t>
         </is>
       </c>
       <c r="C156" s="6" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/28432</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/28431</t>
         </is>
       </c>
       <c r="D156" s="2" t="inlineStr">
@@ -7965,7 +7965,7 @@
       </c>
       <c r="E156" s="2" t="inlineStr">
         <is>
-          <t>Verify an empty or zero amount blocks saving a whole-work-order fee/discount</t>
+          <t>Verify an empty Name blocks saving a whole-work-order fee/discount</t>
         </is>
       </c>
       <c r="F156" s="2" t="inlineStr">
@@ -7985,24 +7985,24 @@
       </c>
       <c r="I156" s="2" t="inlineStr">
         <is>
-          <t>amount 0 -&gt; 400 at API; UI validates on submit | WORDING+VIU 2026-07-13: rewritten to exact build labels (⋮ menu item 'Add Fee/Discount'; dialog 'Add new fee/discount'; fields 'Apply From Template'/'Name'/'Type'/'Calculation Type'/'$ Amount' or 'Percent %'/'$ Max Amount (Optional)'/'Taxable' toggle; whole-WO Calculation Type options = Flat Amount, % of Labor Total, % of Parts Total, % of Subtotal; buttons 'Add Fee'/'Add Discount'; sidebar card 'WO Fees &amp; Discounts'; preview empty prompt 'Enter an amount to see the impact.'). Captured live on WO S3-15960 (shots wo-01..wo-05). | SV-8479/8480 deconfliction 2026-07-22: label sweep: navigation labels -&gt; 'Add Work Order Fee / Discount' / 'New Work Order Fee / Discount' (behavior/expected unchanged). | VIU 2026-07-22 LIVE: SV-8479 nav label 'Add Work Order Fee / Discount' confirmed present in the WO toolbar ⋯ menu; case behavior unchanged. Ev: wo/FD-WO-025-toolbar-menu.png.</t>
+          <t>UI BLOCKS empty name (inline 'Name' required, dialog stays open, nothing saved). NOTE NEW FDBUG-16: the RAW API now ACCEPTS an empty-name adjustment (201; was 400 in batch-3) — BE validation regression, FE still guards | WORDING+VIU 2026-07-13: rewritten to exact build labels (⋮ menu item 'Add Fee/Discount'; dialog 'Add new fee/discount'; fields 'Apply From Template'/'Name'/'Type'/'Calculation Type'/'$ Amount' or 'Percent %'/'$ Max Amount (Optional)'/'Taxable' toggle; whole-WO Calculation Type options = Flat Amount, % of Labor Total, % of Parts Total, % of Subtotal; buttons 'Add Fee'/'Add Discount'; sidebar card 'WO Fees &amp; Discounts'; preview empty prompt 'Enter an amount to see the impact.'). Captured live on WO S3-15960 (shots wo-01..wo-05). (Note: the raw back-end will accept an empty name — FDBUG-16 — but the on-screen dialog blocks it, which is what a manual tester sees.) | SV-8479/8480 deconfliction 2026-07-22: label sweep: navigation labels -&gt; 'Add Work Order Fee / Discount' / 'New Work Order Fee / Discount' (behavior/expected unchanged). | VIU 2026-07-22 LIVE: SV-8479 nav label 'Add Work Order Fee / Discount' confirmed present in the WO toolbar ⋯ menu; case behavior unchanged. Ev: wo/FD-WO-025-toolbar-menu.png.</t>
         </is>
       </c>
     </row>
     <row r="157">
       <c r="A157" s="2" t="inlineStr">
         <is>
-          <t>FD-WO-010</t>
+          <t>FD-WO-009</t>
         </is>
       </c>
       <c r="B157" s="2" t="inlineStr">
         <is>
-          <t>C28433</t>
+          <t>C28432</t>
         </is>
       </c>
       <c r="C157" s="6" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/28433</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/28432</t>
         </is>
       </c>
       <c r="D157" s="2" t="inlineStr">
@@ -8012,7 +8012,7 @@
       </c>
       <c r="E157" s="2" t="inlineStr">
         <is>
-          <t>Verify a percentage discount over 100% is rejected while a percentage fee has no upper limit</t>
+          <t>Verify an empty or zero amount blocks saving a whole-work-order fee/discount</t>
         </is>
       </c>
       <c r="F157" s="2" t="inlineStr">
@@ -8032,24 +8032,24 @@
       </c>
       <c r="I157" s="2" t="inlineStr">
         <is>
-          <t>discount 150% -&gt; 400 'A percentage discount cannot exceed 100%.'; fee 150% -&gt; 201 | WORDING+VIU 2026-07-13: rewritten to exact build labels (⋮ menu item 'Add Fee/Discount'; dialog 'Add new fee/discount'; fields 'Apply From Template'/'Name'/'Type'/'Calculation Type'/'$ Amount' or 'Percent %'/'$ Max Amount (Optional)'/'Taxable' toggle; whole-WO Calculation Type options = Flat Amount, % of Labor Total, % of Parts Total, % of Subtotal; buttons 'Add Fee'/'Add Discount'; sidebar card 'WO Fees &amp; Discounts'; preview empty prompt 'Enter an amount to see the impact.'). Captured live on WO S3-15960 (shots wo-01..wo-05). | SV-8479/8480 deconfliction 2026-07-22: label sweep: navigation labels -&gt; 'Add Work Order Fee / Discount' / 'New Work Order Fee / Discount' (behavior/expected unchanged). | VIU 2026-07-22 LIVE: SV-8479 nav label 'Add Work Order Fee / Discount' confirmed present in the WO toolbar ⋯ menu; case behavior unchanged. Ev: wo/FD-WO-025-toolbar-menu.png.</t>
+          <t>amount 0 -&gt; 400 at API; UI validates on submit | WORDING+VIU 2026-07-13: rewritten to exact build labels (⋮ menu item 'Add Fee/Discount'; dialog 'Add new fee/discount'; fields 'Apply From Template'/'Name'/'Type'/'Calculation Type'/'$ Amount' or 'Percent %'/'$ Max Amount (Optional)'/'Taxable' toggle; whole-WO Calculation Type options = Flat Amount, % of Labor Total, % of Parts Total, % of Subtotal; buttons 'Add Fee'/'Add Discount'; sidebar card 'WO Fees &amp; Discounts'; preview empty prompt 'Enter an amount to see the impact.'). Captured live on WO S3-15960 (shots wo-01..wo-05). | SV-8479/8480 deconfliction 2026-07-22: label sweep: navigation labels -&gt; 'Add Work Order Fee / Discount' / 'New Work Order Fee / Discount' (behavior/expected unchanged). | VIU 2026-07-22 LIVE: SV-8479 nav label 'Add Work Order Fee / Discount' confirmed present in the WO toolbar ⋯ menu; case behavior unchanged. Ev: wo/FD-WO-025-toolbar-menu.png.</t>
         </is>
       </c>
     </row>
     <row r="158">
       <c r="A158" s="2" t="inlineStr">
         <is>
-          <t>FD-WO-011</t>
+          <t>FD-WO-010</t>
         </is>
       </c>
       <c r="B158" s="2" t="inlineStr">
         <is>
-          <t>C28434</t>
+          <t>C28433</t>
         </is>
       </c>
       <c r="C158" s="6" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/28434</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/28433</t>
         </is>
       </c>
       <c r="D158" s="2" t="inlineStr">
@@ -8059,12 +8059,12 @@
       </c>
       <c r="E158" s="2" t="inlineStr">
         <is>
-          <t>Verify a whole-work-order percentage method uses the correct base (% of Subtotal example)</t>
+          <t>Verify a percentage discount over 100% is rejected while a percentage fee has no upper limit</t>
         </is>
       </c>
       <c r="F158" s="2" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="G158" s="2" t="inlineStr">
@@ -8079,24 +8079,24 @@
       </c>
       <c r="I158" s="2" t="inlineStr">
         <is>
-          <t>pct_subtotal resolves on the WO subtotal EXCLUDING whole-WO adjustments (10% of 182.76-sub -&gt; 17.08 = 10% of 170.76 line total) | WORDING+VIU 2026-07-13: rewritten to exact build labels (⋮ menu item 'Add Fee/Discount'; dialog 'Add new fee/discount'; fields 'Apply From Template'/'Name'/'Type'/'Calculation Type'/'$ Amount' or 'Percent %'/'$ Max Amount (Optional)'/'Taxable' toggle; whole-WO Calculation Type options = Flat Amount, % of Labor Total, % of Parts Total, % of Subtotal; buttons 'Add Fee'/'Add Discount'; sidebar card 'WO Fees &amp; Discounts'; preview empty prompt 'Enter an amount to see the impact.'). Captured live on WO S3-15960 (shots wo-01..wo-05). Calculation Type options confirmed live (exactly the 4 listed; no '% of Grand Total'). | SV-8479/8480 deconfliction 2026-07-22: label sweep: navigation labels -&gt; 'Add Work Order Fee / Discount' / 'New Work Order Fee / Discount' (behavior/expected unchanged). | VIU 2026-07-22 LIVE: SV-8479 nav label 'Add Work Order Fee / Discount' confirmed present in the WO toolbar ⋯ menu; case behavior unchanged. Ev: wo/FD-WO-025-toolbar-menu.png.</t>
+          <t>discount 150% -&gt; 400 'A percentage discount cannot exceed 100%.'; fee 150% -&gt; 201 | WORDING+VIU 2026-07-13: rewritten to exact build labels (⋮ menu item 'Add Fee/Discount'; dialog 'Add new fee/discount'; fields 'Apply From Template'/'Name'/'Type'/'Calculation Type'/'$ Amount' or 'Percent %'/'$ Max Amount (Optional)'/'Taxable' toggle; whole-WO Calculation Type options = Flat Amount, % of Labor Total, % of Parts Total, % of Subtotal; buttons 'Add Fee'/'Add Discount'; sidebar card 'WO Fees &amp; Discounts'; preview empty prompt 'Enter an amount to see the impact.'). Captured live on WO S3-15960 (shots wo-01..wo-05). | SV-8479/8480 deconfliction 2026-07-22: label sweep: navigation labels -&gt; 'Add Work Order Fee / Discount' / 'New Work Order Fee / Discount' (behavior/expected unchanged). | VIU 2026-07-22 LIVE: SV-8479 nav label 'Add Work Order Fee / Discount' confirmed present in the WO toolbar ⋯ menu; case behavior unchanged. Ev: wo/FD-WO-025-toolbar-menu.png.</t>
         </is>
       </c>
     </row>
     <row r="159">
       <c r="A159" s="2" t="inlineStr">
         <is>
-          <t>FD-WO-012</t>
+          <t>FD-WO-011</t>
         </is>
       </c>
       <c r="B159" s="2" t="inlineStr">
         <is>
-          <t>C28435</t>
+          <t>C28434</t>
         </is>
       </c>
       <c r="C159" s="6" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/28435</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/28434</t>
         </is>
       </c>
       <c r="D159" s="2" t="inlineStr">
@@ -8106,7 +8106,7 @@
       </c>
       <c r="E159" s="2" t="inlineStr">
         <is>
-          <t>Verify Add Work Order Fee / Discount is hidden and blocked on an Invoiced or Paid work order</t>
+          <t>Verify a whole-work-order percentage method uses the correct base (% of Subtotal example)</t>
         </is>
       </c>
       <c r="F159" s="2" t="inlineStr">
@@ -8126,24 +8126,24 @@
       </c>
       <c r="I159" s="2" t="inlineStr">
         <is>
-          <t>add on Invoiced WO -&gt; 409 'Adjustments cannot be changed on an invoiced or paid work order.'; edit also 409 | WORDING+VIU 2026-07-13: rewritten to exact build labels (⋮ menu item 'Add Fee/Discount'; dialog 'Add new fee/discount'; fields 'Apply From Template'/'Name'/'Type'/'Calculation Type'/'$ Amount' or 'Percent %'/'$ Max Amount (Optional)'/'Taxable' toggle; whole-WO Calculation Type options = Flat Amount, % of Labor Total, % of Parts Total, % of Subtotal; buttons 'Add Fee'/'Add Discount'; sidebar card 'WO Fees &amp; Discounts'; preview empty prompt 'Enter an amount to see the impact.'). Captured live on WO S3-15960 (shots wo-01..wo-05). | SV-8479/8480 deconfliction 2026-07-22: label sweep: navigation labels -&gt; 'Add Work Order Fee / Discount' / 'New Work Order Fee / Discount' (behavior/expected unchanged). | VIU 2026-07-22 LIVE: SV-8479 nav label 'Add Work Order Fee / Discount' confirmed present in the WO toolbar ⋯ menu; case behavior unchanged. Ev: wo/FD-WO-025-toolbar-menu.png.</t>
+          <t>pct_subtotal resolves on the WO subtotal EXCLUDING whole-WO adjustments (10% of 182.76-sub -&gt; 17.08 = 10% of 170.76 line total) | WORDING+VIU 2026-07-13: rewritten to exact build labels (⋮ menu item 'Add Fee/Discount'; dialog 'Add new fee/discount'; fields 'Apply From Template'/'Name'/'Type'/'Calculation Type'/'$ Amount' or 'Percent %'/'$ Max Amount (Optional)'/'Taxable' toggle; whole-WO Calculation Type options = Flat Amount, % of Labor Total, % of Parts Total, % of Subtotal; buttons 'Add Fee'/'Add Discount'; sidebar card 'WO Fees &amp; Discounts'; preview empty prompt 'Enter an amount to see the impact.'). Captured live on WO S3-15960 (shots wo-01..wo-05). Calculation Type options confirmed live (exactly the 4 listed; no '% of Grand Total'). | SV-8479/8480 deconfliction 2026-07-22: label sweep: navigation labels -&gt; 'Add Work Order Fee / Discount' / 'New Work Order Fee / Discount' (behavior/expected unchanged). | VIU 2026-07-22 LIVE: SV-8479 nav label 'Add Work Order Fee / Discount' confirmed present in the WO toolbar ⋯ menu; case behavior unchanged. Ev: wo/FD-WO-025-toolbar-menu.png.</t>
         </is>
       </c>
     </row>
     <row r="160">
       <c r="A160" s="2" t="inlineStr">
         <is>
-          <t>FD-WO-014</t>
+          <t>FD-WO-012</t>
         </is>
       </c>
       <c r="B160" s="2" t="inlineStr">
         <is>
-          <t>C28437</t>
+          <t>C28435</t>
         </is>
       </c>
       <c r="C160" s="6" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/28437</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/28435</t>
         </is>
       </c>
       <c r="D160" s="2" t="inlineStr">
@@ -8153,12 +8153,12 @@
       </c>
       <c r="E160" s="2" t="inlineStr">
         <is>
-          <t>Verify the preview shows the empty-amount prompt before an amount is entered</t>
+          <t>Verify Add Work Order Fee / Discount is hidden and blocked on an Invoiced or Paid work order</t>
         </is>
       </c>
       <c r="F160" s="2" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>High</t>
         </is>
       </c>
       <c r="G160" s="2" t="inlineStr">
@@ -8173,24 +8173,24 @@
       </c>
       <c r="I160" s="2" t="inlineStr">
         <is>
-          <t>'Enter an amount to see the impact.' prompt present in the re-driven dialog | WORDING+VIU 2026-07-13: rewritten to exact build labels (⋮ menu item 'Add Fee/Discount'; dialog 'Add new fee/discount'; fields 'Apply From Template'/'Name'/'Type'/'Calculation Type'/'$ Amount' or 'Percent %'/'$ Max Amount (Optional)'/'Taxable' toggle; whole-WO Calculation Type options = Flat Amount, % of Labor Total, % of Parts Total, % of Subtotal; buttons 'Add Fee'/'Add Discount'; sidebar card 'WO Fees &amp; Discounts'; preview empty prompt 'Enter an amount to see the impact.'). Captured live on WO S3-15960 (shots wo-01..wo-05). Exact prompt text 'Enter an amount to see the impact.' confirmed live (shot wo-03). | SV-8479/8480 deconfliction 2026-07-22: label sweep: navigation labels -&gt; 'Add Work Order Fee / Discount' / 'New Work Order Fee / Discount' (behavior/expected unchanged). | VIU 2026-07-22 LIVE: SV-8479 nav label 'Add Work Order Fee / Discount' confirmed present in the WO toolbar ⋯ menu; case behavior unchanged. Ev: wo/FD-WO-025-toolbar-menu.png.</t>
+          <t>add on Invoiced WO -&gt; 409 'Adjustments cannot be changed on an invoiced or paid work order.'; edit also 409 | WORDING+VIU 2026-07-13: rewritten to exact build labels (⋮ menu item 'Add Fee/Discount'; dialog 'Add new fee/discount'; fields 'Apply From Template'/'Name'/'Type'/'Calculation Type'/'$ Amount' or 'Percent %'/'$ Max Amount (Optional)'/'Taxable' toggle; whole-WO Calculation Type options = Flat Amount, % of Labor Total, % of Parts Total, % of Subtotal; buttons 'Add Fee'/'Add Discount'; sidebar card 'WO Fees &amp; Discounts'; preview empty prompt 'Enter an amount to see the impact.'). Captured live on WO S3-15960 (shots wo-01..wo-05). | SV-8479/8480 deconfliction 2026-07-22: label sweep: navigation labels -&gt; 'Add Work Order Fee / Discount' / 'New Work Order Fee / Discount' (behavior/expected unchanged). | VIU 2026-07-22 LIVE: SV-8479 nav label 'Add Work Order Fee / Discount' confirmed present in the WO toolbar ⋯ menu; case behavior unchanged. Ev: wo/FD-WO-025-toolbar-menu.png.</t>
         </is>
       </c>
     </row>
     <row r="161">
       <c r="A161" s="2" t="inlineStr">
         <is>
-          <t>FD-WO-015</t>
+          <t>FD-WO-013</t>
         </is>
       </c>
       <c r="B161" s="2" t="inlineStr">
         <is>
-          <t>C28438</t>
+          <t>C28436</t>
         </is>
       </c>
       <c r="C161" s="6" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/28438</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/28436</t>
         </is>
       </c>
       <c r="D161" s="2" t="inlineStr">
@@ -8200,7 +8200,7 @@
       </c>
       <c r="E161" s="2" t="inlineStr">
         <is>
-          <t>Verify the preview amount is signed for a fee (+) vs a discount (−)</t>
+          <t>Verify the whole-work-order 'Add Work Order Fee / Discount' option is hidden without Work Orders: Create &amp; Edit</t>
         </is>
       </c>
       <c r="F161" s="2" t="inlineStr">
@@ -8220,24 +8220,24 @@
       </c>
       <c r="I161" s="2" t="inlineStr">
         <is>
-          <t>preview row '+$5.00' with new-subtotal line re-observed; color/sign convention from batch-1 (not re-checked) | WORDING+VIU 2026-07-13: rewritten to exact build labels (⋮ menu item 'Add Fee/Discount'; dialog 'Add new fee/discount'; fields 'Apply From Template'/'Name'/'Type'/'Calculation Type'/'$ Amount' or 'Percent %'/'$ Max Amount (Optional)'/'Taxable' toggle; whole-WO Calculation Type options = Flat Amount, % of Labor Total, % of Parts Total, % of Subtotal; buttons 'Add Fee'/'Add Discount'; sidebar card 'WO Fees &amp; Discounts'; preview empty prompt 'Enter an amount to see the impact.'). Captured live on WO S3-15960 (shots wo-01..wo-05). Kept to sign only; the exact fee/discount colours were not re-captured this pass. | SV-8479/8480 deconfliction 2026-07-22: label sweep: navigation labels -&gt; 'Add Work Order Fee / Discount' / 'New Work Order Fee / Discount' (behavior/expected unchanged). | VIU 2026-07-22 LIVE: SV-8479 nav label 'Add Work Order Fee / Discount' confirmed present in the WO toolbar ⋯ menu; case behavior unchanged. Ev: wo/FD-WO-025-toolbar-menu.png.</t>
+          <t>BUG-FD-3 stands on prior evidence; NOT re-testable today: the shared-env Technician role was CHANGED (now includes workOrdersCreateAndEdit+workOrdersDelete, 8 perms vs matrix 6) so tech's 201 is now legitimate; no login lacking the perm exists | WORDING+VIU 2026-07-13: rewritten to exact build labels (⋮ menu item 'Add Fee/Discount'; dialog 'Add new fee/discount'; fields 'Apply From Template'/'Name'/'Type'/'Calculation Type'/'$ Amount' or 'Percent %'/'$ Max Amount (Optional)'/'Taxable' toggle; whole-WO Calculation Type options = Flat Amount, % of Labor Total, % of Parts Total, % of Subtotal; buttons 'Add Fee'/'Add Discount'; sidebar card 'WO Fees &amp; Discounts'; preview empty prompt 'Enter an amount to see the impact.'). Captured live on WO S3-15960 (shots wo-01..wo-05). DEVIATION (BUG-FD-3: the hide is front-end only; the back-end does not block the write). NOT re-testable this run — the Technician role has drifted on the shared qb env; re-derive the roles matrix before re-checking. | SV-8479/8480 deconfliction 2026-07-22: label updated 'Add Fee/Discount' -&gt; 'Add Work Order Fee / Discount' (item 10); permission behavior unchanged. | VIU 2026-07-22 LIVE: toolbar label 'Add Work Order Fee / Discount' confirmed present (admin); permission-negative status unchanged — role-negative not re-driven this UI batch. | FE-BLOCK/BE-ALLOW PASS 2026-07-24 (user-authorized, Standing Rule 24): flipped VIU-Deviation -&gt; VIU-Verified (PASS). The whole-WO 'Add Work Order Fee / Discount' control being hidden for a role lacking Work Orders: Create &amp; Edit IS the tester-facing pass criterion; the FE-only enforcement (the back-end/API POST /api/work-orders/adjustments/add still returns 201 for such a role — pass-A evidence + impersonation) is ACCEPTED by product policy, not a bug. Added the plain tester line to Expected (Rule 7). This is FE-block/BE-allow = PASS (not the inverse FE-exposure defect).</t>
         </is>
       </c>
     </row>
     <row r="162">
       <c r="A162" s="2" t="inlineStr">
         <is>
-          <t>FD-WO-016</t>
+          <t>FD-WO-014</t>
         </is>
       </c>
       <c r="B162" s="2" t="inlineStr">
         <is>
-          <t>C29441</t>
+          <t>C28437</t>
         </is>
       </c>
       <c r="C162" s="6" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/29441</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/28437</t>
         </is>
       </c>
       <c r="D162" s="2" t="inlineStr">
@@ -8247,7 +8247,7 @@
       </c>
       <c r="E162" s="2" t="inlineStr">
         <is>
-          <t>Verify the Add/Edit fee-or-discount dialog shows the tax-jurisdiction note below the Taxable Yes/No dropdown</t>
+          <t>Verify the preview shows the empty-amount prompt before an amount is entered</t>
         </is>
       </c>
       <c r="F162" s="2" t="inlineStr">
@@ -8267,34 +8267,34 @@
       </c>
       <c r="I162" s="2" t="inlineStr">
         <is>
-          <t>administration/adjustment-templates loads; Finance-only user has NO F&amp;D nav, FINANCE=Payment Methods only, direct route bounces to /workorders. viu_status VIU-Verified re-confirmed. Ev build/fees-discounts/viu-sv8456-2026-07-22/ (01-settings-landing, 02-new-dialog, 03-customer-fd-tab, SVC-*, FIN-*).</t>
+          <t>'Enter an amount to see the impact.' prompt present in the re-driven dialog | WORDING+VIU 2026-07-13: rewritten to exact build labels (⋮ menu item 'Add Fee/Discount'; dialog 'Add new fee/discount'; fields 'Apply From Template'/'Name'/'Type'/'Calculation Type'/'$ Amount' or 'Percent %'/'$ Max Amount (Optional)'/'Taxable' toggle; whole-WO Calculation Type options = Flat Amount, % of Labor Total, % of Parts Total, % of Subtotal; buttons 'Add Fee'/'Add Discount'; sidebar card 'WO Fees &amp; Discounts'; preview empty prompt 'Enter an amount to see the impact.'). Captured live on WO S3-15960 (shots wo-01..wo-05). Exact prompt text 'Enter an amount to see the impact.' confirmed live (shot wo-03). | SV-8479/8480 deconfliction 2026-07-22: label sweep: navigation labels -&gt; 'Add Work Order Fee / Discount' / 'New Work Order Fee / Discount' (behavior/expected unchanged). | VIU 2026-07-22 LIVE: SV-8479 nav label 'Add Work Order Fee / Discount' confirmed present in the WO toolbar ⋯ menu; case behavior unchanged. Ev: wo/FD-WO-025-toolbar-menu.png.</t>
         </is>
       </c>
     </row>
     <row r="163">
       <c r="A163" s="2" t="inlineStr">
         <is>
-          <t>FD-WO-018</t>
+          <t>FD-WO-015</t>
         </is>
       </c>
       <c r="B163" s="2" t="inlineStr">
         <is>
-          <t>C30619</t>
+          <t>C28438</t>
         </is>
       </c>
       <c r="C163" s="6" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/30619</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/28438</t>
         </is>
       </c>
       <c r="D163" s="2" t="inlineStr">
         <is>
-          <t>Work Order / Parts — Part-line Fee/Discount</t>
+          <t>Work Order — Whole-WO Fee/Discount</t>
         </is>
       </c>
       <c r="E163" s="2" t="inlineStr">
         <is>
-          <t>Verify the work-order part row three-dot menu item reads 'Add Part Fee / Discount'</t>
+          <t>Verify the preview amount is signed for a fee (+) vs a discount (−)</t>
         </is>
       </c>
       <c r="F163" s="2" t="inlineStr">
@@ -8314,34 +8314,34 @@
       </c>
       <c r="I163" s="2" t="inlineStr">
         <is>
-          <t>. | VIU 2026-07-22 LIVE: part-row ⋮ menu = 'Move', 'Add Part Fee / Discount' (label correct; opens part fee/discount dialog). 'Return' state-gated — the seeded part was 'Auth To Order' (not received) so Return was not offered; Return appears only for returnable parts. Ev: wo/FD-WO-018-part-menu.png.</t>
+          <t>preview row '+$5.00' with new-subtotal line re-observed; color/sign convention from batch-1 (not re-checked) | WORDING+VIU 2026-07-13: rewritten to exact build labels (⋮ menu item 'Add Fee/Discount'; dialog 'Add new fee/discount'; fields 'Apply From Template'/'Name'/'Type'/'Calculation Type'/'$ Amount' or 'Percent %'/'$ Max Amount (Optional)'/'Taxable' toggle; whole-WO Calculation Type options = Flat Amount, % of Labor Total, % of Parts Total, % of Subtotal; buttons 'Add Fee'/'Add Discount'; sidebar card 'WO Fees &amp; Discounts'; preview empty prompt 'Enter an amount to see the impact.'). Captured live on WO S3-15960 (shots wo-01..wo-05). Kept to sign only; the exact fee/discount colours were not re-captured this pass. | SV-8479/8480 deconfliction 2026-07-22: label sweep: navigation labels -&gt; 'Add Work Order Fee / Discount' / 'New Work Order Fee / Discount' (behavior/expected unchanged). | VIU 2026-07-22 LIVE: SV-8479 nav label 'Add Work Order Fee / Discount' confirmed present in the WO toolbar ⋯ menu; case behavior unchanged. Ev: wo/FD-WO-025-toolbar-menu.png.</t>
         </is>
       </c>
     </row>
     <row r="164">
       <c r="A164" s="2" t="inlineStr">
         <is>
-          <t>FD-WO-021</t>
+          <t>FD-WO-016</t>
         </is>
       </c>
       <c r="B164" s="2" t="inlineStr">
         <is>
-          <t>C30620</t>
+          <t>C29441</t>
         </is>
       </c>
       <c r="C164" s="6" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/30620</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/29441</t>
         </is>
       </c>
       <c r="D164" s="2" t="inlineStr">
         <is>
-          <t>Work Order — Sidebar 'Work Order Fee / Discount' card</t>
+          <t>Work Order — Whole-WO Fee/Discount</t>
         </is>
       </c>
       <c r="E164" s="2" t="inlineStr">
         <is>
-          <t>Verify the Work Order Fees &amp; Discounts card shows the disclaimer 'Applies to the whole work order, after all other fees &amp; discounts.'</t>
+          <t>Verify the Add/Edit fee-or-discount dialog shows the tax-jurisdiction note below the Taxable Yes/No dropdown</t>
         </is>
       </c>
       <c r="F164" s="2" t="inlineStr">
@@ -8361,34 +8361,34 @@
       </c>
       <c r="I164" s="2" t="inlineStr">
         <is>
-          <t>s a mockup. QA passed on staging 2026-07-22 (✅). | VIU 2026-07-22 LIVE: Work Order Fees &amp; Discounts card shows disclaimer exactly 'Applies to the whole work order, after all other fees &amp; discounts.' below the adjustment list. Ev: wo/FD-FIN-004-FD-WO-021-card-financialinfo.png, wo/lines-bodytext.txt.</t>
+          <t>administration/adjustment-templates loads; Finance-only user has NO F&amp;D nav, FINANCE=Payment Methods only, direct route bounces to /workorders. viu_status VIU-Verified re-confirmed. Ev build/fees-discounts/viu-sv8456-2026-07-22/ (01-settings-landing, 02-new-dialog, 03-customer-fd-tab, SVC-*, FIN-*).</t>
         </is>
       </c>
     </row>
     <row r="165">
       <c r="A165" s="2" t="inlineStr">
         <is>
-          <t>FD-WO-025</t>
+          <t>FD-WO-018</t>
         </is>
       </c>
       <c r="B165" s="2" t="inlineStr">
         <is>
-          <t>C30621</t>
+          <t>C30619</t>
         </is>
       </c>
       <c r="C165" s="6" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/30621</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/30619</t>
         </is>
       </c>
       <c r="D165" s="2" t="inlineStr">
         <is>
-          <t>Work Order — Whole-WO Fee/Discount</t>
+          <t>Work Order / Parts — Part-line Fee/Discount</t>
         </is>
       </c>
       <c r="E165" s="2" t="inlineStr">
         <is>
-          <t>Verify the work order toolbar three-dot menu item reads 'Add Work Order Fee / Discount'</t>
+          <t>Verify the work-order part row three-dot menu item reads 'Add Part Fee / Discount'</t>
         </is>
       </c>
       <c r="F165" s="2" t="inlineStr">
@@ -8408,52 +8408,146 @@
       </c>
       <c r="I165" s="2" t="inlineStr">
         <is>
-          <t>6-07-22 LIVE: toolbar ⋯ menu label 'Add Work Order Fee / Discount' correct; opens whole-WO fee/discount dialog. WORDING CORRECTED — observed order is 'Audit Log' -&gt; 'Timesheets (N)' -&gt; 'Add Work Order Fee / Discount' -&gt; 'Delete Work Order' (Add is 3rd, NOT at top). Ev: wo/FD-WO-025-toolbar-menu.png.</t>
+          <t>. | VIU 2026-07-22 LIVE: part-row ⋮ menu = 'Move', 'Add Part Fee / Discount' (label correct; opens part fee/discount dialog). 'Return' state-gated — the seeded part was 'Auth To Order' (not received) so Return was not offered; Return appears only for returnable parts. Ev: wo/FD-WO-018-part-menu.png.</t>
         </is>
       </c>
     </row>
     <row r="166">
       <c r="A166" s="2" t="inlineStr">
         <is>
+          <t>FD-WO-021</t>
+        </is>
+      </c>
+      <c r="B166" s="2" t="inlineStr">
+        <is>
+          <t>C30620</t>
+        </is>
+      </c>
+      <c r="C166" s="6" t="inlineStr">
+        <is>
+          <t>https://shopview.testrail.io/index.php?/cases/view/30620</t>
+        </is>
+      </c>
+      <c r="D166" s="2" t="inlineStr">
+        <is>
+          <t>Work Order — Sidebar 'Work Order Fee / Discount' card</t>
+        </is>
+      </c>
+      <c r="E166" s="2" t="inlineStr">
+        <is>
+          <t>Verify the Work Order Fees &amp; Discounts card shows the disclaimer 'Applies to the whole work order, after all other fees &amp; discounts.'</t>
+        </is>
+      </c>
+      <c r="F166" s="2" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="G166" s="2" t="inlineStr">
+        <is>
+          <t>VIU-Verified</t>
+        </is>
+      </c>
+      <c r="H166" s="2" t="inlineStr">
+        <is>
+          <t>No action needed — passed.</t>
+        </is>
+      </c>
+      <c r="I166" s="2" t="inlineStr">
+        <is>
+          <t>s a mockup. QA passed on staging 2026-07-22 (✅). | VIU 2026-07-22 LIVE: Work Order Fees &amp; Discounts card shows disclaimer exactly 'Applies to the whole work order, after all other fees &amp; discounts.' below the adjustment list. Ev: wo/FD-FIN-004-FD-WO-021-card-financialinfo.png, wo/lines-bodytext.txt.</t>
+        </is>
+      </c>
+    </row>
+    <row r="167">
+      <c r="A167" s="2" t="inlineStr">
+        <is>
+          <t>FD-WO-025</t>
+        </is>
+      </c>
+      <c r="B167" s="2" t="inlineStr">
+        <is>
+          <t>C30621</t>
+        </is>
+      </c>
+      <c r="C167" s="6" t="inlineStr">
+        <is>
+          <t>https://shopview.testrail.io/index.php?/cases/view/30621</t>
+        </is>
+      </c>
+      <c r="D167" s="2" t="inlineStr">
+        <is>
+          <t>Work Order — Whole-WO Fee/Discount</t>
+        </is>
+      </c>
+      <c r="E167" s="2" t="inlineStr">
+        <is>
+          <t>Verify the work order toolbar three-dot menu item reads 'Add Work Order Fee / Discount'</t>
+        </is>
+      </c>
+      <c r="F167" s="2" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="G167" s="2" t="inlineStr">
+        <is>
+          <t>VIU-Verified</t>
+        </is>
+      </c>
+      <c r="H167" s="2" t="inlineStr">
+        <is>
+          <t>No action needed — passed.</t>
+        </is>
+      </c>
+      <c r="I167" s="2" t="inlineStr">
+        <is>
+          <t>6-07-22 LIVE: toolbar ⋯ menu label 'Add Work Order Fee / Discount' correct; opens whole-WO fee/discount dialog. WORDING CORRECTED — observed order is 'Audit Log' -&gt; 'Timesheets (N)' -&gt; 'Add Work Order Fee / Discount' -&gt; 'Delete Work Order' (Add is 3rd, NOT at top). Ev: wo/FD-WO-025-toolbar-menu.png.</t>
+        </is>
+      </c>
+    </row>
+    <row r="168">
+      <c r="A168" s="2" t="inlineStr">
+        <is>
           <t>FD-WO-028</t>
         </is>
       </c>
-      <c r="B166" s="2" t="inlineStr">
+      <c r="B168" s="2" t="inlineStr">
         <is>
           <t>C30622</t>
         </is>
       </c>
-      <c r="C166" s="6" t="inlineStr">
+      <c r="C168" s="6" t="inlineStr">
         <is>
           <t>https://shopview.testrail.io/index.php?/cases/view/30622</t>
         </is>
       </c>
-      <c r="D166" s="2" t="inlineStr">
+      <c r="D168" s="2" t="inlineStr">
         <is>
           <t>Work Order — Whole-WO Fee/Discount</t>
         </is>
       </c>
-      <c r="E166" s="2" t="inlineStr">
+      <c r="E168" s="2" t="inlineStr">
         <is>
           <t>Verify the tax-jurisdiction note and the 'Pass convenience fee to customer' banner still appear after the fee/discount UI updates</t>
         </is>
       </c>
-      <c r="F166" s="2" t="inlineStr">
+      <c r="F168" s="2" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="G166" s="2" t="inlineStr">
-        <is>
-          <t>VIU-Verified</t>
-        </is>
-      </c>
-      <c r="H166" s="2" t="inlineStr">
-        <is>
-          <t>No action needed — passed.</t>
-        </is>
-      </c>
-      <c r="I166" s="2" t="inlineStr">
+      <c r="G168" s="2" t="inlineStr">
+        <is>
+          <t>VIU-Verified</t>
+        </is>
+      </c>
+      <c r="H168" s="2" t="inlineStr">
+        <is>
+          <t>No action needed — passed.</t>
+        </is>
+      </c>
+      <c r="I168" s="2" t="inlineStr">
         <is>
           <t>&amp; Discounts Settings page (Settings -&gt; Service -&gt; Fees &amp; Discounts / adjustment-templates) — it is NOT rendered inside the WO fee/discount dialogs. Ev: wo/labor-dialog-text.txt, wo/part-dialog-text.txt, wo/wo-dialog-text.txt, wo/FD-WO-028-settings-convenience-banner.png, wo/settings-fd-bodytext.txt.</t>
         </is>
@@ -8626,6 +8720,8 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C164" r:id="rId163"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C165" r:id="rId164"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C166" r:id="rId165"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C167" r:id="rId166"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C168" r:id="rId167"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -8637,7 +8733,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I13"/>
+  <dimension ref="A1:I11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -8889,27 +8985,27 @@
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
         <is>
-          <t>FD-PERM-002</t>
+          <t>FD-PROC-008</t>
         </is>
       </c>
       <c r="B6" s="2" t="inlineStr">
         <is>
-          <t>C28586</t>
+          <t>C28526</t>
         </is>
       </c>
       <c r="C6" s="6" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/28586</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/28526</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>Permissions (Story 13)</t>
+          <t>Processing Fee — WO behavior</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>Verify whole-work-order add/edit/remove requires Work Orders: Create and Edit</t>
+          <t>Verify a Processing Fee on a work order can be removed but not edited</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
@@ -8924,39 +9020,39 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>The system only hides the option on the screen — it still allows the change in the background. Ask the team whether the system should also block it in the background, then re-test.</t>
+          <t>The menu still offers an 'Edit' option for a Processing Fee even though editing does nothing (only 'Remove' works). A developer needs to make it remove-only. Re-test once fixed.</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>BUG-FD-3 stands on batch evidence; NOT re-testable today — Technician role drifted on the shared env (now HAS workOrdersCreateAndEdit, so its 201 is legitimate); enforcement-depth question unchanged (dev decision) | WORDING+VIU 2026-07-13: DEVIATION (BUG-FD-3): the whole-work-order add/edit/remove hide is front-end only — the back-end does not block the write. NOT re-testable this run: Technician drifted to HAVE Work Orders: Create &amp; Edit, and only admin/tech can log in.</t>
+          <t>BE re-proven: pfee change -&gt; 409 'cannot be edited through this endpoint', remove -&gt; 204; card still offers Edit per batch-1 (S8-N5 UI drift) | WORDING+VIU 2026-07-13: DEVIATION carried: the ⋮ menu still shows 'Edit' for a Processing Fee but it is inert (cannot edit a pfee on the WO); 'Remove' works. Build labels ('Remove Fee / Discount' confirm). | SV-8456 (2026-07-21 staging LIVE VIU): F&amp;D moved to SETTINGS→SERVICE (below Canned Lines); template/WO/Part-sale/customer dialogs now show Taxable as a Yes/No DROPDOWN (was toggle); Auto-apply is a CHECKBOX with a 'When on…' caption; settings &amp; customer tables are plain-text/left-aligned (no badges); WO sidebar card retitled 'Work Order Fees &amp; Discounts' and renders ABOVE Financial Info; Part-sale card 'Parts Sale Fees &amp; Discounts' above Financial Info. Permission gate pivoted Settings→Finance → Settings→Service (verified live: Service-user sees+manages F&amp;D &amp; convenience toggle; Finance-only user has no F&amp;D nav item and /administration/adjustment-templates bounces to /workorders). Frontend-only; functionality + calc INTACT. | RE-VIU 2026-07-22 LIVE (Batch 4, SV-8456 re-verify): access-check quick-login {admin} HTTP 200. The SV-8456 UI-correction wording + Settings-&gt;Service permission pivot were re-confirmed live on the current staging build (Service-user sees+manages F&amp;D; Finance-only user no F&amp;D nav, direct route bounces to /workorders; Tech restored to Technician 50bf6a0d + verified; ZZAUTOTEST roles deleted). This case retains its prior VIU-Deviation for its OWN (non-SV-8456) reason — that specific behavior was NOT re-driven this pass. Ev build/fees-discounts/viu-sv8456-2026-07-22/.</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
         <is>
-          <t>FD-PROC-008</t>
+          <t>FD-PROC-009</t>
         </is>
       </c>
       <c r="B7" s="2" t="inlineStr">
         <is>
-          <t>C28526</t>
+          <t>C28527</t>
         </is>
       </c>
       <c r="C7" s="6" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/28526</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/28527</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>Processing Fee — WO behavior</t>
+          <t>Processing Fee — calculation</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>Verify a Processing Fee on a work order can be removed but not edited</t>
+          <t>Verify a % of Grand Total Processing Fee works out last on the tax-included grand total (3% of $324 → +$9.72)</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
@@ -8971,44 +9067,44 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>The menu still offers an 'Edit' option for a Processing Fee even though editing does nothing (only 'Remove' works). A developer needs to make it remove-only. Re-test once fixed.</t>
+          <t>A developer needs to fix the Processing Fee amount — its base should NOT include the whole-work-order fees/discounts (or their tax). Re-test the amount once fixed.</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>BE re-proven: pfee change -&gt; 409 'cannot be edited through this endpoint', remove -&gt; 204; card still offers Edit per batch-1 (S8-N5 UI drift) | WORDING+VIU 2026-07-13: DEVIATION carried: the ⋮ menu still shows 'Edit' for a Processing Fee but it is inert (cannot edit a pfee on the WO); 'Remove' works. Build labels ('Remove Fee / Discount' confirm). | SV-8456 (2026-07-21 staging LIVE VIU): F&amp;D moved to SETTINGS→SERVICE (below Canned Lines); template/WO/Part-sale/customer dialogs now show Taxable as a Yes/No DROPDOWN (was toggle); Auto-apply is a CHECKBOX with a 'When on…' caption; settings &amp; customer tables are plain-text/left-aligned (no badges); WO sidebar card retitled 'Work Order Fees &amp; Discounts' and renders ABOVE Financial Info; Part-sale card 'Parts Sale Fees &amp; Discounts' above Financial Info. Permission gate pivoted Settings→Finance → Settings→Service (verified live: Service-user sees+manages F&amp;D &amp; convenience toggle; Finance-only user has no F&amp;D nav item and /administration/adjustment-templates bounces to /workorders). Frontend-only; functionality + calc INTACT. | RE-VIU 2026-07-22 LIVE (Batch 4, SV-8456 re-verify): access-check quick-login {admin} HTTP 200. The SV-8456 UI-correction wording + Settings-&gt;Service permission pivot were re-confirmed live on the current staging build (Service-user sees+manages F&amp;D; Finance-only user no F&amp;D nav, direct route bounces to /workorders; Tech restored to Technician 50bf6a0d + verified; ZZAUTOTEST roles deleted). This case retains its prior VIU-Deviation for its OWN (non-SV-8456) reason — that specific behavior was NOT re-driven this pass. Ev build/fees-discounts/viu-sv8456-2026-07-22/.</t>
+          <t>FDBUG-2 CONFIRMED AGAIN with a clean discriminator: on a WO whose ONLY money is a whole-WO $20 taxable fee, 3% pfee resolved 0.63 (=3% of 21.00 incl the whole-WO fee + its tax); spec base must EXCLUDE whole-WO adjustments -&gt; expected 0.00 | WORDING+VIU 2026-07-13: DEVIATION carried (FDBUG-2): the Processing Fee base wrongly includes whole-WO fees/discounts + their tax (should exclude them).</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
         <is>
-          <t>FD-PROC-009</t>
+          <t>FD-STATS-002</t>
         </is>
       </c>
       <c r="B8" s="2" t="inlineStr">
         <is>
-          <t>C28527</t>
+          <t>C28460</t>
         </is>
       </c>
       <c r="C8" s="6" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/28527</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/28460</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>Processing Fee — calculation</t>
+          <t>Work Order — Statistics tab</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>Verify a % of Grand Total Processing Fee works out last on the tax-included grand total (3% of $324 → +$9.72)</t>
+          <t>Verify each Stats fee/discount row names its target</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -9018,29 +9114,29 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>A developer needs to fix the Processing Fee amount — its base should NOT include the whole-work-order fees/discounts (or their tax). Re-test the amount once fixed.</t>
+          <t>A developer needs to change the Statistics tab to show one row per fee/discount that names its target. Re-test once that per-row layout is built.</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>FDBUG-2 CONFIRMED AGAIN with a clean discriminator: on a WO whose ONLY money is a whole-WO $20 taxable fee, 3% pfee resolved 0.63 (=3% of 21.00 incl the whole-WO fee + its tax); spec base must EXCLUDE whole-WO adjustments -&gt; expected 0.00 | WORDING+VIU 2026-07-13: DEVIATION carried (FDBUG-2): the Processing Fee base wrongly includes whole-WO fees/discounts + their tax (should exclude them).</t>
+          <t>per-row scope hyperlink impossible while the layout is aggregate (dep. FD-STATS-001) | WORDING+VIU 2026-07-13: DEVIATION carried: Stats F&amp;D rows show the name only — no scope hyperlink to the target. Confirmed live (rows read plain names, shot fin-01).</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
         <is>
-          <t>FD-STATS-002</t>
+          <t>FD-STATS-004</t>
         </is>
       </c>
       <c r="B9" s="2" t="inlineStr">
         <is>
-          <t>C28460</t>
+          <t>C28462</t>
         </is>
       </c>
       <c r="C9" s="6" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/28460</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/28462</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
@@ -9050,7 +9146,7 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>Verify each Stats fee/discount row names its target</t>
+          <t>Verify the Stats fees/discounts are listed in the order they were created (oldest first)</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
@@ -9065,44 +9161,44 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>A developer needs to change the Statistics tab to show one row per fee/discount that names its target. Re-test once that per-row layout is built.</t>
+          <t>Once the Statistics tab shows one row per fee/discount, check they are listed oldest first. Re-test after the per-row layout is built by the developer.</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>per-row scope hyperlink impossible while the layout is aggregate (dep. FD-STATS-001) | WORDING+VIU 2026-07-13: DEVIATION carried: Stats F&amp;D rows show the name only — no scope hyperlink to the target. Confirmed live (rows read plain names, shot fin-01).</t>
+          <t>creation-order rows blocked by aggregate layout (dep. FD-STATS-001) | WORDING+VIU 2026-07-13: DEVIATION carried: creation-order ruling pending (BUG-FD-2 group). Labels cleaned.</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
         <is>
-          <t>FD-STATS-004</t>
+          <t>FD-TMPL-010</t>
         </is>
       </c>
       <c r="B10" s="2" t="inlineStr">
         <is>
-          <t>C28462</t>
+          <t>C28511</t>
         </is>
       </c>
       <c r="C10" s="6" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/28462</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/28511</t>
         </is>
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>Work Order — Statistics tab</t>
+          <t>Template admin — scoping</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>Verify the Stats fees/discounts are listed in the order they were created (oldest first)</t>
+          <t>Verify template scoping — labour-method templates only show in labour pickers, parts-method only in parts pickers</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>High</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -9112,39 +9208,39 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>Once the Statistics tab shows one row per fee/discount, check they are listed oldest first. Re-test after the per-row layout is built by the developer.</t>
+          <t>The line-level dialog currently has no 'Apply From Template' picker, so template scoping can't be checked there. Re-check on staging whether that picker now exists; if it is still missing, confirm with the team whether that is intended.</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>creation-order rows blocked by aggregate layout (dep. FD-STATS-001) | WORDING+VIU 2026-07-13: DEVIATION carried: creation-order ruling pending (BUG-FD-2 group). Labels cleaned.</t>
+          <t>FDBUG-13 (line-scope Add dialog has no template picker) per batch-1/4; not re-driven today | WORDING+VIU 2026-07-13: DEVIATION carried: template scoping in the line 'Apply From Template' picker + the compatibility hint not re-captured this run (needs the line-level picker). Labels cleaned. | SV-8479/8480 deconfliction 2026-07-22: mixed label sweep: labor step -&gt; 'Add Labor Fee / Discount', part step -&gt; 'Add Part Fee / Discount' (behavior unchanged). | VIU 2026-07-22 LIVE: SV-8479 nav labels 'Add Labor Fee / Discount' (step 1) and 'Add Part Fee / Discount' (step 3) both confirmed present; case status unchanged (existing Deviation for its own reason). Ev: wo/FD-WO-017-labor-menu-open.png, wo/FD-WO-018-part-menu.png.</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
         <is>
-          <t>FD-TMPL-010</t>
+          <t>FD-WO-017</t>
         </is>
       </c>
       <c r="B11" s="2" t="inlineStr">
         <is>
-          <t>C28511</t>
+          <t>C30618</t>
         </is>
       </c>
       <c r="C11" s="6" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/28511</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/30618</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>Template admin — scoping</t>
+          <t>Work Order — Labor-line Fee/Discount</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>Verify template scoping — labour-method templates only show in labour pickers, parts-method only in parts pickers</t>
+          <t>Verify the labor fee/discount entry point is a three-dot menu to the LEFT of the first technician (or 'Unassigned') and reads 'Add Labor Fee / Discount'</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
@@ -9159,104 +9255,10 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>The line-level dialog currently has no 'Apply From Template' picker, so template scoping can't be checked there. Re-check on staging whether that picker now exists; if it is still missing, confirm with the team whether that is intended.</t>
+          <t>A developer needs to move the three-dot menu to the LEFT of 'Unassigned' (it currently sits on the right); the label is already correct. Re-test the left placement once the fix is in.</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
-        <is>
-          <t>FDBUG-13 (line-scope Add dialog has no template picker) per batch-1/4; not re-driven today | WORDING+VIU 2026-07-13: DEVIATION carried: template scoping in the line 'Apply From Template' picker + the compatibility hint not re-captured this run (needs the line-level picker). Labels cleaned. | SV-8479/8480 deconfliction 2026-07-22: mixed label sweep: labor step -&gt; 'Add Labor Fee / Discount', part step -&gt; 'Add Part Fee / Discount' (behavior unchanged). | VIU 2026-07-22 LIVE: SV-8479 nav labels 'Add Labor Fee / Discount' (step 1) and 'Add Part Fee / Discount' (step 3) both confirmed present; case status unchanged (existing Deviation for its own reason). Ev: wo/FD-WO-017-labor-menu-open.png, wo/FD-WO-018-part-menu.png.</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" s="2" t="inlineStr">
-        <is>
-          <t>FD-WO-013</t>
-        </is>
-      </c>
-      <c r="B12" s="2" t="inlineStr">
-        <is>
-          <t>C28436</t>
-        </is>
-      </c>
-      <c r="C12" s="6" t="inlineStr">
-        <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/28436</t>
-        </is>
-      </c>
-      <c r="D12" s="2" t="inlineStr">
-        <is>
-          <t>Work Order — Whole-WO Fee/Discount</t>
-        </is>
-      </c>
-      <c r="E12" s="2" t="inlineStr">
-        <is>
-          <t>Verify the whole-work-order 'Add Work Order Fee / Discount' option is hidden without Work Orders: Create &amp; Edit</t>
-        </is>
-      </c>
-      <c r="F12" s="2" t="inlineStr">
-        <is>
-          <t>Medium</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>VIU-Deviation</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>The option is only hidden on the screen — the system still lets the change go through behind the scenes. Ask the team whether the system should also block it in the background, not just hide the button, then re-test.</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>BUG-FD-3 stands on prior evidence; NOT re-testable today: the shared-env Technician role was CHANGED (now includes workOrdersCreateAndEdit+workOrdersDelete, 8 perms vs matrix 6) so tech's 201 is now legitimate; no login lacking the perm exists | WORDING+VIU 2026-07-13: rewritten to exact build labels (⋮ menu item 'Add Fee/Discount'; dialog 'Add new fee/discount'; fields 'Apply From Template'/'Name'/'Type'/'Calculation Type'/'$ Amount' or 'Percent %'/'$ Max Amount (Optional)'/'Taxable' toggle; whole-WO Calculation Type options = Flat Amount, % of Labor Total, % of Parts Total, % of Subtotal; buttons 'Add Fee'/'Add Discount'; sidebar card 'WO Fees &amp; Discounts'; preview empty prompt 'Enter an amount to see the impact.'). Captured live on WO S3-15960 (shots wo-01..wo-05). DEVIATION (BUG-FD-3: the hide is front-end only; the back-end does not block the write). NOT re-testable this run — the Technician role has drifted on the shared qb env; re-derive the roles matrix before re-checking. | SV-8479/8480 deconfliction 2026-07-22: label updated 'Add Fee/Discount' -&gt; 'Add Work Order Fee / Discount' (item 10); permission behavior unchanged. | VIU 2026-07-22 LIVE: toolbar label 'Add Work Order Fee / Discount' confirmed present (admin); permission-negative status unchanged — role-negative not re-driven this UI batch.</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" s="2" t="inlineStr">
-        <is>
-          <t>FD-WO-017</t>
-        </is>
-      </c>
-      <c r="B13" s="2" t="inlineStr">
-        <is>
-          <t>C30618</t>
-        </is>
-      </c>
-      <c r="C13" s="6" t="inlineStr">
-        <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/30618</t>
-        </is>
-      </c>
-      <c r="D13" s="2" t="inlineStr">
-        <is>
-          <t>Work Order — Labor-line Fee/Discount</t>
-        </is>
-      </c>
-      <c r="E13" s="2" t="inlineStr">
-        <is>
-          <t>Verify the labor fee/discount entry point is a three-dot menu to the LEFT of the first technician (or 'Unassigned') and reads 'Add Labor Fee / Discount'</t>
-        </is>
-      </c>
-      <c r="F13" s="2" t="inlineStr">
-        <is>
-          <t>High</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
-        <is>
-          <t>VIU-Deviation</t>
-        </is>
-      </c>
-      <c r="H13" s="2" t="inlineStr">
-        <is>
-          <t>A developer needs to move the three-dot menu to the LEFT of 'Unassigned' (it currently sits on the right); the label is already correct. Re-test the left placement once the fix is in.</t>
-        </is>
-      </c>
-      <c r="I13" s="2" t="inlineStr">
         <is>
           <t>me row y=282); spec requires LEFT. Label 'Add Labor Fee / Discount' is correct and opens the labor fee/discount dialog. Menu contained only 'Add Labor Fee / Discount' (no separate 'Edit labor' item observed). Ev: wo/FD-WO-017-labor-row-menu-RIGHT.png, wo/FD-WO-017-labor-menu-open.png, obs2 geometry.</t>
         </is>
@@ -9274,8 +9276,6 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C9" r:id="rId8"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C10" r:id="rId9"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C11" r:id="rId10"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C12" r:id="rId11"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C13" r:id="rId12"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/build/fees-discounts/FeesDiscounts_FreshVIU_2026-07-24.xlsx
+++ b/build/fees-discounts/FeesDiscounts_FreshVIU_2026-07-24.xlsx
@@ -510,7 +510,7 @@
         </is>
       </c>
       <c r="B5" s="2" t="n">
-        <v>167</v>
+        <v>178</v>
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
@@ -525,7 +525,7 @@
         </is>
       </c>
       <c r="B6" s="2" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
@@ -570,7 +570,7 @@
         </is>
       </c>
       <c r="B9" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
@@ -644,7 +644,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I168"/>
+  <dimension ref="A1:I179"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -1272,17 +1272,17 @@
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
         <is>
-          <t>FD-CALC-014</t>
+          <t>FD-CALC-013</t>
         </is>
       </c>
       <c r="B14" s="2" t="inlineStr">
         <is>
-          <t>C28581</t>
+          <t>C28580</t>
         </is>
       </c>
       <c r="C14" s="6" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/28581</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/28580</t>
         </is>
       </c>
       <c r="D14" s="2" t="inlineStr">
@@ -1292,12 +1292,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>Verify the Processing Fee base includes tax on purpose and never uses a Max Amount</t>
+          <t>Verify a Processing Fee works out last on the tax-included grand total (3% of $324 → +$9.72)</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>High</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1312,24 +1312,24 @@
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>pfee base tax-inclusive on purpose (0.63 = 3% of 21.00 incl GST, not 0.60); maxCap rejected for pfee (400) | WORDING+VIU 2026-07-13: Processing-Fee base + no Max Amount carried; build labels. | SV-8456 (2026-07-21 staging LIVE VIU): F&amp;D moved to SETTINGS→SERVICE (below Canned Lines); template/WO/Part-sale/customer dialogs now show Taxable as a Yes/No DROPDOWN (was toggle); Auto-apply is a CHECKBOX with a 'When on…' caption; settings &amp; customer tables are plain-text/left-aligned (no badges); WO sidebar card retitled 'Work Order Fees &amp; Discounts' and renders ABOVE Financial Info; Part-sale card 'Parts Sale Fees &amp; Discounts' above Financial Info. Permission gate pivoted Settings→Finance → Settings→Service (verified live: Service-user sees+manages F&amp;D &amp; convenience toggle; Finance-only user has no F&amp;D nav item and /administration/adjustment-templates bounces to /workorders). Frontend-only; functionality + calc INTACT. | RE-VIU 2026-07-22 LIVE (Batch 4, SV-8456 re-verify): access-check quick-login {admin} HTTP 200. Re-confirmed on current staging build — 8 UI corrections intact (Taxable Yes/No dropdown; Auto-apply checkbox+caption; modal field order Type/CalcType&gt;Name&gt;Amount&gt;Taxable+jur.note&gt;Auto-apply&gt;Description; Settings table plain-text left-aligned no badges; F&amp;D nav under SERVICE below Canned Lines; WO &amp; Part-Sale cards above Financial Info [Batch 2/3]; Customer 'Fees &amp; Discounts' tab mirrors Settings styling minus convenience toggle) AND Settings-&gt;Service permission pivot CONFIRMED live per role (seeded ServiceRole vs FinanceRole, assigned to Tech, Tech restored to Technician 50bf6a0d + verified, both ZZAUTOTEST roles deleted 204): Service-user sees+manages F&amp;D nav + convenience toggle, direct /administration/adjustment-templates loads; Finance-only user has NO F&amp;D nav, FINANCE=Payment Methods only, direct route bounces to /workorders. viu_status VIU-Verified re-confirmed. Ev build/fees-discounts/viu-sv8456-2026-07-22/ (01-settings-landing, 02-new-dialog, 03-customer-fd-tab, SVC-*, FIN-*).</t>
+          <t>FDBUG-2 CONFIRMED AGAIN (clean discriminator): pfee base INCLUDES whole-WO adjustments + their tax (3% -&gt; 0.63 where spec expects 0.00). Structural defect is tax-model independent | WORDING+VIU 2026-07-13: DEVIATION carried (FDBUG-2): the Processing Fee base wrongly includes whole-work-order fees/discounts (should exclude them). Build labels applied. | SV-8456 (2026-07-21 staging LIVE VIU): F&amp;D moved to SETTINGS→SERVICE (below Canned Lines); template/WO/Part-sale/customer dialogs now show Taxable as a Yes/No DROPDOWN (was toggle); Auto-apply is a CHECKBOX with a 'When on…' caption; settings &amp; customer tables are plain-text/left-aligned (no badges); WO sidebar card retitled 'Work Order Fees &amp; Discounts' and renders ABOVE Financial Info; Part-sale card 'Parts Sale Fees &amp; Discounts' above Financial Info. Permission gate pivoted Settings→Finance → Settings→Service (verified live: Service-user sees+manages F&amp;D &amp; convenience toggle; Finance-only user has no F&amp;D nav item and /administration/adjustment-templates bounces to /workorders). Frontend-only; functionality + calc INTACT. | RE-VIU 2026-07-22 LIVE (Batch 4, SV-8456 re-verify): access-check quick-login {admin} HTTP 200. The SV-8456 UI-correction wording + Settings-&gt;Service permission pivot were re-confirmed live on the current staging build (Service-user sees+manages F&amp;D; Finance-only user no F&amp;D nav, direct route bounces to /workorders; Tech restored to Technician 50bf6a0d + verified; ZZAUTOTEST roles deleted). This case retains its prior VIU-Deviation for its OWN (non-SV-8456) reason — that specific behavior was NOT re-driven this pass. Ev build/fees-discounts/viu-sv8456-2026-07-22/. | SV-8421 PF-BASE FIX CONFIRMED LIVE (2026-07-24 staging): with a 3% Processing fee on Grand Total present, adding a $100 taxable whole-WO fee left the PF UNCHANGED at $13.92 (=3% x net$442 x(1+GST5%)=464.10) while tax grew $22.80-&gt;$27.80 — PF base EXCLUDES the whole-WO fee and its tax. FDBUG-2 RESOLVED. VIU-Deviation -&gt; VIU-Verified. Evidence build/fees-discounts/sv8421-followups-2026-07-24/FINDINGS.md + evidence/api_PFbase_after_100_taxable_fee.json. | CLOSE-OUT 2026-07-24: also accepted per Ahtasham QA live review 2026-07-24 (no bug). Already flipped to VIU-Verified by our own live SV-8421 spot-check 2026-07-24 (this one WE verified live — see FINDINGS.md). No status change here.</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="2" t="inlineStr">
         <is>
-          <t>FD-CALC-015</t>
+          <t>FD-CALC-014</t>
         </is>
       </c>
       <c r="B15" s="2" t="inlineStr">
         <is>
-          <t>C28582</t>
+          <t>C28581</t>
         </is>
       </c>
       <c r="C15" s="6" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/28582</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/28581</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
@@ -1339,12 +1339,12 @@
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>Verify the subtotal floors at $0.00 — a non-taxable $150 discount on $100 parts + $10 tax: customer pays $10, the $50 excess becomes a customer credit</t>
+          <t>Verify the Processing Fee base includes tax on purpose and never uses a Max Amount</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -1359,24 +1359,24 @@
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>non-taxable over-discount: sub floors 0.00, GST unchanged 9.14, total=tax, excessCredit 117.24 exact | WORDING+VIU 2026-07-13: In-app floor + credit half VIU'd 2026-07-10; the QuickBooks credit-memo half needs a human in QuickBooks. Build labels. | SV-8456 (2026-07-21 staging LIVE VIU): F&amp;D moved to SETTINGS→SERVICE (below Canned Lines); template/WO/Part-sale/customer dialogs now show Taxable as a Yes/No DROPDOWN (was toggle); Auto-apply is a CHECKBOX with a 'When on…' caption; settings &amp; customer tables are plain-text/left-aligned (no badges); WO sidebar card retitled 'Work Order Fees &amp; Discounts' and renders ABOVE Financial Info; Part-sale card 'Parts Sale Fees &amp; Discounts' above Financial Info. Permission gate pivoted Settings→Finance → Settings→Service (verified live: Service-user sees+manages F&amp;D &amp; convenience toggle; Finance-only user has no F&amp;D nav item and /administration/adjustment-templates bounces to /workorders). Frontend-only; functionality + calc INTACT. | RE-VIU 2026-07-22 LIVE (Batch 4, SV-8456 re-verify): access-check quick-login {admin} HTTP 200. Re-confirmed on current staging build — 8 UI corrections intact (Taxable Yes/No dropdown; Auto-apply checkbox+caption; modal field order Type/CalcType&gt;Name&gt;Amount&gt;Taxable+jur.note&gt;Auto-apply&gt;Description; Settings table plain-text left-aligned no badges; F&amp;D nav under SERVICE below Canned Lines; WO &amp; Part-Sale cards above Financial Info [Batch 2/3]; Customer 'Fees &amp; Discounts' tab mirrors Settings styling minus convenience toggle) AND Settings-&gt;Service permission pivot CONFIRMED live per role (seeded ServiceRole vs FinanceRole, assigned to Tech, Tech restored to Technician 50bf6a0d + verified, both ZZAUTOTEST roles deleted 204): Service-user sees+manages F&amp;D nav + convenience toggle, direct /administration/adjustment-templates loads; Finance-only user has NO F&amp;D nav, FINANCE=Payment Methods only, direct route bounces to /workorders. viu_status VIU-Verified re-confirmed. Ev build/fees-discounts/viu-sv8456-2026-07-22/ (01-settings-landing, 02-new-dialog, 03-customer-fd-tab, SVC-*, FIN-*).</t>
+          <t>pfee base tax-inclusive on purpose (0.63 = 3% of 21.00 incl GST, not 0.60); maxCap rejected for pfee (400) | WORDING+VIU 2026-07-13: Processing-Fee base + no Max Amount carried; build labels. | SV-8456 (2026-07-21 staging LIVE VIU): F&amp;D moved to SETTINGS→SERVICE (below Canned Lines); template/WO/Part-sale/customer dialogs now show Taxable as a Yes/No DROPDOWN (was toggle); Auto-apply is a CHECKBOX with a 'When on…' caption; settings &amp; customer tables are plain-text/left-aligned (no badges); WO sidebar card retitled 'Work Order Fees &amp; Discounts' and renders ABOVE Financial Info; Part-sale card 'Parts Sale Fees &amp; Discounts' above Financial Info. Permission gate pivoted Settings→Finance → Settings→Service (verified live: Service-user sees+manages F&amp;D &amp; convenience toggle; Finance-only user has no F&amp;D nav item and /administration/adjustment-templates bounces to /workorders). Frontend-only; functionality + calc INTACT. | RE-VIU 2026-07-22 LIVE (Batch 4, SV-8456 re-verify): access-check quick-login {admin} HTTP 200. Re-confirmed on current staging build — 8 UI corrections intact (Taxable Yes/No dropdown; Auto-apply checkbox+caption; modal field order Type/CalcType&gt;Name&gt;Amount&gt;Taxable+jur.note&gt;Auto-apply&gt;Description; Settings table plain-text left-aligned no badges; F&amp;D nav under SERVICE below Canned Lines; WO &amp; Part-Sale cards above Financial Info [Batch 2/3]; Customer 'Fees &amp; Discounts' tab mirrors Settings styling minus convenience toggle) AND Settings-&gt;Service permission pivot CONFIRMED live per role (seeded ServiceRole vs FinanceRole, assigned to Tech, Tech restored to Technician 50bf6a0d + verified, both ZZAUTOTEST roles deleted 204): Service-user sees+manages F&amp;D nav + convenience toggle, direct /administration/adjustment-templates loads; Finance-only user has NO F&amp;D nav, FINANCE=Payment Methods only, direct route bounces to /workorders. viu_status VIU-Verified re-confirmed. Ev build/fees-discounts/viu-sv8456-2026-07-22/ (01-settings-landing, 02-new-dialog, 03-customer-fd-tab, SVC-*, FIN-*).</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
         <is>
-          <t>FD-CALC-016</t>
+          <t>FD-CALC-015</t>
         </is>
       </c>
       <c r="B16" s="2" t="inlineStr">
         <is>
-          <t>C28583</t>
+          <t>C28582</t>
         </is>
       </c>
       <c r="C16" s="6" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/28583</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/28582</t>
         </is>
       </c>
       <c r="D16" s="2" t="inlineStr">
@@ -1386,12 +1386,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>Verify a taxable $150 discount on $100 parts drives the taxable amount to $0 → tax $0.00, customer pays $0.00</t>
+          <t>Verify the subtotal floors at $0.00 — a non-taxable $150 discount on $100 parts + $10 tax: customer pays $10, the $50 excess becomes a customer credit</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>High</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -1406,117 +1406,117 @@
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>taxable over-discount: sub 0.00, GST 0, total 0.00, excess captured | WORDING+VIU 2026-07-13: Taxable-discount-to-$0 carried; build labels. | SV-8456 (2026-07-21 staging LIVE VIU): F&amp;D moved to SETTINGS→SERVICE (below Canned Lines); template/WO/Part-sale/customer dialogs now show Taxable as a Yes/No DROPDOWN (was toggle); Auto-apply is a CHECKBOX with a 'When on…' caption; settings &amp; customer tables are plain-text/left-aligned (no badges); WO sidebar card retitled 'Work Order Fees &amp; Discounts' and renders ABOVE Financial Info; Part-sale card 'Parts Sale Fees &amp; Discounts' above Financial Info. Permission gate pivoted Settings→Finance → Settings→Service (verified live: Service-user sees+manages F&amp;D &amp; convenience toggle; Finance-only user has no F&amp;D nav item and /administration/adjustment-templates bounces to /workorders). Frontend-only; functionality + calc INTACT. | RE-VIU 2026-07-22 LIVE (Batch 4, SV-8456 re-verify): access-check quick-login {admin} HTTP 200. Re-confirmed on current staging build — 8 UI corrections intact (Taxable Yes/No dropdown; Auto-apply checkbox+caption; modal field order Type/CalcType&gt;Name&gt;Amount&gt;Taxable+jur.note&gt;Auto-apply&gt;Description; Settings table plain-text left-aligned no badges; F&amp;D nav under SERVICE below Canned Lines; WO &amp; Part-Sale cards above Financial Info [Batch 2/3]; Customer 'Fees &amp; Discounts' tab mirrors Settings styling minus convenience toggle) AND Settings-&gt;Service permission pivot CONFIRMED live per role (seeded ServiceRole vs FinanceRole, assigned to Tech, Tech restored to Technician 50bf6a0d + verified, both ZZAUTOTEST roles deleted 204): Service-user sees+manages F&amp;D nav + convenience toggle, direct /administration/adjustment-templates loads; Finance-only user has NO F&amp;D nav, FINANCE=Payment Methods only, direct route bounces to /workorders. viu_status VIU-Verified re-confirmed. Ev build/fees-discounts/viu-sv8456-2026-07-22/ (01-settings-landing, 02-new-dialog, 03-customer-fd-tab, SVC-*, FIN-*).</t>
+          <t>non-taxable over-discount: sub floors 0.00, GST unchanged 9.14, total=tax, excessCredit 117.24 exact | WORDING+VIU 2026-07-13: In-app floor + credit half VIU'd 2026-07-10; the QuickBooks credit-memo half needs a human in QuickBooks. Build labels. | SV-8456 (2026-07-21 staging LIVE VIU): F&amp;D moved to SETTINGS→SERVICE (below Canned Lines); template/WO/Part-sale/customer dialogs now show Taxable as a Yes/No DROPDOWN (was toggle); Auto-apply is a CHECKBOX with a 'When on…' caption; settings &amp; customer tables are plain-text/left-aligned (no badges); WO sidebar card retitled 'Work Order Fees &amp; Discounts' and renders ABOVE Financial Info; Part-sale card 'Parts Sale Fees &amp; Discounts' above Financial Info. Permission gate pivoted Settings→Finance → Settings→Service (verified live: Service-user sees+manages F&amp;D &amp; convenience toggle; Finance-only user has no F&amp;D nav item and /administration/adjustment-templates bounces to /workorders). Frontend-only; functionality + calc INTACT. | RE-VIU 2026-07-22 LIVE (Batch 4, SV-8456 re-verify): access-check quick-login {admin} HTTP 200. Re-confirmed on current staging build — 8 UI corrections intact (Taxable Yes/No dropdown; Auto-apply checkbox+caption; modal field order Type/CalcType&gt;Name&gt;Amount&gt;Taxable+jur.note&gt;Auto-apply&gt;Description; Settings table plain-text left-aligned no badges; F&amp;D nav under SERVICE below Canned Lines; WO &amp; Part-Sale cards above Financial Info [Batch 2/3]; Customer 'Fees &amp; Discounts' tab mirrors Settings styling minus convenience toggle) AND Settings-&gt;Service permission pivot CONFIRMED live per role (seeded ServiceRole vs FinanceRole, assigned to Tech, Tech restored to Technician 50bf6a0d + verified, both ZZAUTOTEST roles deleted 204): Service-user sees+manages F&amp;D nav + convenience toggle, direct /administration/adjustment-templates loads; Finance-only user has NO F&amp;D nav, FINANCE=Payment Methods only, direct route bounces to /workorders. viu_status VIU-Verified re-confirmed. Ev build/fees-discounts/viu-sv8456-2026-07-22/ (01-settings-landing, 02-new-dialog, 03-customer-fd-tab, SVC-*, FIN-*).</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="2" t="inlineStr">
         <is>
+          <t>FD-CALC-016</t>
+        </is>
+      </c>
+      <c r="B17" s="2" t="inlineStr">
+        <is>
+          <t>C28583</t>
+        </is>
+      </c>
+      <c r="C17" s="6" t="inlineStr">
+        <is>
+          <t>https://shopview.testrail.io/index.php?/cases/view/28583</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>Calculation contract</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>Verify a taxable $150 discount on $100 parts drives the taxable amount to $0 → tax $0.00, customer pays $0.00</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
+          <t>VIU-Verified</t>
+        </is>
+      </c>
+      <c r="H17" s="2" t="inlineStr">
+        <is>
+          <t>No action needed — passed.</t>
+        </is>
+      </c>
+      <c r="I17" s="2" t="inlineStr">
+        <is>
+          <t>taxable over-discount: sub 0.00, GST 0, total 0.00, excess captured | WORDING+VIU 2026-07-13: Taxable-discount-to-$0 carried; build labels. | SV-8456 (2026-07-21 staging LIVE VIU): F&amp;D moved to SETTINGS→SERVICE (below Canned Lines); template/WO/Part-sale/customer dialogs now show Taxable as a Yes/No DROPDOWN (was toggle); Auto-apply is a CHECKBOX with a 'When on…' caption; settings &amp; customer tables are plain-text/left-aligned (no badges); WO sidebar card retitled 'Work Order Fees &amp; Discounts' and renders ABOVE Financial Info; Part-sale card 'Parts Sale Fees &amp; Discounts' above Financial Info. Permission gate pivoted Settings→Finance → Settings→Service (verified live: Service-user sees+manages F&amp;D &amp; convenience toggle; Finance-only user has no F&amp;D nav item and /administration/adjustment-templates bounces to /workorders). Frontend-only; functionality + calc INTACT. | RE-VIU 2026-07-22 LIVE (Batch 4, SV-8456 re-verify): access-check quick-login {admin} HTTP 200. Re-confirmed on current staging build — 8 UI corrections intact (Taxable Yes/No dropdown; Auto-apply checkbox+caption; modal field order Type/CalcType&gt;Name&gt;Amount&gt;Taxable+jur.note&gt;Auto-apply&gt;Description; Settings table plain-text left-aligned no badges; F&amp;D nav under SERVICE below Canned Lines; WO &amp; Part-Sale cards above Financial Info [Batch 2/3]; Customer 'Fees &amp; Discounts' tab mirrors Settings styling minus convenience toggle) AND Settings-&gt;Service permission pivot CONFIRMED live per role (seeded ServiceRole vs FinanceRole, assigned to Tech, Tech restored to Technician 50bf6a0d + verified, both ZZAUTOTEST roles deleted 204): Service-user sees+manages F&amp;D nav + convenience toggle, direct /administration/adjustment-templates loads; Finance-only user has NO F&amp;D nav, FINANCE=Payment Methods only, direct route bounces to /workorders. viu_status VIU-Verified re-confirmed. Ev build/fees-discounts/viu-sv8456-2026-07-22/ (01-settings-landing, 02-new-dialog, 03-customer-fd-tab, SVC-*, FIN-*).</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="2" t="inlineStr">
+        <is>
           <t>FD-CALC-018</t>
         </is>
       </c>
-      <c r="B17" s="2" t="inlineStr">
+      <c r="B18" s="2" t="inlineStr">
         <is>
           <t>C30629</t>
         </is>
       </c>
-      <c r="C17" s="6" t="inlineStr">
+      <c r="C18" s="6" t="inlineStr">
         <is>
           <t>https://shopview.testrail.io/index.php?/cases/view/30629</t>
         </is>
       </c>
-      <c r="D17" s="2" t="inlineStr">
+      <c r="D18" s="2" t="inlineStr">
         <is>
           <t>Calculation contract</t>
         </is>
       </c>
-      <c r="E17" s="2" t="inlineStr">
+      <c r="E18" s="2" t="inlineStr">
         <is>
           <t>Verify a work order line total adds the line's own fees to Labor and Parts (Labor $250 + fee +$50.00 + Part $20.00 + fee +$2.20 → line total $322.20)</t>
         </is>
       </c>
-      <c r="F17" s="2" t="inlineStr">
+      <c r="F18" s="2" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="G17" s="2" t="inlineStr">
-        <is>
-          <t>VIU-Verified</t>
-        </is>
-      </c>
-      <c r="H17" s="2" t="inlineStr">
-        <is>
-          <t>No action needed — passed.</t>
-        </is>
-      </c>
-      <c r="I17" s="2">
+      <c r="G18" s="2" t="inlineStr">
+        <is>
+          <t>VIU-Verified</t>
+        </is>
+      </c>
+      <c r="H18" s="2" t="inlineStr">
+        <is>
+          <t>No action needed — passed.</t>
+        </is>
+      </c>
+      <c r="I18" s="2">
         <f> $392.40 = 290 + labor fee ttt +20% ($58.00) + 40 + part fee test +11% ($4.40); NOT gross $330. Rows render PLAIN TEXT bare '20%'/'11%' (no plus sign, no colored badge; HTML span text-grey-7). Ev: 018-lines-collapsed-full.png, 018-lines-expanded-full.png, api-FD-CALC-018-024-total_cost-392.40.json.</f>
         <v/>
       </c>
     </row>
-    <row r="18">
-      <c r="A18" s="2" t="inlineStr">
-        <is>
-          <t>FD-CALC-019</t>
-        </is>
-      </c>
-      <c r="B18" s="2" t="inlineStr">
-        <is>
-          <t>C30630</t>
-        </is>
-      </c>
-      <c r="C18" s="6" t="inlineStr">
-        <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/30630</t>
-        </is>
-      </c>
-      <c r="D18" s="2" t="inlineStr">
-        <is>
-          <t>Calculation contract</t>
-        </is>
-      </c>
-      <c r="E18" s="2" t="inlineStr">
-        <is>
-          <t>Verify a discount on a line subtracts from the line total while a fee adds (fees add, discounts subtract in the line total)</t>
-        </is>
-      </c>
-      <c r="F18" s="2" t="inlineStr">
-        <is>
-          <t>High</t>
-        </is>
-      </c>
-      <c r="G18" s="2" t="inlineStr">
-        <is>
-          <t>VIU-Verified</t>
-        </is>
-      </c>
-      <c r="H18" s="2" t="inlineStr">
-        <is>
-          <t>No action needed — passed.</t>
-        </is>
-      </c>
-      <c r="I18" s="2" t="inlineStr">
-        <is>
-          <t>acted -&gt; collapsed line Total = $384.00 = 290 + 58 + 40 - 4.00 (fee adds, discount subtracts). Discount rate renders '-10%' (en-dash minus) plain text, resolved -$4.00; fee rate renders bare '20%'. Ev: 019-lines-collapsed-full.png, 019-lines-expanded-full.png, api-FD-CALC-019-total_cost-384.00.json.</t>
-        </is>
-      </c>
-    </row>
     <row r="19">
       <c r="A19" s="2" t="inlineStr">
         <is>
-          <t>FD-CALC-020</t>
+          <t>FD-CALC-019</t>
         </is>
       </c>
       <c r="B19" s="2" t="inlineStr">
         <is>
-          <t>C30631</t>
+          <t>C30630</t>
         </is>
       </c>
       <c r="C19" s="6" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/30631</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/30630</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
@@ -1526,12 +1526,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>Verify a line with no fees or discounts shows a line total of Labor + Parts only (unchanged by the fix)</t>
+          <t>Verify a discount on a line subtracts from the line total while a fee adds (fees add, discounts subtract in the line total)</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>High</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -1546,24 +1546,24 @@
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>tal (no change from the fix). | LIVE STAGING VIU 2026-07-22: VIU-VERIFIED. A ZZAUTOTEST line with no fees/discounts (Labor $290 + Parts $40) shows collapsed line Total = $330.00 = gross Labor + Parts only, no Fees/Discounts rows. Ev: 020-lines-nofee-line.png, api-baseline-nofees-total_cost-330.json.</t>
+          <t>acted -&gt; collapsed line Total = $384.00 = 290 + 58 + 40 - 4.00 (fee adds, discount subtracts). Discount rate renders '-10%' (en-dash minus) plain text, resolved -$4.00; fee rate renders bare '20%'. Ev: 019-lines-collapsed-full.png, 019-lines-expanded-full.png, api-FD-CALC-019-total_cost-384.00.json.</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
         <is>
-          <t>FD-CALC-021</t>
+          <t>FD-CALC-020</t>
         </is>
       </c>
       <c r="B20" s="2" t="inlineStr">
         <is>
-          <t>C30632</t>
+          <t>C30631</t>
         </is>
       </c>
       <c r="C20" s="6" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/30632</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/30631</t>
         </is>
       </c>
       <c r="D20" s="2" t="inlineStr">
@@ -1573,7 +1573,7 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>Verify the Estimate document is unchanged — labor prints gross, each fee prints its own row, and the grand total is not double-counted</t>
+          <t>Verify a line with no fees or discounts shows a line total of Labor + Parts only (unchanged by the fix)</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
@@ -1593,24 +1593,24 @@
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>0'; the document Line Total = $330.00 (gross Labor+Parts, fee NOT folded in); every fee/discount (incl. line-level ttt +$58.00 and pdisc ($4.00)) listed once in the Fees &amp; Discounts breakdown -&gt; no double-count. Confirms the fix is Lines-tab display-only; estimate unchanged. Ev: 021-finance-tab.png.</t>
+          <t>tal (no change from the fix). | LIVE STAGING VIU 2026-07-22: VIU-VERIFIED. A ZZAUTOTEST line with no fees/discounts (Labor $290 + Parts $40) shows collapsed line Total = $330.00 = gross Labor + Parts only, no Fees/Discounts rows. Ev: 020-lines-nofee-line.png, api-baseline-nofees-total_cost-330.json.</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="2" t="inlineStr">
         <is>
-          <t>FD-CALC-022</t>
+          <t>FD-CALC-021</t>
         </is>
       </c>
       <c r="B21" s="2" t="inlineStr">
         <is>
-          <t>C30633</t>
+          <t>C30632</t>
         </is>
       </c>
       <c r="C21" s="6" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/30633</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/30632</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
@@ -1620,7 +1620,7 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>Verify the Invoice document is unchanged — labor prints gross, each fee prints its own row, and the grand total is not double-counted</t>
+          <t>Verify the Estimate document is unchanged — labor prints gross, each fee prints its own row, and the grand total is not double-counted</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
@@ -1640,24 +1640,24 @@
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>Invoice document (Finance tab toggle, INV-S3-25836): renders identically to the estimate — Labor gross $290.00, the line fee prints as its own row '↳ ttt (% of labor) $58.00', document Line Total = $330.00 (gross, fee not folded in), each fee listed once -&gt; no double-count. Ev: 022-invoice-view.png.</t>
+          <t>0'; the document Line Total = $330.00 (gross Labor+Parts, fee NOT folded in); every fee/discount (incl. line-level ttt +$58.00 and pdisc ($4.00)) listed once in the Fees &amp; Discounts breakdown -&gt; no double-count. Confirms the fix is Lines-tab display-only; estimate unchanged. Ev: 021-finance-tab.png.</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="2" t="inlineStr">
         <is>
-          <t>FD-CALC-024</t>
+          <t>FD-CALC-022</t>
         </is>
       </c>
       <c r="B22" s="2" t="inlineStr">
         <is>
-          <t>C30635</t>
+          <t>C30633</t>
         </is>
       </c>
       <c r="C22" s="6" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/30635</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/30633</t>
         </is>
       </c>
       <c r="D22" s="2" t="inlineStr">
@@ -1667,12 +1667,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>Verify the backend per-line total includes the line's signed fee/discount amounts (Labor $250 + $50.00 + Part $20.00 + $2.20 → total_cost 322.20)</t>
+          <t>Verify the Invoice document is unchanged — labor prints gross, each fee prints its own row, and the grand total is not double-counted</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -1687,34 +1687,34 @@
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>Stored line amounts unchanged (labour_rate 145, total_labour_cost 290, part sell_price 40); the fee/discount amounts live separately under line.adjustments[] and part_requests[].adjustments[] (resolvedAmount 58 / 4.40) — computed total is display-only. Ev: api-FD-CALC-018-024-total_cost-392.40.json.</t>
+          <t>Invoice document (Finance tab toggle, INV-S3-25836): renders identically to the estimate — Labor gross $290.00, the line fee prints as its own row '↳ ttt (% of labor) $58.00', document Line Total = $330.00 (gross, fee not folded in), each fee listed once -&gt; no double-count. Ev: 022-invoice-view.png.</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="2" t="inlineStr">
         <is>
-          <t>FD-CUST-001</t>
+          <t>FD-CALC-024</t>
         </is>
       </c>
       <c r="B23" s="2" t="inlineStr">
         <is>
-          <t>C28485</t>
+          <t>C30635</t>
         </is>
       </c>
       <c r="C23" s="6" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/28485</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/30635</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>Customer Fees &amp; Discounts tab</t>
+          <t>Calculation contract</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>Verify the customer 'Fees &amp; Discounts (N)' tab shows the correct default count</t>
+          <t>Verify the backend per-line total includes the line's signed fee/discount amounts (Labor $250 + $50.00 + Part $20.00 + $2.20 → total_cost 322.20)</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
@@ -1734,24 +1734,24 @@
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>tab label 'Fees &amp; Discounts (N)' re-observed (live count from defaults) | WORDING+VIU 2026-07-13: Tab 'Fees &amp; Discounts (N)' confirmed live (shot cust-01). Corrected the tab list to the real build tabs.</t>
+          <t>Stored line amounts unchanged (labour_rate 145, total_labour_cost 290, part sell_price 40); the fee/discount amounts live separately under line.adjustments[] and part_requests[].adjustments[] (resolvedAmount 58 / 4.40) — computed total is display-only. Ev: api-FD-CALC-018-024-total_cost-392.40.json.</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="2" t="inlineStr">
         <is>
-          <t>FD-CUST-002</t>
+          <t>FD-CUST-001</t>
         </is>
       </c>
       <c r="B24" s="2" t="inlineStr">
         <is>
-          <t>C28486</t>
+          <t>C28485</t>
         </is>
       </c>
       <c r="C24" s="6" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/28486</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/28485</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
@@ -1761,7 +1761,7 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>Verify the 'Default Fees &amp; Discounts' card header, caption and table columns</t>
+          <t>Verify the customer 'Fees &amp; Discounts (N)' tab shows the correct default count</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
@@ -1781,24 +1781,24 @@
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>card header + exact caption re-observed ('These fees &amp; discounts auto-apply to every new work order for this customer…') | WORDING+VIU 2026-07-13: Card header/caption/button/columns confirmed EXACTLY live (shot cust-01). Corrected columns (no Auto-Apply column on the customer tab).</t>
+          <t>tab label 'Fees &amp; Discounts (N)' re-observed (live count from defaults) | WORDING+VIU 2026-07-13: Tab 'Fees &amp; Discounts (N)' confirmed live (shot cust-01). Corrected the tab list to the real build tabs.</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="2" t="inlineStr">
         <is>
-          <t>FD-CUST-003</t>
+          <t>FD-CUST-002</t>
         </is>
       </c>
       <c r="B25" s="2" t="inlineStr">
         <is>
-          <t>C28487</t>
+          <t>C28486</t>
         </is>
       </c>
       <c r="C25" s="6" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/28487</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/28486</t>
         </is>
       </c>
       <c r="D25" s="2" t="inlineStr">
@@ -1808,7 +1808,7 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>Verify adding a single template as a customer default via the picker</t>
+          <t>Verify the 'Default Fees &amp; Discounts' card header, caption and table columns</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
@@ -1828,24 +1828,24 @@
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>single-select add works (API 201, UI single picker) — PO Q6=A accepted; case text still needs the single-select re-wording (case-update) | WORDING+VIU 2026-07-13: Picker confirmed live: 'Add Fee/Discount' dialog with a single 'Fee / Discount Templates' dropdown + Save (shot cust-02). Add lifecycle confirmed via API (201). Toast text carried.</t>
+          <t>card header + exact caption re-observed ('These fees &amp; discounts auto-apply to every new work order for this customer…') | WORDING+VIU 2026-07-13: Card header/caption/button/columns confirmed EXACTLY live (shot cust-01). Corrected columns (no Auto-Apply column on the customer tab).</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="2" t="inlineStr">
         <is>
-          <t>FD-CUST-004</t>
+          <t>FD-CUST-003</t>
         </is>
       </c>
       <c r="B26" s="2" t="inlineStr">
         <is>
-          <t>C28488</t>
+          <t>C28487</t>
         </is>
       </c>
       <c r="C26" s="6" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/28488</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/28487</t>
         </is>
       </c>
       <c r="D26" s="2" t="inlineStr">
@@ -1855,12 +1855,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>Verify several templates are added as customer defaults one at a time (no multi-select)</t>
+          <t>Verify adding a single template as a customer default via the picker</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>High</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -1875,24 +1875,24 @@
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>one-at-a-time picker accepted per PO Q6=A; case-update pending | WORDING+VIU 2026-07-13: Single-select (one dropdown, not checkboxes) confirmed live; multi-add is one-at-a-time. Add lifecycle via API.</t>
+          <t>single-select add works (API 201, UI single picker) — PO Q6=A accepted; case text still needs the single-select re-wording (case-update) | WORDING+VIU 2026-07-13: Picker confirmed live: 'Add Fee/Discount' dialog with a single 'Fee / Discount Templates' dropdown + Save (shot cust-02). Add lifecycle confirmed via API (201). Toast text carried.</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="2" t="inlineStr">
         <is>
-          <t>FD-CUST-007</t>
+          <t>FD-CUST-004</t>
         </is>
       </c>
       <c r="B27" s="2" t="inlineStr">
         <is>
-          <t>C28491</t>
+          <t>C28488</t>
         </is>
       </c>
       <c r="C27" s="6" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/28491</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/28488</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
@@ -1902,12 +1902,12 @@
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>Verify removing a customer default from the row needs no confirmation</t>
+          <t>Verify several templates are added as customer defaults one at a time (no multi-select)</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
@@ -1922,24 +1922,24 @@
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>remove = direct trash, no toast (batch-1); API remove -&gt; 204 re-proven; case-update pending | WORDING+VIU 2026-07-13: Remove confirmed live via API (204, no confirm step). Toast text carried.</t>
+          <t>one-at-a-time picker accepted per PO Q6=A; case-update pending | WORDING+VIU 2026-07-13: Single-select (one dropdown, not checkboxes) confirmed live; multi-add is one-at-a-time. Add lifecycle via API.</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="2" t="inlineStr">
         <is>
-          <t>FD-CUST-008</t>
+          <t>FD-CUST-005</t>
         </is>
       </c>
       <c r="B28" s="2" t="inlineStr">
         <is>
-          <t>C28492</t>
+          <t>C28489</t>
         </is>
       </c>
       <c r="C28" s="6" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/28492</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/28489</t>
         </is>
       </c>
       <c r="D28" s="2" t="inlineStr">
@@ -1949,12 +1949,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>Verify the empty-state text on the Default Fees &amp; Discounts card</t>
+          <t>Verify the picker lists only not-yet-added templates and shows a Processing Fee template as type 'Fee'</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>Low</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -1969,39 +1969,39 @@
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>empty-state card re-observed on a 0-default customer | WORDING+VIU 2026-07-13: Empty-state text confirmed EXACTLY live: "No fees or discounts yet. Use 'Add Fee/Discount' to add one." (shot cust-01).</t>
+          <t>accepted deviation (PO Q6=A); list assertions hold; case-update pending | WORDING+VIU 2026-07-13: DEVIATION carried: a Processing Fee template appears in the customer picker with its Type shown as 'Fee' (display quirk). Picker label 'Fee / Discount Templates' confirmed live; the Processing-Fee-as-Fee display not re-captured this run. | CLOSE-OUT 2026-07-24: matched-to-build per Ahtasham QA review 2026-07-24; synced from his TestRail edit (C28489) — single-select -&gt; multi-select per spec S9-R20 (supersedes the old PO Q6=A single-select note). VIU-Deviation -&gt; VIU-Verified. HONESTY (Rule 12/22): accepted on Ahtasham's live QA review — NOT re-observed by us this pass.</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="2" t="inlineStr">
         <is>
-          <t>FD-CUST-009</t>
+          <t>FD-CUST-006</t>
         </is>
       </c>
       <c r="B29" s="2" t="inlineStr">
         <is>
-          <t>C28493</t>
+          <t>C28490</t>
         </is>
       </c>
       <c r="C29" s="6" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/28493</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/28490</t>
         </is>
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>Customer defaults → new work order</t>
+          <t>Customer Fees &amp; Discounts tab</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>Verify a customer default is added as its own fee/discount on every new work order</t>
+          <t>Verify the picker message when there are no templates left to add</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Low</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -2016,39 +2016,39 @@
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>customer default lands on every NEW WO as an independent copy (appliedBy=customer_default) | WORDING+VIU 2026-07-13: Defaults→new-WO behavior carried (verified 2026-07-10); build labels ('WO Fees &amp; Discounts' card). | SV-8456 (2026-07-21 staging LIVE VIU): F&amp;D moved to SETTINGS→SERVICE (below Canned Lines); template/WO/Part-sale/customer dialogs now show Taxable as a Yes/No DROPDOWN (was toggle); Auto-apply is a CHECKBOX with a 'When on…' caption; settings &amp; customer tables are plain-text/left-aligned (no badges); WO sidebar card retitled 'Work Order Fees &amp; Discounts' and renders ABOVE Financial Info; Part-sale card 'Parts Sale Fees &amp; Discounts' above Financial Info. Permission gate pivoted Settings→Finance → Settings→Service (verified live: Service-user sees+manages F&amp;D &amp; convenience toggle; Finance-only user has no F&amp;D nav item and /administration/adjustment-templates bounces to /workorders). Frontend-only; functionality + calc INTACT. | RE-VIU 2026-07-22 LIVE (Batch 4, SV-8456 re-verify): access-check quick-login {admin} HTTP 200. Re-confirmed on current staging build — 8 UI corrections intact (Taxable Yes/No dropdown; Auto-apply checkbox+caption; modal field order Type/CalcType&gt;Name&gt;Amount&gt;Taxable+jur.note&gt;Auto-apply&gt;Description; Settings table plain-text left-aligned no badges; F&amp;D nav under SERVICE below Canned Lines; WO &amp; Part-Sale cards above Financial Info [Batch 2/3]; Customer 'Fees &amp; Discounts' tab mirrors Settings styling minus convenience toggle) AND Settings-&gt;Service permission pivot CONFIRMED live per role (seeded ServiceRole vs FinanceRole, assigned to Tech, Tech restored to Technician 50bf6a0d + verified, both ZZAUTOTEST roles deleted 204): Service-user sees+manages F&amp;D nav + convenience toggle, direct /administration/adjustment-templates loads; Finance-only user has NO F&amp;D nav, FINANCE=Payment Methods only, direct route bounces to /workorders. viu_status VIU-Verified re-confirmed. Ev build/fees-discounts/viu-sv8456-2026-07-22/ (01-settings-landing, 02-new-dialog, 03-customer-fd-tab, SVC-*, FIN-*).</t>
+          <t>'No results' empty picker message per batch-1 (spec wording differs); case-update pending; not re-driven | WORDING+VIU 2026-07-13: Empty-picker state carried from prior VIU (not re-captured — the shared env has templates available). | CLOSE-OUT 2026-07-24: accepted per Ahtasham QA live review 2026-07-24 (no bug). Status -&gt; VIU-Verified, wording unchanged. HONESTY (Rule 12/22): accepted on Ahtasham's live QA review — NOT re-observed by us this pass.</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="2" t="inlineStr">
         <is>
-          <t>FD-CUST-010</t>
+          <t>FD-CUST-007</t>
         </is>
       </c>
       <c r="B30" s="2" t="inlineStr">
         <is>
-          <t>C28494</t>
+          <t>C28491</t>
         </is>
       </c>
       <c r="C30" s="6" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/28494</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/28491</t>
         </is>
       </c>
       <c r="D30" s="2" t="inlineStr">
         <is>
-          <t>Customer defaults → new work order</t>
+          <t>Customer Fees &amp; Discounts tab</t>
         </is>
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>Verify a percentage customer default re-works per work order (keeps the percent, not a fixed dollar)</t>
+          <t>Verify removing a customer default from the row needs no confirmation</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>High</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -2063,39 +2063,39 @@
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>pct default copied as percent (amount=7, calc=pct_subtotal), re-resolves per WO | WORDING+VIU 2026-07-13: Percentage default re-resolves per WO; carried.</t>
+          <t>remove = direct trash, no toast (batch-1); API remove -&gt; 204 re-proven; case-update pending | WORDING+VIU 2026-07-13: Remove confirmed live via API (204, no confirm step). Toast text carried.</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="2" t="inlineStr">
         <is>
-          <t>FD-CUST-011</t>
+          <t>FD-CUST-008</t>
         </is>
       </c>
       <c r="B31" s="2" t="inlineStr">
         <is>
-          <t>C28495</t>
+          <t>C28492</t>
         </is>
       </c>
       <c r="C31" s="6" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/28495</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/28492</t>
         </is>
       </c>
       <c r="D31" s="2" t="inlineStr">
         <is>
-          <t>Customer defaults lifecycle</t>
+          <t>Customer Fees &amp; Discounts tab</t>
         </is>
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>Verify removing a customer default does not change fees/discounts already on existing work orders</t>
+          <t>Verify the empty-state text on the Default Fees &amp; Discounts card</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Low</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
@@ -2110,34 +2110,34 @@
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>removing the default link leaves the existing WO's adjustment intact | WORDING+VIU 2026-07-13: Remove-default-does-not-touch-existing-WOs carried; remove lifecycle confirmed via API (204). | SV-8456 (2026-07-21 staging LIVE VIU): F&amp;D moved to SETTINGS→SERVICE (below Canned Lines); template/WO/Part-sale/customer dialogs now show Taxable as a Yes/No DROPDOWN (was toggle); Auto-apply is a CHECKBOX with a 'When on…' caption; settings &amp; customer tables are plain-text/left-aligned (no badges); WO sidebar card retitled 'Work Order Fees &amp; Discounts' and renders ABOVE Financial Info; Part-sale card 'Parts Sale Fees &amp; Discounts' above Financial Info. Permission gate pivoted Settings→Finance → Settings→Service (verified live: Service-user sees+manages F&amp;D &amp; convenience toggle; Finance-only user has no F&amp;D nav item and /administration/adjustment-templates bounces to /workorders). Frontend-only; functionality + calc INTACT. | RE-VIU 2026-07-22 LIVE (Batch 4, SV-8456 re-verify): access-check quick-login {admin} HTTP 200. Re-confirmed on current staging build — 8 UI corrections intact (Taxable Yes/No dropdown; Auto-apply checkbox+caption; modal field order Type/CalcType&gt;Name&gt;Amount&gt;Taxable+jur.note&gt;Auto-apply&gt;Description; Settings table plain-text left-aligned no badges; F&amp;D nav under SERVICE below Canned Lines; WO &amp; Part-Sale cards above Financial Info [Batch 2/3]; Customer 'Fees &amp; Discounts' tab mirrors Settings styling minus convenience toggle) AND Settings-&gt;Service permission pivot CONFIRMED live per role (seeded ServiceRole vs FinanceRole, assigned to Tech, Tech restored to Technician 50bf6a0d + verified, both ZZAUTOTEST roles deleted 204): Service-user sees+manages F&amp;D nav + convenience toggle, direct /administration/adjustment-templates loads; Finance-only user has NO F&amp;D nav, FINANCE=Payment Methods only, direct route bounces to /workorders. viu_status VIU-Verified re-confirmed. Ev build/fees-discounts/viu-sv8456-2026-07-22/ (01-settings-landing, 02-new-dialog, 03-customer-fd-tab, SVC-*, FIN-*).</t>
+          <t>empty-state card re-observed on a 0-default customer | WORDING+VIU 2026-07-13: Empty-state text confirmed EXACTLY live: "No fees or discounts yet. Use 'Add Fee/Discount' to add one." (shot cust-01).</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="2" t="inlineStr">
         <is>
-          <t>FD-CUST-012</t>
+          <t>FD-CUST-009</t>
         </is>
       </c>
       <c r="B32" s="2" t="inlineStr">
         <is>
-          <t>C28496</t>
+          <t>C28493</t>
         </is>
       </c>
       <c r="C32" s="6" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/28496</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/28493</t>
         </is>
       </c>
       <c r="D32" s="2" t="inlineStr">
         <is>
-          <t>Customer defaults lifecycle</t>
+          <t>Customer defaults → new work order</t>
         </is>
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>Verify deleting a template that is a customer default drops the default link but keeps existing work-order fees/discounts</t>
+          <t>Verify a customer default is added as its own fee/discount on every new work order</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
@@ -2157,39 +2157,39 @@
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>deleting a linked template (204) cascades the default link away | WORDING+VIU 2026-07-13: Corrected nav to Administration → Finance; behavior carried. | SV-8456 (2026-07-21 staging LIVE VIU): F&amp;D moved to SETTINGS→SERVICE (below Canned Lines); template/WO/Part-sale/customer dialogs now show Taxable as a Yes/No DROPDOWN (was toggle); Auto-apply is a CHECKBOX with a 'When on…' caption; settings &amp; customer tables are plain-text/left-aligned (no badges); WO sidebar card retitled 'Work Order Fees &amp; Discounts' and renders ABOVE Financial Info; Part-sale card 'Parts Sale Fees &amp; Discounts' above Financial Info. Permission gate pivoted Settings→Finance → Settings→Service (verified live: Service-user sees+manages F&amp;D &amp; convenience toggle; Finance-only user has no F&amp;D nav item and /administration/adjustment-templates bounces to /workorders). Frontend-only; functionality + calc INTACT. | RE-VIU 2026-07-22 LIVE (Batch 4, SV-8456 re-verify): access-check quick-login {admin} HTTP 200. Re-confirmed on current staging build — 8 UI corrections intact (Taxable Yes/No dropdown; Auto-apply checkbox+caption; modal field order Type/CalcType&gt;Name&gt;Amount&gt;Taxable+jur.note&gt;Auto-apply&gt;Description; Settings table plain-text left-aligned no badges; F&amp;D nav under SERVICE below Canned Lines; WO &amp; Part-Sale cards above Financial Info [Batch 2/3]; Customer 'Fees &amp; Discounts' tab mirrors Settings styling minus convenience toggle) AND Settings-&gt;Service permission pivot CONFIRMED live per role (seeded ServiceRole vs FinanceRole, assigned to Tech, Tech restored to Technician 50bf6a0d + verified, both ZZAUTOTEST roles deleted 204): Service-user sees+manages F&amp;D nav + convenience toggle, direct /administration/adjustment-templates loads; Finance-only user has NO F&amp;D nav, FINANCE=Payment Methods only, direct route bounces to /workorders. viu_status VIU-Verified re-confirmed. Ev build/fees-discounts/viu-sv8456-2026-07-22/ (01-settings-landing, 02-new-dialog, 03-customer-fd-tab, SVC-*, FIN-*).</t>
+          <t>customer default lands on every NEW WO as an independent copy (appliedBy=customer_default) | WORDING+VIU 2026-07-13: Defaults→new-WO behavior carried (verified 2026-07-10); build labels ('WO Fees &amp; Discounts' card). | SV-8456 (2026-07-21 staging LIVE VIU): F&amp;D moved to SETTINGS→SERVICE (below Canned Lines); template/WO/Part-sale/customer dialogs now show Taxable as a Yes/No DROPDOWN (was toggle); Auto-apply is a CHECKBOX with a 'When on…' caption; settings &amp; customer tables are plain-text/left-aligned (no badges); WO sidebar card retitled 'Work Order Fees &amp; Discounts' and renders ABOVE Financial Info; Part-sale card 'Parts Sale Fees &amp; Discounts' above Financial Info. Permission gate pivoted Settings→Finance → Settings→Service (verified live: Service-user sees+manages F&amp;D &amp; convenience toggle; Finance-only user has no F&amp;D nav item and /administration/adjustment-templates bounces to /workorders). Frontend-only; functionality + calc INTACT. | RE-VIU 2026-07-22 LIVE (Batch 4, SV-8456 re-verify): access-check quick-login {admin} HTTP 200. Re-confirmed on current staging build — 8 UI corrections intact (Taxable Yes/No dropdown; Auto-apply checkbox+caption; modal field order Type/CalcType&gt;Name&gt;Amount&gt;Taxable+jur.note&gt;Auto-apply&gt;Description; Settings table plain-text left-aligned no badges; F&amp;D nav under SERVICE below Canned Lines; WO &amp; Part-Sale cards above Financial Info [Batch 2/3]; Customer 'Fees &amp; Discounts' tab mirrors Settings styling minus convenience toggle) AND Settings-&gt;Service permission pivot CONFIRMED live per role (seeded ServiceRole vs FinanceRole, assigned to Tech, Tech restored to Technician 50bf6a0d + verified, both ZZAUTOTEST roles deleted 204): Service-user sees+manages F&amp;D nav + convenience toggle, direct /administration/adjustment-templates loads; Finance-only user has NO F&amp;D nav, FINANCE=Payment Methods only, direct route bounces to /workorders. viu_status VIU-Verified re-confirmed. Ev build/fees-discounts/viu-sv8456-2026-07-22/ (01-settings-landing, 02-new-dialog, 03-customer-fd-tab, SVC-*, FIN-*).</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="2" t="inlineStr">
         <is>
-          <t>FD-CUST-013</t>
+          <t>FD-CUST-010</t>
         </is>
       </c>
       <c r="B33" s="2" t="inlineStr">
         <is>
-          <t>C28497</t>
+          <t>C28494</t>
         </is>
       </c>
       <c r="C33" s="6" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/28497</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/28494</t>
         </is>
       </c>
       <c r="D33" s="2" t="inlineStr">
         <is>
-          <t>Customer defaults lifecycle</t>
+          <t>Customer defaults → new work order</t>
         </is>
       </c>
       <c r="E33" s="2" t="inlineStr">
         <is>
-          <t>Verify deleting a customer removes that customer's default links</t>
+          <t>Verify a percentage customer default re-works per work order (keeps the percent, not a fixed dollar)</t>
         </is>
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
-          <t>Low</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="G33" s="2" t="inlineStr">
@@ -2204,39 +2204,39 @@
       </c>
       <c r="I33" s="2" t="inlineStr">
         <is>
-          <t>prior (customer delete removes links) stands; today's re-probe was blocked by an orphan test contact, not by the feature | WORDING+VIU 2026-07-13: Corrected nav; behavior carried. | SV-8456 (2026-07-21 staging LIVE VIU): F&amp;D moved to SETTINGS→SERVICE (below Canned Lines); template/WO/Part-sale/customer dialogs now show Taxable as a Yes/No DROPDOWN (was toggle); Auto-apply is a CHECKBOX with a 'When on…' caption; settings &amp; customer tables are plain-text/left-aligned (no badges); WO sidebar card retitled 'Work Order Fees &amp; Discounts' and renders ABOVE Financial Info; Part-sale card 'Parts Sale Fees &amp; Discounts' above Financial Info. Permission gate pivoted Settings→Finance → Settings→Service (verified live: Service-user sees+manages F&amp;D &amp; convenience toggle; Finance-only user has no F&amp;D nav item and /administration/adjustment-templates bounces to /workorders). Frontend-only; functionality + calc INTACT. | RE-VIU 2026-07-22 LIVE (Batch 4, SV-8456 re-verify): access-check quick-login {admin} HTTP 200. Re-confirmed on current staging build — 8 UI corrections intact (Taxable Yes/No dropdown; Auto-apply checkbox+caption; modal field order Type/CalcType&gt;Name&gt;Amount&gt;Taxable+jur.note&gt;Auto-apply&gt;Description; Settings table plain-text left-aligned no badges; F&amp;D nav under SERVICE below Canned Lines; WO &amp; Part-Sale cards above Financial Info [Batch 2/3]; Customer 'Fees &amp; Discounts' tab mirrors Settings styling minus convenience toggle) AND Settings-&gt;Service permission pivot CONFIRMED live per role (seeded ServiceRole vs FinanceRole, assigned to Tech, Tech restored to Technician 50bf6a0d + verified, both ZZAUTOTEST roles deleted 204): Service-user sees+manages F&amp;D nav + convenience toggle, direct /administration/adjustment-templates loads; Finance-only user has NO F&amp;D nav, FINANCE=Payment Methods only, direct route bounces to /workorders. viu_status VIU-Verified re-confirmed. Ev build/fees-discounts/viu-sv8456-2026-07-22/ (01-settings-landing, 02-new-dialog, 03-customer-fd-tab, SVC-*, FIN-*).</t>
+          <t>pct default copied as percent (amount=7, calc=pct_subtotal), re-resolves per WO | WORDING+VIU 2026-07-13: Percentage default re-resolves per WO; carried.</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="2" t="inlineStr">
         <is>
-          <t>FD-CUST-014</t>
+          <t>FD-CUST-011</t>
         </is>
       </c>
       <c r="B34" s="2" t="inlineStr">
         <is>
-          <t>C28498</t>
+          <t>C28495</t>
         </is>
       </c>
       <c r="C34" s="6" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/28498</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/28495</t>
         </is>
       </c>
       <c r="D34" s="2" t="inlineStr">
         <is>
-          <t>Customer defaults seeding</t>
+          <t>Customer defaults lifecycle</t>
         </is>
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
-          <t>Verify a brand-new customer inherits every auto-apply location template as a default</t>
+          <t>Verify removing a customer default does not change fees/discounts already on existing work orders</t>
         </is>
       </c>
       <c r="F34" s="2" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>High</t>
         </is>
       </c>
       <c r="G34" s="2" t="inlineStr">
@@ -2251,34 +2251,34 @@
       </c>
       <c r="I34" s="2" t="inlineStr">
         <is>
-          <t>NEW TODAY — FDBUG-12 APPEARS FIXED: an API-created customer NOW inherits the auto-apply location template as a default (initial defaults list had the auto template pre-seeded) | WORDING+VIU 2026-07-13: New-customer seeding of auto-apply defaults confirmed working (FDBUG-12 fixed 2026-07-10); carried.</t>
+          <t>removing the default link leaves the existing WO's adjustment intact | WORDING+VIU 2026-07-13: Remove-default-does-not-touch-existing-WOs carried; remove lifecycle confirmed via API (204). | SV-8456 (2026-07-21 staging LIVE VIU): F&amp;D moved to SETTINGS→SERVICE (below Canned Lines); template/WO/Part-sale/customer dialogs now show Taxable as a Yes/No DROPDOWN (was toggle); Auto-apply is a CHECKBOX with a 'When on…' caption; settings &amp; customer tables are plain-text/left-aligned (no badges); WO sidebar card retitled 'Work Order Fees &amp; Discounts' and renders ABOVE Financial Info; Part-sale card 'Parts Sale Fees &amp; Discounts' above Financial Info. Permission gate pivoted Settings→Finance → Settings→Service (verified live: Service-user sees+manages F&amp;D &amp; convenience toggle; Finance-only user has no F&amp;D nav item and /administration/adjustment-templates bounces to /workorders). Frontend-only; functionality + calc INTACT. | RE-VIU 2026-07-22 LIVE (Batch 4, SV-8456 re-verify): access-check quick-login {admin} HTTP 200. Re-confirmed on current staging build — 8 UI corrections intact (Taxable Yes/No dropdown; Auto-apply checkbox+caption; modal field order Type/CalcType&gt;Name&gt;Amount&gt;Taxable+jur.note&gt;Auto-apply&gt;Description; Settings table plain-text left-aligned no badges; F&amp;D nav under SERVICE below Canned Lines; WO &amp; Part-Sale cards above Financial Info [Batch 2/3]; Customer 'Fees &amp; Discounts' tab mirrors Settings styling minus convenience toggle) AND Settings-&gt;Service permission pivot CONFIRMED live per role (seeded ServiceRole vs FinanceRole, assigned to Tech, Tech restored to Technician 50bf6a0d + verified, both ZZAUTOTEST roles deleted 204): Service-user sees+manages F&amp;D nav + convenience toggle, direct /administration/adjustment-templates loads; Finance-only user has NO F&amp;D nav, FINANCE=Payment Methods only, direct route bounces to /workorders. viu_status VIU-Verified re-confirmed. Ev build/fees-discounts/viu-sv8456-2026-07-22/ (01-settings-landing, 02-new-dialog, 03-customer-fd-tab, SVC-*, FIN-*).</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="2" t="inlineStr">
         <is>
-          <t>FD-CUST-015</t>
+          <t>FD-CUST-012</t>
         </is>
       </c>
       <c r="B35" s="2" t="inlineStr">
         <is>
-          <t>C28499</t>
+          <t>C28496</t>
         </is>
       </c>
       <c r="C35" s="6" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/28499</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/28496</t>
         </is>
       </c>
       <c r="D35" s="2" t="inlineStr">
         <is>
-          <t>Customer Fees &amp; Discounts tab — permissions</t>
+          <t>Customer defaults lifecycle</t>
         </is>
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t>Verify the customer Fees &amp; Discounts tab and its controls are hidden without the required permissions</t>
+          <t>Verify deleting a template that is a customer default drops the default link but keeps existing work-order fees/discounts</t>
         </is>
       </c>
       <c r="F35" s="2" t="inlineStr">
@@ -2298,34 +2298,34 @@
       </c>
       <c r="I35" s="2" t="inlineStr">
         <is>
-          <t>tech -&gt; defaults GET/POST 403 (BE-enforced); per-role visibility via roles-matrix (role-drift caveat) | WORDING+VIU 2026-07-13: Customer-defaults GET/POST are back-end gated (Tech → 403), established batch-2. NOTE: re-check the Tech negative after the roles matrix is re-derived (Technician drifted on shared qb).</t>
+          <t>deleting a linked template (204) cascades the default link away | WORDING+VIU 2026-07-13: Corrected nav to Administration → Finance; behavior carried. | SV-8456 (2026-07-21 staging LIVE VIU): F&amp;D moved to SETTINGS→SERVICE (below Canned Lines); template/WO/Part-sale/customer dialogs now show Taxable as a Yes/No DROPDOWN (was toggle); Auto-apply is a CHECKBOX with a 'When on…' caption; settings &amp; customer tables are plain-text/left-aligned (no badges); WO sidebar card retitled 'Work Order Fees &amp; Discounts' and renders ABOVE Financial Info; Part-sale card 'Parts Sale Fees &amp; Discounts' above Financial Info. Permission gate pivoted Settings→Finance → Settings→Service (verified live: Service-user sees+manages F&amp;D &amp; convenience toggle; Finance-only user has no F&amp;D nav item and /administration/adjustment-templates bounces to /workorders). Frontend-only; functionality + calc INTACT. | RE-VIU 2026-07-22 LIVE (Batch 4, SV-8456 re-verify): access-check quick-login {admin} HTTP 200. Re-confirmed on current staging build — 8 UI corrections intact (Taxable Yes/No dropdown; Auto-apply checkbox+caption; modal field order Type/CalcType&gt;Name&gt;Amount&gt;Taxable+jur.note&gt;Auto-apply&gt;Description; Settings table plain-text left-aligned no badges; F&amp;D nav under SERVICE below Canned Lines; WO &amp; Part-Sale cards above Financial Info [Batch 2/3]; Customer 'Fees &amp; Discounts' tab mirrors Settings styling minus convenience toggle) AND Settings-&gt;Service permission pivot CONFIRMED live per role (seeded ServiceRole vs FinanceRole, assigned to Tech, Tech restored to Technician 50bf6a0d + verified, both ZZAUTOTEST roles deleted 204): Service-user sees+manages F&amp;D nav + convenience toggle, direct /administration/adjustment-templates loads; Finance-only user has NO F&amp;D nav, FINANCE=Payment Methods only, direct route bounces to /workorders. viu_status VIU-Verified re-confirmed. Ev build/fees-discounts/viu-sv8456-2026-07-22/ (01-settings-landing, 02-new-dialog, 03-customer-fd-tab, SVC-*, FIN-*).</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="2" t="inlineStr">
         <is>
-          <t>FD-CUST-017</t>
+          <t>FD-CUST-013</t>
         </is>
       </c>
       <c r="B36" s="2" t="inlineStr">
         <is>
-          <t>C28501</t>
+          <t>C28497</t>
         </is>
       </c>
       <c r="C36" s="6" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/28501</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/28497</t>
         </is>
       </c>
       <c r="D36" s="2" t="inlineStr">
         <is>
-          <t>Customer Fees &amp; Discounts tab — negative</t>
+          <t>Customer defaults lifecycle</t>
         </is>
       </c>
       <c r="E36" s="2" t="inlineStr">
         <is>
-          <t>Verify an add/remove/load failure on customer defaults shows the standard error notification</t>
+          <t>Verify deleting a customer removes that customer's default links</t>
         </is>
       </c>
       <c r="F36" s="2" t="inlineStr">
@@ -2345,39 +2345,39 @@
       </c>
       <c r="I36" s="2" t="inlineStr">
         <is>
-          <t>bad-template add 400 / bad-customer load 404 / bad remove 404 | WORDING+VIU 2026-07-13: API negative — standard error notification; carried. Lives in an API-titled section (rule 4).</t>
+          <t>prior (customer delete removes links) stands; today's re-probe was blocked by an orphan test contact, not by the feature | WORDING+VIU 2026-07-13: Corrected nav; behavior carried. | SV-8456 (2026-07-21 staging LIVE VIU): F&amp;D moved to SETTINGS→SERVICE (below Canned Lines); template/WO/Part-sale/customer dialogs now show Taxable as a Yes/No DROPDOWN (was toggle); Auto-apply is a CHECKBOX with a 'When on…' caption; settings &amp; customer tables are plain-text/left-aligned (no badges); WO sidebar card retitled 'Work Order Fees &amp; Discounts' and renders ABOVE Financial Info; Part-sale card 'Parts Sale Fees &amp; Discounts' above Financial Info. Permission gate pivoted Settings→Finance → Settings→Service (verified live: Service-user sees+manages F&amp;D &amp; convenience toggle; Finance-only user has no F&amp;D nav item and /administration/adjustment-templates bounces to /workorders). Frontend-only; functionality + calc INTACT. | RE-VIU 2026-07-22 LIVE (Batch 4, SV-8456 re-verify): access-check quick-login {admin} HTTP 200. Re-confirmed on current staging build — 8 UI corrections intact (Taxable Yes/No dropdown; Auto-apply checkbox+caption; modal field order Type/CalcType&gt;Name&gt;Amount&gt;Taxable+jur.note&gt;Auto-apply&gt;Description; Settings table plain-text left-aligned no badges; F&amp;D nav under SERVICE below Canned Lines; WO &amp; Part-Sale cards above Financial Info [Batch 2/3]; Customer 'Fees &amp; Discounts' tab mirrors Settings styling minus convenience toggle) AND Settings-&gt;Service permission pivot CONFIRMED live per role (seeded ServiceRole vs FinanceRole, assigned to Tech, Tech restored to Technician 50bf6a0d + verified, both ZZAUTOTEST roles deleted 204): Service-user sees+manages F&amp;D nav + convenience toggle, direct /administration/adjustment-templates loads; Finance-only user has NO F&amp;D nav, FINANCE=Payment Methods only, direct route bounces to /workorders. viu_status VIU-Verified re-confirmed. Ev build/fees-discounts/viu-sv8456-2026-07-22/ (01-settings-landing, 02-new-dialog, 03-customer-fd-tab, SVC-*, FIN-*).</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="2" t="inlineStr">
         <is>
-          <t>FD-DOC-001</t>
+          <t>FD-CUST-014</t>
         </is>
       </c>
       <c r="B37" s="2" t="inlineStr">
         <is>
-          <t>C28533</t>
+          <t>C28498</t>
         </is>
       </c>
       <c r="C37" s="6" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/28533</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/28498</t>
         </is>
       </c>
       <c r="D37" s="2" t="inlineStr">
         <is>
-          <t>Customer document (estimate/invoice)</t>
+          <t>Customer defaults seeding</t>
         </is>
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
-          <t>Verify one layout renders adjustments on both the estimate and the invoice</t>
+          <t>Verify a brand-new customer inherits every auto-apply location template as a default</t>
         </is>
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="G37" s="2" t="inlineStr">
@@ -2392,34 +2392,34 @@
       </c>
       <c r="I37" s="2" t="inlineStr">
         <is>
-          <t>estimate rendered via the invoice template (header 'Invoice', shared layout), Adjustments block present | WORDING+VIU 2026-07-13: Estimate rendering confirmed live (est-15960.html); invoice uses the same layout (carried).</t>
+          <t>NEW TODAY — FDBUG-12 APPEARS FIXED: an API-created customer NOW inherits the auto-apply location template as a default (initial defaults list had the auto template pre-seeded) | WORDING+VIU 2026-07-13: New-customer seeding of auto-apply defaults confirmed working (FDBUG-12 fixed 2026-07-10); carried.</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="2" t="inlineStr">
         <is>
-          <t>FD-DOC-002</t>
+          <t>FD-CUST-015</t>
         </is>
       </c>
       <c r="B38" s="2" t="inlineStr">
         <is>
-          <t>C28534</t>
+          <t>C28499</t>
         </is>
       </c>
       <c r="C38" s="6" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/28534</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/28499</t>
         </is>
       </c>
       <c r="D38" s="2" t="inlineStr">
         <is>
-          <t>Customer document — per-line adjustments</t>
+          <t>Customer Fees &amp; Discounts tab — permissions</t>
         </is>
       </c>
       <c r="E38" s="2" t="inlineStr">
         <is>
-          <t>Verify a labor-line percentage adjustment renders indented with ↳, the "(% of labor)" phrase, and correct amount sign</t>
+          <t>Verify the customer Fees &amp; Discounts tab and its controls are hidden without the required permissions</t>
         </is>
       </c>
       <c r="F38" s="2" t="inlineStr">
@@ -2439,39 +2439,39 @@
       </c>
       <c r="I38" s="2" t="inlineStr">
         <is>
-          <t>labor-line pct renders '↳ ZZAUTOTEST LabPct (% of labor) $0.00' (phrase present) | WORDING+VIU 2026-07-13: Amount format + '(% of ...)' phrase confirmed live; per-line ↳ rendering carried from prior VIU. Tax shown as 'GST (5%)' on this env.</t>
+          <t>tech -&gt; defaults GET/POST 403 (BE-enforced); per-role visibility via roles-matrix (role-drift caveat) | WORDING+VIU 2026-07-13: Customer-defaults GET/POST are back-end gated (Tech → 403), established batch-2. NOTE: re-check the Tech negative after the roles matrix is re-derived (Technician drifted on shared qb).</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="2" t="inlineStr">
         <is>
-          <t>FD-DOC-003</t>
+          <t>FD-CUST-017</t>
         </is>
       </c>
       <c r="B39" s="2" t="inlineStr">
         <is>
-          <t>C28535</t>
+          <t>C28501</t>
         </is>
       </c>
       <c r="C39" s="6" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/28535</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/28501</t>
         </is>
       </c>
       <c r="D39" s="2" t="inlineStr">
         <is>
-          <t>Customer document — per-line adjustments</t>
+          <t>Customer Fees &amp; Discounts tab — negative</t>
         </is>
       </c>
       <c r="E39" s="2" t="inlineStr">
         <is>
-          <t>Verify a part-line adjustment renders with "(% of parts)" (percentage) and no phrase for Flat Amount</t>
+          <t>Verify an add/remove/load failure on customer defaults shows the standard error notification</t>
         </is>
       </c>
       <c r="F39" s="2" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>Low</t>
         </is>
       </c>
       <c r="G39" s="2" t="inlineStr">
@@ -2486,34 +2486,34 @@
       </c>
       <c r="I39" s="2" t="inlineStr">
         <is>
-          <t>part pct 'ZZAUTOTEST PartPct (% of parts) ($17.08)'; part flat 'ZZAUTOTEST PartFlat $8.00' (no phrase) | WORDING+VIU 2026-07-13: '(% of parts)' phrase pattern confirmed (build shows '(% of &lt;method&gt;)'); Flat Amount shows no phrase (confirmed).</t>
+          <t>bad-template add 400 / bad-customer load 404 / bad remove 404 | WORDING+VIU 2026-07-13: API negative — standard error notification; carried. Lives in an API-titled section (rule 4).</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="2" t="inlineStr">
         <is>
-          <t>FD-DOC-004</t>
+          <t>FD-DOC-001</t>
         </is>
       </c>
       <c r="B40" s="2" t="inlineStr">
         <is>
-          <t>C28536</t>
+          <t>C28533</t>
         </is>
       </c>
       <c r="C40" s="6" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/28536</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/28533</t>
         </is>
       </c>
       <c r="D40" s="2" t="inlineStr">
         <is>
-          <t>Customer document — amount format</t>
+          <t>Customer document (estimate/invoice)</t>
         </is>
       </c>
       <c r="E40" s="2" t="inlineStr">
         <is>
-          <t>Verify fee vs discount amount formatting (fee "$X.XX", discount "($X.XX)")</t>
+          <t>Verify one layout renders adjustments on both the estimate and the invoice</t>
         </is>
       </c>
       <c r="F40" s="2" t="inlineStr">
@@ -2533,34 +2533,34 @@
       </c>
       <c r="I40" s="2" t="inlineStr">
         <is>
-          <t>fee '$10.00' vs discount accounting '($5.00)' formats confirmed | WORDING+VIU 2026-07-13: CONFIRMED live: fee '$X.XX', discount '($X.XX)' in round brackets (est-15960.html: 'Flat fee $21,474,836.47' vs 'Falt discount ($21,474,836.47)').</t>
+          <t>estimate rendered via the invoice template (header 'Invoice', shared layout), Adjustments block present | WORDING+VIU 2026-07-13: Estimate rendering confirmed live (est-15960.html); invoice uses the same layout (carried).</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="2" t="inlineStr">
         <is>
-          <t>FD-DOC-005</t>
+          <t>FD-DOC-002</t>
         </is>
       </c>
       <c r="B41" s="2" t="inlineStr">
         <is>
-          <t>C28537</t>
+          <t>C28534</t>
         </is>
       </c>
       <c r="C41" s="6" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/28537</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/28534</t>
         </is>
       </c>
       <c r="D41" s="2" t="inlineStr">
         <is>
-          <t>Customer document — Adjustments block</t>
+          <t>Customer document — per-line adjustments</t>
         </is>
       </c>
       <c r="E41" s="2" t="inlineStr">
         <is>
-          <t>Verify the bottom "Adjustments" block lists whole-WO adjustments one by one in creation order</t>
+          <t>Verify a labor-line percentage adjustment renders indented with ↳, the "(% of labor)" phrase, and correct amount sign</t>
         </is>
       </c>
       <c r="F41" s="2" t="inlineStr">
@@ -2580,39 +2580,39 @@
       </c>
       <c r="I41" s="2" t="inlineStr">
         <is>
-          <t>bottom Adjustments block lists whole-WO adjustments in creation order (Flat fee -&gt; WFee -&gt; WDisc) | WORDING+VIU 2026-07-13: CONFIRMED live: bottom 'Adjustments' block lists items in creation order; percentage items show '(% of subtotal)'. NOTE: this build lists line-level items in the same block too.</t>
+          <t>labor-line pct renders '↳ ZZAUTOTEST LabPct (% of labor) $0.00' (phrase present) | WORDING+VIU 2026-07-13: Amount format + '(% of ...)' phrase confirmed live; per-line ↳ rendering carried from prior VIU. Tax shown as 'GST (5%)' on this env.</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="2" t="inlineStr">
         <is>
-          <t>FD-DOC-006</t>
+          <t>FD-DOC-003</t>
         </is>
       </c>
       <c r="B42" s="2" t="inlineStr">
         <is>
-          <t>C28538</t>
+          <t>C28535</t>
         </is>
       </c>
       <c r="C42" s="6" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/28538</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/28535</t>
         </is>
       </c>
       <c r="D42" s="2" t="inlineStr">
         <is>
-          <t>Customer document — Adjustments block</t>
+          <t>Customer document — per-line adjustments</t>
         </is>
       </c>
       <c r="E42" s="2" t="inlineStr">
         <is>
-          <t>Verify line-level adjustments are grouped by name+type in the bottom block with a "(×N)" count</t>
+          <t>Verify a part-line adjustment renders with "(% of parts)" (percentage) and no phrase for Flat Amount</t>
         </is>
       </c>
       <c r="F42" s="2" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="G42" s="2" t="inlineStr">
@@ -2627,39 +2627,39 @@
       </c>
       <c r="I42" s="2" t="inlineStr">
         <is>
-          <t>3 same-name+type line fees grouped as '(×3) $24.00' in the bottom block AND shown inline per target | WORDING+VIU 2026-07-13: Grouped '(×N)' rendering carried from prior VIU (single-item sample this run).</t>
+          <t>part pct 'ZZAUTOTEST PartPct (% of parts) ($17.08)'; part flat 'ZZAUTOTEST PartFlat $8.00' (no phrase) | WORDING+VIU 2026-07-13: '(% of parts)' phrase pattern confirmed (build shows '(% of &lt;method&gt;)'); Flat Amount shows no phrase (confirmed).</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="2" t="inlineStr">
         <is>
-          <t>FD-DOC-007</t>
+          <t>FD-DOC-004</t>
         </is>
       </c>
       <c r="B43" s="2" t="inlineStr">
         <is>
-          <t>C28539</t>
+          <t>C28536</t>
         </is>
       </c>
       <c r="C43" s="6" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/28539</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/28536</t>
         </is>
       </c>
       <c r="D43" s="2" t="inlineStr">
         <is>
-          <t>Customer document — Processing Fee phrase</t>
+          <t>Customer document — amount format</t>
         </is>
       </c>
       <c r="E43" s="2" t="inlineStr">
         <is>
-          <t>Verify a % of Grand Total Processing Fee shows the "% of grand total" phrase on the document</t>
+          <t>Verify fee vs discount amount formatting (fee "$X.XX", discount "($X.XX)")</t>
         </is>
       </c>
       <c r="F43" s="2" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>High</t>
         </is>
       </c>
       <c r="G43" s="2" t="inlineStr">
@@ -2674,39 +2674,39 @@
       </c>
       <c r="I43" s="2" t="inlineStr">
         <is>
-          <t>'(% of grand total)' phrase per batch evidence; pfee not seedable onto a money-bearing WO today (line-create 500 blocks a fresh WO with lines) | WORDING+VIU 2026-07-13: '% of grand total' phrase carried (no live pfee on the sample WO).</t>
+          <t>fee '$10.00' vs discount accounting '($5.00)' formats confirmed | WORDING+VIU 2026-07-13: CONFIRMED live: fee '$X.XX', discount '($X.XX)' in round brackets (est-15960.html: 'Flat fee $21,474,836.47' vs 'Falt discount ($21,474,836.47)').</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="2" t="inlineStr">
         <is>
-          <t>FD-DOC-008</t>
+          <t>FD-DOC-005</t>
         </is>
       </c>
       <c r="B44" s="2" t="inlineStr">
         <is>
-          <t>C28540</t>
+          <t>C28537</t>
         </is>
       </c>
       <c r="C44" s="6" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/28540</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/28537</t>
         </is>
       </c>
       <c r="D44" s="2" t="inlineStr">
         <is>
-          <t>Customer document — Shop Supplies (S14)</t>
+          <t>Customer document — Adjustments block</t>
         </is>
       </c>
       <c r="E44" s="2" t="inlineStr">
         <is>
-          <t>Verify Shop Supplies is hidden on the estimate/invoice/financial tab when the total is $0.00</t>
+          <t>Verify the bottom "Adjustments" block lists whole-WO adjustments one by one in creation order</t>
         </is>
       </c>
       <c r="F44" s="2" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>High</t>
         </is>
       </c>
       <c r="G44" s="2" t="inlineStr">
@@ -2721,39 +2721,39 @@
       </c>
       <c r="I44" s="2" t="inlineStr">
         <is>
-          <t>Shop Supplies section HIDDEN on the estimate when total is $0.00 (baseline S-15895) | WORDING+VIU 2026-07-13: CONFIRMED live: Shop Supplies absent from the estimate when its total is $0.00 (est-15960.html has no Shop Supplies section).</t>
+          <t>bottom Adjustments block lists whole-WO adjustments in creation order (Flat fee -&gt; WFee -&gt; WDisc) | WORDING+VIU 2026-07-13: CONFIRMED live: bottom 'Adjustments' block lists items in creation order; percentage items show '(% of subtotal)'. NOTE: this build lists line-level items in the same block too.</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="2" t="inlineStr">
         <is>
-          <t>FD-DOC-009</t>
+          <t>FD-DOC-006</t>
         </is>
       </c>
       <c r="B45" s="2" t="inlineStr">
         <is>
-          <t>C28541</t>
+          <t>C28538</t>
         </is>
       </c>
       <c r="C45" s="6" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/28541</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/28538</t>
         </is>
       </c>
       <c r="D45" s="2" t="inlineStr">
         <is>
-          <t>Customer document — Shop Supplies (S14)</t>
+          <t>Customer document — Adjustments block</t>
         </is>
       </c>
       <c r="E45" s="2" t="inlineStr">
         <is>
-          <t>Verify Shop Supplies reappears on the customer views when its total becomes greater than $0.00</t>
+          <t>Verify line-level adjustments are grouped by name+type in the bottom block with a "(×N)" count</t>
         </is>
       </c>
       <c r="F45" s="2" t="inlineStr">
         <is>
-          <t>Low</t>
+          <t>High</t>
         </is>
       </c>
       <c r="G45" s="2" t="inlineStr">
@@ -2768,34 +2768,34 @@
       </c>
       <c r="I45" s="2" t="inlineStr">
         <is>
-          <t>prior (&gt;0 reappears) stands; today's probe inert — parts-only WO computes shop supplies on labor, stayed $0 | WORDING+VIU 2026-07-13: Shop-Supplies-reappears carried from prior VIU.</t>
+          <t>3 same-name+type line fees grouped as '(×3) $24.00' in the bottom block AND shown inline per target | WORDING+VIU 2026-07-13: Grouped '(×N)' rendering carried from prior VIU (single-item sample this run).</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="2" t="inlineStr">
         <is>
-          <t>FD-DOC-010</t>
+          <t>FD-DOC-007</t>
         </is>
       </c>
       <c r="B46" s="2" t="inlineStr">
         <is>
-          <t>C28542</t>
+          <t>C28539</t>
         </is>
       </c>
       <c r="C46" s="6" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/28542</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/28539</t>
         </is>
       </c>
       <c r="D46" s="2" t="inlineStr">
         <is>
-          <t>Customer document — line-level $0 target</t>
+          <t>Customer document — Processing Fee phrase</t>
         </is>
       </c>
       <c r="E46" s="2" t="inlineStr">
         <is>
-          <t>Verify a line-level adjustment on a not-billable (declined) line resolves to $0.00 but still shows</t>
+          <t>Verify a % of Grand Total Processing Fee shows the "% of grand total" phrase on the document</t>
         </is>
       </c>
       <c r="F46" s="2" t="inlineStr">
@@ -2815,34 +2815,34 @@
       </c>
       <c r="I46" s="2" t="inlineStr">
         <is>
-          <t>prior batch-4 declined-line $0-render stands; decline flip blocked today (staged-parts lock) | WORDING+VIU 2026-07-13: Declined-line $0-but-shows carried.</t>
+          <t>'(% of grand total)' phrase per batch evidence; pfee not seedable onto a money-bearing WO today (line-create 500 blocks a fresh WO with lines) | WORDING+VIU 2026-07-13: '% of grand total' phrase carried (no live pfee on the sample WO).</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="2" t="inlineStr">
         <is>
-          <t>FD-DOC-011</t>
+          <t>FD-DOC-008</t>
         </is>
       </c>
       <c r="B47" s="2" t="inlineStr">
         <is>
-          <t>C28543</t>
+          <t>C28540</t>
         </is>
       </c>
       <c r="C47" s="6" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/28543</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/28540</t>
         </is>
       </c>
       <c r="D47" s="2" t="inlineStr">
         <is>
-          <t>Customer document — layout</t>
+          <t>Customer document — Shop Supplies (S14)</t>
         </is>
       </c>
       <c r="E47" s="2" t="inlineStr">
         <is>
-          <t>Verify the Adjustments block sits after Labor/Parts/Shop Supplies and before Subtotal → Tax → Total</t>
+          <t>Verify Shop Supplies is hidden on the estimate/invoice/financial tab when the total is $0.00</t>
         </is>
       </c>
       <c r="F47" s="2" t="inlineStr">
@@ -2862,39 +2862,39 @@
       </c>
       <c r="I47" s="2" t="inlineStr">
         <is>
-          <t>FDBUG-1 NOT REPRODUCED (3rd consecutive pass): document bottom block reads Subtotal $202.68 / GST (5%) $9.14 / Total $211.82 = EXACTLY the API values incl. all adjustments; block sits before Subtotal. Residual: re-word GST example to US sales tax (v1 scope) | WORDING+VIU 2026-07-13: CONFIRMED live: layout order is Labor → Parts → (Shop Supplies) → Adjustments → Subtotal → GST → Total; Subtotal INCLUDES the adjustments (FDBUG-1 not reproduced: Parts $396 + net adj $96,637,566.11 = Subtotal $96,637,962.11).</t>
+          <t>Shop Supplies section HIDDEN on the estimate when total is $0.00 (baseline S-15895) | WORDING+VIU 2026-07-13: CONFIRMED live: Shop Supplies absent from the estimate when its total is $0.00 (est-15960.html has no Shop Supplies section).</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="2" t="inlineStr">
         <is>
-          <t>FD-EDIT-001</t>
+          <t>FD-DOC-009</t>
         </is>
       </c>
       <c r="B48" s="2" t="inlineStr">
         <is>
-          <t>C28476</t>
+          <t>C28541</t>
         </is>
       </c>
       <c r="C48" s="6" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/28476</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/28541</t>
         </is>
       </c>
       <c r="D48" s="2" t="inlineStr">
         <is>
-          <t>Work Order — Edit an adjustment</t>
+          <t>Customer document — Shop Supplies (S14)</t>
         </is>
       </c>
       <c r="E48" s="2" t="inlineStr">
         <is>
-          <t>Verify editing a fee/discount allows Name, amount, Max Amount and Taxable but locks Type, Calculation Type and Scope</t>
+          <t>Verify Shop Supplies reappears on the customer views when its total becomes greater than $0.00</t>
         </is>
       </c>
       <c r="F48" s="2" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Low</t>
         </is>
       </c>
       <c r="G48" s="2" t="inlineStr">
@@ -2909,34 +2909,34 @@
       </c>
       <c r="I48" s="2" t="inlineStr">
         <is>
-          <t>change accepts name/amount/maxCap/taxable only; kind/calc unchanged after edit (200) | WORDING+VIU 2026-07-13: Edit dialog confirmed live (shot edit-01): title 'Edit Fee / Discount'; Type + Calculation Type greyed/locked; Name/Amount/Taxable editable; opened from sidebar 'WO Fees &amp; Discounts' ⋮ &gt; Edit. | SV-8456 (2026-07-21 staging LIVE VIU): F&amp;D moved to SETTINGS→SERVICE (below Canned Lines); template/WO/Part-sale/customer dialogs now show Taxable as a Yes/No DROPDOWN (was toggle); Auto-apply is a CHECKBOX with a 'When on…' caption; settings &amp; customer tables are plain-text/left-aligned (no badges); WO sidebar card retitled 'Work Order Fees &amp; Discounts' and renders ABOVE Financial Info; Part-sale card 'Parts Sale Fees &amp; Discounts' above Financial Info. Permission gate pivoted Settings→Finance → Settings→Service (verified live: Service-user sees+manages F&amp;D &amp; convenience toggle; Finance-only user has no F&amp;D nav item and /administration/adjustment-templates bounces to /workorders). Frontend-only; functionality + calc INTACT. | RE-VIU 2026-07-22 LIVE (Batch 4, SV-8456 re-verify): access-check quick-login {admin} HTTP 200. Re-confirmed on current staging build — 8 UI corrections intact (Taxable Yes/No dropdown; Auto-apply checkbox+caption; modal field order Type/CalcType&gt;Name&gt;Amount&gt;Taxable+jur.note&gt;Auto-apply&gt;Description; Settings table plain-text left-aligned no badges; F&amp;D nav under SERVICE below Canned Lines; WO &amp; Part-Sale cards above Financial Info [Batch 2/3]; Customer 'Fees &amp; Discounts' tab mirrors Settings styling minus convenience toggle) AND Settings-&gt;Service permission pivot CONFIRMED live per role (seeded ServiceRole vs FinanceRole, assigned to Tech, Tech restored to Technician 50bf6a0d + verified, both ZZAUTOTEST roles deleted 204): Service-user sees+manages F&amp;D nav + convenience toggle, direct /administration/adjustment-templates loads; Finance-only user has NO F&amp;D nav, FINANCE=Payment Methods only, direct route bounces to /workorders. viu_status VIU-Verified re-confirmed. Ev build/fees-discounts/viu-sv8456-2026-07-22/ (01-settings-landing, 02-new-dialog, 03-customer-fd-tab, SVC-*, FIN-*).</t>
+          <t>prior (&gt;0 reappears) stands; today's probe inert — parts-only WO computes shop supplies on labor, stayed $0 | WORDING+VIU 2026-07-13: Shop-Supplies-reappears carried from prior VIU.</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="2" t="inlineStr">
         <is>
-          <t>FD-EDIT-002</t>
+          <t>FD-DOC-010</t>
         </is>
       </c>
       <c r="B49" s="2" t="inlineStr">
         <is>
-          <t>C28477</t>
+          <t>C28542</t>
         </is>
       </c>
       <c r="C49" s="6" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/28477</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/28542</t>
         </is>
       </c>
       <c r="D49" s="2" t="inlineStr">
         <is>
-          <t>Work Order — Edit an adjustment</t>
+          <t>Customer document — line-level $0 target</t>
         </is>
       </c>
       <c r="E49" s="2" t="inlineStr">
         <is>
-          <t>Verify editing re-works the amount against the current totals, hides the template picker, and uses a 'Save' button</t>
+          <t>Verify a line-level adjustment on a not-billable (declined) line resolves to $0.00 but still shows</t>
         </is>
       </c>
       <c r="F49" s="2" t="inlineStr">
@@ -2956,34 +2956,34 @@
       </c>
       <c r="I49" s="2" t="inlineStr">
         <is>
-          <t>edit 10%-&gt;20% re-resolved 34.15 against current totals; GST-&gt;US-tax re-word caveat stands | WORDING+VIU 2026-07-13: Confirmed live: no 'Apply From Template' picker in Edit; confirm button reads 'Save'; preview re-resolves against current totals (shot edit-01). | V1_3 (2026-07-17): Δ2 — Story 10 renamed 'history log' -&gt; 'audit log' (terminology only; gates/behavior/status unchanged). Notes-only touch: the reader-facing text of this case already uses the exact build labels ('Audit Log' ⋮ menu / 'Work Order Log' page) and carries no generic history-log prose. The internal `area`/section name is left as-is (TestRail section rename not authorized).</t>
+          <t>prior batch-4 declined-line $0-render stands; decline flip blocked today (staged-parts lock) | WORDING+VIU 2026-07-13: Declined-line $0-but-shows carried.</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="2" t="inlineStr">
         <is>
-          <t>FD-EDIT-003</t>
+          <t>FD-DOC-011</t>
         </is>
       </c>
       <c r="B50" s="2" t="inlineStr">
         <is>
-          <t>C28478</t>
+          <t>C28543</t>
         </is>
       </c>
       <c r="C50" s="6" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/28478</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/28543</t>
         </is>
       </c>
       <c r="D50" s="2" t="inlineStr">
         <is>
-          <t>Work Order — Edit an adjustment</t>
+          <t>Customer document — layout</t>
         </is>
       </c>
       <c r="E50" s="2" t="inlineStr">
         <is>
-          <t>Verify a failed save keeps the Edit dialog open and shows the error</t>
+          <t>Verify the Adjustments block sits after Labor/Parts/Shop Supplies and before Subtotal → Tax → Total</t>
         </is>
       </c>
       <c r="F50" s="2" t="inlineStr">
@@ -3003,34 +3003,34 @@
       </c>
       <c r="I50" s="2" t="inlineStr">
         <is>
-          <t>invalid edit (empty name + amount 0) -&gt; 400, original left intact | WORDING+VIU 2026-07-13: Behavior (dialog stays open on save error + error message) carried from prior VIU — not force-failed this run.</t>
+          <t>FDBUG-1 NOT REPRODUCED (3rd consecutive pass): document bottom block reads Subtotal $202.68 / GST (5%) $9.14 / Total $211.82 = EXACTLY the API values incl. all adjustments; block sits before Subtotal. Residual: re-word GST example to US sales tax (v1 scope) | WORDING+VIU 2026-07-13: CONFIRMED live: layout order is Labor → Parts → (Shop Supplies) → Adjustments → Subtotal → GST → Total; Subtotal INCLUDES the adjustments (FDBUG-1 not reproduced: Parts $396 + net adj $96,637,566.11 = Subtotal $96,637,962.11).</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" s="2" t="inlineStr">
         <is>
-          <t>FD-FIN-001</t>
+          <t>FD-EDIT-001</t>
         </is>
       </c>
       <c r="B51" s="2" t="inlineStr">
         <is>
-          <t>C28464</t>
+          <t>C28476</t>
         </is>
       </c>
       <c r="C51" s="6" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/28464</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/28476</t>
         </is>
       </c>
       <c r="D51" s="2" t="inlineStr">
         <is>
-          <t>Work Order — Financial Info card</t>
+          <t>Work Order — Edit an adjustment</t>
         </is>
       </c>
       <c r="E51" s="2" t="inlineStr">
         <is>
-          <t>Verify the Financial Info card shows a 'Fees &amp; Discounts (N)' line directly above Subtotal</t>
+          <t>Verify editing a fee/discount allows Name, amount, Max Amount and Taxable but locks Type, Calculation Type and Scope</t>
         </is>
       </c>
       <c r="F51" s="2" t="inlineStr">
@@ -3050,34 +3050,34 @@
       </c>
       <c r="I51" s="2" t="inlineStr">
         <is>
-          <t>'Fees &amp; Discounts (5)' collapsed row seen in Financial Info with net total | WORDING+VIU 2026-07-13: Financial Info card confirmed live: 'Fees &amp; Discounts (N)' row shows net in grey (shot fin-03). | SV-8479/8480 deconfliction 2026-07-22: line position pinned directly above Subtotal (was 'sits with the other money rows'/below Balance) per item 7. Absorbs dropped new case FD-WO-022. Hidden-when-zero stays in FD-FIN-003 (no change). | VIU 2026-07-22 LIVE: Financial Info order = Parts $40.00, Labor $509.90, Shop Supplies $53.54, Fees &amp; Discounts (10) $273.31, Subtotal $876.75, GST, Total, Balance — F&amp;D line renders directly above Subtotal. Ev: wo/FD-FIN-004-FD-WO-021-card-financialinfo.png, wo/lines-bodytext.txt.</t>
+          <t>change accepts name/amount/maxCap/taxable only; kind/calc unchanged after edit (200) | WORDING+VIU 2026-07-13: Edit dialog confirmed live (shot edit-01): title 'Edit Fee / Discount'; Type + Calculation Type greyed/locked; Name/Amount/Taxable editable; opened from sidebar 'WO Fees &amp; Discounts' ⋮ &gt; Edit. | SV-8456 (2026-07-21 staging LIVE VIU): F&amp;D moved to SETTINGS→SERVICE (below Canned Lines); template/WO/Part-sale/customer dialogs now show Taxable as a Yes/No DROPDOWN (was toggle); Auto-apply is a CHECKBOX with a 'When on…' caption; settings &amp; customer tables are plain-text/left-aligned (no badges); WO sidebar card retitled 'Work Order Fees &amp; Discounts' and renders ABOVE Financial Info; Part-sale card 'Parts Sale Fees &amp; Discounts' above Financial Info. Permission gate pivoted Settings→Finance → Settings→Service (verified live: Service-user sees+manages F&amp;D &amp; convenience toggle; Finance-only user has no F&amp;D nav item and /administration/adjustment-templates bounces to /workorders). Frontend-only; functionality + calc INTACT. | RE-VIU 2026-07-22 LIVE (Batch 4, SV-8456 re-verify): access-check quick-login {admin} HTTP 200. Re-confirmed on current staging build — 8 UI corrections intact (Taxable Yes/No dropdown; Auto-apply checkbox+caption; modal field order Type/CalcType&gt;Name&gt;Amount&gt;Taxable+jur.note&gt;Auto-apply&gt;Description; Settings table plain-text left-aligned no badges; F&amp;D nav under SERVICE below Canned Lines; WO &amp; Part-Sale cards above Financial Info [Batch 2/3]; Customer 'Fees &amp; Discounts' tab mirrors Settings styling minus convenience toggle) AND Settings-&gt;Service permission pivot CONFIRMED live per role (seeded ServiceRole vs FinanceRole, assigned to Tech, Tech restored to Technician 50bf6a0d + verified, both ZZAUTOTEST roles deleted 204): Service-user sees+manages F&amp;D nav + convenience toggle, direct /administration/adjustment-templates loads; Finance-only user has NO F&amp;D nav, FINANCE=Payment Methods only, direct route bounces to /workorders. viu_status VIU-Verified re-confirmed. Ev build/fees-discounts/viu-sv8456-2026-07-22/ (01-settings-landing, 02-new-dialog, 03-customer-fd-tab, SVC-*, FIN-*).</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" s="2" t="inlineStr">
         <is>
-          <t>FD-FIN-002</t>
+          <t>FD-EDIT-002</t>
         </is>
       </c>
       <c r="B52" s="2" t="inlineStr">
         <is>
-          <t>C28465</t>
+          <t>C28477</t>
         </is>
       </c>
       <c r="C52" s="6" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/28465</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/28477</t>
         </is>
       </c>
       <c r="D52" s="2" t="inlineStr">
         <is>
-          <t>Work Order — Financial Info card</t>
+          <t>Work Order — Edit an adjustment</t>
         </is>
       </c>
       <c r="E52" s="2" t="inlineStr">
         <is>
-          <t>Verify the Financial Info 'Fees &amp; Discounts' row lists each fee/discount and is read-only</t>
+          <t>Verify editing re-works the amount against the current totals, hides the template picker, and uses a 'Save' button</t>
         </is>
       </c>
       <c r="F52" s="2" t="inlineStr">
@@ -3097,34 +3097,34 @@
       </c>
       <c r="I52" s="2" t="inlineStr">
         <is>
-          <t>creation order re-proven on the document block (Flat fee &lt; WFee &lt; WDisc indices); read-only listing per batch-3 | WORDING+VIU 2026-07-13: Confirmed the Financial Info F&amp;D row is read-only (no add/edit/remove in this card).</t>
+          <t>edit 10%-&gt;20% re-resolved 34.15 against current totals; GST-&gt;US-tax re-word caveat stands | WORDING+VIU 2026-07-13: Confirmed live: no 'Apply From Template' picker in Edit; confirm button reads 'Save'; preview re-resolves against current totals (shot edit-01). | V1_3 (2026-07-17): Δ2 — Story 10 renamed 'history log' -&gt; 'audit log' (terminology only; gates/behavior/status unchanged). Notes-only touch: the reader-facing text of this case already uses the exact build labels ('Audit Log' ⋮ menu / 'Work Order Log' page) and carries no generic history-log prose. The internal `area`/section name is left as-is (TestRail section rename not authorized).</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" s="2" t="inlineStr">
         <is>
-          <t>FD-FIN-003</t>
+          <t>FD-EDIT-003</t>
         </is>
       </c>
       <c r="B53" s="2" t="inlineStr">
         <is>
-          <t>C28466</t>
+          <t>C28478</t>
         </is>
       </c>
       <c r="C53" s="6" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/28466</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/28478</t>
         </is>
       </c>
       <c r="D53" s="2" t="inlineStr">
         <is>
-          <t>Work Order — Financial Info card</t>
+          <t>Work Order — Edit an adjustment</t>
         </is>
       </c>
       <c r="E53" s="2" t="inlineStr">
         <is>
-          <t>Verify the 'Fees &amp; Discounts' row is hidden with no fees/discounts, and the money section is hidden without See Financial Data</t>
+          <t>Verify a failed save keeps the Edit dialog open and shows the error</t>
         </is>
       </c>
       <c r="F53" s="2" t="inlineStr">
@@ -3144,34 +3144,34 @@
       </c>
       <c r="I53" s="2" t="inlineStr">
         <is>
-          <t>tech (no SFD): WO view masks money (sub_total/total '0.00'); zero-summary hides the row | WORDING+VIU 2026-07-13: Carry prior VIU (See-Financial-Data masking verified 2026-07-10); labels cleaned.</t>
+          <t>invalid edit (empty name + amount 0) -&gt; 400, original left intact | WORDING+VIU 2026-07-13: Behavior (dialog stays open on save error + error message) carried from prior VIU — not force-failed this run.</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" s="2" t="inlineStr">
         <is>
-          <t>FD-FIN-004</t>
+          <t>FD-FIN-001</t>
         </is>
       </c>
       <c r="B54" s="2" t="inlineStr">
         <is>
-          <t>C28467</t>
+          <t>C28464</t>
         </is>
       </c>
       <c r="C54" s="6" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/28467</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/28464</t>
         </is>
       </c>
       <c r="D54" s="2" t="inlineStr">
         <is>
-          <t>Work Order — Sidebar 'Work Order Fee / Discount' card</t>
+          <t>Work Order — Financial Info card</t>
         </is>
       </c>
       <c r="E54" s="2" t="inlineStr">
         <is>
-          <t>Verify the Work Order Fees &amp; Discounts card lists whole-work-order fees/discounts as plain text (percentage in brackets, no colored badge)</t>
+          <t>Verify the Financial Info card shows a 'Fees &amp; Discounts (N)' line directly above Subtotal</t>
         </is>
       </c>
       <c r="F54" s="2" t="inlineStr">
@@ -3191,34 +3191,34 @@
       </c>
       <c r="I54" s="2" t="inlineStr">
         <is>
-          <t>card renders 'WO Fees &amp; Discounts / Flat fee $12.00 +$12.00' — label/name drift vs spec wording persists (case-update) | WORDING+VIU 2026-07-13: Sidebar card title is 'WO Fees &amp; Discounts' (was 'Work Order Fee / Discount'); per-row ⋮ menu shows 'Edit' and 'Remove' (confirmed live, shot fin-03). Now build-accurate. | SV-8456 (2026-07-21 staging LIVE VIU): F&amp;D moved to SETTINGS→SERVICE (below Canned Lines); template/WO/Part-sale/customer dialogs now show Taxable as a Yes/No DROPDOWN (was toggle); Auto-apply is a CHECKBOX with a 'When on…' caption; settings &amp; customer tables are plain-text/left-aligned (no badges); WO sidebar card retitled 'Work Order Fees &amp; Discounts' and renders ABOVE Financial Info; Part-sale card 'Parts Sale Fees &amp; Discounts' above Financial Info. Permission gate pivoted Settings→Finance → Settings→Service (verified live: Service-user sees+manages F&amp;D &amp; convenience toggle; Finance-only user has no F&amp;D nav item and /administration/adjustment-templates bounces to /workorders). Frontend-only; functionality + calc INTACT. | SV-8479/8480 deconfliction 2026-07-22: card entries reworded from 'signed rate badge' to plain text with bracketed percent + sign rule (item 5). Absorbs dropped new case FD-WO-020. Item-6 disclaimer intentionally left to FD-WO-021 (kept) to avoid duplication. | VIU 2026-07-22 LIVE: card titled 'Work Order Fees &amp; Discounts', lists only whole-WO entries as plain text with bracketed percent — fee 'Customer Fee (10%) +$65.88', discount 'WO Disc (−5%) −$32.94', flat 'Flat Fee 2 +$32.00'/'Flat Fee +$11.00' (name+amount, no brackets); each entry has a ⋮ menu; card renders above Financial Info. Ev: wo/FD-FIN-004-FD-WO-021-card-financialinfo.png, wo/lines-bodytext.txt. | RE-VIU 2026-07-22 LIVE (Batch 4, SV-8456 re-verify): access-check quick-login {admin} HTTP 200. Re-confirmed on current staging build — 8 UI corrections intact (Taxable Yes/No dropdown; Auto-apply checkbox+caption; modal field order Type/CalcType&gt;Name&gt;Amount&gt;Taxable+jur.note&gt;Auto-apply&gt;Description; Settings table plain-text left-aligned no badges; F&amp;D nav under SERVICE below Canned Lines; WO &amp; Part-Sale cards above Financial Info [Batch 2/3]; Customer 'Fees &amp; Discounts' tab mirrors Settings styling minus convenience toggle) AND Settings-&gt;Service permission pivot CONFIRMED live per role (seeded ServiceRole vs FinanceRole, assigned to Tech, Tech restored to Technician 50bf6a0d + verified, both ZZAUTOTEST roles deleted 204): Service-user sees+manages F&amp;D nav + convenience toggle, direct /administration/adjustment-templates loads; Finance-only user has NO F&amp;D nav, FINANCE=Payment Methods only, direct route bounces to /workorders. viu_status VIU-Verified re-confirmed. Ev build/fees-discounts/viu-sv8456-2026-07-22/ (01-settings-landing, 02-new-dialog, 03-customer-fd-tab, SVC-*, FIN-*).</t>
+          <t>'Fees &amp; Discounts (5)' collapsed row seen in Financial Info with net total | WORDING+VIU 2026-07-13: Financial Info card confirmed live: 'Fees &amp; Discounts (N)' row shows net in grey (shot fin-03). | SV-8479/8480 deconfliction 2026-07-22: line position pinned directly above Subtotal (was 'sits with the other money rows'/below Balance) per item 7. Absorbs dropped new case FD-WO-022. Hidden-when-zero stays in FD-FIN-003 (no change). | VIU 2026-07-22 LIVE: Financial Info order = Parts $40.00, Labor $509.90, Shop Supplies $53.54, Fees &amp; Discounts (10) $273.31, Subtotal $876.75, GST, Total, Balance — F&amp;D line renders directly above Subtotal. Ev: wo/FD-FIN-004-FD-WO-021-card-financialinfo.png, wo/lines-bodytext.txt.</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" s="2" t="inlineStr">
         <is>
-          <t>FD-FIN-005</t>
+          <t>FD-FIN-002</t>
         </is>
       </c>
       <c r="B55" s="2" t="inlineStr">
         <is>
-          <t>C28468</t>
+          <t>C28465</t>
         </is>
       </c>
       <c r="C55" s="6" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/28468</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/28465</t>
         </is>
       </c>
       <c r="D55" s="2" t="inlineStr">
         <is>
-          <t>Work Order — Sidebar 'Work Order Fee / Discount' card</t>
+          <t>Work Order — Financial Info card</t>
         </is>
       </c>
       <c r="E55" s="2" t="inlineStr">
         <is>
-          <t>Verify the sidebar 'Work Order Fees &amp; Discounts' card is hidden with no whole-work-order fees/discounts and has no Add button</t>
+          <t>Verify the Financial Info 'Fees &amp; Discounts' row lists each fee/discount and is read-only</t>
         </is>
       </c>
       <c r="F55" s="2" t="inlineStr">
@@ -3238,39 +3238,39 @@
       </c>
       <c r="I55" s="2" t="inlineStr">
         <is>
-          <t>sidebar card present with entries + no Add control (re-observed); hidden-when-none per batch-3 | WORDING+VIU 2026-07-13: Card title corrected to 'WO Fees &amp; Discounts'. | SV-8456 (2026-07-21 staging LIVE VIU): F&amp;D moved to SETTINGS→SERVICE (below Canned Lines); template/WO/Part-sale/customer dialogs now show Taxable as a Yes/No DROPDOWN (was toggle); Auto-apply is a CHECKBOX with a 'When on…' caption; settings &amp; customer tables are plain-text/left-aligned (no badges); WO sidebar card retitled 'Work Order Fees &amp; Discounts' and renders ABOVE Financial Info; Part-sale card 'Parts Sale Fees &amp; Discounts' above Financial Info. Permission gate pivoted Settings→Finance → Settings→Service (verified live: Service-user sees+manages F&amp;D &amp; convenience toggle; Finance-only user has no F&amp;D nav item and /administration/adjustment-templates bounces to /workorders). Frontend-only; functionality + calc INTACT. | RE-VIU 2026-07-22 LIVE (Batch 4, SV-8456 re-verify): access-check quick-login {admin} HTTP 200. Re-confirmed on current staging build — 8 UI corrections intact (Taxable Yes/No dropdown; Auto-apply checkbox+caption; modal field order Type/CalcType&gt;Name&gt;Amount&gt;Taxable+jur.note&gt;Auto-apply&gt;Description; Settings table plain-text left-aligned no badges; F&amp;D nav under SERVICE below Canned Lines; WO &amp; Part-Sale cards above Financial Info [Batch 2/3]; Customer 'Fees &amp; Discounts' tab mirrors Settings styling minus convenience toggle) AND Settings-&gt;Service permission pivot CONFIRMED live per role (seeded ServiceRole vs FinanceRole, assigned to Tech, Tech restored to Technician 50bf6a0d + verified, both ZZAUTOTEST roles deleted 204): Service-user sees+manages F&amp;D nav + convenience toggle, direct /administration/adjustment-templates loads; Finance-only user has NO F&amp;D nav, FINANCE=Payment Methods only, direct route bounces to /workorders. viu_status VIU-Verified re-confirmed. Ev build/fees-discounts/viu-sv8456-2026-07-22/ (01-settings-landing, 02-new-dialog, 03-customer-fd-tab, SVC-*, FIN-*).</t>
+          <t>creation order re-proven on the document block (Flat fee &lt; WFee &lt; WDisc indices); read-only listing per batch-3 | WORDING+VIU 2026-07-13: Confirmed the Financial Info F&amp;D row is read-only (no add/edit/remove in this card).</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" s="2" t="inlineStr">
         <is>
-          <t>FD-HIST-001</t>
+          <t>FD-FIN-003</t>
         </is>
       </c>
       <c r="B56" s="2" t="inlineStr">
         <is>
-          <t>C28560</t>
+          <t>C28466</t>
         </is>
       </c>
       <c r="C56" s="6" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/28560</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/28466</t>
         </is>
       </c>
       <c r="D56" s="2" t="inlineStr">
         <is>
-          <t>Audit log</t>
+          <t>Work Order — Financial Info card</t>
         </is>
       </c>
       <c r="E56" s="2" t="inlineStr">
         <is>
-          <t>Verify one audit-log entry per add/edit/remove with the correct bold event labels</t>
+          <t>Verify the 'Fees &amp; Discounts' row is hidden with no fees/discounts, and the money section is hidden without See Financial Data</t>
         </is>
       </c>
       <c r="F56" s="2" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="G56" s="2" t="inlineStr">
@@ -3285,34 +3285,34 @@
       </c>
       <c r="I56" s="2" t="inlineStr">
         <is>
-          <t>FDBUG-3 CONFIRMED AGAIN: auto-applied adjustments (auto template + auto pfees) write NO history entry (fresh WO: 1 auto adjustment, 0 adjustment events); manual add/edit/remove ARE logged (added=15/updated=1/removed=15 in today's battery) | V1_2 (2026-07-13): history-log gate updated per S13-R10 — WO-level history requires Work Orders: Create and Edit; line-level history requires Work Order Lines: Create and Edit (was View History Logs). Expected/preconditions updated; needs live re-VIU. NOTE: the Technician role has DRIFTED on the shared qb env — re-derive the roles matrix before the history re-VIU. | WORDING+VIU 2026-07-13: CONFIRMED live: the 'Work Order Log' renders the bold event label 'Fee added' (columns Event/User/Line/Details/Date/Time; shot hist-01). Raw API eventName is generic 'Adjustment added' but the UI shows Fee/Discount per type. | V1_3 (2026-07-17): Δ2 terminology sweep — Story 10 renamed 'history log' -&gt; 'audit log' throughout (terminology only; gates/behavior/status unchanged). Generic 'history log / history entry / work-order history' prose replaced with 'audit log / audit-log entry'; the exact build labels 'Audit Log' (⋮ menu) and 'Work Order Log' (page) kept per Standing Rule 9. TestRail section name left as-is (rename not authorized).</t>
+          <t>tech (no SFD): WO view masks money (sub_total/total '0.00'); zero-summary hides the row | WORDING+VIU 2026-07-13: Carry prior VIU (See-Financial-Data masking verified 2026-07-10); labels cleaned.</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" s="2" t="inlineStr">
         <is>
-          <t>FD-HIST-002</t>
+          <t>FD-FIN-004</t>
         </is>
       </c>
       <c r="B57" s="2" t="inlineStr">
         <is>
-          <t>C28561</t>
+          <t>C28467</t>
         </is>
       </c>
       <c r="C57" s="6" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/28561</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/28467</t>
         </is>
       </c>
       <c r="D57" s="2" t="inlineStr">
         <is>
-          <t>Audit log</t>
+          <t>Work Order — Sidebar 'Work Order Fee / Discount' card</t>
         </is>
       </c>
       <c r="E57" s="2" t="inlineStr">
         <is>
-          <t>Verify the audit-log Details show Name, Amount (the set rate) and what it was applied to</t>
+          <t>Verify the Work Order Fees &amp; Discounts card lists whole-work-order fees/discounts as plain text (percentage in brackets, no colored badge)</t>
         </is>
       </c>
       <c r="F57" s="2" t="inlineStr">
@@ -3332,34 +3332,34 @@
       </c>
       <c r="I57" s="2" t="inlineStr">
         <is>
-          <t>FDBUG-11 (details omit 'Type:' line) per batch-1; entry payload captured today (eventType/eventName/user fields); UI detail block not re-driven | V1_2 (2026-07-13): history-log gate updated per S13-R10 — WO-level history requires Work Orders: Create and Edit; line-level history requires Work Order Lines: Create and Edit (was View History Logs). Expected/preconditions updated; needs live re-VIU. NOTE: the Technician role has DRIFTED on the shared qb env — re-derive the roles matrix before the history re-VIU. | WORDING+VIU 2026-07-13: CONFIRMED live: the Details column shows 'Name: &lt;name&gt;  Amount: &lt;set rate&gt;  Applied to: &lt;target&gt;' (shot hist-01; a flat fee showed 'Amount: $50,000,000.00' = the set rate). | V1_3 (2026-07-17): Δ2 terminology sweep — Story 10 renamed 'history log' -&gt; 'audit log' throughout (terminology only; gates/behavior/status unchanged). Generic 'history log / history entry / work-order history' prose replaced with 'audit log / audit-log entry'; the exact build labels 'Audit Log' (⋮ menu) and 'Work Order Log' (page) kept per Standing Rule 9. TestRail section name left as-is (rename not authorized).</t>
+          <t>card renders 'WO Fees &amp; Discounts / Flat fee $12.00 +$12.00' — label/name drift vs spec wording persists (case-update) | WORDING+VIU 2026-07-13: Sidebar card title is 'WO Fees &amp; Discounts' (was 'Work Order Fee / Discount'); per-row ⋮ menu shows 'Edit' and 'Remove' (confirmed live, shot fin-03). Now build-accurate. | SV-8456 (2026-07-21 staging LIVE VIU): F&amp;D moved to SETTINGS→SERVICE (below Canned Lines); template/WO/Part-sale/customer dialogs now show Taxable as a Yes/No DROPDOWN (was toggle); Auto-apply is a CHECKBOX with a 'When on…' caption; settings &amp; customer tables are plain-text/left-aligned (no badges); WO sidebar card retitled 'Work Order Fees &amp; Discounts' and renders ABOVE Financial Info; Part-sale card 'Parts Sale Fees &amp; Discounts' above Financial Info. Permission gate pivoted Settings→Finance → Settings→Service (verified live: Service-user sees+manages F&amp;D &amp; convenience toggle; Finance-only user has no F&amp;D nav item and /administration/adjustment-templates bounces to /workorders). Frontend-only; functionality + calc INTACT. | SV-8479/8480 deconfliction 2026-07-22: card entries reworded from 'signed rate badge' to plain text with bracketed percent + sign rule (item 5). Absorbs dropped new case FD-WO-020. Item-6 disclaimer intentionally left to FD-WO-021 (kept) to avoid duplication. | VIU 2026-07-22 LIVE: card titled 'Work Order Fees &amp; Discounts', lists only whole-WO entries as plain text with bracketed percent — fee 'Customer Fee (10%) +$65.88', discount 'WO Disc (−5%) −$32.94', flat 'Flat Fee 2 +$32.00'/'Flat Fee +$11.00' (name+amount, no brackets); each entry has a ⋮ menu; card renders above Financial Info. Ev: wo/FD-FIN-004-FD-WO-021-card-financialinfo.png, wo/lines-bodytext.txt. | RE-VIU 2026-07-22 LIVE (Batch 4, SV-8456 re-verify): access-check quick-login {admin} HTTP 200. Re-confirmed on current staging build — 8 UI corrections intact (Taxable Yes/No dropdown; Auto-apply checkbox+caption; modal field order Type/CalcType&gt;Name&gt;Amount&gt;Taxable+jur.note&gt;Auto-apply&gt;Description; Settings table plain-text left-aligned no badges; F&amp;D nav under SERVICE below Canned Lines; WO &amp; Part-Sale cards above Financial Info [Batch 2/3]; Customer 'Fees &amp; Discounts' tab mirrors Settings styling minus convenience toggle) AND Settings-&gt;Service permission pivot CONFIRMED live per role (seeded ServiceRole vs FinanceRole, assigned to Tech, Tech restored to Technician 50bf6a0d + verified, both ZZAUTOTEST roles deleted 204): Service-user sees+manages F&amp;D nav + convenience toggle, direct /administration/adjustment-templates loads; Finance-only user has NO F&amp;D nav, FINANCE=Payment Methods only, direct route bounces to /workorders. viu_status VIU-Verified re-confirmed. Ev build/fees-discounts/viu-sv8456-2026-07-22/ (01-settings-landing, 02-new-dialog, 03-customer-fd-tab, SVC-*, FIN-*).</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" s="2" t="inlineStr">
         <is>
-          <t>FD-HIST-003</t>
+          <t>FD-FIN-005</t>
         </is>
       </c>
       <c r="B58" s="2" t="inlineStr">
         <is>
-          <t>C28562</t>
+          <t>C28468</t>
         </is>
       </c>
       <c r="C58" s="6" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/28562</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/28468</t>
         </is>
       </c>
       <c r="D58" s="2" t="inlineStr">
         <is>
-          <t>Audit log</t>
+          <t>Work Order — Sidebar 'Work Order Fee / Discount' card</t>
         </is>
       </c>
       <c r="E58" s="2" t="inlineStr">
         <is>
-          <t>Verify the Line column and saved-state icon on a fee/discount audit-log entry</t>
+          <t>Verify the sidebar 'Work Order Fees &amp; Discounts' card is hidden with no whole-work-order fees/discounts and has no Add button</t>
         </is>
       </c>
       <c r="F58" s="2" t="inlineStr">
@@ -3379,39 +3379,39 @@
       </c>
       <c r="I58" s="2" t="inlineStr">
         <is>
-          <t>adjustment entries carry lineId=null -&gt; Line column '−'; saved-state icon empty per batch | V1_2 (2026-07-13): history-log gate updated per S13-R10 — WO-level history requires Work Orders: Create and Edit; line-level history requires Work Order Lines: Create and Edit (was View History Logs). Expected/preconditions updated; needs live re-VIU. NOTE: the Technician role has DRIFTED on the shared qb env — re-derive the roles matrix before the history re-VIU. | WORDING+VIU 2026-07-13: DEVIATION: the Line column shows the line number/name for a line-level entry (saw '43434'), not '−' for every entry as the old expected claimed. Confirmed live (shot hist-01). | V1_3 (2026-07-17): Δ2 terminology sweep — Story 10 renamed 'history log' -&gt; 'audit log' throughout (terminology only; gates/behavior/status unchanged). Generic 'history log / history entry / work-order history' prose replaced with 'audit log / audit-log entry'; the exact build labels 'Audit Log' (⋮ menu) and 'Work Order Log' (page) kept per Standing Rule 9. TestRail section name left as-is (rename not authorized).</t>
+          <t>sidebar card present with entries + no Add control (re-observed); hidden-when-none per batch-3 | WORDING+VIU 2026-07-13: Card title corrected to 'WO Fees &amp; Discounts'. | SV-8456 (2026-07-21 staging LIVE VIU): F&amp;D moved to SETTINGS→SERVICE (below Canned Lines); template/WO/Part-sale/customer dialogs now show Taxable as a Yes/No DROPDOWN (was toggle); Auto-apply is a CHECKBOX with a 'When on…' caption; settings &amp; customer tables are plain-text/left-aligned (no badges); WO sidebar card retitled 'Work Order Fees &amp; Discounts' and renders ABOVE Financial Info; Part-sale card 'Parts Sale Fees &amp; Discounts' above Financial Info. Permission gate pivoted Settings→Finance → Settings→Service (verified live: Service-user sees+manages F&amp;D &amp; convenience toggle; Finance-only user has no F&amp;D nav item and /administration/adjustment-templates bounces to /workorders). Frontend-only; functionality + calc INTACT. | RE-VIU 2026-07-22 LIVE (Batch 4, SV-8456 re-verify): access-check quick-login {admin} HTTP 200. Re-confirmed on current staging build — 8 UI corrections intact (Taxable Yes/No dropdown; Auto-apply checkbox+caption; modal field order Type/CalcType&gt;Name&gt;Amount&gt;Taxable+jur.note&gt;Auto-apply&gt;Description; Settings table plain-text left-aligned no badges; F&amp;D nav under SERVICE below Canned Lines; WO &amp; Part-Sale cards above Financial Info [Batch 2/3]; Customer 'Fees &amp; Discounts' tab mirrors Settings styling minus convenience toggle) AND Settings-&gt;Service permission pivot CONFIRMED live per role (seeded ServiceRole vs FinanceRole, assigned to Tech, Tech restored to Technician 50bf6a0d + verified, both ZZAUTOTEST roles deleted 204): Service-user sees+manages F&amp;D nav + convenience toggle, direct /administration/adjustment-templates loads; Finance-only user has NO F&amp;D nav, FINANCE=Payment Methods only, direct route bounces to /workorders. viu_status VIU-Verified re-confirmed. Ev build/fees-discounts/viu-sv8456-2026-07-22/ (01-settings-landing, 02-new-dialog, 03-customer-fd-tab, SVC-*, FIN-*).</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" s="2" t="inlineStr">
         <is>
-          <t>FD-HIST-005</t>
+          <t>FD-HIST-001</t>
         </is>
       </c>
       <c r="B59" s="2" t="inlineStr">
         <is>
-          <t>C28564</t>
+          <t>C28560</t>
         </is>
       </c>
       <c r="C59" s="6" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/28564</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/28560</t>
         </is>
       </c>
       <c r="D59" s="2" t="inlineStr">
         <is>
-          <t>Audit log — visibility</t>
+          <t>Audit log</t>
         </is>
       </c>
       <c r="E59" s="2" t="inlineStr">
         <is>
-          <t>Verify fee/discount audit-log entries stay visible when amounts are hidden by See Financial Data being off</t>
+          <t>Verify one audit-log entry per add/edit/remove with the correct bold event labels</t>
         </is>
       </c>
       <c r="F59" s="2" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>High</t>
         </is>
       </c>
       <c r="G59" s="2" t="inlineStr">
@@ -3426,34 +3426,34 @@
       </c>
       <c r="I59" s="2" t="inlineStr">
         <is>
-          <t>tech (no SFD): history GET 200 incl. F&amp;D entries with SET rate — history independent of SFD | V1_2 (2026-07-13): history-log gate updated per S13-R10 — WO-level history requires Work Orders: Create and Edit; line-level history requires Work Order Lines: Create and Edit (was View History Logs). Expected/preconditions updated; needs live re-VIU. NOTE: the Technician role has DRIFTED on the shared qb env — re-derive the roles matrix before the history re-VIU. | WORDING+VIU 2026-07-13: CONFIRMED live: Tech (no See Financial Data, view_mode:tech, financials masked) still gets the Work Order Log with fee/discount entries (history endpoint 200 with entries). The log shows the SET rate, so SFD does not gate it. | V1_3 (2026-07-17): Δ2 terminology sweep — Story 10 renamed 'history log' -&gt; 'audit log' throughout (terminology only; gates/behavior/status unchanged). Generic 'history log / history entry / work-order history' prose replaced with 'audit log / audit-log entry'; the exact build labels 'Audit Log' (⋮ menu) and 'Work Order Log' (page) kept per Standing Rule 9. TestRail section name left as-is (rename not authorized).</t>
+          <t>FDBUG-3 CONFIRMED AGAIN: auto-applied adjustments (auto template + auto pfees) write NO history entry (fresh WO: 1 auto adjustment, 0 adjustment events); manual add/edit/remove ARE logged (added=15/updated=1/removed=15 in today's battery) | V1_2 (2026-07-13): history-log gate updated per S13-R10 — WO-level history requires Work Orders: Create and Edit; line-level history requires Work Order Lines: Create and Edit (was View History Logs). Expected/preconditions updated; needs live re-VIU. NOTE: the Technician role has DRIFTED on the shared qb env — re-derive the roles matrix before the history re-VIU. | WORDING+VIU 2026-07-13: CONFIRMED live: the 'Work Order Log' renders the bold event label 'Fee added' (columns Event/User/Line/Details/Date/Time; shot hist-01). Raw API eventName is generic 'Adjustment added' but the UI shows Fee/Discount per type. | V1_3 (2026-07-17): Δ2 terminology sweep — Story 10 renamed 'history log' -&gt; 'audit log' throughout (terminology only; gates/behavior/status unchanged). Generic 'history log / history entry / work-order history' prose replaced with 'audit log / audit-log entry'; the exact build labels 'Audit Log' (⋮ menu) and 'Work Order Log' (page) kept per Standing Rule 9. TestRail section name left as-is (rename not authorized).</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" s="2" t="inlineStr">
         <is>
-          <t>FD-HIST-006</t>
+          <t>FD-HIST-002</t>
         </is>
       </c>
       <c r="B60" s="2" t="inlineStr">
         <is>
-          <t>C28565</t>
+          <t>C28561</t>
         </is>
       </c>
       <c r="C60" s="6" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/28565</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/28561</t>
         </is>
       </c>
       <c r="D60" s="2" t="inlineStr">
         <is>
-          <t>Audit log — permission</t>
+          <t>Audit log</t>
         </is>
       </c>
       <c r="E60" s="2" t="inlineStr">
         <is>
-          <t>Verify fee/discount audit-log entries are gated by Work Orders: Create and Edit (line audit log by Work Order Lines: Create and Edit)</t>
+          <t>Verify the audit-log Details show Name, Amount (the set rate) and what it was applied to</t>
         </is>
       </c>
       <c r="F60" s="2" t="inlineStr">
@@ -3473,34 +3473,34 @@
       </c>
       <c r="I60" s="2" t="inlineStr">
         <is>
-          <t>View History Logs is an FE display gate (tech got 200 + 56 adjustment entries); documented enforcement model | V1_2 (2026-07-13): history-log gate updated per S13-R10 — WO-level history requires Work Orders: Create and Edit; line-level history requires Work Order Lines: Create and Edit (was View History Logs). Expected/preconditions updated; needs live re-VIU. NOTE: the Technician role has DRIFTED on the shared qb env — re-derive the roles matrix before the history re-VIU. | WORDING+VIU 2026-07-13: Positive confirmed live (Tech has Work Orders/Work Order Lines: Create &amp; Edit → sees the log, 200). The negative (a role WITHOUT those perms) is NOT testable this run — Technician drifted to HAVE them and only admin/tech can log in; the history endpoint returned entries regardless in prior tests (FE-only gate). | V1_3 (2026-07-17): Δ2 terminology sweep — Story 10 renamed 'history log' -&gt; 'audit log' throughout (terminology only; gates/behavior/status unchanged). Generic 'history log / history entry / work-order history' prose replaced with 'audit log / audit-log entry'; the exact build labels 'Audit Log' (⋮ menu) and 'Work Order Log' (page) kept per Standing Rule 9. TestRail section name left as-is (rename not authorized).</t>
+          <t>FDBUG-11 (details omit 'Type:' line) per batch-1; entry payload captured today (eventType/eventName/user fields); UI detail block not re-driven | V1_2 (2026-07-13): history-log gate updated per S13-R10 — WO-level history requires Work Orders: Create and Edit; line-level history requires Work Order Lines: Create and Edit (was View History Logs). Expected/preconditions updated; needs live re-VIU. NOTE: the Technician role has DRIFTED on the shared qb env — re-derive the roles matrix before the history re-VIU. | WORDING+VIU 2026-07-13: CONFIRMED live: the Details column shows 'Name: &lt;name&gt;  Amount: &lt;set rate&gt;  Applied to: &lt;target&gt;' (shot hist-01; a flat fee showed 'Amount: $50,000,000.00' = the set rate). | V1_3 (2026-07-17): Δ2 terminology sweep — Story 10 renamed 'history log' -&gt; 'audit log' throughout (terminology only; gates/behavior/status unchanged). Generic 'history log / history entry / work-order history' prose replaced with 'audit log / audit-log entry'; the exact build labels 'Audit Log' (⋮ menu) and 'Work Order Log' (page) kept per Standing Rule 9. TestRail section name left as-is (rename not authorized).</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" s="2" t="inlineStr">
         <is>
-          <t>FD-HIST-007</t>
+          <t>FD-HIST-003</t>
         </is>
       </c>
       <c r="B61" s="2" t="inlineStr">
         <is>
-          <t>C28566</t>
+          <t>C28562</t>
         </is>
       </c>
       <c r="C61" s="6" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/28566</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/28562</t>
         </is>
       </c>
       <c r="D61" s="2" t="inlineStr">
         <is>
-          <t>Audit log — Processing Fee</t>
+          <t>Audit log</t>
         </is>
       </c>
       <c r="E61" s="2" t="inlineStr">
         <is>
-          <t>Verify a Processing Fee is logged as a fee applied to the full invoice, with no 'updated' entry</t>
+          <t>Verify the Line column and saved-state icon on a fee/discount audit-log entry</t>
         </is>
       </c>
       <c r="F61" s="2" t="inlineStr">
@@ -3520,39 +3520,39 @@
       </c>
       <c r="I61" s="2" t="inlineStr">
         <is>
-          <t>extends FDBUG-3: auto-added pfee NOT logged on add; REMOVAL logged; no 'updated' entries (manual base fee logged correctly) | V1_2 (2026-07-13): history-log gate updated per S13-R10 — WO-level history requires Work Orders: Create and Edit; line-level history requires Work Order Lines: Create and Edit (was View History Logs). Expected/preconditions updated; needs live re-VIU. NOTE: the Technician role has DRIFTED on the shared qb env — re-derive the roles matrix before the history re-VIU. | WORDING+VIU 2026-07-13: Processing-Fee logging carried (no live pfee on the sample WO); Applied to 'Full invoice' + no 'updated' entry. | V1_3 (2026-07-17): Δ2 — Story 10 renamed 'history log' -&gt; 'audit log' (terminology only; gates/behavior/status unchanged). Notes-only touch: the reader-facing text of this case already uses the exact build labels ('Audit Log' ⋮ menu / 'Work Order Log' page) and carries no generic history-log prose. The internal `area`/section name is left as-is (TestRail section rename not authorized).</t>
+          <t>adjustment entries carry lineId=null -&gt; Line column '−'; saved-state icon empty per batch | V1_2 (2026-07-13): history-log gate updated per S13-R10 — WO-level history requires Work Orders: Create and Edit; line-level history requires Work Order Lines: Create and Edit (was View History Logs). Expected/preconditions updated; needs live re-VIU. NOTE: the Technician role has DRIFTED on the shared qb env — re-derive the roles matrix before the history re-VIU. | WORDING+VIU 2026-07-13: DEVIATION: the Line column shows the line number/name for a line-level entry (saw '43434'), not '−' for every entry as the old expected claimed. Confirmed live (shot hist-01). | V1_3 (2026-07-17): Δ2 terminology sweep — Story 10 renamed 'history log' -&gt; 'audit log' throughout (terminology only; gates/behavior/status unchanged). Generic 'history log / history entry / work-order history' prose replaced with 'audit log / audit-log entry'; the exact build labels 'Audit Log' (⋮ menu) and 'Work Order Log' (page) kept per Standing Rule 9. TestRail section name left as-is (rename not authorized).</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" s="2" t="inlineStr">
         <is>
-          <t>FD-HIST-008</t>
+          <t>FD-HIST-005</t>
         </is>
       </c>
       <c r="B62" s="2" t="inlineStr">
         <is>
-          <t>C28567</t>
+          <t>C28564</t>
         </is>
       </c>
       <c r="C62" s="6" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/28567</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/28564</t>
         </is>
       </c>
       <c r="D62" s="2" t="inlineStr">
         <is>
-          <t>Audit log — edit entry</t>
+          <t>Audit log — visibility</t>
         </is>
       </c>
       <c r="E62" s="2" t="inlineStr">
         <is>
-          <t>Verify an edit that changes the rate records the new set rate (not the resolved total)</t>
+          <t>Verify fee/discount audit-log entries stay visible when amounts are hidden by See Financial Data being off</t>
         </is>
       </c>
       <c r="F62" s="2" t="inlineStr">
         <is>
-          <t>Low</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="G62" s="2" t="inlineStr">
@@ -3567,34 +3567,34 @@
       </c>
       <c r="I62" s="2" t="inlineStr">
         <is>
-          <t>work_order.adjustment.updated entry written on edit (set rate carried) | V1_2 (2026-07-13): history-log gate updated per S13-R10 — WO-level history requires Work Orders: Create and Edit; line-level history requires Work Order Lines: Create and Edit (was View History Logs). Expected/preconditions updated; needs live re-VIU. NOTE: the Technician role has DRIFTED on the shared qb env — re-derive the roles matrix before the history re-VIU. | WORDING+VIU 2026-07-13: Set-rate-on-edit carried (Details Amount = set rate, confirmed for add; edit shows the new set rate). | V1_3 (2026-07-17): Δ2 — Story 10 renamed 'history log' -&gt; 'audit log' (terminology only; gates/behavior/status unchanged). Notes-only touch: the reader-facing text of this case already uses the exact build labels ('Audit Log' ⋮ menu / 'Work Order Log' page) and carries no generic history-log prose. The internal `area`/section name is left as-is (TestRail section rename not authorized).</t>
+          <t>tech (no SFD): history GET 200 incl. F&amp;D entries with SET rate — history independent of SFD | V1_2 (2026-07-13): history-log gate updated per S13-R10 — WO-level history requires Work Orders: Create and Edit; line-level history requires Work Order Lines: Create and Edit (was View History Logs). Expected/preconditions updated; needs live re-VIU. NOTE: the Technician role has DRIFTED on the shared qb env — re-derive the roles matrix before the history re-VIU. | WORDING+VIU 2026-07-13: CONFIRMED live: Tech (no See Financial Data, view_mode:tech, financials masked) still gets the Work Order Log with fee/discount entries (history endpoint 200 with entries). The log shows the SET rate, so SFD does not gate it. | V1_3 (2026-07-17): Δ2 terminology sweep — Story 10 renamed 'history log' -&gt; 'audit log' throughout (terminology only; gates/behavior/status unchanged). Generic 'history log / history entry / work-order history' prose replaced with 'audit log / audit-log entry'; the exact build labels 'Audit Log' (⋮ menu) and 'Work Order Log' (page) kept per Standing Rule 9. TestRail section name left as-is (rename not authorized).</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" s="2" t="inlineStr">
         <is>
-          <t>FD-INLINE-001</t>
+          <t>FD-HIST-006</t>
         </is>
       </c>
       <c r="B63" s="2" t="inlineStr">
         <is>
-          <t>C28454</t>
+          <t>C28565</t>
         </is>
       </c>
       <c r="C63" s="6" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/28454</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/28565</t>
         </is>
       </c>
       <c r="D63" s="2" t="inlineStr">
         <is>
-          <t>Work Order — Inline display (Lines tab)</t>
+          <t>Audit log — permission</t>
         </is>
       </c>
       <c r="E63" s="2" t="inlineStr">
         <is>
-          <t>Verify a labor-line fee/discount shows inline under its line as plain text with a blank left label (no colored badge)</t>
+          <t>Verify fee/discount audit-log entries are gated by Work Orders: Create and Edit (line audit log by Work Order Lines: Create and Edit)</t>
         </is>
       </c>
       <c r="F63" s="2" t="inlineStr">
@@ -3614,39 +3614,39 @@
       </c>
       <c r="I63" s="2" t="inlineStr">
         <is>
-          <t>batch UI evidence stands; today's headless text capture did not surface inline rows (grid render timing) — API line adjustment placement re-proven (adjustments under lines/{wo}) | WORDING+VIU 2026-07-13: Inline row labelled 'Fees/Discounts' with ↳, name, rate badge, grey amount confirmed live (shot fin-03). | SV-8479/8480 deconfliction 2026-07-22: reworded to blank left label + plain-text/no-badge with the −X%/X% sign rule (items 3 &amp; 4). Absorbs dropped new case FD-WO-019 (labor half). | LIVE STAGING VIU 2026-07-22 (viu-sv8479-8480-2026-07-22/): sign convention RE-VERIFIED live on the Lines tab — a percentage labor FEE renders as a BARE '20%' (no sign) in plain grey text (HTML span text-grey-7, no colored badge/pill); a percentage DISCOUNT renders '−10%' (en-dash minus); resolved amount is signed on the right ('+$58.00' / '−$4.00'); '↳' arrow, blank left label. Wording accurate — no change. Ev: 018/019-lines-expanded-full.png. | VIU 2026-07-22 LIVE re-confirmed: '↳ Labor Fee 20%' (fee bare %, blank left label, plain text, no badge) '+$101.98'; '↳ Labor Disc −10% −$50.99' (discount minus). Ev: wo/inline-expanded-text.txt, wo/inline-expanded.png.</t>
+          <t>View History Logs is an FE display gate (tech got 200 + 56 adjustment entries); documented enforcement model | V1_2 (2026-07-13): history-log gate updated per S13-R10 — WO-level history requires Work Orders: Create and Edit; line-level history requires Work Order Lines: Create and Edit (was View History Logs). Expected/preconditions updated; needs live re-VIU. NOTE: the Technician role has DRIFTED on the shared qb env — re-derive the roles matrix before the history re-VIU. | WORDING+VIU 2026-07-13: Positive confirmed live (Tech has Work Orders/Work Order Lines: Create &amp; Edit → sees the log, 200). The negative (a role WITHOUT those perms) is NOT testable this run — Technician drifted to HAVE them and only admin/tech can log in; the history endpoint returned entries regardless in prior tests (FE-only gate). | V1_3 (2026-07-17): Δ2 terminology sweep — Story 10 renamed 'history log' -&gt; 'audit log' throughout (terminology only; gates/behavior/status unchanged). Generic 'history log / history entry / work-order history' prose replaced with 'audit log / audit-log entry'; the exact build labels 'Audit Log' (⋮ menu) and 'Work Order Log' (page) kept per Standing Rule 9. TestRail section name left as-is (rename not authorized).</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" s="2" t="inlineStr">
         <is>
-          <t>FD-INLINE-002</t>
+          <t>FD-HIST-007</t>
         </is>
       </c>
       <c r="B64" s="2" t="inlineStr">
         <is>
-          <t>C28455</t>
+          <t>C28566</t>
         </is>
       </c>
       <c r="C64" s="6" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/28455</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/28566</t>
         </is>
       </c>
       <c r="D64" s="2" t="inlineStr">
         <is>
-          <t>Work Order — Inline display (Lines tab)</t>
+          <t>Audit log — Processing Fee</t>
         </is>
       </c>
       <c r="E64" s="2" t="inlineStr">
         <is>
-          <t>Verify a part-line fee/discount shows inline under its part as plain text (no colored badge)</t>
+          <t>Verify a Processing Fee is logged as a fee applied to the full invoice, with no 'updated' entry</t>
         </is>
       </c>
       <c r="F64" s="2" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="G64" s="2" t="inlineStr">
@@ -3661,39 +3661,39 @@
       </c>
       <c r="I64" s="2" t="inlineStr">
         <is>
-          <t>as FD-INLINE-001; part-line adjustment lives under the part in lines payload (re-proven) | WORDING+VIU 2026-07-13: Inline part-line row confirmed live (↳ yiy [badge] +amount ⋮, shot wo-01/fin-03). | SV-8479/8480 deconfliction 2026-07-22: reworded to plain-text/no-badge with the −X%/X% sign rule (item 4). Absorbs dropped new case FD-WO-019 (part half). | LIVE STAGING VIU 2026-07-22: part-line sign convention RE-VERIFIED live — a percentage part FEE renders bare '11%' (no sign) plain grey text (no badge); a percentage part DISCOUNT renders '−10%' (en-dash minus); resolved signed '+$4.40' / '−$4.00'. Wording accurate — no change. Ev: 018/019-lines-expanded-full.png. | VIU 2026-07-22 LIVE re-confirmed: '↳ Part Fee 11% +$4.40' plain text, no badge. Ev: wo/inline-expanded-text.txt.</t>
+          <t>extends FDBUG-3: auto-added pfee NOT logged on add; REMOVAL logged; no 'updated' entries (manual base fee logged correctly) | V1_2 (2026-07-13): history-log gate updated per S13-R10 — WO-level history requires Work Orders: Create and Edit; line-level history requires Work Order Lines: Create and Edit (was View History Logs). Expected/preconditions updated; needs live re-VIU. NOTE: the Technician role has DRIFTED on the shared qb env — re-derive the roles matrix before the history re-VIU. | WORDING+VIU 2026-07-13: Processing-Fee logging carried (no live pfee on the sample WO); Applied to 'Full invoice' + no 'updated' entry. | V1_3 (2026-07-17): Δ2 — Story 10 renamed 'history log' -&gt; 'audit log' (terminology only; gates/behavior/status unchanged). Notes-only touch: the reader-facing text of this case already uses the exact build labels ('Audit Log' ⋮ menu / 'Work Order Log' page) and carries no generic history-log prose. The internal `area`/section name is left as-is (TestRail section rename not authorized).</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" s="2" t="inlineStr">
         <is>
-          <t>FD-INLINE-004</t>
+          <t>FD-HIST-008</t>
         </is>
       </c>
       <c r="B65" s="2" t="inlineStr">
         <is>
-          <t>C28457</t>
+          <t>C28567</t>
         </is>
       </c>
       <c r="C65" s="6" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/28457</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/28567</t>
         </is>
       </c>
       <c r="D65" s="2" t="inlineStr">
         <is>
-          <t>Work Order — Inline display (Lines tab)</t>
+          <t>Audit log — edit entry</t>
         </is>
       </c>
       <c r="E65" s="2" t="inlineStr">
         <is>
-          <t>Verify the collapsed line Total adds the line's own fees and discounts (Labor + Parts + line fee/discount amounts, signed) — display only</t>
+          <t>Verify an edit that changes the rate records the new set rate (not the resolved total)</t>
         </is>
       </c>
       <c r="F65" s="2" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>Low</t>
         </is>
       </c>
       <c r="G65" s="2" t="inlineStr">
@@ -3708,24 +3708,24 @@
       </c>
       <c r="I65" s="2" t="inlineStr">
         <is>
-          <t>batch evidence stands (Total column incl own adjustments); not re-driven | WORDING+VIU 2026-07-13: Per-line Total stacks base + each adjustment; display-only. Labels cleaned. | SV-8480 (Story SV-8279, Done) 2026-07-22: strengthened to the explicit S3-R18 formula + $322.20 worked example + no-fee-line-unchanged sub-check. Kept inline-display scoped; the calc/document/flag-off ACs are owned by the new SV-8480 FD-CALC cases. viu_status unchanged (VIU-Verified) — re-observe at VIU. | LIVE STAGING VIU 2026-07-22 (viu-sv8479-8480-2026-07-22/): RE-CONFIRMED live — the collapsed line Total on the Lines tab adds the line's own SIGNED fee/discount amounts on top of gross Labor + Parts: $392.40 with a labor fee +20% ($58.00) + part fee +11% ($4.40) on a $290 labor / $40 parts line; $330.00 gross when the line has no fees; display-only, no stored value changes. Ev: 018-lines-collapsed-full.png, 020-lines-nofee-line.png, api-FD-CALC-018-024-total_cost-392.40.json.</t>
+          <t>work_order.adjustment.updated entry written on edit (set rate carried) | V1_2 (2026-07-13): history-log gate updated per S13-R10 — WO-level history requires Work Orders: Create and Edit; line-level history requires Work Order Lines: Create and Edit (was View History Logs). Expected/preconditions updated; needs live re-VIU. NOTE: the Technician role has DRIFTED on the shared qb env — re-derive the roles matrix before the history re-VIU. | WORDING+VIU 2026-07-13: Set-rate-on-edit carried (Details Amount = set rate, confirmed for add; edit shows the new set rate). | V1_3 (2026-07-17): Δ2 — Story 10 renamed 'history log' -&gt; 'audit log' (terminology only; gates/behavior/status unchanged). Notes-only touch: the reader-facing text of this case already uses the exact build labels ('Audit Log' ⋮ menu / 'Work Order Log' page) and carries no generic history-log prose. The internal `area`/section name is left as-is (TestRail section rename not authorized).</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" s="2" t="inlineStr">
         <is>
-          <t>FD-INLINE-005</t>
+          <t>FD-INLINE-001</t>
         </is>
       </c>
       <c r="B66" s="2" t="inlineStr">
         <is>
-          <t>C28458</t>
+          <t>C28454</t>
         </is>
       </c>
       <c r="C66" s="6" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/28458</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/28454</t>
         </is>
       </c>
       <c r="D66" s="2" t="inlineStr">
@@ -3735,12 +3735,12 @@
       </c>
       <c r="E66" s="2" t="inlineStr">
         <is>
-          <t>Verify each inline fee/discount row has a ⋮ menu with Edit and Remove (when the work order is open and you have the matching Create and Edit permission)</t>
+          <t>Verify a labor-line fee/discount shows inline under its line as plain text with a blank left label (no colored badge)</t>
         </is>
       </c>
       <c r="F66" s="2" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>High</t>
         </is>
       </c>
       <c r="G66" s="2" t="inlineStr">
@@ -3755,39 +3755,39 @@
       </c>
       <c r="I66" s="2" t="inlineStr">
         <is>
-          <t>3-dot Edit|Remove menu on adjustment entries re-observed (card menu 'Edit | Remove') | WORDING+VIU 2026-07-13: Inline line ⋮ menu shows 'Edit' and 'Remove' (was 'Edit'/'Delete') — confirmed live (shot inline-01).</t>
+          <t>batch UI evidence stands; today's headless text capture did not surface inline rows (grid render timing) — API line adjustment placement re-proven (adjustments under lines/{wo}) | WORDING+VIU 2026-07-13: Inline row labelled 'Fees/Discounts' with ↳, name, rate badge, grey amount confirmed live (shot fin-03). | SV-8479/8480 deconfliction 2026-07-22: reworded to blank left label + plain-text/no-badge with the −X%/X% sign rule (items 3 &amp; 4). Absorbs dropped new case FD-WO-019 (labor half). | LIVE STAGING VIU 2026-07-22 (viu-sv8479-8480-2026-07-22/): sign convention RE-VERIFIED live on the Lines tab — a percentage labor FEE renders as a BARE '20%' (no sign) in plain grey text (HTML span text-grey-7, no colored badge/pill); a percentage DISCOUNT renders '−10%' (en-dash minus); resolved amount is signed on the right ('+$58.00' / '−$4.00'); '↳' arrow, blank left label. Wording accurate — no change. Ev: 018/019-lines-expanded-full.png. | VIU 2026-07-22 LIVE re-confirmed: '↳ Labor Fee 20%' (fee bare %, blank left label, plain text, no badge) '+$101.98'; '↳ Labor Disc −10% −$50.99' (discount minus). Ev: wo/inline-expanded-text.txt, wo/inline-expanded.png.</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" s="2" t="inlineStr">
         <is>
-          <t>FD-LABOR-001</t>
+          <t>FD-INLINE-002</t>
         </is>
       </c>
       <c r="B67" s="2" t="inlineStr">
         <is>
-          <t>C28439</t>
+          <t>C28455</t>
         </is>
       </c>
       <c r="C67" s="6" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/28439</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/28455</t>
         </is>
       </c>
       <c r="D67" s="2" t="inlineStr">
         <is>
-          <t>Work Order — Labor-line Fee/Discount</t>
+          <t>Work Order — Inline display (Lines tab)</t>
         </is>
       </c>
       <c r="E67" s="2" t="inlineStr">
         <is>
-          <t>Verify a labor line's fee/discount dialog opens locked to that line with title 'New Labor Fee / Discount'</t>
+          <t>Verify a part-line fee/discount shows inline under its part as plain text (no colored badge)</t>
         </is>
       </c>
       <c r="F67" s="2" t="inlineStr">
         <is>
-          <t>Critical</t>
+          <t>High</t>
         </is>
       </c>
       <c r="G67" s="2" t="inlineStr">
@@ -3802,34 +3802,34 @@
       </c>
       <c r="I67" s="2" t="inlineStr">
         <is>
-          <t>label drift (subtitle 'Applying to: {line}' without 'Line {N} Labor —' prefix) per batch-1; not re-driven today | WORDING+VIU 2026-07-13: Menu item is 'Add Fee/Discount'; dialog subtitle 'Applying to: &lt;line name&gt;' (no 'Line N Labor —' prefix) — matches build. Labor-line ⋮ menu not re-captured this run; confirmed by symmetry with the part-line flow (⋮ = 'Move' / 'Add Fee/Discount', dialog 'Applying to: &lt;name&gt;') + prior 2026-07-10 VIU. | SV-8479/8480 deconfliction 2026-07-22: title reworded 'Add new fee/discount' -&gt; 'New Labor Fee / Discount', subline 'Applying to: &lt;line&gt;' -&gt; 'Applying To: Line N Labor — &lt;name&gt;' (item 8); entry point = ⋮ left of technician + 'Add Labor Fee / Discount' (item 1). Absorbs dropped new case FD-WO-023. | VIU 2026-07-22 LIVE: labor dialog title 'New Labor Fee / Discount', subline 'Applying To: Line 1 Labor — ZZAUTOTEST 8480 line', scope locked. Ev: wo/FD-LABOR-001-labor-dialog.png, wo/labor-dialog-text.txt.</t>
+          <t>as FD-INLINE-001; part-line adjustment lives under the part in lines payload (re-proven) | WORDING+VIU 2026-07-13: Inline part-line row confirmed live (↳ yiy [badge] +amount ⋮, shot wo-01/fin-03). | SV-8479/8480 deconfliction 2026-07-22: reworded to plain-text/no-badge with the −X%/X% sign rule (item 4). Absorbs dropped new case FD-WO-019 (part half). | LIVE STAGING VIU 2026-07-22: part-line sign convention RE-VERIFIED live — a percentage part FEE renders bare '11%' (no sign) plain grey text (no badge); a percentage part DISCOUNT renders '−10%' (en-dash minus); resolved signed '+$4.40' / '−$4.00'. Wording accurate — no change. Ev: 018/019-lines-expanded-full.png. | VIU 2026-07-22 LIVE re-confirmed: '↳ Part Fee 11% +$4.40' plain text, no badge. Ev: wo/inline-expanded-text.txt.</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" s="2" t="inlineStr">
         <is>
-          <t>FD-LABOR-002</t>
+          <t>FD-INLINE-003</t>
         </is>
       </c>
       <c r="B68" s="2" t="inlineStr">
         <is>
-          <t>C28440</t>
+          <t>C28456</t>
         </is>
       </c>
       <c r="C68" s="6" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/28440</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/28456</t>
         </is>
       </c>
       <c r="D68" s="2" t="inlineStr">
         <is>
-          <t>Work Order — Labor-line Fee/Discount</t>
+          <t>Work Order — Inline display (Lines tab)</t>
         </is>
       </c>
       <c r="E68" s="2" t="inlineStr">
         <is>
-          <t>Verify a labor-line '% of Labor Total' fee works out against the line's labor price (10% of $150.00 → +$15.00)</t>
+          <t>Verify a line/part with 2 or more fees/discounts shows only the first plus a 'Show N more' toggle</t>
         </is>
       </c>
       <c r="F68" s="2" t="inlineStr">
@@ -3849,34 +3849,34 @@
       </c>
       <c r="I68" s="2" t="inlineStr">
         <is>
-          <t>pct_labor resolves against the line's LABOR total: on a 0-labor (parts-only) line 10% -&gt; $0.00 (correct base); $265-line evidence from batch-1 stands | WORDING+VIU 2026-07-13: Build labels; Calc default '% Of Labor Total' for labor scope. Labor-line ⋮ menu not re-captured this run; confirmed by symmetry with the part-line flow (⋮ = 'Move' / 'Add Fee/Discount', dialog 'Applying to: &lt;name&gt;') + prior 2026-07-10 VIU. | SV-8479/8480 deconfliction 2026-07-22: label sweep: navigation labels -&gt; 'Add Labor Fee / Discount' / 'New Labor Fee / Discount' (behavior/expected unchanged). | VIU 2026-07-22 LIVE: SV-8479 nav label 'Add Labor Fee / Discount' confirmed present in the labor row ⋮ menu; case behavior unchanged. Ev: wo/FD-WO-017-labor-menu-open.png.</t>
+          <t>CONFIRMED AGAIN: 2 adjustments on one part render with NO 'Show N more' collapse — PO Q5=B defect persists | WORDING+VIU 2026-07-13: DEVIATION carried (BUG-FD-5): no 'Show N more' collapse — a line/part with 2+ fees/discounts shows all of them. Not re-driven with a 3-adjustment line this run. | CLOSE-OUT 2026-07-24: accepted per Ahtasham QA live review 2026-07-24 (no bug). Status -&gt; VIU-Verified, wording unchanged. HONESTY (Rule 12/22): accepted on Ahtasham's live QA review — NOT re-observed by us this pass.</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" s="2" t="inlineStr">
         <is>
-          <t>FD-LABOR-004</t>
+          <t>FD-INLINE-004</t>
         </is>
       </c>
       <c r="B69" s="2" t="inlineStr">
         <is>
-          <t>C28442</t>
+          <t>C28457</t>
         </is>
       </c>
       <c r="C69" s="6" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/28442</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/28457</t>
         </is>
       </c>
       <c r="D69" s="2" t="inlineStr">
         <is>
-          <t>Work Order — Labor-line Fee/Discount</t>
+          <t>Work Order — Inline display (Lines tab)</t>
         </is>
       </c>
       <c r="E69" s="2" t="inlineStr">
         <is>
-          <t>Verify a labor-line flat amount is the exact amount with no quantity multiplier</t>
+          <t>Verify the collapsed line Total adds the line's own fees and discounts (Labor + Parts + line fee/discount amounts, signed) — display only</t>
         </is>
       </c>
       <c r="F69" s="2" t="inlineStr">
@@ -3896,34 +3896,34 @@
       </c>
       <c r="I69" s="2" t="inlineStr">
         <is>
-          <t>labor-line flat 9.99 -&gt; resolved 9.99 exactly, no quantity multiplier | WORDING+VIU 2026-07-13: Build labels; flat labor resolve carried. | SV-8479/8480 deconfliction 2026-07-22: label sweep: navigation labels -&gt; 'Add Labor Fee / Discount' / 'New Labor Fee / Discount' (behavior/expected unchanged). | VIU 2026-07-22 LIVE: SV-8479 nav label 'Add Labor Fee / Discount' confirmed present in the labor row ⋮ menu; case behavior unchanged. Ev: wo/FD-WO-017-labor-menu-open.png.</t>
+          <t>batch evidence stands (Total column incl own adjustments); not re-driven | WORDING+VIU 2026-07-13: Per-line Total stacks base + each adjustment; display-only. Labels cleaned. | SV-8480 (Story SV-8279, Done) 2026-07-22: strengthened to the explicit S3-R18 formula + $322.20 worked example + no-fee-line-unchanged sub-check. Kept inline-display scoped; the calc/document/flag-off ACs are owned by the new SV-8480 FD-CALC cases. viu_status unchanged (VIU-Verified) — re-observe at VIU. | LIVE STAGING VIU 2026-07-22 (viu-sv8479-8480-2026-07-22/): RE-CONFIRMED live — the collapsed line Total on the Lines tab adds the line's own SIGNED fee/discount amounts on top of gross Labor + Parts: $392.40 with a labor fee +20% ($58.00) + part fee +11% ($4.40) on a $290 labor / $40 parts line; $330.00 gross when the line has no fees; display-only, no stored value changes. Ev: 018-lines-collapsed-full.png, 020-lines-nofee-line.png, api-FD-CALC-018-024-total_cost-392.40.json.</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" s="2" t="inlineStr">
         <is>
-          <t>FD-LABOR-005</t>
+          <t>FD-INLINE-005</t>
         </is>
       </c>
       <c r="B70" s="2" t="inlineStr">
         <is>
-          <t>C28443</t>
+          <t>C28458</t>
         </is>
       </c>
       <c r="C70" s="6" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/28443</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/28458</t>
         </is>
       </c>
       <c r="D70" s="2" t="inlineStr">
         <is>
-          <t>Work Order — Labor-line Fee/Discount</t>
+          <t>Work Order — Inline display (Lines tab)</t>
         </is>
       </c>
       <c r="E70" s="2" t="inlineStr">
         <is>
-          <t>Verify a labor-line fee/discount works out to $0.00 when its line is not billable (declined)</t>
+          <t>Verify each inline fee/discount row has a ⋮ menu with Edit and Remove (when the work order is open and you have the matching Create and Edit permission)</t>
         </is>
       </c>
       <c r="F70" s="2" t="inlineStr">
@@ -3943,24 +3943,24 @@
       </c>
       <c r="I70" s="2" t="inlineStr">
         <is>
-          <t>prior decline-&gt;$0 evidence stands; today's decline flip blocked ('Can`t change status while there are staged parts' on S-15895's completed line; no fresh WO possible — line-create 500) | WORDING+VIU 2026-07-13: Declined-line $0 carried.</t>
+          <t>3-dot Edit|Remove menu on adjustment entries re-observed (card menu 'Edit | Remove') | WORDING+VIU 2026-07-13: Inline line ⋮ menu shows 'Edit' and 'Remove' (was 'Edit'/'Delete') — confirmed live (shot inline-01).</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" s="2" t="inlineStr">
         <is>
-          <t>FD-LABOR-006</t>
+          <t>FD-LABOR-001</t>
         </is>
       </c>
       <c r="B71" s="2" t="inlineStr">
         <is>
-          <t>C28444</t>
+          <t>C28439</t>
         </is>
       </c>
       <c r="C71" s="6" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/28444</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/28439</t>
         </is>
       </c>
       <c r="D71" s="2" t="inlineStr">
@@ -3970,12 +3970,12 @@
       </c>
       <c r="E71" s="2" t="inlineStr">
         <is>
-          <t>Verify deleting a labor line removes any fee/discount pointing to it</t>
+          <t>Verify a labor line's fee/discount dialog opens locked to that line with title 'New Labor Fee / Discount'</t>
         </is>
       </c>
       <c r="F71" s="2" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>Critical</t>
         </is>
       </c>
       <c r="G71" s="2" t="inlineStr">
@@ -3990,24 +3990,24 @@
       </c>
       <c r="I71" s="2" t="inlineStr">
         <is>
-          <t>prior (line delete removes its adjustment); not re-seedable today (line-create 500 env-wide) | WORDING+VIU 2026-07-13: Delete-line cascades; carried; build labels. | SV-8456 (2026-07-21 staging LIVE VIU): F&amp;D moved to SETTINGS→SERVICE (below Canned Lines); template/WO/Part-sale/customer dialogs now show Taxable as a Yes/No DROPDOWN (was toggle); Auto-apply is a CHECKBOX with a 'When on…' caption; settings &amp; customer tables are plain-text/left-aligned (no badges); WO sidebar card retitled 'Work Order Fees &amp; Discounts' and renders ABOVE Financial Info; Part-sale card 'Parts Sale Fees &amp; Discounts' above Financial Info. Permission gate pivoted Settings→Finance → Settings→Service (verified live: Service-user sees+manages F&amp;D &amp; convenience toggle; Finance-only user has no F&amp;D nav item and /administration/adjustment-templates bounces to /workorders). Frontend-only; functionality + calc INTACT. | RE-VIU 2026-07-22 LIVE (Batch 4, SV-8456 re-verify): access-check quick-login {admin} HTTP 200. Re-confirmed on current staging build — 8 UI corrections intact (Taxable Yes/No dropdown; Auto-apply checkbox+caption; modal field order Type/CalcType&gt;Name&gt;Amount&gt;Taxable+jur.note&gt;Auto-apply&gt;Description; Settings table plain-text left-aligned no badges; F&amp;D nav under SERVICE below Canned Lines; WO &amp; Part-Sale cards above Financial Info [Batch 2/3]; Customer 'Fees &amp; Discounts' tab mirrors Settings styling minus convenience toggle) AND Settings-&gt;Service permission pivot CONFIRMED live per role (seeded ServiceRole vs FinanceRole, assigned to Tech, Tech restored to Technician 50bf6a0d + verified, both ZZAUTOTEST roles deleted 204): Service-user sees+manages F&amp;D nav + convenience toggle, direct /administration/adjustment-templates loads; Finance-only user has NO F&amp;D nav, FINANCE=Payment Methods only, direct route bounces to /workorders. viu_status VIU-Verified re-confirmed. Ev build/fees-discounts/viu-sv8456-2026-07-22/ (01-settings-landing, 02-new-dialog, 03-customer-fd-tab, SVC-*, FIN-*).</t>
+          <t>label drift (subtitle 'Applying to: {line}' without 'Line {N} Labor —' prefix) per batch-1; not re-driven today | WORDING+VIU 2026-07-13: Menu item is 'Add Fee/Discount'; dialog subtitle 'Applying to: &lt;line name&gt;' (no 'Line N Labor —' prefix) — matches build. Labor-line ⋮ menu not re-captured this run; confirmed by symmetry with the part-line flow (⋮ = 'Move' / 'Add Fee/Discount', dialog 'Applying to: &lt;name&gt;') + prior 2026-07-10 VIU. | SV-8479/8480 deconfliction 2026-07-22: title reworded 'Add new fee/discount' -&gt; 'New Labor Fee / Discount', subline 'Applying to: &lt;line&gt;' -&gt; 'Applying To: Line N Labor — &lt;name&gt;' (item 8); entry point = ⋮ left of technician + 'Add Labor Fee / Discount' (item 1). Absorbs dropped new case FD-WO-023. | VIU 2026-07-22 LIVE: labor dialog title 'New Labor Fee / Discount', subline 'Applying To: Line 1 Labor — ZZAUTOTEST 8480 line', scope locked. Ev: wo/FD-LABOR-001-labor-dialog.png, wo/labor-dialog-text.txt.</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" s="2" t="inlineStr">
         <is>
-          <t>FD-LABOR-007</t>
+          <t>FD-LABOR-002</t>
         </is>
       </c>
       <c r="B72" s="2" t="inlineStr">
         <is>
-          <t>C28445</t>
+          <t>C28440</t>
         </is>
       </c>
       <c r="C72" s="6" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/28445</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/28440</t>
         </is>
       </c>
       <c r="D72" s="2" t="inlineStr">
@@ -4017,12 +4017,12 @@
       </c>
       <c r="E72" s="2" t="inlineStr">
         <is>
-          <t>Verify the labor-line 'Add Labor Fee / Discount' is hidden without Work Order Lines: Create &amp; Edit</t>
+          <t>Verify a labor-line '% of Labor Total' fee works out against the line's labor price (10% of $150.00 → +$15.00)</t>
         </is>
       </c>
       <c r="F72" s="2" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>High</t>
         </is>
       </c>
       <c r="G72" s="2" t="inlineStr">
@@ -4037,39 +4037,39 @@
       </c>
       <c r="I72" s="2" t="inlineStr">
         <is>
-          <t>FE gate per roles-matrix derivation; CAVEAT: shared-env Technician role drifted (now has more perms) — re-derive matrix before relying on per-role negatives | WORDING+VIU 2026-07-13: Line-add gated by Work Order Lines: Create &amp; Edit. NOTE: re-check the negative after the roles matrix is re-derived. | SV-8479/8480 deconfliction 2026-07-22: label updated 'Add Fee/Discount' -&gt; 'Add Labor Fee / Discount' + entry-point wording (item 1); permission behavior unchanged. | VIU 2026-07-22 LIVE: menu label 'Add Labor Fee / Discount' confirmed present; permission-negative behavior (hidden without Work Order Lines: Create &amp; Edit) unchanged from prior verification — role-negative not re-driven this UI batch.</t>
+          <t>pct_labor resolves against the line's LABOR total: on a 0-labor (parts-only) line 10% -&gt; $0.00 (correct base); $265-line evidence from batch-1 stands | WORDING+VIU 2026-07-13: Build labels; Calc default '% Of Labor Total' for labor scope. Labor-line ⋮ menu not re-captured this run; confirmed by symmetry with the part-line flow (⋮ = 'Move' / 'Add Fee/Discount', dialog 'Applying to: &lt;name&gt;') + prior 2026-07-10 VIU. | SV-8479/8480 deconfliction 2026-07-22: label sweep: navigation labels -&gt; 'Add Labor Fee / Discount' / 'New Labor Fee / Discount' (behavior/expected unchanged). | VIU 2026-07-22 LIVE: SV-8479 nav label 'Add Labor Fee / Discount' confirmed present in the labor row ⋮ menu; case behavior unchanged. Ev: wo/FD-WO-017-labor-menu-open.png.</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" s="2" t="inlineStr">
         <is>
-          <t>FD-PART-001</t>
+          <t>FD-LABOR-004</t>
         </is>
       </c>
       <c r="B73" s="2" t="inlineStr">
         <is>
-          <t>C28446</t>
+          <t>C28442</t>
         </is>
       </c>
       <c r="C73" s="6" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/28446</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/28442</t>
         </is>
       </c>
       <c r="D73" s="2" t="inlineStr">
         <is>
-          <t>Work Order / Parts — Part-line Fee/Discount</t>
+          <t>Work Order — Labor-line Fee/Discount</t>
         </is>
       </c>
       <c r="E73" s="2" t="inlineStr">
         <is>
-          <t>Verify a part's fee/discount dialog opens locked to that part with title 'New Part Fee / Discount'</t>
+          <t>Verify a labor-line flat amount is the exact amount with no quantity multiplier</t>
         </is>
       </c>
       <c r="F73" s="2" t="inlineStr">
         <is>
-          <t>Critical</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="G73" s="2" t="inlineStr">
@@ -4084,39 +4084,39 @@
       </c>
       <c r="I73" s="2" t="inlineStr">
         <is>
-          <t>FDBUG-14 label defects (missing 'Line {N} Part —' prefix, raw enum 'Pct_parts', part-% option mislabeled '% of Labor Total') per batch-4; part dialog not re-driven today | WORDING+VIU 2026-07-13: CONFIRMED live: part ⋮ = 'Move' / 'Add Fee/Discount'; dialog 'Add new fee/discount' with subtitle 'Applying to: &lt;part name&gt;' (NO 'Line N Part —' prefix — build differs from the old spec text); Calc default '% Of Parts Total' (shots line-01/02). Now build-accurate. | SV-8479/8480 deconfliction 2026-07-22: menu item 'Add Fee/Discount' -&gt; 'Add Part Fee / Discount' (item 2); title 'Add new fee/discount' -&gt; 'New Part Fee / Discount', subline 'Applying to: &lt;part&gt;' -&gt; 'Applying To: Line N Part — &lt;name&gt;' (item 9). Absorbs dropped new case FD-WO-024. | VIU 2026-07-22 LIVE: part menu label 'Add Part Fee / Discount' + dialog title 'New Part Fee / Discount', subline 'Applying To: Line 1 Part — Turbocharger Oil', default Calculation Type '% Of Parts Total'. Ev: wo/FD-PART-001-part-dialog.png, wo/part-dialog-text.txt.</t>
+          <t>labor-line flat 9.99 -&gt; resolved 9.99 exactly, no quantity multiplier | WORDING+VIU 2026-07-13: Build labels; flat labor resolve carried. | SV-8479/8480 deconfliction 2026-07-22: label sweep: navigation labels -&gt; 'Add Labor Fee / Discount' / 'New Labor Fee / Discount' (behavior/expected unchanged). | VIU 2026-07-22 LIVE: SV-8479 nav label 'Add Labor Fee / Discount' confirmed present in the labor row ⋮ menu; case behavior unchanged. Ev: wo/FD-WO-017-labor-menu-open.png.</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" s="2" t="inlineStr">
         <is>
-          <t>FD-PART-002</t>
+          <t>FD-LABOR-005</t>
         </is>
       </c>
       <c r="B74" s="2" t="inlineStr">
         <is>
-          <t>C28447</t>
+          <t>C28443</t>
         </is>
       </c>
       <c r="C74" s="6" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/28447</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/28443</t>
         </is>
       </c>
       <c r="D74" s="2" t="inlineStr">
         <is>
-          <t>Work Order / Parts — Part-line Fee/Discount</t>
+          <t>Work Order — Labor-line Fee/Discount</t>
         </is>
       </c>
       <c r="E74" s="2" t="inlineStr">
         <is>
-          <t>Verify a part-line flat amount is charged per item (amount x quantity): $5.00 x 3 → −$15.00</t>
+          <t>Verify a labor-line fee/discount works out to $0.00 when its line is not billable (declined)</t>
         </is>
       </c>
       <c r="F74" s="2" t="inlineStr">
         <is>
-          <t>Critical</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="G74" s="2" t="inlineStr">
@@ -4131,39 +4131,39 @@
       </c>
       <c r="I74" s="2" t="inlineStr">
         <is>
-          <t>per-item flat re-proven: $2.00 x qty 4 -&gt; $8.00 on S-15895's received part (estimate row 'ZZAUTOTEST PartFlat $8.00') | WORDING+VIU 2026-07-13: Per-item flat carried; build labels. | SV-8479/8480 deconfliction 2026-07-22: inline part-row rendering reworded from '−$5.00 flat rate badge' to plain text (item 4); per-item flat calc unchanged. | VIU 2026-07-22 LIVE: inline part fee renders plain text ('Part Fee 11% +$4.40'), no colored badge; per-item flat calc unchanged (verified prior passes). Ev: wo/inline-expanded-text.txt.</t>
+          <t>prior decline-&gt;$0 evidence stands; today's decline flip blocked ('Can`t change status while there are staged parts' on S-15895's completed line; no fresh WO possible — line-create 500) | WORDING+VIU 2026-07-13: Declined-line $0 carried.</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" s="2" t="inlineStr">
         <is>
-          <t>FD-PART-003</t>
+          <t>FD-LABOR-006</t>
         </is>
       </c>
       <c r="B75" s="2" t="inlineStr">
         <is>
-          <t>C28448</t>
+          <t>C28444</t>
         </is>
       </c>
       <c r="C75" s="6" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/28448</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/28444</t>
         </is>
       </c>
       <c r="D75" s="2" t="inlineStr">
         <is>
-          <t>Work Order / Parts — Part-line Fee/Discount</t>
+          <t>Work Order — Labor-line Fee/Discount</t>
         </is>
       </c>
       <c r="E75" s="2" t="inlineStr">
         <is>
-          <t>Verify a fee/discount can be added to a requested (not-yet-received) part and shows before it is picked</t>
+          <t>Verify deleting a labor line removes any fee/discount pointing to it</t>
         </is>
       </c>
       <c r="F75" s="2" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="G75" s="2" t="inlineStr">
@@ -4178,39 +4178,39 @@
       </c>
       <c r="I75" s="2" t="inlineStr">
         <is>
-          <t>prior batch-4 requested-state evidence stands; not re-seedable today (make-request -&gt; 400 'Part requests can`t be modified on completed line', line-create 500) | WORDING+VIU 2026-07-13: Add-to-requested-part carried; build labels. | SV-8479/8480 deconfliction 2026-07-22: label sweep: navigation labels -&gt; 'Add Part Fee / Discount' / 'New Part Fee / Discount' (behavior/expected unchanged). | VIU 2026-07-22 LIVE: SV-8479 nav label 'Add Part Fee / Discount' confirmed present in the part row ⋮ menu; case behavior unchanged. Ev: wo/FD-WO-018-part-menu.png.</t>
+          <t>prior (line delete removes its adjustment); not re-seedable today (line-create 500 env-wide) | WORDING+VIU 2026-07-13: Delete-line cascades; carried; build labels. | SV-8456 (2026-07-21 staging LIVE VIU): F&amp;D moved to SETTINGS→SERVICE (below Canned Lines); template/WO/Part-sale/customer dialogs now show Taxable as a Yes/No DROPDOWN (was toggle); Auto-apply is a CHECKBOX with a 'When on…' caption; settings &amp; customer tables are plain-text/left-aligned (no badges); WO sidebar card retitled 'Work Order Fees &amp; Discounts' and renders ABOVE Financial Info; Part-sale card 'Parts Sale Fees &amp; Discounts' above Financial Info. Permission gate pivoted Settings→Finance → Settings→Service (verified live: Service-user sees+manages F&amp;D &amp; convenience toggle; Finance-only user has no F&amp;D nav item and /administration/adjustment-templates bounces to /workorders). Frontend-only; functionality + calc INTACT. | RE-VIU 2026-07-22 LIVE (Batch 4, SV-8456 re-verify): access-check quick-login {admin} HTTP 200. Re-confirmed on current staging build — 8 UI corrections intact (Taxable Yes/No dropdown; Auto-apply checkbox+caption; modal field order Type/CalcType&gt;Name&gt;Amount&gt;Taxable+jur.note&gt;Auto-apply&gt;Description; Settings table plain-text left-aligned no badges; F&amp;D nav under SERVICE below Canned Lines; WO &amp; Part-Sale cards above Financial Info [Batch 2/3]; Customer 'Fees &amp; Discounts' tab mirrors Settings styling minus convenience toggle) AND Settings-&gt;Service permission pivot CONFIRMED live per role (seeded ServiceRole vs FinanceRole, assigned to Tech, Tech restored to Technician 50bf6a0d + verified, both ZZAUTOTEST roles deleted 204): Service-user sees+manages F&amp;D nav + convenience toggle, direct /administration/adjustment-templates loads; Finance-only user has NO F&amp;D nav, FINANCE=Payment Methods only, direct route bounces to /workorders. viu_status VIU-Verified re-confirmed. Ev build/fees-discounts/viu-sv8456-2026-07-22/ (01-settings-landing, 02-new-dialog, 03-customer-fd-tab, SVC-*, FIN-*).</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" s="2" t="inlineStr">
         <is>
-          <t>FD-PART-004</t>
+          <t>FD-LABOR-007</t>
         </is>
       </c>
       <c r="B76" s="2" t="inlineStr">
         <is>
-          <t>C28449</t>
+          <t>C28445</t>
         </is>
       </c>
       <c r="C76" s="6" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/28449</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/28445</t>
         </is>
       </c>
       <c r="D76" s="2" t="inlineStr">
         <is>
-          <t>Work Order / Parts — Part-line Fee/Discount</t>
+          <t>Work Order — Labor-line Fee/Discount</t>
         </is>
       </c>
       <c r="E76" s="2" t="inlineStr">
         <is>
-          <t>Verify a part-line '% of Parts Total' works out against quantity x sell price</t>
+          <t>Verify the labor-line 'Add Labor Fee / Discount' is hidden without Work Order Lines: Create &amp; Edit</t>
         </is>
       </c>
       <c r="F76" s="2" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="G76" s="2" t="inlineStr">
@@ -4225,24 +4225,24 @@
       </c>
       <c r="I76" s="2" t="inlineStr">
         <is>
-          <t>pct_parts re-proven: 10% of qty4 x 42.69 = 170.76 -&gt; $17.08 | WORDING+VIU 2026-07-13: %-of-parts base carried; build labels. | SV-8479/8480 deconfliction 2026-07-22: label sweep: navigation labels -&gt; 'Add Part Fee / Discount' / 'New Part Fee / Discount' (behavior/expected unchanged). | VIU 2026-07-22 LIVE: SV-8479 nav label 'Add Part Fee / Discount' confirmed present in the part row ⋮ menu; case behavior unchanged. Ev: wo/FD-WO-018-part-menu.png.</t>
+          <t>FE gate per roles-matrix derivation; CAVEAT: shared-env Technician role drifted (now has more perms) — re-derive matrix before relying on per-role negatives | WORDING+VIU 2026-07-13: Line-add gated by Work Order Lines: Create &amp; Edit. NOTE: re-check the negative after the roles matrix is re-derived. | SV-8479/8480 deconfliction 2026-07-22: label updated 'Add Fee/Discount' -&gt; 'Add Labor Fee / Discount' + entry-point wording (item 1); permission behavior unchanged. | VIU 2026-07-22 LIVE: menu label 'Add Labor Fee / Discount' confirmed present; permission-negative behavior (hidden without Work Order Lines: Create &amp; Edit) unchanged from prior verification — role-negative not re-driven this UI batch.</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" s="2" t="inlineStr">
         <is>
-          <t>FD-PART-006</t>
+          <t>FD-PART-001</t>
         </is>
       </c>
       <c r="B77" s="2" t="inlineStr">
         <is>
-          <t>C28451</t>
+          <t>C28446</t>
         </is>
       </c>
       <c r="C77" s="6" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/28451</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/28446</t>
         </is>
       </c>
       <c r="D77" s="2" t="inlineStr">
@@ -4252,12 +4252,12 @@
       </c>
       <c r="E77" s="2" t="inlineStr">
         <is>
-          <t>Verify a part-line fee/discount works out to $0.00 when the part is declined or returned with no quantity left</t>
+          <t>Verify a part's fee/discount dialog opens locked to that part with title 'New Part Fee / Discount'</t>
         </is>
       </c>
       <c r="F77" s="2" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>Critical</t>
         </is>
       </c>
       <c r="G77" s="2" t="inlineStr">
@@ -4272,24 +4272,24 @@
       </c>
       <c r="I77" s="2" t="inlineStr">
         <is>
-          <t>prior decline-&gt;$0 (batch-4) stands; decline flip blocked today (staged-parts lock) | WORDING+VIU 2026-07-13: Declined/returned part $0 carried.</t>
+          <t>FDBUG-14 label defects (missing 'Line {N} Part —' prefix, raw enum 'Pct_parts', part-% option mislabeled '% of Labor Total') per batch-4; part dialog not re-driven today | WORDING+VIU 2026-07-13: CONFIRMED live: part ⋮ = 'Move' / 'Add Fee/Discount'; dialog 'Add new fee/discount' with subtitle 'Applying to: &lt;part name&gt;' (NO 'Line N Part —' prefix — build differs from the old spec text); Calc default '% Of Parts Total' (shots line-01/02). Now build-accurate. | SV-8479/8480 deconfliction 2026-07-22: menu item 'Add Fee/Discount' -&gt; 'Add Part Fee / Discount' (item 2); title 'Add new fee/discount' -&gt; 'New Part Fee / Discount', subline 'Applying to: &lt;part&gt;' -&gt; 'Applying To: Line N Part — &lt;name&gt;' (item 9). Absorbs dropped new case FD-WO-024. | VIU 2026-07-22 LIVE: part menu label 'Add Part Fee / Discount' + dialog title 'New Part Fee / Discount', subline 'Applying To: Line 1 Part — Turbocharger Oil', default Calculation Type '% Of Parts Total'. Ev: wo/FD-PART-001-part-dialog.png, wo/part-dialog-text.txt.</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" s="2" t="inlineStr">
         <is>
-          <t>FD-PART-007</t>
+          <t>FD-PART-002</t>
         </is>
       </c>
       <c r="B78" s="2" t="inlineStr">
         <is>
-          <t>C28452</t>
+          <t>C28447</t>
         </is>
       </c>
       <c r="C78" s="6" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/28452</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/28447</t>
         </is>
       </c>
       <c r="D78" s="2" t="inlineStr">
@@ -4299,12 +4299,12 @@
       </c>
       <c r="E78" s="2" t="inlineStr">
         <is>
-          <t>Verify deleting a part removes any fee/discount pointing to it</t>
+          <t>Verify a part-line flat amount is charged per item (amount x quantity): $5.00 x 3 → −$15.00</t>
         </is>
       </c>
       <c r="F78" s="2" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>Critical</t>
         </is>
       </c>
       <c r="G78" s="2" t="inlineStr">
@@ -4319,24 +4319,24 @@
       </c>
       <c r="I78" s="2" t="inlineStr">
         <is>
-          <t>prior delete-cascade (batch-4) stands; not re-seedable today | WORDING+VIU 2026-07-13: Delete-part cascades; carried; build labels.</t>
+          <t>per-item flat re-proven: $2.00 x qty 4 -&gt; $8.00 on S-15895's received part (estimate row 'ZZAUTOTEST PartFlat $8.00') | WORDING+VIU 2026-07-13: Per-item flat carried; build labels. | SV-8479/8480 deconfliction 2026-07-22: inline part-row rendering reworded from '−$5.00 flat rate badge' to plain text (item 4); per-item flat calc unchanged. | VIU 2026-07-22 LIVE: inline part fee renders plain text ('Part Fee 11% +$4.40'), no colored badge; per-item flat calc unchanged (verified prior passes). Ev: wo/inline-expanded-text.txt.</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" s="2" t="inlineStr">
         <is>
-          <t>FD-PART-008</t>
+          <t>FD-PART-003</t>
         </is>
       </c>
       <c r="B79" s="2" t="inlineStr">
         <is>
-          <t>C28453</t>
+          <t>C28448</t>
         </is>
       </c>
       <c r="C79" s="6" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/28453</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/28448</t>
         </is>
       </c>
       <c r="D79" s="2" t="inlineStr">
@@ -4346,12 +4346,12 @@
       </c>
       <c r="E79" s="2" t="inlineStr">
         <is>
-          <t>Verify the per-item flat amount edge: quantity 1 is the base amount (−$5.00)</t>
+          <t>Verify a fee/discount can be added to a requested (not-yet-received) part and shows before it is picked</t>
         </is>
       </c>
       <c r="F79" s="2" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>High</t>
         </is>
       </c>
       <c r="G79" s="2" t="inlineStr">
@@ -4366,34 +4366,34 @@
       </c>
       <c r="I79" s="2" t="inlineStr">
         <is>
-          <t>qty-1 flat = base amount (batch); per-item semantics re-proven today at qty 4 | WORDING+VIU 2026-07-13: Per-item edge carried; build labels.</t>
+          <t>prior batch-4 requested-state evidence stands; not re-seedable today (make-request -&gt; 400 'Part requests can`t be modified on completed line', line-create 500) | WORDING+VIU 2026-07-13: Add-to-requested-part carried; build labels. | SV-8479/8480 deconfliction 2026-07-22: label sweep: navigation labels -&gt; 'Add Part Fee / Discount' / 'New Part Fee / Discount' (behavior/expected unchanged). | VIU 2026-07-22 LIVE: SV-8479 nav label 'Add Part Fee / Discount' confirmed present in the part row ⋮ menu; case behavior unchanged. Ev: wo/FD-WO-018-part-menu.png.</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" s="2" t="inlineStr">
         <is>
-          <t>FD-PCOL-001</t>
+          <t>FD-PART-004</t>
         </is>
       </c>
       <c r="B80" s="2" t="inlineStr">
         <is>
-          <t>C28469</t>
+          <t>C28449</t>
         </is>
       </c>
       <c r="C80" s="6" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/28469</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/28449</t>
         </is>
       </c>
       <c r="D80" s="2" t="inlineStr">
         <is>
-          <t>Parts page — 'FEES &amp; DISCOUNTS' column</t>
+          <t>Work Order / Parts — Part-line Fee/Discount</t>
         </is>
       </c>
       <c r="E80" s="2" t="inlineStr">
         <is>
-          <t>Verify the Parts page 'Fees &amp; Discounts' column shows a single fee/discount's name and rate</t>
+          <t>Verify a part-line '% of Parts Total' works out against quantity x sell price</t>
         </is>
       </c>
       <c r="F80" s="2" t="inlineStr">
@@ -4413,39 +4413,39 @@
       </c>
       <c r="I80" s="2" t="inlineStr">
         <is>
-          <t>RE-CHECKED TODAY on a freshly created part sale (P3-127): NO 'Fees &amp; Discounts' column on the part-sale page; API add against a part-sale id -&gt; 400 needs-target (no part-sale adjustment surface). Story 11 still NOT BUILT (shot 12-part-sale) | WORDING+VIU 2026-07-13:  NOT BUILT: Story 11 (Part Sales fees/discounts) has not shipped — the Parts page has no 'Fees &amp; Discounts' column and there is no part-sale F&amp;D surface. Wording made build-accurate/layman for when it ships; status stays Blocked-NotBuilt. | STAGING VIU 2026-07-20 staging LIVE VIU: Column shows single fee/discount name+rate (Fee $6.00 / Discount -11%). Live staging (ps-scrolled).</t>
+          <t>pct_parts re-proven: 10% of qty4 x 42.69 = 170.76 -&gt; $17.08 | WORDING+VIU 2026-07-13: %-of-parts base carried; build labels. | SV-8479/8480 deconfliction 2026-07-22: label sweep: navigation labels -&gt; 'Add Part Fee / Discount' / 'New Part Fee / Discount' (behavior/expected unchanged). | VIU 2026-07-22 LIVE: SV-8479 nav label 'Add Part Fee / Discount' confirmed present in the part row ⋮ menu; case behavior unchanged. Ev: wo/FD-WO-018-part-menu.png.</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" s="2" t="inlineStr">
         <is>
-          <t>FD-PCOL-002</t>
+          <t>FD-PART-005</t>
         </is>
       </c>
       <c r="B81" s="2" t="inlineStr">
         <is>
-          <t>C28470</t>
+          <t>C28450</t>
         </is>
       </c>
       <c r="C81" s="6" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/28470</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/28450</t>
         </is>
       </c>
       <c r="D81" s="2" t="inlineStr">
         <is>
-          <t>Parts page — 'FEES &amp; DISCOUNTS' column</t>
+          <t>Work Order / Parts — Part-line Fee/Discount</t>
         </is>
       </c>
       <c r="E81" s="2" t="inlineStr">
         <is>
-          <t>Verify the parts-sale 'Fees &amp; Discounts' column shows values as plain text with a '+N' overflow count (no colored badge)</t>
+          <t>Verify a part-line fee/discount stays attached when the part changes from requested to received</t>
         </is>
       </c>
       <c r="F81" s="2" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="G81" s="2" t="inlineStr">
@@ -4460,39 +4460,39 @@
       </c>
       <c r="I81" s="2" t="inlineStr">
         <is>
-          <t>Story 11 surface absent (re-checked today) | WORDING+VIU 2026-07-13:  NOT BUILT: Story 11 (Part Sales fees/discounts) has not shipped — the Parts page has no 'Fees &amp; Discounts' column and there is no part-sale F&amp;D surface. Wording made build-accurate/layman for when it ships; status stays Blocked-NotBuilt. | STAGING VIU 2026-07-20 staging LIVE VIU: +N badge on multi-fee part (Fee $6.00 +1). Live staging (psB4-badge.png). | SV-8479/8480 deconfliction 2026-07-22: column values + '+N' overflow reworded from badges to plain text with the sign rule (item 16). Absorbs dropped new case FD-PSALE-005. (FD-PCOL-001 already plain text — no change.) | SV-8479 Batch-3 STAGING LIVE VIU 2026-07-22 (part-sale surface): seeded ZZAUTOTEST part sale P3-1118 (2 fee-less rows + NEXUS 2-adj) + whole-sale percent/flat/discount; observed live as admin (Part Sales C&amp;E + SFD). Evidence build/fees-discounts/viu-sv8479-8480-2026-07-22/psale/. Live: NEXUS cell = 'Part Fee 11% +1' plain text, no badge, fee no sign.</t>
+          <t>STILL PENDING: requested-&gt;received transition unreachable — line-create 500s env-wide, make-request rejected on completed lines, receiving subsystem needs a fresh order | WORDING+VIU 2026-07-13: BLOCKED/PENDING: requested→received transition blocked by the env-wide WO line-create 500 + completed-line part-request lock — cannot drive the transition. Build labels applied. | CLOSE-OUT 2026-07-24: accepted per Ahtasham QA live review 2026-07-24 (no bug). Status -&gt; VIU-Verified, wording unchanged. HONESTY (Rule 12/22): accepted on Ahtasham's live QA review — NOT re-observed by us this pass.</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" s="2" t="inlineStr">
         <is>
-          <t>FD-PCOL-004</t>
+          <t>FD-PART-006</t>
         </is>
       </c>
       <c r="B82" s="2" t="inlineStr">
         <is>
-          <t>C28472</t>
+          <t>C28451</t>
         </is>
       </c>
       <c r="C82" s="6" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/28472</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/28451</t>
         </is>
       </c>
       <c r="D82" s="2" t="inlineStr">
         <is>
-          <t>Parts page — breakdown modal</t>
+          <t>Work Order / Parts — Part-line Fee/Discount</t>
         </is>
       </c>
       <c r="E82" s="2" t="inlineStr">
         <is>
-          <t>Verify clicking a filled 'Fees &amp; Discounts' cell opens the per-part breakdown with the right columns</t>
+          <t>Verify a part-line fee/discount works out to $0.00 when the part is declined or returned with no quantity left</t>
         </is>
       </c>
       <c r="F82" s="2" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="G82" s="2" t="inlineStr">
@@ -4507,34 +4507,34 @@
       </c>
       <c r="I82" s="2" t="inlineStr">
         <is>
-          <t>Story 11 surface absent (re-checked today) | WORDING+VIU 2026-07-13:  NOT BUILT: Story 11 (Part Sales fees/discounts) has not shipped — the Parts page has no 'Fees &amp; Discounts' column and there is no part-sale F&amp;D surface. Wording made build-accurate/layman for when it ships; status stays Blocked-NotBuilt. | STAGING VIU 2026-07-20 staging LIVE VIU: Filled cell opens viewer with Name/Type/Calculation/Amount/Max Amount columns. Live staging (psC-viewer2rows.png).</t>
+          <t>prior decline-&gt;$0 (batch-4) stands; decline flip blocked today (staged-parts lock) | WORDING+VIU 2026-07-13: Declined/returned part $0 carried.</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" s="2" t="inlineStr">
         <is>
-          <t>FD-PCOL-005</t>
+          <t>FD-PART-007</t>
         </is>
       </c>
       <c r="B83" s="2" t="inlineStr">
         <is>
-          <t>C28473</t>
+          <t>C28452</t>
         </is>
       </c>
       <c r="C83" s="6" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/28473</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/28452</t>
         </is>
       </c>
       <c r="D83" s="2" t="inlineStr">
         <is>
-          <t>Parts page — breakdown modal</t>
+          <t>Work Order / Parts — Part-line Fee/Discount</t>
         </is>
       </c>
       <c r="E83" s="2" t="inlineStr">
         <is>
-          <t>Verify the breakdown 'Net adjustment' row equals the signed sum of the part's fees/discounts</t>
+          <t>Verify deleting a part removes any fee/discount pointing to it</t>
         </is>
       </c>
       <c r="F83" s="2" t="inlineStr">
@@ -4554,39 +4554,39 @@
       </c>
       <c r="I83" s="2" t="inlineStr">
         <is>
-          <t>Story 11 surface absent (re-checked today) | WORDING+VIU 2026-07-13:  NOT BUILT: Story 11 (Part Sales fees/discounts) has not shipped — the Parts page has no 'Fees &amp; Discounts' column and there is no part-sale F&amp;D surface. Wording made build-accurate/layman for when it ships; status stays Blocked-NotBuilt. | STAGING VIU 2026-07-20 staging LIVE VIU: Viewer Net adjustment = signed sum (+$12.00 + $2.00 = +$14.00). Live staging (psC-viewer2rows.png).</t>
+          <t>prior delete-cascade (batch-4) stands; not re-seedable today | WORDING+VIU 2026-07-13: Delete-part cascades; carried; build labels.</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" s="2" t="inlineStr">
         <is>
-          <t>FD-PCOL-006</t>
+          <t>FD-PART-008</t>
         </is>
       </c>
       <c r="B84" s="2" t="inlineStr">
         <is>
-          <t>C28474</t>
+          <t>C28453</t>
         </is>
       </c>
       <c r="C84" s="6" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/28474</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/28453</t>
         </is>
       </c>
       <c r="D84" s="2" t="inlineStr">
         <is>
-          <t>Parts page — breakdown modal</t>
+          <t>Work Order / Parts — Part-line Fee/Discount</t>
         </is>
       </c>
       <c r="E84" s="2" t="inlineStr">
         <is>
-          <t>Verify a per-row Remove on the breakdown removes the fee/discount and the cell returns to its empty state (no '+ Add' button)</t>
+          <t>Verify the per-item flat amount edge: quantity 1 is the base amount (−$5.00)</t>
         </is>
       </c>
       <c r="F84" s="2" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="G84" s="2" t="inlineStr">
@@ -4601,34 +4601,34 @@
       </c>
       <c r="I84" s="2" t="inlineStr">
         <is>
-          <t>Story 11 surface absent (re-checked today) | WORDING+VIU 2026-07-13:  NOT BUILT: Story 11 (Part Sales fees/discounts) has not shipped — the Parts page has no 'Fees &amp; Discounts' column and there is no part-sale F&amp;D surface. Wording made build-accurate/layman for when it ships; status stays Blocked-NotBuilt. | STAGING VIU 2026-07-20 staging LIVE VIU: Per-row Remove -&gt; confirm Remove Fee / Discount -&gt; row removed. Live staging (psE-confirm/afterremove). | SV-8479/8480 deconfliction 2026-07-22: empty-state reworded: the removed '+ Add' button is gone; add via the per-row ⋮ (item 13). | SV-8479 Batch-3 STAGING LIVE VIU 2026-07-22 (part-sale surface): seeded ZZAUTOTEST part sale P3-1118 (2 fee-less rows + NEXUS 2-adj) + whole-sale percent/flat/discount; observed live as admin (Part Sales C&amp;E + SFD). Evidence build/fees-discounts/viu-sv8479-8480-2026-07-22/psale/. Live: breakdown viewer per-row delete -&gt; confirm 'Remove Fee / Discount' -&gt; removed -&gt; empty state, no '+ Add'.</t>
+          <t>qty-1 flat = base amount (batch); per-item semantics re-proven today at qty 4 | WORDING+VIU 2026-07-13: Per-item edge carried; build labels.</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" s="2" t="inlineStr">
         <is>
-          <t>FD-PERM-001</t>
+          <t>FD-PCOL-001</t>
         </is>
       </c>
       <c r="B85" s="2" t="inlineStr">
         <is>
-          <t>C28585</t>
+          <t>C28469</t>
         </is>
       </c>
       <c r="C85" s="6" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/28585</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/28469</t>
         </is>
       </c>
       <c r="D85" s="2" t="inlineStr">
         <is>
-          <t>Permissions (Story 13)</t>
+          <t>Parts page — 'FEES &amp; DISCOUNTS' column</t>
         </is>
       </c>
       <c r="E85" s="2" t="inlineStr">
         <is>
-          <t>Verify See Financial Data controls all fee/discount dollar amounts (without it, amounts are hidden)</t>
+          <t>Verify the Parts page 'Fees &amp; Discounts' column shows a single fee/discount's name and rate</t>
         </is>
       </c>
       <c r="F85" s="2" t="inlineStr">
@@ -4648,34 +4648,34 @@
       </c>
       <c r="I85" s="2" t="inlineStr">
         <is>
-          <t>tech (no SFD): WO view masks all money (sub_total/total '0.00') | WORDING+VIU 2026-07-13: CONFIRMED live 2026-07-13: Tech (no See Financial Data, view_mode:tech) → WO view sub_total masked to '0.00' (amounts hidden).</t>
+          <t>RE-CHECKED TODAY on a freshly created part sale (P3-127): NO 'Fees &amp; Discounts' column on the part-sale page; API add against a part-sale id -&gt; 400 needs-target (no part-sale adjustment surface). Story 11 still NOT BUILT (shot 12-part-sale) | WORDING+VIU 2026-07-13:  NOT BUILT: Story 11 (Part Sales fees/discounts) has not shipped — the Parts page has no 'Fees &amp; Discounts' column and there is no part-sale F&amp;D surface. Wording made build-accurate/layman for when it ships; status stays Blocked-NotBuilt. | STAGING VIU 2026-07-20 staging LIVE VIU: Column shows single fee/discount name+rate (Fee $6.00 / Discount -11%). Live staging (ps-scrolled).</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" s="2" t="inlineStr">
         <is>
-          <t>FD-PERM-002</t>
+          <t>FD-PCOL-002</t>
         </is>
       </c>
       <c r="B86" s="2" t="inlineStr">
         <is>
-          <t>C28586</t>
+          <t>C28470</t>
         </is>
       </c>
       <c r="C86" s="6" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/28586</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/28470</t>
         </is>
       </c>
       <c r="D86" s="2" t="inlineStr">
         <is>
-          <t>Permissions (Story 13)</t>
+          <t>Parts page — 'FEES &amp; DISCOUNTS' column</t>
         </is>
       </c>
       <c r="E86" s="2" t="inlineStr">
         <is>
-          <t>Verify whole-work-order add/edit/remove requires Work Orders: Create and Edit</t>
+          <t>Verify the parts-sale 'Fees &amp; Discounts' column shows values as plain text with a '+N' overflow count (no colored badge)</t>
         </is>
       </c>
       <c r="F86" s="2" t="inlineStr">
@@ -4695,34 +4695,34 @@
       </c>
       <c r="I86" s="2" t="inlineStr">
         <is>
-          <t>BUG-FD-3 stands on batch evidence; NOT re-testable today — Technician role drifted on the shared env (now HAS workOrdersCreateAndEdit, so its 201 is legitimate); enforcement-depth question unchanged (dev decision) | WORDING+VIU 2026-07-13: DEVIATION (BUG-FD-3): the whole-work-order add/edit/remove hide is front-end only — the back-end does not block the write. NOT re-testable this run: Technician drifted to HAVE Work Orders: Create &amp; Edit, and only admin/tech can log in. | FE-BLOCK/BE-ALLOW PASS 2026-07-24 (user-authorized, Standing Rule 24): flipped VIU-Deviation -&gt; VIU-Verified (PASS). The FE hiding the whole-WO add/edit/remove controls for a role without Work Orders: Create &amp; Edit IS the tester-facing pass criterion; the back-end/API not independently enforcing it (POST /api/work-orders/adjustments/add returns 201 for such a role — pass-A evidence + Sales-Rep impersonation) is ACCEPTED by product policy per Rule 24, not a bug/enforcement-gap. Added the plain tester line to Expected (Rule 7). This is FE-block/BE-allow = PASS (not the inverse FE-exposure defect).</t>
+          <t>Story 11 surface absent (re-checked today) | WORDING+VIU 2026-07-13:  NOT BUILT: Story 11 (Part Sales fees/discounts) has not shipped — the Parts page has no 'Fees &amp; Discounts' column and there is no part-sale F&amp;D surface. Wording made build-accurate/layman for when it ships; status stays Blocked-NotBuilt. | STAGING VIU 2026-07-20 staging LIVE VIU: +N badge on multi-fee part (Fee $6.00 +1). Live staging (psB4-badge.png). | SV-8479/8480 deconfliction 2026-07-22: column values + '+N' overflow reworded from badges to plain text with the sign rule (item 16). Absorbs dropped new case FD-PSALE-005. (FD-PCOL-001 already plain text — no change.) | SV-8479 Batch-3 STAGING LIVE VIU 2026-07-22 (part-sale surface): seeded ZZAUTOTEST part sale P3-1118 (2 fee-less rows + NEXUS 2-adj) + whole-sale percent/flat/discount; observed live as admin (Part Sales C&amp;E + SFD). Evidence build/fees-discounts/viu-sv8479-8480-2026-07-22/psale/. Live: NEXUS cell = 'Part Fee 11% +1' plain text, no badge, fee no sign.</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" s="2" t="inlineStr">
         <is>
-          <t>FD-PERM-003</t>
+          <t>FD-PCOL-004</t>
         </is>
       </c>
       <c r="B87" s="2" t="inlineStr">
         <is>
-          <t>C28587</t>
+          <t>C28472</t>
         </is>
       </c>
       <c r="C87" s="6" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/28587</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/28472</t>
         </is>
       </c>
       <c r="D87" s="2" t="inlineStr">
         <is>
-          <t>Permissions (Story 13)</t>
+          <t>Parts page — breakdown modal</t>
         </is>
       </c>
       <c r="E87" s="2" t="inlineStr">
         <is>
-          <t>Verify labor-line and part-line add/edit/remove requires Work Order Lines: Create and Edit</t>
+          <t>Verify clicking a filled 'Fees &amp; Discounts' cell opens the per-part breakdown with the right columns</t>
         </is>
       </c>
       <c r="F87" s="2" t="inlineStr">
@@ -4742,39 +4742,39 @@
       </c>
       <c r="I87" s="2" t="inlineStr">
         <is>
-          <t>positive half fresh (tech WITH lines-C&amp;E: line add 201/remove 204); negative half via roles-matrix FE derivation (role-drift caveat) | WORDING+VIU 2026-07-13: Positive: Tech HAS Work Order Lines: Create &amp; Edit. Negative not testable (Tech drifted to have it). Line-level gate carried from prior derivation.</t>
+          <t>Story 11 surface absent (re-checked today) | WORDING+VIU 2026-07-13:  NOT BUILT: Story 11 (Part Sales fees/discounts) has not shipped — the Parts page has no 'Fees &amp; Discounts' column and there is no part-sale F&amp;D surface. Wording made build-accurate/layman for when it ships; status stays Blocked-NotBuilt. | STAGING VIU 2026-07-20 staging LIVE VIU: Filled cell opens viewer with Name/Type/Calculation/Amount/Max Amount columns. Live staging (psC-viewer2rows.png).</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" s="2" t="inlineStr">
         <is>
-          <t>FD-PERM-004</t>
+          <t>FD-PCOL-005</t>
         </is>
       </c>
       <c r="B88" s="2" t="inlineStr">
         <is>
-          <t>C28588</t>
+          <t>C28473</t>
         </is>
       </c>
       <c r="C88" s="6" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/28588</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/28473</t>
         </is>
       </c>
       <c r="D88" s="2" t="inlineStr">
         <is>
-          <t>Permissions (Story 13)</t>
+          <t>Parts page — breakdown modal</t>
         </is>
       </c>
       <c r="E88" s="2" t="inlineStr">
         <is>
-          <t>Verify part-sale add/edit/remove requires Part Sales: Create and Edit plus See Financial Data</t>
+          <t>Verify the breakdown 'Net adjustment' row equals the signed sum of the part's fees/discounts</t>
         </is>
       </c>
       <c r="F88" s="2" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="G88" s="2" t="inlineStr">
@@ -4789,34 +4789,34 @@
       </c>
       <c r="I88" s="2" t="inlineStr">
         <is>
-          <t>Part Sales adjustment surface absent (Story 11 re-checked today) | WORDING+VIU 2026-07-13: NOT BUILT: Story 11 Part Sales fees/discounts not shipped; cannot test the Part Sales permission gate. | STAGING VIU 2026-07-20 staging LIVE VIU: Admin (Part Sales C&amp;E + SFD) can add/edit/remove part-sale F&amp;D; Tech (no Part Sales perms) has Parts nav hidden entirely. Live staging.</t>
+          <t>Story 11 surface absent (re-checked today) | WORDING+VIU 2026-07-13:  NOT BUILT: Story 11 (Part Sales fees/discounts) has not shipped — the Parts page has no 'Fees &amp; Discounts' column and there is no part-sale F&amp;D surface. Wording made build-accurate/layman for when it ships; status stays Blocked-NotBuilt. | STAGING VIU 2026-07-20 staging LIVE VIU: Viewer Net adjustment = signed sum (+$12.00 + $2.00 = +$14.00). Live staging (psC-viewer2rows.png).</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" s="2" t="inlineStr">
         <is>
-          <t>FD-PERM-005</t>
+          <t>FD-PCOL-006</t>
         </is>
       </c>
       <c r="B89" s="2" t="inlineStr">
         <is>
-          <t>C28589</t>
+          <t>C28474</t>
         </is>
       </c>
       <c r="C89" s="6" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/28589</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/28474</t>
         </is>
       </c>
       <c r="D89" s="2" t="inlineStr">
         <is>
-          <t>Permissions (Story 13)</t>
+          <t>Parts page — breakdown modal</t>
         </is>
       </c>
       <c r="E89" s="2" t="inlineStr">
         <is>
-          <t>Verify any add/edit/remove of a fee/discount also needs See Financial Data on</t>
+          <t>Verify a per-row Remove on the breakdown removes the fee/discount and the cell returns to its empty state (no '+ Add' button)</t>
         </is>
       </c>
       <c r="F89" s="2" t="inlineStr">
@@ -4836,24 +4836,24 @@
       </c>
       <c r="I89" s="2" t="inlineStr">
         <is>
-          <t>SFD prerequisite: controls live on SFD-masked surfaces (tech masked view re-confirmed) | WORDING+VIU 2026-07-13: See-Financial-Data masking confirmed live (Tech financials masked). The add/edit/remove controls sit on the masked screens, so they are unreachable without SFD.</t>
+          <t>Story 11 surface absent (re-checked today) | WORDING+VIU 2026-07-13:  NOT BUILT: Story 11 (Part Sales fees/discounts) has not shipped — the Parts page has no 'Fees &amp; Discounts' column and there is no part-sale F&amp;D surface. Wording made build-accurate/layman for when it ships; status stays Blocked-NotBuilt. | STAGING VIU 2026-07-20 staging LIVE VIU: Per-row Remove -&gt; confirm Remove Fee / Discount -&gt; row removed. Live staging (psE-confirm/afterremove). | SV-8479/8480 deconfliction 2026-07-22: empty-state reworded: the removed '+ Add' button is gone; add via the per-row ⋮ (item 13). | SV-8479 Batch-3 STAGING LIVE VIU 2026-07-22 (part-sale surface): seeded ZZAUTOTEST part sale P3-1118 (2 fee-less rows + NEXUS 2-adj) + whole-sale percent/flat/discount; observed live as admin (Part Sales C&amp;E + SFD). Evidence build/fees-discounts/viu-sv8479-8480-2026-07-22/psale/. Live: breakdown viewer per-row delete -&gt; confirm 'Remove Fee / Discount' -&gt; removed -&gt; empty state, no '+ Add'.</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" s="2" t="inlineStr">
         <is>
-          <t>FD-PERM-006</t>
+          <t>FD-PERM-001</t>
         </is>
       </c>
       <c r="B90" s="2" t="inlineStr">
         <is>
-          <t>C28590</t>
+          <t>C28585</t>
         </is>
       </c>
       <c r="C90" s="6" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/28590</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/28585</t>
         </is>
       </c>
       <c r="D90" s="2" t="inlineStr">
@@ -4863,7 +4863,7 @@
       </c>
       <c r="E90" s="2" t="inlineStr">
         <is>
-          <t>Verify removing a fee/discount uses Create and Edit, not the separate Delete permission</t>
+          <t>Verify See Financial Data controls all fee/discount dollar amounts (without it, amounts are hidden)</t>
         </is>
       </c>
       <c r="F90" s="2" t="inlineStr">
@@ -4883,24 +4883,24 @@
       </c>
       <c r="I90" s="2" t="inlineStr">
         <is>
-          <t>removal uses the same Create&amp;Edit gate (tech remove 204; no Delete-perm dependency) | WORDING+VIU 2026-07-13: Remove via Create &amp; Edit (not a separate Delete) carried.</t>
+          <t>tech (no SFD): WO view masks all money (sub_total/total '0.00') | WORDING+VIU 2026-07-13: CONFIRMED live 2026-07-13: Tech (no See Financial Data, view_mode:tech) → WO view sub_total masked to '0.00' (amounts hidden).</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" s="2" t="inlineStr">
         <is>
-          <t>FD-PERM-007</t>
+          <t>FD-PERM-002</t>
         </is>
       </c>
       <c r="B91" s="2" t="inlineStr">
         <is>
-          <t>C28591</t>
+          <t>C28586</t>
         </is>
       </c>
       <c r="C91" s="6" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/28591</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/28586</t>
         </is>
       </c>
       <c r="D91" s="2" t="inlineStr">
@@ -4910,7 +4910,7 @@
       </c>
       <c r="E91" s="2" t="inlineStr">
         <is>
-          <t>Verify create/edit/delete of a fee/discount template needs Settings → Service</t>
+          <t>Verify whole-work-order add/edit/remove requires Work Orders: Create and Edit</t>
         </is>
       </c>
       <c r="F91" s="2" t="inlineStr">
@@ -4930,24 +4930,24 @@
       </c>
       <c r="I91" s="2" t="inlineStr">
         <is>
-          <t>templates admin BE-enforced: tech GET/POST 403 | WORDING+VIU 2026-07-13: CONFIRMED live: Tech (no Settings → Finance) → GET templates 403 'Access denied.' | SV-8456 (2026-07-21 staging LIVE VIU): F&amp;D moved to SETTINGS→SERVICE (below Canned Lines); template/WO/Part-sale/customer dialogs now show Taxable as a Yes/No DROPDOWN (was toggle); Auto-apply is a CHECKBOX with a 'When on…' caption; settings &amp; customer tables are plain-text/left-aligned (no badges); WO sidebar card retitled 'Work Order Fees &amp; Discounts' and renders ABOVE Financial Info; Part-sale card 'Parts Sale Fees &amp; Discounts' above Financial Info. Permission gate pivoted Settings→Finance → Settings→Service (verified live: Service-user sees+manages F&amp;D &amp; convenience toggle; Finance-only user has no F&amp;D nav item and /administration/adjustment-templates bounces to /workorders). Frontend-only; functionality + calc INTACT. | RE-VIU 2026-07-22 LIVE (Batch 4, SV-8456 re-verify): access-check quick-login {admin} HTTP 200. Re-confirmed on current staging build — 8 UI corrections intact (Taxable Yes/No dropdown; Auto-apply checkbox+caption; modal field order Type/CalcType&gt;Name&gt;Amount&gt;Taxable+jur.note&gt;Auto-apply&gt;Description; Settings table plain-text left-aligned no badges; F&amp;D nav under SERVICE below Canned Lines; WO &amp; Part-Sale cards above Financial Info [Batch 2/3]; Customer 'Fees &amp; Discounts' tab mirrors Settings styling minus convenience toggle) AND Settings-&gt;Service permission pivot CONFIRMED live per role (seeded ServiceRole vs FinanceRole, assigned to Tech, Tech restored to Technician 50bf6a0d + verified, both ZZAUTOTEST roles deleted 204): Service-user sees+manages F&amp;D nav + convenience toggle, direct /administration/adjustment-templates loads; Finance-only user has NO F&amp;D nav, FINANCE=Payment Methods only, direct route bounces to /workorders. viu_status VIU-Verified re-confirmed. Ev build/fees-discounts/viu-sv8456-2026-07-22/ (01-settings-landing, 02-new-dialog, 03-customer-fd-tab, SVC-*, FIN-*).</t>
+          <t>BUG-FD-3 stands on batch evidence; NOT re-testable today — Technician role drifted on the shared env (now HAS workOrdersCreateAndEdit, so its 201 is legitimate); enforcement-depth question unchanged (dev decision) | WORDING+VIU 2026-07-13: DEVIATION (BUG-FD-3): the whole-work-order add/edit/remove hide is front-end only — the back-end does not block the write. NOT re-testable this run: Technician drifted to HAVE Work Orders: Create &amp; Edit, and only admin/tech can log in. | FE-BLOCK/BE-ALLOW PASS 2026-07-24 (user-authorized, Standing Rule 24): flipped VIU-Deviation -&gt; VIU-Verified (PASS). The FE hiding the whole-WO add/edit/remove controls for a role without Work Orders: Create &amp; Edit IS the tester-facing pass criterion; the back-end/API not independently enforcing it (POST /api/work-orders/adjustments/add returns 201 for such a role — pass-A evidence + Sales-Rep impersonation) is ACCEPTED by product policy per Rule 24, not a bug/enforcement-gap. Added the plain tester line to Expected (Rule 7). This is FE-block/BE-allow = PASS (not the inverse FE-exposure defect).</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" s="2" t="inlineStr">
         <is>
-          <t>FD-PERM-008</t>
+          <t>FD-PERM-003</t>
         </is>
       </c>
       <c r="B92" s="2" t="inlineStr">
         <is>
-          <t>C28592</t>
+          <t>C28587</t>
         </is>
       </c>
       <c r="C92" s="6" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/28592</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/28587</t>
         </is>
       </c>
       <c r="D92" s="2" t="inlineStr">
@@ -4957,7 +4957,7 @@
       </c>
       <c r="E92" s="2" t="inlineStr">
         <is>
-          <t>Verify viewing/changing a customer's default fees &amp; discounts needs BOTH Customer Management: Create and Edit AND Manage Accounts Payable and Receivable</t>
+          <t>Verify labor-line and part-line add/edit/remove requires Work Order Lines: Create and Edit</t>
         </is>
       </c>
       <c r="F92" s="2" t="inlineStr">
@@ -4977,24 +4977,24 @@
       </c>
       <c r="I92" s="2" t="inlineStr">
         <is>
-          <t>customer defaults BE-enforced: tech GET 403 + POST 403 | WORDING+VIU 2026-07-13: CONFIRMED live: Tech (no Manage AP/AR, no Customer Mgmt C&amp;E) → customer default-adjustments GET 403 AND POST 403 'Access denied.'</t>
+          <t>positive half fresh (tech WITH lines-C&amp;E: line add 201/remove 204); negative half via roles-matrix FE derivation (role-drift caveat) | WORDING+VIU 2026-07-13: Positive: Tech HAS Work Order Lines: Create &amp; Edit. Negative not testable (Tech drifted to have it). Line-level gate carried from prior derivation.</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" s="2" t="inlineStr">
         <is>
-          <t>FD-PERM-009</t>
+          <t>FD-PERM-004</t>
         </is>
       </c>
       <c r="B93" s="2" t="inlineStr">
         <is>
-          <t>C28593</t>
+          <t>C28588</t>
         </is>
       </c>
       <c r="C93" s="6" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/28593</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/28588</t>
         </is>
       </c>
       <c r="D93" s="2" t="inlineStr">
@@ -5004,12 +5004,12 @@
       </c>
       <c r="E93" s="2" t="inlineStr">
         <is>
-          <t>Verify seeing fee/discount entries in the work-order audit log needs Work Orders: Create and Edit (line audit log needs Work Order Lines: Create and Edit)</t>
+          <t>Verify part-sale add/edit/remove requires Part Sales: Create and Edit plus See Financial Data</t>
         </is>
       </c>
       <c r="F93" s="2" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>High</t>
         </is>
       </c>
       <c r="G93" s="2" t="inlineStr">
@@ -5024,24 +5024,24 @@
       </c>
       <c r="I93" s="2" t="inlineStr">
         <is>
-          <t>history entries: BE serves them regardless (tech 200) — FE display gate per enforcement model; entries carry set rate | V1_2 (2026-07-13): history-log gate updated per S13-R10 — WO-level history requires Work Orders: Create and Edit; line-level history requires Work Order Lines: Create and Edit (was View History Logs). Expected/preconditions updated; needs live re-VIU. NOTE: the Technician role has DRIFTED on the shared qb env — re-derive the roles matrix before the history re-VIU. | WORDING+VIU 2026-07-13: Positive confirmed live (Tech has Work Orders/Work Order Lines: Create &amp; Edit → Work Order Log 200 with fee/discount entries; the log shows the set rate so See Financial Data does not gate it — Tech's financials are masked yet history shows). The no-permission negative is NOT testable this run (Tech drifted to have the perms; only admin/tech log in). | V1_3 (2026-07-17): Δ2 terminology sweep — Story 10 renamed 'history log' -&gt; 'audit log' throughout (terminology only; gates/behavior/status unchanged). Generic 'history log / history entry / work-order history' prose replaced with 'audit log / audit-log entry'; the exact build labels 'Audit Log' (⋮ menu) and 'Work Order Log' (page) kept per Standing Rule 9. TestRail section name left as-is (rename not authorized).</t>
+          <t>Part Sales adjustment surface absent (Story 11 re-checked today) | WORDING+VIU 2026-07-13: NOT BUILT: Story 11 Part Sales fees/discounts not shipped; cannot test the Part Sales permission gate. | STAGING VIU 2026-07-20 staging LIVE VIU: Admin (Part Sales C&amp;E + SFD) can add/edit/remove part-sale F&amp;D; Tech (no Part Sales perms) has Parts nav hidden entirely. Live staging.</t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="A94" s="2" t="inlineStr">
         <is>
-          <t>FD-PERM-010</t>
+          <t>FD-PERM-005</t>
         </is>
       </c>
       <c r="B94" s="2" t="inlineStr">
         <is>
-          <t>C28594</t>
+          <t>C28589</t>
         </is>
       </c>
       <c r="C94" s="6" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/28594</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/28589</t>
         </is>
       </c>
       <c r="D94" s="2" t="inlineStr">
@@ -5051,7 +5051,7 @@
       </c>
       <c r="E94" s="2" t="inlineStr">
         <is>
-          <t>Verify both are required — the Fees &amp; Discounts feature on AND the matching permission</t>
+          <t>Verify any add/edit/remove of a fee/discount also needs See Financial Data on</t>
         </is>
       </c>
       <c r="F94" s="2" t="inlineStr">
@@ -5071,24 +5071,24 @@
       </c>
       <c r="I94" s="2" t="inlineStr">
         <is>
-          <t>flag ON + permission still required (tech 403 on templates/defaults with flag ON) | WORDING+VIU 2026-07-13: Permission gating confirmed live (templates/customer-defaults 403; SFD masking). Feature is ON. Both-gates model holds. | V1_3 (2026-07-17): Δ2 terminology sweep — Story 10 renamed 'history log' -&gt; 'audit log' throughout (terminology only; gates/behavior/status unchanged). Generic 'history log / history entry / work-order history' prose replaced with 'audit log / audit-log entry'; the exact build labels 'Audit Log' (⋮ menu) and 'Work Order Log' (page) kept per Standing Rule 9. TestRail section name left as-is (rename not authorized).</t>
+          <t>SFD prerequisite: controls live on SFD-masked surfaces (tech masked view re-confirmed) | WORDING+VIU 2026-07-13: See-Financial-Data masking confirmed live (Tech financials masked). The add/edit/remove controls sit on the masked screens, so they are unreachable without SFD.</t>
         </is>
       </c>
     </row>
     <row r="95">
       <c r="A95" s="2" t="inlineStr">
         <is>
-          <t>FD-PERM-011</t>
+          <t>FD-PERM-006</t>
         </is>
       </c>
       <c r="B95" s="2" t="inlineStr">
         <is>
-          <t>C28595</t>
+          <t>C28590</t>
         </is>
       </c>
       <c r="C95" s="6" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/28595</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/28590</t>
         </is>
       </c>
       <c r="D95" s="2" t="inlineStr">
@@ -5098,12 +5098,12 @@
       </c>
       <c r="E95" s="2" t="inlineStr">
         <is>
-          <t>Verify add/edit/remove is blocked when the work order is Invoiced/Paid or you are viewing history</t>
+          <t>Verify removing a fee/discount uses Create and Edit, not the separate Delete permission</t>
         </is>
       </c>
       <c r="F95" s="2" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>High</t>
         </is>
       </c>
       <c r="G95" s="2" t="inlineStr">
@@ -5118,34 +5118,34 @@
       </c>
       <c r="I95" s="2" t="inlineStr">
         <is>
-          <t>Invoiced WO: add 409 + edit 409 (BE-enforced lock) | WORDING+VIU 2026-07-13: Invoiced/Paid block is back-end enforced (409) — established; carried. | SV-8479/8480 deconfliction 2026-07-22: label sweep: navigation labels -&gt; 'Add Work Order Fee / Discount' / 'New Work Order Fee / Discount' (behavior/expected unchanged). | VIU 2026-07-22 LIVE: SV-8479 nav label 'Add Work Order Fee / Discount' confirmed present in the WO toolbar ⋯ menu; case behavior unchanged. Ev: wo/FD-WO-025-toolbar-menu.png.</t>
+          <t>removal uses the same Create&amp;Edit gate (tech remove 204; no Delete-perm dependency) | WORDING+VIU 2026-07-13: Remove via Create &amp; Edit (not a separate Delete) carried.</t>
         </is>
       </c>
     </row>
     <row r="96">
       <c r="A96" s="2" t="inlineStr">
         <is>
-          <t>FD-PROC-001</t>
+          <t>FD-PERM-007</t>
         </is>
       </c>
       <c r="B96" s="2" t="inlineStr">
         <is>
-          <t>C28519</t>
+          <t>C28591</t>
         </is>
       </c>
       <c r="C96" s="6" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/28519</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/28591</t>
         </is>
       </c>
       <c r="D96" s="2" t="inlineStr">
         <is>
-          <t>Processing Fee — template builder</t>
+          <t>Permissions (Story 13)</t>
         </is>
       </c>
       <c r="E96" s="2" t="inlineStr">
         <is>
-          <t>Verify 'Processing Fee' is a third Type in the template builder</t>
+          <t>Verify create/edit/delete of a fee/discount template needs Settings → Service</t>
         </is>
       </c>
       <c r="F96" s="2" t="inlineStr">
@@ -5165,34 +5165,34 @@
       </c>
       <c r="I96" s="2" t="inlineStr">
         <is>
-          <t>RE-CHECKED TODAY: template-builder Type options are exactly [Fee, Discount] — Processing Fee STILL MISSING from the builder UI (PO Q3=B says in-scope; FDBUG-8; shot 02-template-dialog) | WORDING+VIU 2026-07-13: Confirmed live: Type dropdown = Fee/Discount only. NOT BUILT: the template Type dropdown offers only Fee/Discount (no 'Processing Fee'); the Story-8 Processing-Fee builder UI has not shipped. The back-end DOES accept kind=processing_fee via API (201). Re-test when the builder ships. | STAGING VIU 2026-07-20 staging LIVE VIU: Type dropdown offers Fee, Discount, Processing Fee (admin template dialog). Live-observed staging (proc-type-open).</t>
+          <t>templates admin BE-enforced: tech GET/POST 403 | WORDING+VIU 2026-07-13: CONFIRMED live: Tech (no Settings → Finance) → GET templates 403 'Access denied.' | SV-8456 (2026-07-21 staging LIVE VIU): F&amp;D moved to SETTINGS→SERVICE (below Canned Lines); template/WO/Part-sale/customer dialogs now show Taxable as a Yes/No DROPDOWN (was toggle); Auto-apply is a CHECKBOX with a 'When on…' caption; settings &amp; customer tables are plain-text/left-aligned (no badges); WO sidebar card retitled 'Work Order Fees &amp; Discounts' and renders ABOVE Financial Info; Part-sale card 'Parts Sale Fees &amp; Discounts' above Financial Info. Permission gate pivoted Settings→Finance → Settings→Service (verified live: Service-user sees+manages F&amp;D &amp; convenience toggle; Finance-only user has no F&amp;D nav item and /administration/adjustment-templates bounces to /workorders). Frontend-only; functionality + calc INTACT. | RE-VIU 2026-07-22 LIVE (Batch 4, SV-8456 re-verify): access-check quick-login {admin} HTTP 200. Re-confirmed on current staging build — 8 UI corrections intact (Taxable Yes/No dropdown; Auto-apply checkbox+caption; modal field order Type/CalcType&gt;Name&gt;Amount&gt;Taxable+jur.note&gt;Auto-apply&gt;Description; Settings table plain-text left-aligned no badges; F&amp;D nav under SERVICE below Canned Lines; WO &amp; Part-Sale cards above Financial Info [Batch 2/3]; Customer 'Fees &amp; Discounts' tab mirrors Settings styling minus convenience toggle) AND Settings-&gt;Service permission pivot CONFIRMED live per role (seeded ServiceRole vs FinanceRole, assigned to Tech, Tech restored to Technician 50bf6a0d + verified, both ZZAUTOTEST roles deleted 204): Service-user sees+manages F&amp;D nav + convenience toggle, direct /administration/adjustment-templates loads; Finance-only user has NO F&amp;D nav, FINANCE=Payment Methods only, direct route bounces to /workorders. viu_status VIU-Verified re-confirmed. Ev build/fees-discounts/viu-sv8456-2026-07-22/ (01-settings-landing, 02-new-dialog, 03-customer-fd-tab, SVC-*, FIN-*).</t>
         </is>
       </c>
     </row>
     <row r="97">
       <c r="A97" s="2" t="inlineStr">
         <is>
-          <t>FD-PROC-002</t>
+          <t>FD-PERM-008</t>
         </is>
       </c>
       <c r="B97" s="2" t="inlineStr">
         <is>
-          <t>C28520</t>
+          <t>C28592</t>
         </is>
       </c>
       <c r="C97" s="6" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/28520</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/28592</t>
         </is>
       </c>
       <c r="D97" s="2" t="inlineStr">
         <is>
-          <t>Processing Fee — methods</t>
+          <t>Permissions (Story 13)</t>
         </is>
       </c>
       <c r="E97" s="2" t="inlineStr">
         <is>
-          <t>Verify a Processing Fee offers only Flat Amount and % of Grand Total</t>
+          <t>Verify viewing/changing a customer's default fees &amp; discounts needs BOTH Customer Management: Create and Edit AND Manage Accounts Payable and Receivable</t>
         </is>
       </c>
       <c r="F97" s="2" t="inlineStr">
@@ -5212,34 +5212,34 @@
       </c>
       <c r="I97" s="2" t="inlineStr">
         <is>
-          <t>builder UI absent (re-checked today); BE method constraint re-proven separately (pct_labor rejected for processing_fee) | WORDING+VIU 2026-07-13: Builder not shipped. NOT BUILT: the template Type dropdown offers only Fee/Discount (no 'Processing Fee'); the Story-8 Processing-Fee builder UI has not shipped. The back-end DOES accept kind=processing_fee via API (201). Re-test when the builder ships. | STAGING VIU 2026-07-20 staging LIVE VIU: Processing Fee Calc Type = Flat Amount + % of Grand Total only. Live staging (proc-fee-calc-open.png).</t>
+          <t>customer defaults BE-enforced: tech GET 403 + POST 403 | WORDING+VIU 2026-07-13: CONFIRMED live: Tech (no Manage AP/AR, no Customer Mgmt C&amp;E) → customer default-adjustments GET 403 AND POST 403 'Access denied.'</t>
         </is>
       </c>
     </row>
     <row r="98">
       <c r="A98" s="2" t="inlineStr">
         <is>
-          <t>FD-PROC-003</t>
+          <t>FD-PERM-009</t>
         </is>
       </c>
       <c r="B98" s="2" t="inlineStr">
         <is>
-          <t>C28521</t>
+          <t>C28593</t>
         </is>
       </c>
       <c r="C98" s="6" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/28521</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/28593</t>
         </is>
       </c>
       <c r="D98" s="2" t="inlineStr">
         <is>
-          <t>Processing Fee — no Max Amount</t>
+          <t>Permissions (Story 13)</t>
         </is>
       </c>
       <c r="E98" s="2" t="inlineStr">
         <is>
-          <t>Verify the Max Amount field is hidden for a Processing Fee (both methods)</t>
+          <t>Verify seeing fee/discount entries in the work-order audit log needs Work Orders: Create and Edit (line audit log needs Work Order Lines: Create and Edit)</t>
         </is>
       </c>
       <c r="F98" s="2" t="inlineStr">
@@ -5259,34 +5259,34 @@
       </c>
       <c r="I98" s="2" t="inlineStr">
         <is>
-          <t>builder UI absent (re-checked today); BE rejects pfee maxCap (400) | WORDING+VIU 2026-07-13: Builder not shipped. NOT BUILT: the template Type dropdown offers only Fee/Discount (no 'Processing Fee'); the Story-8 Processing-Fee builder UI has not shipped. The back-end DOES accept kind=processing_fee via API (201). Re-test when the builder ships. | STAGING VIU 2026-07-20 staging LIVE VIU: No Max Amount field for Processing Fee (both methods). Live staging (proc-fee-full.png).</t>
+          <t>history entries: BE serves them regardless (tech 200) — FE display gate per enforcement model; entries carry set rate | V1_2 (2026-07-13): history-log gate updated per S13-R10 — WO-level history requires Work Orders: Create and Edit; line-level history requires Work Order Lines: Create and Edit (was View History Logs). Expected/preconditions updated; needs live re-VIU. NOTE: the Technician role has DRIFTED on the shared qb env — re-derive the roles matrix before the history re-VIU. | WORDING+VIU 2026-07-13: Positive confirmed live (Tech has Work Orders/Work Order Lines: Create &amp; Edit → Work Order Log 200 with fee/discount entries; the log shows the set rate so See Financial Data does not gate it — Tech's financials are masked yet history shows). The no-permission negative is NOT testable this run (Tech drifted to have the perms; only admin/tech log in). | V1_3 (2026-07-17): Δ2 terminology sweep — Story 10 renamed 'history log' -&gt; 'audit log' throughout (terminology only; gates/behavior/status unchanged). Generic 'history log / history entry / work-order history' prose replaced with 'audit log / audit-log entry'; the exact build labels 'Audit Log' (⋮ menu) and 'Work Order Log' (page) kept per Standing Rule 9. TestRail section name left as-is (rename not authorized).</t>
         </is>
       </c>
     </row>
     <row r="99">
       <c r="A99" s="2" t="inlineStr">
         <is>
-          <t>FD-PROC-004</t>
+          <t>FD-PERM-010</t>
         </is>
       </c>
       <c r="B99" s="2" t="inlineStr">
         <is>
-          <t>C28522</t>
+          <t>C28594</t>
         </is>
       </c>
       <c r="C99" s="6" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/28522</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/28594</t>
         </is>
       </c>
       <c r="D99" s="2" t="inlineStr">
         <is>
-          <t>Processing Fee — taxable + jurisdiction note</t>
+          <t>Permissions (Story 13)</t>
         </is>
       </c>
       <c r="E99" s="2" t="inlineStr">
         <is>
-          <t>Verify the Processing Fee Taxable defaults to Yes and shows the tax-jurisdiction note</t>
+          <t>Verify both are required — the Fees &amp; Discounts feature on AND the matching permission</t>
         </is>
       </c>
       <c r="F99" s="2" t="inlineStr">
@@ -5306,39 +5306,39 @@
       </c>
       <c r="I99" s="2" t="inlineStr">
         <is>
-          <t>builder UI absent (re-checked today) | WORDING+VIU 2026-07-13: Builder not shipped; when it ships, also check the §5-R15 note (currently absent in the whole-WO dialog per FD-WO-016). NOT BUILT: the template Type dropdown offers only Fee/Discount (no 'Processing Fee'); the Story-8 Processing-Fee builder UI has not shipped. The back-end DOES accept kind=processing_fee via API (201). Re-test when the builder ships. | V1_3 (2026-07-17): Δ1 — §5-R15 gains one appended sentence (spec verbatim): 'The note is shown only to users with See Financial Data.' Expected gains the gate qualifier. This dialog is the one place the gate is independently observable (Story-7 admin access needs no See Financial Data, while the WO Add/Edit dialog already requires it — spec-diff §H.b). Status stays Blocked-NotBuilt (Story-8 builder UI absent); check the note + gate when the builder ships. | STAGING VIU 2026-07-20 staging LIVE VIU: Processing Fee Taxable defaults Yes + jurisdiction note present; note gated on See Financial Data (Tech w/o SFD sees toggle, not note). Live staging (proc-fee-full.png / tech-tmpl-dialog.png).</t>
+          <t>flag ON + permission still required (tech 403 on templates/defaults with flag ON) | WORDING+VIU 2026-07-13: Permission gating confirmed live (templates/customer-defaults 403; SFD masking). Feature is ON. Both-gates model holds. | V1_3 (2026-07-17): Δ2 terminology sweep — Story 10 renamed 'history log' -&gt; 'audit log' throughout (terminology only; gates/behavior/status unchanged). Generic 'history log / history entry / work-order history' prose replaced with 'audit log / audit-log entry'; the exact build labels 'Audit Log' (⋮ menu) and 'Work Order Log' (page) kept per Standing Rule 9. TestRail section name left as-is (rename not authorized).</t>
         </is>
       </c>
     </row>
     <row r="100">
       <c r="A100" s="2" t="inlineStr">
         <is>
-          <t>FD-PROC-005</t>
+          <t>FD-PERM-011</t>
         </is>
       </c>
       <c r="B100" s="2" t="inlineStr">
         <is>
-          <t>C28523</t>
+          <t>C28595</t>
         </is>
       </c>
       <c r="C100" s="6" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/28523</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/28595</t>
         </is>
       </c>
       <c r="D100" s="2" t="inlineStr">
         <is>
-          <t>Processing Fee — no manual add</t>
+          <t>Permissions (Story 13)</t>
         </is>
       </c>
       <c r="E100" s="2" t="inlineStr">
         <is>
-          <t>Verify a Processing Fee cannot be added to a work order by hand</t>
+          <t>Verify add/edit/remove is blocked when the work order is Invoiced/Paid or you are viewing history</t>
         </is>
       </c>
       <c r="F100" s="2" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="G100" s="2" t="inlineStr">
@@ -5353,34 +5353,34 @@
       </c>
       <c r="I100" s="2" t="inlineStr">
         <is>
-          <t>manual pfee add -&gt; 400 'A processing fee cannot be added manually.'; manual pct_grand_total fee also rejected for scope | WORDING+VIU 2026-07-13: Confirmed: WO Add Type dropdown = Fee/Discord only (no Processing Fee); build labels ('Add Fee/Discount', 'Apply From Template'). | SV-8479/8480 deconfliction 2026-07-22: label sweep: navigation labels -&gt; 'Add Work Order Fee / Discount' / 'New Work Order Fee / Discount' (behavior/expected unchanged). | VIU 2026-07-22 LIVE: SV-8479 nav label 'Add Work Order Fee / Discount' confirmed present in the WO toolbar ⋯ menu; case behavior unchanged. Ev: wo/FD-WO-025-toolbar-menu.png.</t>
+          <t>Invoiced WO: add 409 + edit 409 (BE-enforced lock) | WORDING+VIU 2026-07-13: Invoiced/Paid block is back-end enforced (409) — established; carried. | SV-8479/8480 deconfliction 2026-07-22: label sweep: navigation labels -&gt; 'Add Work Order Fee / Discount' / 'New Work Order Fee / Discount' (behavior/expected unchanged). | VIU 2026-07-22 LIVE: SV-8479 nav label 'Add Work Order Fee / Discount' confirmed present in the WO toolbar ⋯ menu; case behavior unchanged. Ev: wo/FD-WO-025-toolbar-menu.png.</t>
         </is>
       </c>
     </row>
     <row r="101">
       <c r="A101" s="2" t="inlineStr">
         <is>
-          <t>FD-PROC-006</t>
+          <t>FD-PROC-001</t>
         </is>
       </c>
       <c r="B101" s="2" t="inlineStr">
         <is>
-          <t>C28524</t>
+          <t>C28519</t>
         </is>
       </c>
       <c r="C101" s="6" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/28524</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/28519</t>
         </is>
       </c>
       <c r="D101" s="2" t="inlineStr">
         <is>
-          <t>Processing Fee — auto-apply</t>
+          <t>Processing Fee — template builder</t>
         </is>
       </c>
       <c r="E101" s="2" t="inlineStr">
         <is>
-          <t>Verify a Processing Fee reaches a new work order via location auto-apply</t>
+          <t>Verify 'Processing Fee' is a third Type in the template builder</t>
         </is>
       </c>
       <c r="F101" s="2" t="inlineStr">
@@ -5400,39 +5400,39 @@
       </c>
       <c r="I101" s="2" t="inlineStr">
         <is>
-          <t>auto-apply pfee template landed on a fresh WO (kind=processing_fee, appliedBy=auto) | WORDING+VIU 2026-07-13: Reaches WO via auto-apply (pfee accepted by BE); build labels. Menu option is 'Remove' (Edit inert for a pfee). | SV-8456 (2026-07-21 staging LIVE VIU): F&amp;D moved to SETTINGS→SERVICE (below Canned Lines); template/WO/Part-sale/customer dialogs now show Taxable as a Yes/No DROPDOWN (was toggle); Auto-apply is a CHECKBOX with a 'When on…' caption; settings &amp; customer tables are plain-text/left-aligned (no badges); WO sidebar card retitled 'Work Order Fees &amp; Discounts' and renders ABOVE Financial Info; Part-sale card 'Parts Sale Fees &amp; Discounts' above Financial Info. Permission gate pivoted Settings→Finance → Settings→Service (verified live: Service-user sees+manages F&amp;D &amp; convenience toggle; Finance-only user has no F&amp;D nav item and /administration/adjustment-templates bounces to /workorders). Frontend-only; functionality + calc INTACT. | RE-VIU 2026-07-22 LIVE (Batch 4, SV-8456 re-verify): access-check quick-login {admin} HTTP 200. Re-confirmed on current staging build — 8 UI corrections intact (Taxable Yes/No dropdown; Auto-apply checkbox+caption; modal field order Type/CalcType&gt;Name&gt;Amount&gt;Taxable+jur.note&gt;Auto-apply&gt;Description; Settings table plain-text left-aligned no badges; F&amp;D nav under SERVICE below Canned Lines; WO &amp; Part-Sale cards above Financial Info [Batch 2/3]; Customer 'Fees &amp; Discounts' tab mirrors Settings styling minus convenience toggle) AND Settings-&gt;Service permission pivot CONFIRMED live per role (seeded ServiceRole vs FinanceRole, assigned to Tech, Tech restored to Technician 50bf6a0d + verified, both ZZAUTOTEST roles deleted 204): Service-user sees+manages F&amp;D nav + convenience toggle, direct /administration/adjustment-templates loads; Finance-only user has NO F&amp;D nav, FINANCE=Payment Methods only, direct route bounces to /workorders. viu_status VIU-Verified re-confirmed. Ev build/fees-discounts/viu-sv8456-2026-07-22/ (01-settings-landing, 02-new-dialog, 03-customer-fd-tab, SVC-*, FIN-*).</t>
+          <t>RE-CHECKED TODAY: template-builder Type options are exactly [Fee, Discount] — Processing Fee STILL MISSING from the builder UI (PO Q3=B says in-scope; FDBUG-8; shot 02-template-dialog) | WORDING+VIU 2026-07-13: Confirmed live: Type dropdown = Fee/Discount only. NOT BUILT: the template Type dropdown offers only Fee/Discount (no 'Processing Fee'); the Story-8 Processing-Fee builder UI has not shipped. The back-end DOES accept kind=processing_fee via API (201). Re-test when the builder ships. | STAGING VIU 2026-07-20 staging LIVE VIU: Type dropdown offers Fee, Discount, Processing Fee (admin template dialog). Live-observed staging (proc-type-open).</t>
         </is>
       </c>
     </row>
     <row r="102">
       <c r="A102" s="2" t="inlineStr">
         <is>
-          <t>FD-PROC-007</t>
+          <t>FD-PROC-002</t>
         </is>
       </c>
       <c r="B102" s="2" t="inlineStr">
         <is>
-          <t>C28525</t>
+          <t>C28520</t>
         </is>
       </c>
       <c r="C102" s="6" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/28525</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/28520</t>
         </is>
       </c>
       <c r="D102" s="2" t="inlineStr">
         <is>
-          <t>Processing Fee — customer default</t>
+          <t>Processing Fee — methods</t>
         </is>
       </c>
       <c r="E102" s="2" t="inlineStr">
         <is>
-          <t>Verify a Processing Fee reaches a new work order via a customer default</t>
+          <t>Verify a Processing Fee offers only Flat Amount and % of Grand Total</t>
         </is>
       </c>
       <c r="F102" s="2" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>High</t>
         </is>
       </c>
       <c r="G102" s="2" t="inlineStr">
@@ -5447,34 +5447,34 @@
       </c>
       <c r="I102" s="2" t="inlineStr">
         <is>
-          <t>customer-default pfee landed on a fresh WO (kind=processing_fee, appliedBy=customer_default, amount 2.5) | WORDING+VIU 2026-07-13: Reaches WO via customer default; build labels. | SV-8456 (2026-07-21 staging LIVE VIU): F&amp;D moved to SETTINGS→SERVICE (below Canned Lines); template/WO/Part-sale/customer dialogs now show Taxable as a Yes/No DROPDOWN (was toggle); Auto-apply is a CHECKBOX with a 'When on…' caption; settings &amp; customer tables are plain-text/left-aligned (no badges); WO sidebar card retitled 'Work Order Fees &amp; Discounts' and renders ABOVE Financial Info; Part-sale card 'Parts Sale Fees &amp; Discounts' above Financial Info. Permission gate pivoted Settings→Finance → Settings→Service (verified live: Service-user sees+manages F&amp;D &amp; convenience toggle; Finance-only user has no F&amp;D nav item and /administration/adjustment-templates bounces to /workorders). Frontend-only; functionality + calc INTACT. | RE-VIU 2026-07-22 LIVE (Batch 4, SV-8456 re-verify): access-check quick-login {admin} HTTP 200. Re-confirmed on current staging build — 8 UI corrections intact (Taxable Yes/No dropdown; Auto-apply checkbox+caption; modal field order Type/CalcType&gt;Name&gt;Amount&gt;Taxable+jur.note&gt;Auto-apply&gt;Description; Settings table plain-text left-aligned no badges; F&amp;D nav under SERVICE below Canned Lines; WO &amp; Part-Sale cards above Financial Info [Batch 2/3]; Customer 'Fees &amp; Discounts' tab mirrors Settings styling minus convenience toggle) AND Settings-&gt;Service permission pivot CONFIRMED live per role (seeded ServiceRole vs FinanceRole, assigned to Tech, Tech restored to Technician 50bf6a0d + verified, both ZZAUTOTEST roles deleted 204): Service-user sees+manages F&amp;D nav + convenience toggle, direct /administration/adjustment-templates loads; Finance-only user has NO F&amp;D nav, FINANCE=Payment Methods only, direct route bounces to /workorders. viu_status VIU-Verified re-confirmed. Ev build/fees-discounts/viu-sv8456-2026-07-22/ (01-settings-landing, 02-new-dialog, 03-customer-fd-tab, SVC-*, FIN-*).</t>
+          <t>builder UI absent (re-checked today); BE method constraint re-proven separately (pct_labor rejected for processing_fee) | WORDING+VIU 2026-07-13: Builder not shipped. NOT BUILT: the template Type dropdown offers only Fee/Discount (no 'Processing Fee'); the Story-8 Processing-Fee builder UI has not shipped. The back-end DOES accept kind=processing_fee via API (201). Re-test when the builder ships. | STAGING VIU 2026-07-20 staging LIVE VIU: Processing Fee Calc Type = Flat Amount + % of Grand Total only. Live staging (proc-fee-calc-open.png).</t>
         </is>
       </c>
     </row>
     <row r="103">
       <c r="A103" s="2" t="inlineStr">
         <is>
-          <t>FD-PROC-010</t>
+          <t>FD-PROC-003</t>
         </is>
       </c>
       <c r="B103" s="2" t="inlineStr">
         <is>
-          <t>C28528</t>
+          <t>C28521</t>
         </is>
       </c>
       <c r="C103" s="6" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/28528</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/28521</t>
         </is>
       </c>
       <c r="D103" s="2" t="inlineStr">
         <is>
-          <t>Processing Fee — negative</t>
+          <t>Processing Fee — no Max Amount</t>
         </is>
       </c>
       <c r="E103" s="2" t="inlineStr">
         <is>
-          <t>Verify a Processing Fee with a Max Amount or a disallowed method is rejected</t>
+          <t>Verify the Max Amount field is hidden for a Processing Fee (both methods)</t>
         </is>
       </c>
       <c r="F103" s="2" t="inlineStr">
@@ -5494,39 +5494,39 @@
       </c>
       <c r="I103" s="2" t="inlineStr">
         <is>
-          <t>pfee template with maxCap -&gt; 400; pfee with pct_labor -&gt; 400 'not allowed for a processing_fee' | WORDING+VIU 2026-07-13: Confirmed live 2026-07-13 via API: Max cap → 400 'A processing fee cannot have a minimum or maximum cap.'; disallowed method → 400 'Calculation type "pct_subtotal" is not allowed for a processing_fee.' Lives in an API-titled section.</t>
+          <t>builder UI absent (re-checked today); BE rejects pfee maxCap (400) | WORDING+VIU 2026-07-13: Builder not shipped. NOT BUILT: the template Type dropdown offers only Fee/Discount (no 'Processing Fee'); the Story-8 Processing-Fee builder UI has not shipped. The back-end DOES accept kind=processing_fee via API (201). Re-test when the builder ships. | STAGING VIU 2026-07-20 staging LIVE VIU: No Max Amount field for Processing Fee (both methods). Live staging (proc-fee-full.png).</t>
         </is>
       </c>
     </row>
     <row r="104">
       <c r="A104" s="2" t="inlineStr">
         <is>
-          <t>FD-PROC-011</t>
+          <t>FD-PROC-004</t>
         </is>
       </c>
       <c r="B104" s="2" t="inlineStr">
         <is>
-          <t>C28529</t>
+          <t>C28522</t>
         </is>
       </c>
       <c r="C104" s="6" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/28529</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/28522</t>
         </is>
       </c>
       <c r="D104" s="2" t="inlineStr">
         <is>
-          <t>Processing Fee — sign</t>
+          <t>Processing Fee — taxable + jurisdiction note</t>
         </is>
       </c>
       <c r="E104" s="2" t="inlineStr">
         <is>
-          <t>Verify a Processing Fee always adds to the total (never a discount)</t>
+          <t>Verify the Processing Fee Taxable defaults to Yes and shows the tax-jurisdiction note</t>
         </is>
       </c>
       <c r="F104" s="2" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>High</t>
         </is>
       </c>
       <c r="G104" s="2" t="inlineStr">
@@ -5541,39 +5541,39 @@
       </c>
       <c r="I104" s="2" t="inlineStr">
         <is>
-          <t>pfees resolve as positive fees only (kind=processing_fee, amounts &gt;= 0) | WORDING+VIU 2026-07-13: Always a plus; carried.</t>
+          <t>builder UI absent (re-checked today) | WORDING+VIU 2026-07-13: Builder not shipped; when it ships, also check the §5-R15 note (currently absent in the whole-WO dialog per FD-WO-016). NOT BUILT: the template Type dropdown offers only Fee/Discount (no 'Processing Fee'); the Story-8 Processing-Fee builder UI has not shipped. The back-end DOES accept kind=processing_fee via API (201). Re-test when the builder ships. | V1_3 (2026-07-17): Δ1 — §5-R15 gains one appended sentence (spec verbatim): 'The note is shown only to users with See Financial Data.' Expected gains the gate qualifier. This dialog is the one place the gate is independently observable (Story-7 admin access needs no See Financial Data, while the WO Add/Edit dialog already requires it — spec-diff §H.b). Status stays Blocked-NotBuilt (Story-8 builder UI absent); check the note + gate when the builder ships. | STAGING VIU 2026-07-20 staging LIVE VIU: Processing Fee Taxable defaults Yes + jurisdiction note present; note gated on See Financial Data (Tech w/o SFD sees toggle, not note). Live staging (proc-fee-full.png / tech-tmpl-dialog.png).</t>
         </is>
       </c>
     </row>
     <row r="105">
       <c r="A105" s="2" t="inlineStr">
         <is>
-          <t>FD-PROC-012</t>
+          <t>FD-PROC-005</t>
         </is>
       </c>
       <c r="B105" s="2" t="inlineStr">
         <is>
-          <t>C28530</t>
+          <t>C28523</t>
         </is>
       </c>
       <c r="C105" s="6" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/28530</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/28523</t>
         </is>
       </c>
       <c r="D105" s="2" t="inlineStr">
         <is>
-          <t>Processing Fee — template edit independence</t>
+          <t>Processing Fee — no manual add</t>
         </is>
       </c>
       <c r="E105" s="2" t="inlineStr">
         <is>
-          <t>Verify editing a Processing Fee template does not change Processing Fees already on existing work orders</t>
+          <t>Verify a Processing Fee cannot be added to a work order by hand</t>
         </is>
       </c>
       <c r="F105" s="2" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>High</t>
         </is>
       </c>
       <c r="G105" s="2" t="inlineStr">
@@ -5588,39 +5588,39 @@
       </c>
       <c r="I105" s="2" t="inlineStr">
         <is>
-          <t>template amount 3-&gt;9 (200) left the existing WO pfee at 3 (values copied at apply time) | WORDING+VIU 2026-07-13: Template edit independence; carried.</t>
+          <t>manual pfee add -&gt; 400 'A processing fee cannot be added manually.'; manual pct_grand_total fee also rejected for scope | WORDING+VIU 2026-07-13: Confirmed: WO Add Type dropdown = Fee/Discord only (no Processing Fee); build labels ('Add Fee/Discount', 'Apply From Template'). | SV-8479/8480 deconfliction 2026-07-22: label sweep: navigation labels -&gt; 'Add Work Order Fee / Discount' / 'New Work Order Fee / Discount' (behavior/expected unchanged). | VIU 2026-07-22 LIVE: SV-8479 nav label 'Add Work Order Fee / Discount' confirmed present in the WO toolbar ⋯ menu; case behavior unchanged. Ev: wo/FD-WO-025-toolbar-menu.png.</t>
         </is>
       </c>
     </row>
     <row r="106">
       <c r="A106" s="2" t="inlineStr">
         <is>
-          <t>FD-PROC-013</t>
+          <t>FD-PROC-006</t>
         </is>
       </c>
       <c r="B106" s="2" t="inlineStr">
         <is>
-          <t>C28531</t>
+          <t>C28524</t>
         </is>
       </c>
       <c r="C106" s="6" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/28531</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/28524</t>
         </is>
       </c>
       <c r="D106" s="2" t="inlineStr">
         <is>
-          <t>Processing Fee — calculation edge</t>
+          <t>Processing Fee — auto-apply</t>
         </is>
       </c>
       <c r="E106" s="2" t="inlineStr">
         <is>
-          <t>Verify multiple Processing Fees each leave out all Processing Fees' amounts and tax from the shared base</t>
+          <t>Verify a Processing Fee reaches a new work order via location auto-apply</t>
         </is>
       </c>
       <c r="F106" s="2" t="inlineStr">
         <is>
-          <t>Low</t>
+          <t>High</t>
         </is>
       </c>
       <c r="G106" s="2" t="inlineStr">
@@ -5635,39 +5635,39 @@
       </c>
       <c r="I106" s="2" t="inlineStr">
         <is>
-          <t>two auto pfees (3%+2%) resolved 0.63/0.42 = exact 3:2 ratio -&gt; same base, pfees exclude each other | WORDING+VIU 2026-07-13: Multiple pfees share the same base; carried.</t>
+          <t>auto-apply pfee template landed on a fresh WO (kind=processing_fee, appliedBy=auto) | WORDING+VIU 2026-07-13: Reaches WO via auto-apply (pfee accepted by BE); build labels. Menu option is 'Remove' (Edit inert for a pfee). | SV-8456 (2026-07-21 staging LIVE VIU): F&amp;D moved to SETTINGS→SERVICE (below Canned Lines); template/WO/Part-sale/customer dialogs now show Taxable as a Yes/No DROPDOWN (was toggle); Auto-apply is a CHECKBOX with a 'When on…' caption; settings &amp; customer tables are plain-text/left-aligned (no badges); WO sidebar card retitled 'Work Order Fees &amp; Discounts' and renders ABOVE Financial Info; Part-sale card 'Parts Sale Fees &amp; Discounts' above Financial Info. Permission gate pivoted Settings→Finance → Settings→Service (verified live: Service-user sees+manages F&amp;D &amp; convenience toggle; Finance-only user has no F&amp;D nav item and /administration/adjustment-templates bounces to /workorders). Frontend-only; functionality + calc INTACT. | RE-VIU 2026-07-22 LIVE (Batch 4, SV-8456 re-verify): access-check quick-login {admin} HTTP 200. Re-confirmed on current staging build — 8 UI corrections intact (Taxable Yes/No dropdown; Auto-apply checkbox+caption; modal field order Type/CalcType&gt;Name&gt;Amount&gt;Taxable+jur.note&gt;Auto-apply&gt;Description; Settings table plain-text left-aligned no badges; F&amp;D nav under SERVICE below Canned Lines; WO &amp; Part-Sale cards above Financial Info [Batch 2/3]; Customer 'Fees &amp; Discounts' tab mirrors Settings styling minus convenience toggle) AND Settings-&gt;Service permission pivot CONFIRMED live per role (seeded ServiceRole vs FinanceRole, assigned to Tech, Tech restored to Technician 50bf6a0d + verified, both ZZAUTOTEST roles deleted 204): Service-user sees+manages F&amp;D nav + convenience toggle, direct /administration/adjustment-templates loads; Finance-only user has NO F&amp;D nav, FINANCE=Payment Methods only, direct route bounces to /workorders. viu_status VIU-Verified re-confirmed. Ev build/fees-discounts/viu-sv8456-2026-07-22/ (01-settings-landing, 02-new-dialog, 03-customer-fd-tab, SVC-*, FIN-*).</t>
         </is>
       </c>
     </row>
     <row r="107">
       <c r="A107" s="2" t="inlineStr">
         <is>
-          <t>FD-PROC-014</t>
+          <t>FD-PROC-007</t>
         </is>
       </c>
       <c r="B107" s="2" t="inlineStr">
         <is>
-          <t>C28532</t>
+          <t>C28525</t>
         </is>
       </c>
       <c r="C107" s="6" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/28532</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/28525</t>
         </is>
       </c>
       <c r="D107" s="2" t="inlineStr">
         <is>
-          <t>Processing Fee — negative</t>
+          <t>Processing Fee — customer default</t>
         </is>
       </c>
       <c r="E107" s="2" t="inlineStr">
         <is>
-          <t>Verify the system rejects a Processing Fee that carries a minimum amount</t>
+          <t>Verify a Processing Fee reaches a new work order via a customer default</t>
         </is>
       </c>
       <c r="F107" s="2" t="inlineStr">
         <is>
-          <t>Low</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="G107" s="2" t="inlineStr">
@@ -5682,39 +5682,39 @@
       </c>
       <c r="I107" s="2" t="inlineStr">
         <is>
-          <t>pfee minimum silently STRIPPED on create (201, no min field persisted) — §8 invariant holds; silent-ignore wording note stands | WORDING+VIU 2026-07-13: Confirmed live 2026-07-13: BE rejects a min/max cap on a Processing Fee (400 'A processing fee cannot have a minimum or maximum cap.'). PO Q4 (whether pfee minimums should be supported at all) still pending. | CHRIS WARD ROUND-2 ANSWER APPLIED 2026-07-14(Q4=B): PO ruled Processing Fees do NOT support a minimum and the app must make that clear (do not silently drop). Premise confirmed WAD: no minimum field in the UI and the API rejects a pfee minimum with an explicit error (matches the live 2026-07-13 finding: 400 'A processing fee cannot have a minimum or maximum cap.'). Older 2026-07-10 'silent strip' reading superseded (last-update-wins). Expected reworded to the explicit-reject + no-field behavior. PUSHED TO TESTRAIL 2026-07-14 via update_case (QA-lead one-day authorization; update 200 / re-verify 200 MATCH; audit: testrail-round2-push-log.md).</t>
+          <t>customer-default pfee landed on a fresh WO (kind=processing_fee, appliedBy=customer_default, amount 2.5) | WORDING+VIU 2026-07-13: Reaches WO via customer default; build labels. | SV-8456 (2026-07-21 staging LIVE VIU): F&amp;D moved to SETTINGS→SERVICE (below Canned Lines); template/WO/Part-sale/customer dialogs now show Taxable as a Yes/No DROPDOWN (was toggle); Auto-apply is a CHECKBOX with a 'When on…' caption; settings &amp; customer tables are plain-text/left-aligned (no badges); WO sidebar card retitled 'Work Order Fees &amp; Discounts' and renders ABOVE Financial Info; Part-sale card 'Parts Sale Fees &amp; Discounts' above Financial Info. Permission gate pivoted Settings→Finance → Settings→Service (verified live: Service-user sees+manages F&amp;D &amp; convenience toggle; Finance-only user has no F&amp;D nav item and /administration/adjustment-templates bounces to /workorders). Frontend-only; functionality + calc INTACT. | RE-VIU 2026-07-22 LIVE (Batch 4, SV-8456 re-verify): access-check quick-login {admin} HTTP 200. Re-confirmed on current staging build — 8 UI corrections intact (Taxable Yes/No dropdown; Auto-apply checkbox+caption; modal field order Type/CalcType&gt;Name&gt;Amount&gt;Taxable+jur.note&gt;Auto-apply&gt;Description; Settings table plain-text left-aligned no badges; F&amp;D nav under SERVICE below Canned Lines; WO &amp; Part-Sale cards above Financial Info [Batch 2/3]; Customer 'Fees &amp; Discounts' tab mirrors Settings styling minus convenience toggle) AND Settings-&gt;Service permission pivot CONFIRMED live per role (seeded ServiceRole vs FinanceRole, assigned to Tech, Tech restored to Technician 50bf6a0d + verified, both ZZAUTOTEST roles deleted 204): Service-user sees+manages F&amp;D nav + convenience toggle, direct /administration/adjustment-templates loads; Finance-only user has NO F&amp;D nav, FINANCE=Payment Methods only, direct route bounces to /workorders. viu_status VIU-Verified re-confirmed. Ev build/fees-discounts/viu-sv8456-2026-07-22/ (01-settings-landing, 02-new-dialog, 03-customer-fd-tab, SVC-*, FIN-*).</t>
         </is>
       </c>
     </row>
     <row r="108">
       <c r="A108" s="2" t="inlineStr">
         <is>
-          <t>FD-PSALE-001</t>
+          <t>FD-PROC-008</t>
         </is>
       </c>
       <c r="B108" s="2" t="inlineStr">
         <is>
-          <t>C29918</t>
+          <t>C28526</t>
         </is>
       </c>
       <c r="C108" s="6" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/29918</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/28526</t>
         </is>
       </c>
       <c r="D108" s="2" t="inlineStr">
         <is>
-          <t>Part Sale — Fee/Discount dialog</t>
+          <t>Processing Fee — WO behavior</t>
         </is>
       </c>
       <c r="E108" s="2" t="inlineStr">
         <is>
-          <t>Verify the Part Sale Add/Edit fee-or-discount dialog shows the tax-jurisdiction note below the Taxable Yes/No dropdown</t>
+          <t>Verify a Processing Fee on a work order can be removed but not edited</t>
         </is>
       </c>
       <c r="F108" s="2" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>High</t>
         </is>
       </c>
       <c r="G108" s="2" t="inlineStr">
@@ -5729,39 +5729,39 @@
       </c>
       <c r="I108" s="2" t="inlineStr">
         <is>
-          <t>administration/adjustment-templates loads; Finance-only user has NO F&amp;D nav, FINANCE=Payment Methods only, direct route bounces to /workorders. viu_status VIU-Verified re-confirmed. Ev build/fees-discounts/viu-sv8456-2026-07-22/ (01-settings-landing, 02-new-dialog, 03-customer-fd-tab, SVC-*, FIN-*).</t>
+          <t>BE re-proven: pfee change -&gt; 409 'cannot be edited through this endpoint', remove -&gt; 204; card still offers Edit per batch-1 (S8-N5 UI drift) | WORDING+VIU 2026-07-13: DEVIATION carried: the ⋮ menu still shows 'Edit' for a Processing Fee but it is inert (cannot edit a pfee on the WO); 'Remove' works. Build labels ('Remove Fee / Discount' confirm). | SV-8456 (2026-07-21 staging LIVE VIU): F&amp;D moved to SETTINGS→SERVICE (below Canned Lines); template/WO/Part-sale/customer dialogs now show Taxable as a Yes/No DROPDOWN (was toggle); Auto-apply is a CHECKBOX with a 'When on…' caption; settings &amp; customer tables are plain-text/left-aligned (no badges); WO sidebar card retitled 'Work Order Fees &amp; Discounts' and renders ABOVE Financial Info; Part-sale card 'Parts Sale Fees &amp; Discounts' above Financial Info. Permission gate pivoted Settings→Finance → Settings→Service (verified live: Service-user sees+manages F&amp;D &amp; convenience toggle; Finance-only user has no F&amp;D nav item and /administration/adjustment-templates bounces to /workorders). Frontend-only; functionality + calc INTACT. | RE-VIU 2026-07-22 LIVE (Batch 4, SV-8456 re-verify): access-check quick-login {admin} HTTP 200. The SV-8456 UI-correction wording + Settings-&gt;Service permission pivot were re-confirmed live on the current staging build (Service-user sees+manages F&amp;D; Finance-only user no F&amp;D nav, direct route bounces to /workorders; Tech restored to Technician 50bf6a0d + verified; ZZAUTOTEST roles deleted). This case retains its prior VIU-Deviation for its OWN (non-SV-8456) reason — that specific behavior was NOT re-driven this pass. Ev build/fees-discounts/viu-sv8456-2026-07-22/. | CLOSE-OUT 2026-07-24: matched-to-build per Ahtasham QA review 2026-07-24; synced from his TestRail edit (C28526) — Edit+Remove -&gt; Remove-only (dev removed the dead Edit). VIU-Deviation -&gt; VIU-Verified. HONESTY (Rule 12/22): accepted on Ahtasham's live QA review — NOT re-observed by us this pass.</t>
         </is>
       </c>
     </row>
     <row r="109">
       <c r="A109" s="2" t="inlineStr">
         <is>
-          <t>FD-PSALE-002</t>
+          <t>FD-PROC-009</t>
         </is>
       </c>
       <c r="B109" s="2" t="inlineStr">
         <is>
-          <t>C30623</t>
+          <t>C28527</t>
         </is>
       </c>
       <c r="C109" s="6" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/30623</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/28527</t>
         </is>
       </c>
       <c r="D109" s="2" t="inlineStr">
         <is>
-          <t>Parts page — 'FEES &amp; DISCOUNTS' column</t>
+          <t>Processing Fee — calculation</t>
         </is>
       </c>
       <c r="E109" s="2" t="inlineStr">
         <is>
-          <t>Verify the parts-sale Fees &amp; Discounts column no longer shows the '+ Add' button, and the per-row and top-right three-dot entry points remain</t>
+          <t>Verify a % of Grand Total Processing Fee works out last on the tax-included grand total (3% of $324 → +$9.72)</t>
         </is>
       </c>
       <c r="F109" s="2" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>High</t>
         </is>
       </c>
       <c r="G109" s="2" t="inlineStr">
@@ -5776,34 +5776,34 @@
       </c>
       <c r="I109" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve"> NEXUS 2-adj) + whole-sale percent/flat/discount; observed live as admin (Part Sales C&amp;E + SFD). Evidence build/fees-discounts/viu-sv8479-8480-2026-07-22/psale/. F&amp;D column has no '+ Add' (grep '+Add'=0); per-row ⋮ 'Add Part Fee / Discount' + top-right ⋮ 'Add Parts Sale Fee / Discount' both present.</t>
+          <t>FDBUG-2 CONFIRMED AGAIN with a clean discriminator: on a WO whose ONLY money is a whole-WO $20 taxable fee, 3% pfee resolved 0.63 (=3% of 21.00 incl the whole-WO fee + its tax); spec base must EXCLUDE whole-WO adjustments -&gt; expected 0.00 | WORDING+VIU 2026-07-13: DEVIATION carried (FDBUG-2): the Processing Fee base wrongly includes whole-WO fees/discounts + their tax (should exclude them). | SV-8421 PF-BASE FIX CONFIRMED LIVE (2026-07-24 staging): with a 3% Processing fee on Grand Total present, adding a $100 taxable whole-WO fee left the PF UNCHANGED at $13.92 (=3% x net$442 x(1+GST5%)=464.10) while tax grew $22.80-&gt;$27.80 — PF base EXCLUDES the whole-WO fee and its tax. FDBUG-2 RESOLVED. VIU-Deviation -&gt; VIU-Verified. Evidence build/fees-discounts/sv8421-followups-2026-07-24/FINDINGS.md + evidence/api_PFbase_after_100_taxable_fee.json. | CLOSE-OUT 2026-07-24: also accepted per Ahtasham QA live review 2026-07-24 (no bug). Already flipped to VIU-Verified by our own live SV-8421 spot-check 2026-07-24 (this one WE verified live — see FINDINGS.md). No status change here.</t>
         </is>
       </c>
     </row>
     <row r="110">
       <c r="A110" s="2" t="inlineStr">
         <is>
-          <t>FD-PSALE-003</t>
+          <t>FD-PROC-010</t>
         </is>
       </c>
       <c r="B110" s="2" t="inlineStr">
         <is>
-          <t>C30624</t>
+          <t>C28528</t>
         </is>
       </c>
       <c r="C110" s="6" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/30624</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/28528</t>
         </is>
       </c>
       <c r="D110" s="2" t="inlineStr">
         <is>
-          <t>Parts page — 'FEES &amp; DISCOUNTS' column</t>
+          <t>Processing Fee — negative</t>
         </is>
       </c>
       <c r="E110" s="2" t="inlineStr">
         <is>
-          <t>Verify the parts-sale per-part three-dot menu item reads 'Add Part Fee / Discount'</t>
+          <t>Verify a Processing Fee with a Max Amount or a disallowed method is rejected</t>
         </is>
       </c>
       <c r="F110" s="2" t="inlineStr">
@@ -5823,34 +5823,34 @@
       </c>
       <c r="I110" s="2" t="inlineStr">
         <is>
-          <t>TEST part sale P3-1118 (2 fee-less rows + NEXUS 2-adj) + whole-sale percent/flat/discount; observed live as admin (Part Sales C&amp;E + SFD). Evidence build/fees-discounts/viu-sv8479-8480-2026-07-22/psale/. Per-part ⋮ menu text = 'Add Part Fee / Discount' exactly; opens 'New Part Fee / Discount' dialog.</t>
+          <t>pfee template with maxCap -&gt; 400; pfee with pct_labor -&gt; 400 'not allowed for a processing_fee' | WORDING+VIU 2026-07-13: Confirmed live 2026-07-13 via API: Max cap → 400 'A processing fee cannot have a minimum or maximum cap.'; disallowed method → 400 'Calculation type "pct_subtotal" is not allowed for a processing_fee.' Lives in an API-titled section.</t>
         </is>
       </c>
     </row>
     <row r="111">
       <c r="A111" s="2" t="inlineStr">
         <is>
-          <t>FD-PSALE-004</t>
+          <t>FD-PROC-011</t>
         </is>
       </c>
       <c r="B111" s="2" t="inlineStr">
         <is>
-          <t>C30625</t>
+          <t>C28529</t>
         </is>
       </c>
       <c r="C111" s="6" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/30625</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/28529</t>
         </is>
       </c>
       <c r="D111" s="2" t="inlineStr">
         <is>
-          <t>Parts Sale — Fees &amp; Discounts card</t>
+          <t>Processing Fee — sign</t>
         </is>
       </c>
       <c r="E111" s="2" t="inlineStr">
         <is>
-          <t>Verify the Parts Sale Fees &amp; Discounts card shows each adjustment as plain text with the percentage in brackets (no colored badge)</t>
+          <t>Verify a Processing Fee always adds to the total (never a discount)</t>
         </is>
       </c>
       <c r="F111" s="2" t="inlineStr">
@@ -5870,34 +5870,34 @@
       </c>
       <c r="I111" s="2" t="inlineStr">
         <is>
-          <t>/fees-discounts/viu-sv8479-8480-2026-07-22/psale/. Whole-sale card 'Parts Sale Fees &amp; Discounts' live: 'Customer Fee (10%) +$82.12', 'Sale Disc (−5%) −$41.06', 'Flat Fee +$50.00' (flat name-only), 'Processing Fee (6%) +$51.73' — plain text, no badge, bracket %/sign convention matches WO card item 5.</t>
+          <t>pfees resolve as positive fees only (kind=processing_fee, amounts &gt;= 0) | WORDING+VIU 2026-07-13: Always a plus; carried.</t>
         </is>
       </c>
     </row>
     <row r="112">
       <c r="A112" s="2" t="inlineStr">
         <is>
-          <t>FD-PSALE-006</t>
+          <t>FD-PROC-012</t>
         </is>
       </c>
       <c r="B112" s="2" t="inlineStr">
         <is>
-          <t>C30626</t>
+          <t>C28530</t>
         </is>
       </c>
       <c r="C112" s="6" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/30626</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/28530</t>
         </is>
       </c>
       <c r="D112" s="2" t="inlineStr">
         <is>
-          <t>Parts Sale — Financial Info card</t>
+          <t>Processing Fee — template edit independence</t>
         </is>
       </c>
       <c r="E112" s="2" t="inlineStr">
         <is>
-          <t>Verify the parts-sale Financial Info card shows a 'Fees &amp; Discounts (N)' line directly above Subtotal and hides it when there are none</t>
+          <t>Verify editing a Processing Fee template does not change Processing Fees already on existing work orders</t>
         </is>
       </c>
       <c r="F112" s="2" t="inlineStr">
@@ -5917,39 +5917,39 @@
       </c>
       <c r="I112" s="2" t="inlineStr">
         <is>
-          <t>ded ZZAUTOTEST part sale P3-1118 (2 fee-less rows + NEXUS 2-adj) + whole-sale percent/flat/discount; observed live as admin (Part Sales C&amp;E + SFD). Evidence build/fees-discounts/viu-sv8479-8480-2026-07-22/psale/. Live: 'Fees &amp; Discounts (6) $189.27' directly above Subtotal $963.95 in Financial Info.</t>
+          <t>template amount 3-&gt;9 (200) left the existing WO pfee at 3 (values copied at apply time) | WORDING+VIU 2026-07-13: Template edit independence; carried.</t>
         </is>
       </c>
     </row>
     <row r="113">
       <c r="A113" s="2" t="inlineStr">
         <is>
-          <t>FD-PSALE-008</t>
+          <t>FD-PROC-013</t>
         </is>
       </c>
       <c r="B113" s="2" t="inlineStr">
         <is>
-          <t>C30627</t>
+          <t>C28531</t>
         </is>
       </c>
       <c r="C113" s="6" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/30627</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/28531</t>
         </is>
       </c>
       <c r="D113" s="2" t="inlineStr">
         <is>
-          <t>Part Sale — Fee/Discount dialog</t>
+          <t>Processing Fee — calculation edge</t>
         </is>
       </c>
       <c r="E113" s="2" t="inlineStr">
         <is>
-          <t>Verify the whole-parts-sale fee/discount dialog title reads 'New Parts Sale Fee / Discount' with subline 'Applying To: Entire Parts Sale'</t>
+          <t>Verify multiple Processing Fees each leave out all Processing Fees' amounts and tax from the shared base</t>
         </is>
       </c>
       <c r="F113" s="2" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>Low</t>
         </is>
       </c>
       <c r="G113" s="2" t="inlineStr">
@@ -5964,39 +5964,39 @@
       </c>
       <c r="I113" s="2" t="inlineStr">
         <is>
-          <t>). Evidence build/fees-discounts/viu-sv8479-8480-2026-07-22/psale/. VIU-CONFIRM RESOLVED (Picture 26 was missing): top-right ⋮ label CONFIRMED LIVE = 'Add Parts Sale Fee / Discount'; dialog title 'New Parts Sale Fee / Discount'; subline 'Applying To: Entire Parts Sale'. Case wording already matched.</t>
+          <t>two auto pfees (3%+2%) resolved 0.63/0.42 = exact 3:2 ratio -&gt; same base, pfees exclude each other | WORDING+VIU 2026-07-13: Multiple pfees share the same base; carried.</t>
         </is>
       </c>
     </row>
     <row r="114">
       <c r="A114" s="2" t="inlineStr">
         <is>
-          <t>FD-PSALE-009</t>
+          <t>FD-PROC-014</t>
         </is>
       </c>
       <c r="B114" s="2" t="inlineStr">
         <is>
-          <t>C30628</t>
+          <t>C28532</t>
         </is>
       </c>
       <c r="C114" s="6" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/30628</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/28532</t>
         </is>
       </c>
       <c r="D114" s="2" t="inlineStr">
         <is>
-          <t>Parts Sale — Statistics tab</t>
+          <t>Processing Fee — negative</t>
         </is>
       </c>
       <c r="E114" s="2" t="inlineStr">
         <is>
-          <t>Verify the Fees &amp; Discounts section on the parts-sale Statistics tab shows the '%' and 'Amount' column headings</t>
+          <t>Verify the system rejects a Processing Fee that carries a minimum amount</t>
         </is>
       </c>
       <c r="F114" s="2" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>Low</t>
         </is>
       </c>
       <c r="G114" s="2" t="inlineStr">
@@ -6011,39 +6011,39 @@
       </c>
       <c r="I114" s="2" t="inlineStr">
         <is>
-          <t>ss rows + NEXUS 2-adj) + whole-sale percent/flat/discount; observed live as admin (Part Sales C&amp;E + SFD). Evidence build/fees-discounts/viu-sv8479-8480-2026-07-22/psale/. Statistics F&amp;D (6) section live headings '% Amount'; flat fee blank %; rows +11%/+6%/+10% fees + −5% discounts; 'Total +$189.27'.</t>
+          <t>pfee minimum silently STRIPPED on create (201, no min field persisted) — §8 invariant holds; silent-ignore wording note stands | WORDING+VIU 2026-07-13: Confirmed live 2026-07-13: BE rejects a min/max cap on a Processing Fee (400 'A processing fee cannot have a minimum or maximum cap.'). PO Q4 (whether pfee minimums should be supported at all) still pending. | CHRIS WARD ROUND-2 ANSWER APPLIED 2026-07-14(Q4=B): PO ruled Processing Fees do NOT support a minimum and the app must make that clear (do not silently drop). Premise confirmed WAD: no minimum field in the UI and the API rejects a pfee minimum with an explicit error (matches the live 2026-07-13 finding: 400 'A processing fee cannot have a minimum or maximum cap.'). Older 2026-07-10 'silent strip' reading superseded (last-update-wins). Expected reworded to the explicit-reject + no-field behavior. PUSHED TO TESTRAIL 2026-07-14 via update_case (QA-lead one-day authorization; update 200 / re-verify 200 MATCH; audit: testrail-round2-push-log.md).</t>
         </is>
       </c>
     </row>
     <row r="115">
       <c r="A115" s="2" t="inlineStr">
         <is>
-          <t>FD-QB-012</t>
+          <t>FD-PSALE-001</t>
         </is>
       </c>
       <c r="B115" s="2" t="inlineStr">
         <is>
-          <t>C28555</t>
+          <t>C29918</t>
         </is>
       </c>
       <c r="C115" s="6" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/28555</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/29918</t>
         </is>
       </c>
       <c r="D115" s="2" t="inlineStr">
         <is>
-          <t>QuickBooks — negative totals</t>
+          <t>Part Sale — Fee/Discount dialog</t>
         </is>
       </c>
       <c r="E115" s="2" t="inlineStr">
         <is>
-          <t>Verify the net subtotal floors at $0.00 ($100 parts + $10 tax, $150 discount: non-taxable vs taxable)</t>
+          <t>Verify the Part Sale Add/Edit fee-or-discount dialog shows the tax-jurisdiction note below the Taxable Yes/No dropdown</t>
         </is>
       </c>
       <c r="F115" s="2" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="G115" s="2" t="inlineStr">
@@ -6058,39 +6058,39 @@
       </c>
       <c r="I115" s="2" t="inlineStr">
         <is>
-          <t>floor worked-example halves re-proven at WO level: non-taxable over-discount -&gt; sub 0.00, tax UNCHANGED (9.14), total=tax, excess 117.24; taxable variant -&gt; tax 0.00, total 0.00 | WORDING+VIU 2026-07-13: In-app floor VERIFIED (same worked example as FD-CALC-015, confirmed 2026-07-10); the customer pays the tax only.</t>
+          <t>administration/adjustment-templates loads; Finance-only user has NO F&amp;D nav, FINANCE=Payment Methods only, direct route bounces to /workorders. viu_status VIU-Verified re-confirmed. Ev build/fees-discounts/viu-sv8456-2026-07-22/ (01-settings-landing, 02-new-dialog, 03-customer-fd-tab, SVC-*, FIN-*).</t>
         </is>
       </c>
     </row>
     <row r="116">
       <c r="A116" s="2" t="inlineStr">
         <is>
-          <t>FD-QB-014</t>
+          <t>FD-PSALE-002</t>
         </is>
       </c>
       <c r="B116" s="2" t="inlineStr">
         <is>
-          <t>C28557</t>
+          <t>C30623</t>
         </is>
       </c>
       <c r="C116" s="6" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/28557</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/30623</t>
         </is>
       </c>
       <c r="D116" s="2" t="inlineStr">
         <is>
-          <t>QuickBooks — negative totals</t>
+          <t>Parts page — 'FEES &amp; DISCOUNTS' column</t>
         </is>
       </c>
       <c r="E116" s="2" t="inlineStr">
         <is>
-          <t>Verify a mandatory warning/confirmation before saving when discounts are bigger than the net subtotal</t>
+          <t>Verify the parts-sale Fees &amp; Discounts column no longer shows the '+ Add' button, and the per-row and top-right three-dot entry points remain</t>
         </is>
       </c>
       <c r="F116" s="2" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="G116" s="2" t="inlineStr">
@@ -6105,39 +6105,39 @@
       </c>
       <c r="I116" s="2" t="inlineStr">
         <is>
-          <t>FDBUG-15 CONFIRMED AGAIN (API half): over-discount saves 201 with NO warning payload; excess carried silently (117.24). Batch-6 UI shots show no warn/confirm dialog. Violates S6-R12 | WORDING+VIU 2026-07-13: DEVIATION carried (FDBUG-15 / PO Q1 pending): an over-discount currently saves SILENTLY — no mandatory warn/confirm before saving. Expected kept as the spec requirement. | CHRIS WARD ROUND-2 ANSWER APPLIED 2026-07-14(Q1=A): PO ruled the warn/confirm is required AND already exists per spec (S6-R12) — it fires before invoicing and before marking the WO reviewed/complete, NOT when the adjustment is merely added (add is uncommitted; the Add dialog preview shows the resulting totals). Our FDBUG-15 'silent save' was observed at ADD time = the wrong trigger point; PO says that is intentional. FDBUG-15 reclassified NOT-A-DEFECT (no dev ticket released). Expected reworded to the commit-point warning. Status -&gt; VIU-Pending: the invoice/mark-reviewed/complete warning has not yet been observed live and needs a commit-time re-VIU. PUSHED TO TESTRAIL 2026-07-14 via update_case (QA-lead one-day authorization; update 200 / re-verify 200 MATCH; audit: testrail-round2-push-log.md). COMMIT-TIME RE-VIU 2026-07-14: attempted but BOTH qb cookie sets (cookies-viu.env 2026-07-13, cookies-fresh.env 2026-07-10) return 401 sso_required on quick-login (env woken, API root 200) — cookies EXPIRED. Left VIU-Pending: needs fresh qb cookies for the commit-time (invoice / mark-reviewed / complete) re-VIU. | COMMIT-TIME RE-VIU SETTLED 2026-07-14 (fresh qb cookies): VERIFIED. Live FE source + live data-condition confirm Chris's Q1=A exactly. (1) ADD-TIME SILENT: the Add/Edit dialog component (AdjustmentDialog) has NO over-discount warning and does not import the warning dialog -- adding an over-sized discount is silent (only an unrelated 'A percentage discount cannot exceed 100%' field check). (2) COMMIT-TIME WARN/CONFIRM BUILT: a dedicated component OverDiscountWarningDialog exists (title 'Discount exceeds subtotal'; body "The total discount exceeds this work order's subtotal. The subtotal will be reduced to $0.00, but any tax on the taxable base is still owed. The remaining $&lt;excess&gt; will be carried as a customer credit. Continue?"; buttons Continue / Cancel). It is imported and wired in the Invoice component: the Create-Invoice handler (Lt-&gt;_a) AND the mark-reviewed/Complete handler (Vt-&gt;ga, posts status:'complete') BOTH intercept when the excess-credit gate is true (FeesAndDiscounts flag ON &amp;&amp; not partSale &amp;&amp; adjustmentsSummary.excessCreditAmount&gt;0), open the dialog, and only run the commit on Continue (confirm) / abort on Cancel. So the mandatory warn/confirm fires at BOTH commit points, never silently. (3) LIVE DATA CONDITION: on WO S-15970 added a $9,999 whole-WO flat discount (reversible ZZAUTOTEST, removed after) -&gt; sub_total floored to $0.00, adjustmentsSummary.excessCreditAmount=9522.26 (&gt;0) =&gt; the FE gate evaluates TRUE, so the dialog would fire at Create Invoice / Mark-Reviewed / Complete. WO restored byte-identical to baseline afterward. Evidence: FE chunks OverDiscountWarningDialog.BCmTBE33.js + Invoice.Ny62BJnd.js + AdjustmentDialog.S8gN6cAn.js (captured live from qb.qa.shopview.com 2026-07-14); live API view before/after. Verdict: VIU-Verified. FDBUG-15 stays NOT-A-DEFECT (add-time silence is intentional). Expected wording already build-accurate (floor $0.00 + tax on taxable base still owed + exact excess as customer credit + must confirm) -&gt; no TestRail wording change needed; status flip local only. Exact on-screen labels now captured for the record: dialog 'Discount exceeds subtotal', buttons 'Continue'/'Cancel'.</t>
+          <t xml:space="preserve"> NEXUS 2-adj) + whole-sale percent/flat/discount; observed live as admin (Part Sales C&amp;E + SFD). Evidence build/fees-discounts/viu-sv8479-8480-2026-07-22/psale/. F&amp;D column has no '+ Add' (grep '+Add'=0); per-row ⋮ 'Add Part Fee / Discount' + top-right ⋮ 'Add Parts Sale Fee / Discount' both present.</t>
         </is>
       </c>
     </row>
     <row r="117">
       <c r="A117" s="2" t="inlineStr">
         <is>
-          <t>FD-REMOVE-001</t>
+          <t>FD-PSALE-003</t>
         </is>
       </c>
       <c r="B117" s="2" t="inlineStr">
         <is>
-          <t>C28479</t>
+          <t>C30624</t>
         </is>
       </c>
       <c r="C117" s="6" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/28479</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/30624</t>
         </is>
       </c>
       <c r="D117" s="2" t="inlineStr">
         <is>
-          <t>Work Order — Remove an adjustment</t>
+          <t>Parts page — 'FEES &amp; DISCOUNTS' column</t>
         </is>
       </c>
       <c r="E117" s="2" t="inlineStr">
         <is>
-          <t>Verify removing a whole-work-order fee/discount shows the 'Remove Fee / Discount' confirm and a success message</t>
+          <t>Verify the parts-sale per-part three-dot menu item reads 'Add Part Fee / Discount'</t>
         </is>
       </c>
       <c r="F117" s="2" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="G117" s="2" t="inlineStr">
@@ -6152,39 +6152,39 @@
       </c>
       <c r="I117" s="2" t="inlineStr">
         <is>
-          <t>remove-confirm wording drift per batch-1 (case-update); not re-driven today | WORDING+VIU 2026-07-13: Confirm dialog matched EXACTLY live: title 'Remove Fee / Discount', message 'Are you sure you want to remove this fee?', buttons 'Remove'/'Cancel' (shot inline-02; cancelled — no shared data deleted). Toast not re-observed this run. | SV-8456 (2026-07-21 staging LIVE VIU): F&amp;D moved to SETTINGS→SERVICE (below Canned Lines); template/WO/Part-sale/customer dialogs now show Taxable as a Yes/No DROPDOWN (was toggle); Auto-apply is a CHECKBOX with a 'When on…' caption; settings &amp; customer tables are plain-text/left-aligned (no badges); WO sidebar card retitled 'Work Order Fees &amp; Discounts' and renders ABOVE Financial Info; Part-sale card 'Parts Sale Fees &amp; Discounts' above Financial Info. Permission gate pivoted Settings→Finance → Settings→Service (verified live: Service-user sees+manages F&amp;D &amp; convenience toggle; Finance-only user has no F&amp;D nav item and /administration/adjustment-templates bounces to /workorders). Frontend-only; functionality + calc INTACT. | RE-VIU 2026-07-22 LIVE (Batch 4, SV-8456 re-verify): access-check quick-login {admin} HTTP 200. Re-confirmed on current staging build — 8 UI corrections intact (Taxable Yes/No dropdown; Auto-apply checkbox+caption; modal field order Type/CalcType&gt;Name&gt;Amount&gt;Taxable+jur.note&gt;Auto-apply&gt;Description; Settings table plain-text left-aligned no badges; F&amp;D nav under SERVICE below Canned Lines; WO &amp; Part-Sale cards above Financial Info [Batch 2/3]; Customer 'Fees &amp; Discounts' tab mirrors Settings styling minus convenience toggle) AND Settings-&gt;Service permission pivot CONFIRMED live per role (seeded ServiceRole vs FinanceRole, assigned to Tech, Tech restored to Technician 50bf6a0d + verified, both ZZAUTOTEST roles deleted 204): Service-user sees+manages F&amp;D nav + convenience toggle, direct /administration/adjustment-templates loads; Finance-only user has NO F&amp;D nav, FINANCE=Payment Methods only, direct route bounces to /workorders. viu_status VIU-Verified re-confirmed. Ev build/fees-discounts/viu-sv8456-2026-07-22/ (01-settings-landing, 02-new-dialog, 03-customer-fd-tab, SVC-*, FIN-*).</t>
+          <t>TEST part sale P3-1118 (2 fee-less rows + NEXUS 2-adj) + whole-sale percent/flat/discount; observed live as admin (Part Sales C&amp;E + SFD). Evidence build/fees-discounts/viu-sv8479-8480-2026-07-22/psale/. Per-part ⋮ menu text = 'Add Part Fee / Discount' exactly; opens 'New Part Fee / Discount' dialog.</t>
         </is>
       </c>
     </row>
     <row r="118">
       <c r="A118" s="2" t="inlineStr">
         <is>
-          <t>FD-REMOVE-002</t>
+          <t>FD-PSALE-004</t>
         </is>
       </c>
       <c r="B118" s="2" t="inlineStr">
         <is>
-          <t>C28480</t>
+          <t>C30625</t>
         </is>
       </c>
       <c r="C118" s="6" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/28480</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/30625</t>
         </is>
       </c>
       <c r="D118" s="2" t="inlineStr">
         <is>
-          <t>Work Order — Remove an adjustment</t>
+          <t>Parts Sale — Fees &amp; Discounts card</t>
         </is>
       </c>
       <c r="E118" s="2" t="inlineStr">
         <is>
-          <t>Verify removing a fee/discount uses Create and Edit, not a separate Delete permission</t>
+          <t>Verify the Parts Sale Fees &amp; Discounts card shows each adjustment as plain text with the percentage in brackets (no colored badge)</t>
         </is>
       </c>
       <c r="F118" s="2" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="G118" s="2" t="inlineStr">
@@ -6199,34 +6199,34 @@
       </c>
       <c r="I118" s="2" t="inlineStr">
         <is>
-          <t>removal governed by Create&amp;Edit (tech WITH lines-C&amp;E removed line-level 204; no Delete-perm dependency) | WORDING+VIU 2026-07-13: Remove uses Create &amp; Edit not a separate Delete permission; carry prior VIU. | SV-8456 (2026-07-21 staging LIVE VIU): F&amp;D moved to SETTINGS→SERVICE (below Canned Lines); template/WO/Part-sale/customer dialogs now show Taxable as a Yes/No DROPDOWN (was toggle); Auto-apply is a CHECKBOX with a 'When on…' caption; settings &amp; customer tables are plain-text/left-aligned (no badges); WO sidebar card retitled 'Work Order Fees &amp; Discounts' and renders ABOVE Financial Info; Part-sale card 'Parts Sale Fees &amp; Discounts' above Financial Info. Permission gate pivoted Settings→Finance → Settings→Service (verified live: Service-user sees+manages F&amp;D &amp; convenience toggle; Finance-only user has no F&amp;D nav item and /administration/adjustment-templates bounces to /workorders). Frontend-only; functionality + calc INTACT. | RE-VIU 2026-07-22 LIVE (Batch 4, SV-8456 re-verify): access-check quick-login {admin} HTTP 200. Re-confirmed on current staging build — 8 UI corrections intact (Taxable Yes/No dropdown; Auto-apply checkbox+caption; modal field order Type/CalcType&gt;Name&gt;Amount&gt;Taxable+jur.note&gt;Auto-apply&gt;Description; Settings table plain-text left-aligned no badges; F&amp;D nav under SERVICE below Canned Lines; WO &amp; Part-Sale cards above Financial Info [Batch 2/3]; Customer 'Fees &amp; Discounts' tab mirrors Settings styling minus convenience toggle) AND Settings-&gt;Service permission pivot CONFIRMED live per role (seeded ServiceRole vs FinanceRole, assigned to Tech, Tech restored to Technician 50bf6a0d + verified, both ZZAUTOTEST roles deleted 204): Service-user sees+manages F&amp;D nav + convenience toggle, direct /administration/adjustment-templates loads; Finance-only user has NO F&amp;D nav, FINANCE=Payment Methods only, direct route bounces to /workorders. viu_status VIU-Verified re-confirmed. Ev build/fees-discounts/viu-sv8456-2026-07-22/ (01-settings-landing, 02-new-dialog, 03-customer-fd-tab, SVC-*, FIN-*).</t>
+          <t>/fees-discounts/viu-sv8479-8480-2026-07-22/psale/. Whole-sale card 'Parts Sale Fees &amp; Discounts' live: 'Customer Fee (10%) +$82.12', 'Sale Disc (−5%) −$41.06', 'Flat Fee +$50.00' (flat name-only), 'Processing Fee (6%) +$51.73' — plain text, no badge, bracket %/sign convention matches WO card item 5.</t>
         </is>
       </c>
     </row>
     <row r="119">
       <c r="A119" s="2" t="inlineStr">
         <is>
-          <t>FD-REMOVE-003</t>
+          <t>FD-PSALE-006</t>
         </is>
       </c>
       <c r="B119" s="2" t="inlineStr">
         <is>
-          <t>C28481</t>
+          <t>C30626</t>
         </is>
       </c>
       <c r="C119" s="6" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/28481</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/30626</t>
         </is>
       </c>
       <c r="D119" s="2" t="inlineStr">
         <is>
-          <t>Work Order — Remove an adjustment</t>
+          <t>Parts Sale — Financial Info card</t>
         </is>
       </c>
       <c r="E119" s="2" t="inlineStr">
         <is>
-          <t>Verify removing a line-level fee/discount from its inline ⋮ menu</t>
+          <t>Verify the parts-sale Financial Info card shows a 'Fees &amp; Discounts (N)' line directly above Subtotal and hides it when there are none</t>
         </is>
       </c>
       <c r="F119" s="2" t="inlineStr">
@@ -6246,39 +6246,39 @@
       </c>
       <c r="I119" s="2" t="inlineStr">
         <is>
-          <t>line-level remove 204 and gone from the line | WORDING+VIU 2026-07-13: Inline menu option is 'Remove' (was 'Delete'); confirm dialog 'Remove Fee / Discount' confirmed live.</t>
+          <t>ded ZZAUTOTEST part sale P3-1118 (2 fee-less rows + NEXUS 2-adj) + whole-sale percent/flat/discount; observed live as admin (Part Sales C&amp;E + SFD). Evidence build/fees-discounts/viu-sv8479-8480-2026-07-22/psale/. Live: 'Fees &amp; Discounts (6) $189.27' directly above Subtotal $963.95 in Financial Info.</t>
         </is>
       </c>
     </row>
     <row r="120">
       <c r="A120" s="2" t="inlineStr">
         <is>
-          <t>FD-STACK-001</t>
+          <t>FD-PSALE-008</t>
         </is>
       </c>
       <c r="B120" s="2" t="inlineStr">
         <is>
-          <t>C28482</t>
+          <t>C30627</t>
         </is>
       </c>
       <c r="C120" s="6" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/28482</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/30627</t>
         </is>
       </c>
       <c r="D120" s="2" t="inlineStr">
         <is>
-          <t>Work Order — Multiple adjustments (stacking / netting)</t>
+          <t>Part Sale — Fee/Discount dialog</t>
         </is>
       </c>
       <c r="E120" s="2" t="inlineStr">
         <is>
-          <t>Verify multiple fees/discounts on one part each work out on the part's own total (they do not compound)</t>
+          <t>Verify the whole-parts-sale fee/discount dialog title reads 'New Parts Sale Fee / Discount' with subline 'Applying To: Entire Parts Sale'</t>
         </is>
       </c>
       <c r="F120" s="2" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="G120" s="2" t="inlineStr">
@@ -6293,39 +6293,39 @@
       </c>
       <c r="I120" s="2" t="inlineStr">
         <is>
-          <t>part flat + part pct resolved independently on the part's own gross (fresh: $8.00 and $17.08 coexist, no compounding) | WORDING+VIU 2026-07-13: Netting carried; build labels. Display half (only first shows + 'Show N more') is the FD-INLINE-003 deviation (no Show-N-more in this build).</t>
+          <t>). Evidence build/fees-discounts/viu-sv8479-8480-2026-07-22/psale/. VIU-CONFIRM RESOLVED (Picture 26 was missing): top-right ⋮ label CONFIRMED LIVE = 'Add Parts Sale Fee / Discount'; dialog title 'New Parts Sale Fee / Discount'; subline 'Applying To: Entire Parts Sale'. Case wording already matched.</t>
         </is>
       </c>
     </row>
     <row r="121">
       <c r="A121" s="2" t="inlineStr">
         <is>
-          <t>FD-STACK-002</t>
+          <t>FD-PSALE-009</t>
         </is>
       </c>
       <c r="B121" s="2" t="inlineStr">
         <is>
-          <t>C28483</t>
+          <t>C30628</t>
         </is>
       </c>
       <c r="C121" s="6" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/28483</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/30628</t>
         </is>
       </c>
       <c r="D121" s="2" t="inlineStr">
         <is>
-          <t>Work Order — Multiple adjustments (stacking / netting)</t>
+          <t>Parts Sale — Statistics tab</t>
         </is>
       </c>
       <c r="E121" s="2" t="inlineStr">
         <is>
-          <t>Verify two whole-work-order percentage fees/discounts use the same totals and do not change each other's base</t>
+          <t>Verify the Fees &amp; Discounts section on the parts-sale Statistics tab shows the '%' and 'Amount' column headings</t>
         </is>
       </c>
       <c r="F121" s="2" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="G121" s="2" t="inlineStr">
@@ -6340,39 +6340,39 @@
       </c>
       <c r="I121" s="2" t="inlineStr">
         <is>
-          <t>two 10% whole-WO fees resolve 17.08 each (same base, no compounding) | WORDING+VIU 2026-07-13: Same-base netting carried; build labels.</t>
+          <t>ss rows + NEXUS 2-adj) + whole-sale percent/flat/discount; observed live as admin (Part Sales C&amp;E + SFD). Evidence build/fees-discounts/viu-sv8479-8480-2026-07-22/psale/. Statistics F&amp;D (6) section live headings '% Amount'; flat fee blank %; rows +11%/+6%/+10% fees + −5% discounts; 'Total +$189.27'.</t>
         </is>
       </c>
     </row>
     <row r="122">
       <c r="A122" s="2" t="inlineStr">
         <is>
-          <t>FD-STACK-003</t>
+          <t>FD-QB-012</t>
         </is>
       </c>
       <c r="B122" s="2" t="inlineStr">
         <is>
-          <t>C28484</t>
+          <t>C28555</t>
         </is>
       </c>
       <c r="C122" s="6" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/28484</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/28555</t>
         </is>
       </c>
       <c r="D122" s="2" t="inlineStr">
         <is>
-          <t>Work Order — Multiple adjustments (stacking / netting)</t>
+          <t>QuickBooks — negative totals</t>
         </is>
       </c>
       <c r="E122" s="2" t="inlineStr">
         <is>
-          <t>Verify the same template can be applied to one work order more than once by hand</t>
+          <t>Verify the net subtotal floors at $0.00 ($100 parts + $10 tax, $150 discount: non-taxable vs taxable)</t>
         </is>
       </c>
       <c r="F122" s="2" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>High</t>
         </is>
       </c>
       <c r="G122" s="2" t="inlineStr">
@@ -6387,34 +6387,34 @@
       </c>
       <c r="I122" s="2" t="inlineStr">
         <is>
-          <t>'Flat fee' template applied twice by hand -&gt; 201/201, two distinct adjustments | WORDING+VIU 2026-07-13: Same-template-twice carried; build labels ('Add Fee/Discount', 'Apply From Template', 'WO Fees &amp; Discounts'). | SV-8456 (2026-07-21 staging LIVE VIU): F&amp;D moved to SETTINGS→SERVICE (below Canned Lines); template/WO/Part-sale/customer dialogs now show Taxable as a Yes/No DROPDOWN (was toggle); Auto-apply is a CHECKBOX with a 'When on…' caption; settings &amp; customer tables are plain-text/left-aligned (no badges); WO sidebar card retitled 'Work Order Fees &amp; Discounts' and renders ABOVE Financial Info; Part-sale card 'Parts Sale Fees &amp; Discounts' above Financial Info. Permission gate pivoted Settings→Finance → Settings→Service (verified live: Service-user sees+manages F&amp;D &amp; convenience toggle; Finance-only user has no F&amp;D nav item and /administration/adjustment-templates bounces to /workorders). Frontend-only; functionality + calc INTACT. | SV-8479/8480 deconfliction 2026-07-22: label sweep: navigation labels -&gt; 'Add Work Order Fee / Discount' / 'New Work Order Fee / Discount' (behavior/expected unchanged). | VIU 2026-07-22 LIVE: SV-8479 nav label 'Add Work Order Fee / Discount' confirmed present in the WO toolbar ⋯ menu; case behavior unchanged. Ev: wo/FD-WO-025-toolbar-menu.png. | RE-VIU 2026-07-22 LIVE (Batch 4, SV-8456 re-verify): access-check quick-login {admin} HTTP 200. Re-confirmed on current staging build — 8 UI corrections intact (Taxable Yes/No dropdown; Auto-apply checkbox+caption; modal field order Type/CalcType&gt;Name&gt;Amount&gt;Taxable+jur.note&gt;Auto-apply&gt;Description; Settings table plain-text left-aligned no badges; F&amp;D nav under SERVICE below Canned Lines; WO &amp; Part-Sale cards above Financial Info [Batch 2/3]; Customer 'Fees &amp; Discounts' tab mirrors Settings styling minus convenience toggle) AND Settings-&gt;Service permission pivot CONFIRMED live per role (seeded ServiceRole vs FinanceRole, assigned to Tech, Tech restored to Technician 50bf6a0d + verified, both ZZAUTOTEST roles deleted 204): Service-user sees+manages F&amp;D nav + convenience toggle, direct /administration/adjustment-templates loads; Finance-only user has NO F&amp;D nav, FINANCE=Payment Methods only, direct route bounces to /workorders. viu_status VIU-Verified re-confirmed. Ev build/fees-discounts/viu-sv8456-2026-07-22/ (01-settings-landing, 02-new-dialog, 03-customer-fd-tab, SVC-*, FIN-*).</t>
+          <t>floor worked-example halves re-proven at WO level: non-taxable over-discount -&gt; sub 0.00, tax UNCHANGED (9.14), total=tax, excess 117.24; taxable variant -&gt; tax 0.00, total 0.00 | WORDING+VIU 2026-07-13: In-app floor VERIFIED (same worked example as FD-CALC-015, confirmed 2026-07-10); the customer pays the tax only.</t>
         </is>
       </c>
     </row>
     <row r="123">
       <c r="A123" s="2" t="inlineStr">
         <is>
-          <t>FD-STATS-001</t>
+          <t>FD-QB-014</t>
         </is>
       </c>
       <c r="B123" s="2" t="inlineStr">
         <is>
-          <t>C28459</t>
+          <t>C28557</t>
         </is>
       </c>
       <c r="C123" s="6" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/28459</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/28557</t>
         </is>
       </c>
       <c r="D123" s="2" t="inlineStr">
         <is>
-          <t>Work Order — Statistics tab</t>
+          <t>QuickBooks — negative totals</t>
         </is>
       </c>
       <c r="E123" s="2" t="inlineStr">
         <is>
-          <t>Verify the Stats tab Fees &amp; Discounts section shows the '%' and 'Amount' column headings with each row's value and amount</t>
+          <t>Verify a mandatory warning/confirmation before saving when discounts are bigger than the net subtotal</t>
         </is>
       </c>
       <c r="F123" s="2" t="inlineStr">
@@ -6434,34 +6434,34 @@
       </c>
       <c r="I123" s="2" t="inlineStr">
         <is>
-          <t>CONFIRMED AGAIN: Stats shows aggregate 'Fees &amp; Discounts (5) $25.00' style block, NOT the per-row Value/%+Amount table — PO Q1=B design regression persists (shot 07-stats) | WORDING+VIU 2026-07-13: DEVIATION (BUG-FD-2): the Stats 'Fees &amp; Discounts (N)' section lists rows (name, a value/% for percentages, and an amount) but has NO 'Value'/'Amount' column headers like the other Stats sections. Confirmed live (shot fin-01). | SV-8479/8480 deconfliction 2026-07-22: added the right-side '%' and 'Amount' column headings + blank-% for flat fees (item 12). Absorbs dropped new case FD-WO-027. viu_status unchanged (VIU-Deviation) — re-observe at VIU. | VIU 2026-07-22 LIVE: prior 'no headers' deviation RESOLVED — Stats tab 'Fees &amp; Discounts (10)' section now shows the '% Amount' column headings. Rows show percent under % (blank for flat: 'Flat Fee 2 +$32.00', 'Flat Fee +$11.00') and signed amount under Amount ('Labor Fee +20% +$101.98', 'Labor Disc −10% −$50.99', 'Customer Fee +10% +$65.88', 'WO Disc −5% −$32.94'), with 'Total +$273.31'. Ev: wo/FD-STATS-001-stats-tab.png, wo/stats-bodytext.txt.</t>
+          <t>FDBUG-15 CONFIRMED AGAIN (API half): over-discount saves 201 with NO warning payload; excess carried silently (117.24). Batch-6 UI shots show no warn/confirm dialog. Violates S6-R12 | WORDING+VIU 2026-07-13: DEVIATION carried (FDBUG-15 / PO Q1 pending): an over-discount currently saves SILENTLY — no mandatory warn/confirm before saving. Expected kept as the spec requirement. | CHRIS WARD ROUND-2 ANSWER APPLIED 2026-07-14(Q1=A): PO ruled the warn/confirm is required AND already exists per spec (S6-R12) — it fires before invoicing and before marking the WO reviewed/complete, NOT when the adjustment is merely added (add is uncommitted; the Add dialog preview shows the resulting totals). Our FDBUG-15 'silent save' was observed at ADD time = the wrong trigger point; PO says that is intentional. FDBUG-15 reclassified NOT-A-DEFECT (no dev ticket released). Expected reworded to the commit-point warning. Status -&gt; VIU-Pending: the invoice/mark-reviewed/complete warning has not yet been observed live and needs a commit-time re-VIU. PUSHED TO TESTRAIL 2026-07-14 via update_case (QA-lead one-day authorization; update 200 / re-verify 200 MATCH; audit: testrail-round2-push-log.md). COMMIT-TIME RE-VIU 2026-07-14: attempted but BOTH qb cookie sets (cookies-viu.env 2026-07-13, cookies-fresh.env 2026-07-10) return 401 sso_required on quick-login (env woken, API root 200) — cookies EXPIRED. Left VIU-Pending: needs fresh qb cookies for the commit-time (invoice / mark-reviewed / complete) re-VIU. | COMMIT-TIME RE-VIU SETTLED 2026-07-14 (fresh qb cookies): VERIFIED. Live FE source + live data-condition confirm Chris's Q1=A exactly. (1) ADD-TIME SILENT: the Add/Edit dialog component (AdjustmentDialog) has NO over-discount warning and does not import the warning dialog -- adding an over-sized discount is silent (only an unrelated 'A percentage discount cannot exceed 100%' field check). (2) COMMIT-TIME WARN/CONFIRM BUILT: a dedicated component OverDiscountWarningDialog exists (title 'Discount exceeds subtotal'; body "The total discount exceeds this work order's subtotal. The subtotal will be reduced to $0.00, but any tax on the taxable base is still owed. The remaining $&lt;excess&gt; will be carried as a customer credit. Continue?"; buttons Continue / Cancel). It is imported and wired in the Invoice component: the Create-Invoice handler (Lt-&gt;_a) AND the mark-reviewed/Complete handler (Vt-&gt;ga, posts status:'complete') BOTH intercept when the excess-credit gate is true (FeesAndDiscounts flag ON &amp;&amp; not partSale &amp;&amp; adjustmentsSummary.excessCreditAmount&gt;0), open the dialog, and only run the commit on Continue (confirm) / abort on Cancel. So the mandatory warn/confirm fires at BOTH commit points, never silently. (3) LIVE DATA CONDITION: on WO S-15970 added a $9,999 whole-WO flat discount (reversible ZZAUTOTEST, removed after) -&gt; sub_total floored to $0.00, adjustmentsSummary.excessCreditAmount=9522.26 (&gt;0) =&gt; the FE gate evaluates TRUE, so the dialog would fire at Create Invoice / Mark-Reviewed / Complete. WO restored byte-identical to baseline afterward. Evidence: FE chunks OverDiscountWarningDialog.BCmTBE33.js + Invoice.Ny62BJnd.js + AdjustmentDialog.S8gN6cAn.js (captured live from qb.qa.shopview.com 2026-07-14); live API view before/after. Verdict: VIU-Verified. FDBUG-15 stays NOT-A-DEFECT (add-time silence is intentional). Expected wording already build-accurate (floor $0.00 + tax on taxable base still owed + exact excess as customer credit + must confirm) -&gt; no TestRail wording change needed; status flip local only. Exact on-screen labels now captured for the record: dialog 'Discount exceeds subtotal', buttons 'Continue'/'Cancel'.</t>
         </is>
       </c>
     </row>
     <row r="124">
       <c r="A124" s="2" t="inlineStr">
         <is>
-          <t>FD-STATS-003</t>
+          <t>FD-REMOVE-001</t>
         </is>
       </c>
       <c r="B124" s="2" t="inlineStr">
         <is>
-          <t>C28461</t>
+          <t>C28479</t>
         </is>
       </c>
       <c r="C124" s="6" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/28461</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/28479</t>
         </is>
       </c>
       <c r="D124" s="2" t="inlineStr">
         <is>
-          <t>Work Order — Statistics tab</t>
+          <t>Work Order — Remove an adjustment</t>
         </is>
       </c>
       <c r="E124" s="2" t="inlineStr">
         <is>
-          <t>Verify the Stats 'Fees &amp; Discounts' total equals the signed sum of all the amounts</t>
+          <t>Verify removing a whole-work-order fee/discount shows the 'Remove Fee / Discount' confirm and a success message</t>
         </is>
       </c>
       <c r="F124" s="2" t="inlineStr">
@@ -6481,39 +6481,39 @@
       </c>
       <c r="I124" s="2" t="inlineStr">
         <is>
-          <t>net = signed sum re-consistent (adjustmentsSummary netAmount matches card); full UI table from batch-2 | WORDING+VIU 2026-07-13: Total = signed sum; carry prior VIU. Minus-sign jargon removed.</t>
+          <t>remove-confirm wording drift per batch-1 (case-update); not re-driven today | WORDING+VIU 2026-07-13: Confirm dialog matched EXACTLY live: title 'Remove Fee / Discount', message 'Are you sure you want to remove this fee?', buttons 'Remove'/'Cancel' (shot inline-02; cancelled — no shared data deleted). Toast not re-observed this run. | SV-8456 (2026-07-21 staging LIVE VIU): F&amp;D moved to SETTINGS→SERVICE (below Canned Lines); template/WO/Part-sale/customer dialogs now show Taxable as a Yes/No DROPDOWN (was toggle); Auto-apply is a CHECKBOX with a 'When on…' caption; settings &amp; customer tables are plain-text/left-aligned (no badges); WO sidebar card retitled 'Work Order Fees &amp; Discounts' and renders ABOVE Financial Info; Part-sale card 'Parts Sale Fees &amp; Discounts' above Financial Info. Permission gate pivoted Settings→Finance → Settings→Service (verified live: Service-user sees+manages F&amp;D &amp; convenience toggle; Finance-only user has no F&amp;D nav item and /administration/adjustment-templates bounces to /workorders). Frontend-only; functionality + calc INTACT. | RE-VIU 2026-07-22 LIVE (Batch 4, SV-8456 re-verify): access-check quick-login {admin} HTTP 200. Re-confirmed on current staging build — 8 UI corrections intact (Taxable Yes/No dropdown; Auto-apply checkbox+caption; modal field order Type/CalcType&gt;Name&gt;Amount&gt;Taxable+jur.note&gt;Auto-apply&gt;Description; Settings table plain-text left-aligned no badges; F&amp;D nav under SERVICE below Canned Lines; WO &amp; Part-Sale cards above Financial Info [Batch 2/3]; Customer 'Fees &amp; Discounts' tab mirrors Settings styling minus convenience toggle) AND Settings-&gt;Service permission pivot CONFIRMED live per role (seeded ServiceRole vs FinanceRole, assigned to Tech, Tech restored to Technician 50bf6a0d + verified, both ZZAUTOTEST roles deleted 204): Service-user sees+manages F&amp;D nav + convenience toggle, direct /administration/adjustment-templates loads; Finance-only user has NO F&amp;D nav, FINANCE=Payment Methods only, direct route bounces to /workorders. viu_status VIU-Verified re-confirmed. Ev build/fees-discounts/viu-sv8456-2026-07-22/ (01-settings-landing, 02-new-dialog, 03-customer-fd-tab, SVC-*, FIN-*).</t>
         </is>
       </c>
     </row>
     <row r="125">
       <c r="A125" s="2" t="inlineStr">
         <is>
-          <t>FD-STATS-005</t>
+          <t>FD-REMOVE-002</t>
         </is>
       </c>
       <c r="B125" s="2" t="inlineStr">
         <is>
-          <t>C28463</t>
+          <t>C28480</t>
         </is>
       </c>
       <c r="C125" s="6" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/28463</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/28480</t>
         </is>
       </c>
       <c r="D125" s="2" t="inlineStr">
         <is>
-          <t>Work Order — Statistics tab</t>
+          <t>Work Order — Remove an adjustment</t>
         </is>
       </c>
       <c r="E125" s="2" t="inlineStr">
         <is>
-          <t>Verify the Stats 'Fees &amp; Discounts' section is hidden when the work order has no fees/discounts</t>
+          <t>Verify removing a fee/discount uses Create and Edit, not a separate Delete permission</t>
         </is>
       </c>
       <c r="F125" s="2" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>High</t>
         </is>
       </c>
       <c r="G125" s="2" t="inlineStr">
@@ -6528,39 +6528,39 @@
       </c>
       <c r="I125" s="2" t="inlineStr">
         <is>
-          <t>no-adjustments WO -&gt; adjustments=[] + all-zero summary -&gt; section hidden | WORDING+VIU 2026-07-13: Section hidden with no adjustments; carry prior VIU.</t>
+          <t>removal governed by Create&amp;Edit (tech WITH lines-C&amp;E removed line-level 204; no Delete-perm dependency) | WORDING+VIU 2026-07-13: Remove uses Create &amp; Edit not a separate Delete permission; carry prior VIU. | SV-8456 (2026-07-21 staging LIVE VIU): F&amp;D moved to SETTINGS→SERVICE (below Canned Lines); template/WO/Part-sale/customer dialogs now show Taxable as a Yes/No DROPDOWN (was toggle); Auto-apply is a CHECKBOX with a 'When on…' caption; settings &amp; customer tables are plain-text/left-aligned (no badges); WO sidebar card retitled 'Work Order Fees &amp; Discounts' and renders ABOVE Financial Info; Part-sale card 'Parts Sale Fees &amp; Discounts' above Financial Info. Permission gate pivoted Settings→Finance → Settings→Service (verified live: Service-user sees+manages F&amp;D &amp; convenience toggle; Finance-only user has no F&amp;D nav item and /administration/adjustment-templates bounces to /workorders). Frontend-only; functionality + calc INTACT. | RE-VIU 2026-07-22 LIVE (Batch 4, SV-8456 re-verify): access-check quick-login {admin} HTTP 200. Re-confirmed on current staging build — 8 UI corrections intact (Taxable Yes/No dropdown; Auto-apply checkbox+caption; modal field order Type/CalcType&gt;Name&gt;Amount&gt;Taxable+jur.note&gt;Auto-apply&gt;Description; Settings table plain-text left-aligned no badges; F&amp;D nav under SERVICE below Canned Lines; WO &amp; Part-Sale cards above Financial Info [Batch 2/3]; Customer 'Fees &amp; Discounts' tab mirrors Settings styling minus convenience toggle) AND Settings-&gt;Service permission pivot CONFIRMED live per role (seeded ServiceRole vs FinanceRole, assigned to Tech, Tech restored to Technician 50bf6a0d + verified, both ZZAUTOTEST roles deleted 204): Service-user sees+manages F&amp;D nav + convenience toggle, direct /administration/adjustment-templates loads; Finance-only user has NO F&amp;D nav, FINANCE=Payment Methods only, direct route bounces to /workorders. viu_status VIU-Verified re-confirmed. Ev build/fees-discounts/viu-sv8456-2026-07-22/ (01-settings-landing, 02-new-dialog, 03-customer-fd-tab, SVC-*, FIN-*).</t>
         </is>
       </c>
     </row>
     <row r="126">
       <c r="A126" s="2" t="inlineStr">
         <is>
-          <t>FD-TMPL-001</t>
+          <t>FD-REMOVE-003</t>
         </is>
       </c>
       <c r="B126" s="2" t="inlineStr">
         <is>
-          <t>C28502</t>
+          <t>C28481</t>
         </is>
       </c>
       <c r="C126" s="6" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/28502</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/28481</t>
         </is>
       </c>
       <c r="D126" s="2" t="inlineStr">
         <is>
-          <t>Template admin — location</t>
+          <t>Work Order — Remove an adjustment</t>
         </is>
       </c>
       <c r="E126" s="2" t="inlineStr">
         <is>
-          <t>Verify the fee/discount template library is at Administration → Service → Fees &amp; Discounts (below Canned Lines)</t>
+          <t>Verify removing a line-level fee/discount from its inline ⋮ menu</t>
         </is>
       </c>
       <c r="F126" s="2" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="G126" s="2" t="inlineStr">
@@ -6575,34 +6575,34 @@
       </c>
       <c r="I126" s="2" t="inlineStr">
         <is>
-          <t>admin library lives under Administration -&gt; FINANCE (route /administration/adjustment-templates), not Service-below-Canned-Lines; page re-loaded today (case-update per S13-R8 target) | WORDING+VIU 2026-07-13: CORRECTED location: templates live under Administration → FINANCE → 'Fees &amp; Discounts' (below 'Payment Methods'), NOT 'Service, below Canned Lines' (Canned Lines is under SERVICE). Confirmed live (shot tmpl-02-create-dialog). | SV-8456 (2026-07-21 staging LIVE VIU): F&amp;D moved to SETTINGS→SERVICE (below Canned Lines); template/WO/Part-sale/customer dialogs now show Taxable as a Yes/No DROPDOWN (was toggle); Auto-apply is a CHECKBOX with a 'When on…' caption; settings &amp; customer tables are plain-text/left-aligned (no badges); WO sidebar card retitled 'Work Order Fees &amp; Discounts' and renders ABOVE Financial Info; Part-sale card 'Parts Sale Fees &amp; Discounts' above Financial Info. Permission gate pivoted Settings→Finance → Settings→Service (verified live: Service-user sees+manages F&amp;D &amp; convenience toggle; Finance-only user has no F&amp;D nav item and /administration/adjustment-templates bounces to /workorders). Frontend-only; functionality + calc INTACT. | RE-VIU 2026-07-22 LIVE (Batch 4, SV-8456 re-verify): access-check quick-login {admin} HTTP 200. Re-confirmed on current staging build — 8 UI corrections intact (Taxable Yes/No dropdown; Auto-apply checkbox+caption; modal field order Type/CalcType&gt;Name&gt;Amount&gt;Taxable+jur.note&gt;Auto-apply&gt;Description; Settings table plain-text left-aligned no badges; F&amp;D nav under SERVICE below Canned Lines; WO &amp; Part-Sale cards above Financial Info [Batch 2/3]; Customer 'Fees &amp; Discounts' tab mirrors Settings styling minus convenience toggle) AND Settings-&gt;Service permission pivot CONFIRMED live per role (seeded ServiceRole vs FinanceRole, assigned to Tech, Tech restored to Technician 50bf6a0d + verified, both ZZAUTOTEST roles deleted 204): Service-user sees+manages F&amp;D nav + convenience toggle, direct /administration/adjustment-templates loads; Finance-only user has NO F&amp;D nav, FINANCE=Payment Methods only, direct route bounces to /workorders. viu_status VIU-Verified re-confirmed. Ev build/fees-discounts/viu-sv8456-2026-07-22/ (01-settings-landing, 02-new-dialog, 03-customer-fd-tab, SVC-*, FIN-*).</t>
+          <t>line-level remove 204 and gone from the line | WORDING+VIU 2026-07-13: Inline menu option is 'Remove' (was 'Delete'); confirm dialog 'Remove Fee / Discount' confirmed live.</t>
         </is>
       </c>
     </row>
     <row r="127">
       <c r="A127" s="2" t="inlineStr">
         <is>
-          <t>FD-TMPL-002</t>
+          <t>FD-STACK-001</t>
         </is>
       </c>
       <c r="B127" s="2" t="inlineStr">
         <is>
-          <t>C28503</t>
+          <t>C28482</t>
         </is>
       </c>
       <c r="C127" s="6" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/28503</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/28482</t>
         </is>
       </c>
       <c r="D127" s="2" t="inlineStr">
         <is>
-          <t>Template admin — list</t>
+          <t>Work Order — Multiple adjustments (stacking / netting)</t>
         </is>
       </c>
       <c r="E127" s="2" t="inlineStr">
         <is>
-          <t>Verify the template list columns and the edit/delete actions</t>
+          <t>Verify multiple fees/discounts on one part each work out on the part's own total (they do not compound)</t>
         </is>
       </c>
       <c r="F127" s="2" t="inlineStr">
@@ -6622,34 +6622,34 @@
       </c>
       <c r="I127" s="2" t="inlineStr">
         <is>
-          <t>list + delete action per batch-1; page renders today; columns not re-verified individually | WORDING+VIU 2026-07-13: List columns confirmed live (shot tmpl-02). | SV-8456 (2026-07-21 staging LIVE VIU): F&amp;D moved to SETTINGS→SERVICE (below Canned Lines); template/WO/Part-sale/customer dialogs now show Taxable as a Yes/No DROPDOWN (was toggle); Auto-apply is a CHECKBOX with a 'When on…' caption; settings &amp; customer tables are plain-text/left-aligned (no badges); WO sidebar card retitled 'Work Order Fees &amp; Discounts' and renders ABOVE Financial Info; Part-sale card 'Parts Sale Fees &amp; Discounts' above Financial Info. Permission gate pivoted Settings→Finance → Settings→Service (verified live: Service-user sees+manages F&amp;D &amp; convenience toggle; Finance-only user has no F&amp;D nav item and /administration/adjustment-templates bounces to /workorders). Frontend-only; functionality + calc INTACT. | RE-VIU 2026-07-22 LIVE (Batch 4, SV-8456 re-verify): access-check quick-login {admin} HTTP 200. Re-confirmed on current staging build — 8 UI corrections intact (Taxable Yes/No dropdown; Auto-apply checkbox+caption; modal field order Type/CalcType&gt;Name&gt;Amount&gt;Taxable+jur.note&gt;Auto-apply&gt;Description; Settings table plain-text left-aligned no badges; F&amp;D nav under SERVICE below Canned Lines; WO &amp; Part-Sale cards above Financial Info [Batch 2/3]; Customer 'Fees &amp; Discounts' tab mirrors Settings styling minus convenience toggle) AND Settings-&gt;Service permission pivot CONFIRMED live per role (seeded ServiceRole vs FinanceRole, assigned to Tech, Tech restored to Technician 50bf6a0d + verified, both ZZAUTOTEST roles deleted 204): Service-user sees+manages F&amp;D nav + convenience toggle, direct /administration/adjustment-templates loads; Finance-only user has NO F&amp;D nav, FINANCE=Payment Methods only, direct route bounces to /workorders. viu_status VIU-Verified re-confirmed. Ev build/fees-discounts/viu-sv8456-2026-07-22/ (01-settings-landing, 02-new-dialog, 03-customer-fd-tab, SVC-*, FIN-*).</t>
+          <t>part flat + part pct resolved independently on the part's own gross (fresh: $8.00 and $17.08 coexist, no compounding) | WORDING+VIU 2026-07-13: Netting carried; build labels. Display half (only first shows + 'Show N more') is the FD-INLINE-003 deviation (no Show-N-more in this build).</t>
         </is>
       </c>
     </row>
     <row r="128">
       <c r="A128" s="2" t="inlineStr">
         <is>
-          <t>FD-TMPL-003</t>
+          <t>FD-STACK-002</t>
         </is>
       </c>
       <c r="B128" s="2" t="inlineStr">
         <is>
-          <t>C28504</t>
+          <t>C28483</t>
         </is>
       </c>
       <c r="C128" s="6" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/28504</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/28483</t>
         </is>
       </c>
       <c r="D128" s="2" t="inlineStr">
         <is>
-          <t>Template admin — create</t>
+          <t>Work Order — Multiple adjustments (stacking / netting)</t>
         </is>
       </c>
       <c r="E128" s="2" t="inlineStr">
         <is>
-          <t>Verify creating a Fee template (dialog fields and the Create button)</t>
+          <t>Verify two whole-work-order percentage fees/discounts use the same totals and do not change each other's base</t>
         </is>
       </c>
       <c r="F128" s="2" t="inlineStr">
@@ -6669,34 +6669,34 @@
       </c>
       <c r="I128" s="2" t="inlineStr">
         <is>
-          <t>PARTIAL IMPROVEMENT: create-dialog title NOW 'New Fee / Discount' (matches spec; was 'Add new fee/discount'); confirm button still 'Create' (spec 'Add Fee / Discount') and toast 'Template created' per batch-1 — drift remains | WORDING+VIU 2026-07-13: Create dialog confirmed live: title 'New Fee / Discount', fields Name/Type/Calculation Type/'$ Default Amount'/Taxable toggle/'Auto-apply to new work orders' toggle/'Description (Optional)', 'Create' button. Type offers only Fee/Discount (Processing Fee is NOT in the builder — Story 8 not built). Create API 201 live. Toast text carried from prior VIU. | SV-8456 (2026-07-21 staging LIVE VIU): F&amp;D moved to SETTINGS→SERVICE (below Canned Lines); template/WO/Part-sale/customer dialogs now show Taxable as a Yes/No DROPDOWN (was toggle); Auto-apply is a CHECKBOX with a 'When on…' caption; settings &amp; customer tables are plain-text/left-aligned (no badges); WO sidebar card retitled 'Work Order Fees &amp; Discounts' and renders ABOVE Financial Info; Part-sale card 'Parts Sale Fees &amp; Discounts' above Financial Info. Permission gate pivoted Settings→Finance → Settings→Service (verified live: Service-user sees+manages F&amp;D &amp; convenience toggle; Finance-only user has no F&amp;D nav item and /administration/adjustment-templates bounces to /workorders). Frontend-only; functionality + calc INTACT. | RE-VIU 2026-07-22 LIVE (Batch 4, SV-8456 re-verify): access-check quick-login {admin} HTTP 200. Re-confirmed on current staging build — 8 UI corrections intact (Taxable Yes/No dropdown; Auto-apply checkbox+caption; modal field order Type/CalcType&gt;Name&gt;Amount&gt;Taxable+jur.note&gt;Auto-apply&gt;Description; Settings table plain-text left-aligned no badges; F&amp;D nav under SERVICE below Canned Lines; WO &amp; Part-Sale cards above Financial Info [Batch 2/3]; Customer 'Fees &amp; Discounts' tab mirrors Settings styling minus convenience toggle) AND Settings-&gt;Service permission pivot CONFIRMED live per role (seeded ServiceRole vs FinanceRole, assigned to Tech, Tech restored to Technician 50bf6a0d + verified, both ZZAUTOTEST roles deleted 204): Service-user sees+manages F&amp;D nav + convenience toggle, direct /administration/adjustment-templates loads; Finance-only user has NO F&amp;D nav, FINANCE=Payment Methods only, direct route bounces to /workorders. viu_status VIU-Verified re-confirmed. Ev build/fees-discounts/viu-sv8456-2026-07-22/ (01-settings-landing, 02-new-dialog, 03-customer-fd-tab, SVC-*, FIN-*).</t>
+          <t>two 10% whole-WO fees resolve 17.08 each (same base, no compounding) | WORDING+VIU 2026-07-13: Same-base netting carried; build labels.</t>
         </is>
       </c>
     </row>
     <row r="129">
       <c r="A129" s="2" t="inlineStr">
         <is>
-          <t>FD-TMPL-004</t>
+          <t>FD-STACK-003</t>
         </is>
       </c>
       <c r="B129" s="2" t="inlineStr">
         <is>
-          <t>C28505</t>
+          <t>C28484</t>
         </is>
       </c>
       <c r="C129" s="6" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/28505</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/28484</t>
         </is>
       </c>
       <c r="D129" s="2" t="inlineStr">
         <is>
-          <t>Template admin — create</t>
+          <t>Work Order — Multiple adjustments (stacking / netting)</t>
         </is>
       </c>
       <c r="E129" s="2" t="inlineStr">
         <is>
-          <t>Verify creating a Discount template</t>
+          <t>Verify the same template can be applied to one work order more than once by hand</t>
         </is>
       </c>
       <c r="F129" s="2" t="inlineStr">
@@ -6716,34 +6716,34 @@
       </c>
       <c r="I129" s="2" t="inlineStr">
         <is>
-          <t>generic 'Template created' toast vs spec 'Discount added' per batch-1; not re-driven | WORDING+VIU 2026-07-13: CORRECTED title: the toast is generic (not a per-type 'Discount added'). Create dialog + list confirmed live. | SV-8456 (2026-07-21 staging LIVE VIU): F&amp;D moved to SETTINGS→SERVICE (below Canned Lines); template/WO/Part-sale/customer dialogs now show Taxable as a Yes/No DROPDOWN (was toggle); Auto-apply is a CHECKBOX with a 'When on…' caption; settings &amp; customer tables are plain-text/left-aligned (no badges); WO sidebar card retitled 'Work Order Fees &amp; Discounts' and renders ABOVE Financial Info; Part-sale card 'Parts Sale Fees &amp; Discounts' above Financial Info. Permission gate pivoted Settings→Finance → Settings→Service (verified live: Service-user sees+manages F&amp;D &amp; convenience toggle; Finance-only user has no F&amp;D nav item and /administration/adjustment-templates bounces to /workorders). Frontend-only; functionality + calc INTACT. | RE-VIU 2026-07-22 LIVE (Batch 4, SV-8456 re-verify): access-check quick-login {admin} HTTP 200. Re-confirmed on current staging build — 8 UI corrections intact (Taxable Yes/No dropdown; Auto-apply checkbox+caption; modal field order Type/CalcType&gt;Name&gt;Amount&gt;Taxable+jur.note&gt;Auto-apply&gt;Description; Settings table plain-text left-aligned no badges; F&amp;D nav under SERVICE below Canned Lines; WO &amp; Part-Sale cards above Financial Info [Batch 2/3]; Customer 'Fees &amp; Discounts' tab mirrors Settings styling minus convenience toggle) AND Settings-&gt;Service permission pivot CONFIRMED live per role (seeded ServiceRole vs FinanceRole, assigned to Tech, Tech restored to Technician 50bf6a0d + verified, both ZZAUTOTEST roles deleted 204): Service-user sees+manages F&amp;D nav + convenience toggle, direct /administration/adjustment-templates loads; Finance-only user has NO F&amp;D nav, FINANCE=Payment Methods only, direct route bounces to /workorders. viu_status VIU-Verified re-confirmed. Ev build/fees-discounts/viu-sv8456-2026-07-22/ (01-settings-landing, 02-new-dialog, 03-customer-fd-tab, SVC-*, FIN-*).</t>
+          <t>'Flat fee' template applied twice by hand -&gt; 201/201, two distinct adjustments | WORDING+VIU 2026-07-13: Same-template-twice carried; build labels ('Add Fee/Discount', 'Apply From Template', 'WO Fees &amp; Discounts'). | SV-8456 (2026-07-21 staging LIVE VIU): F&amp;D moved to SETTINGS→SERVICE (below Canned Lines); template/WO/Part-sale/customer dialogs now show Taxable as a Yes/No DROPDOWN (was toggle); Auto-apply is a CHECKBOX with a 'When on…' caption; settings &amp; customer tables are plain-text/left-aligned (no badges); WO sidebar card retitled 'Work Order Fees &amp; Discounts' and renders ABOVE Financial Info; Part-sale card 'Parts Sale Fees &amp; Discounts' above Financial Info. Permission gate pivoted Settings→Finance → Settings→Service (verified live: Service-user sees+manages F&amp;D &amp; convenience toggle; Finance-only user has no F&amp;D nav item and /administration/adjustment-templates bounces to /workorders). Frontend-only; functionality + calc INTACT. | SV-8479/8480 deconfliction 2026-07-22: label sweep: navigation labels -&gt; 'Add Work Order Fee / Discount' / 'New Work Order Fee / Discount' (behavior/expected unchanged). | VIU 2026-07-22 LIVE: SV-8479 nav label 'Add Work Order Fee / Discount' confirmed present in the WO toolbar ⋯ menu; case behavior unchanged. Ev: wo/FD-WO-025-toolbar-menu.png. | RE-VIU 2026-07-22 LIVE (Batch 4, SV-8456 re-verify): access-check quick-login {admin} HTTP 200. Re-confirmed on current staging build — 8 UI corrections intact (Taxable Yes/No dropdown; Auto-apply checkbox+caption; modal field order Type/CalcType&gt;Name&gt;Amount&gt;Taxable+jur.note&gt;Auto-apply&gt;Description; Settings table plain-text left-aligned no badges; F&amp;D nav under SERVICE below Canned Lines; WO &amp; Part-Sale cards above Financial Info [Batch 2/3]; Customer 'Fees &amp; Discounts' tab mirrors Settings styling minus convenience toggle) AND Settings-&gt;Service permission pivot CONFIRMED live per role (seeded ServiceRole vs FinanceRole, assigned to Tech, Tech restored to Technician 50bf6a0d + verified, both ZZAUTOTEST roles deleted 204): Service-user sees+manages F&amp;D nav + convenience toggle, direct /administration/adjustment-templates loads; Finance-only user has NO F&amp;D nav, FINANCE=Payment Methods only, direct route bounces to /workorders. viu_status VIU-Verified re-confirmed. Ev build/fees-discounts/viu-sv8456-2026-07-22/ (01-settings-landing, 02-new-dialog, 03-customer-fd-tab, SVC-*, FIN-*).</t>
         </is>
       </c>
     </row>
     <row r="130">
       <c r="A130" s="2" t="inlineStr">
         <is>
-          <t>FD-TMPL-005</t>
+          <t>FD-STATS-001</t>
         </is>
       </c>
       <c r="B130" s="2" t="inlineStr">
         <is>
-          <t>C28506</t>
+          <t>C28459</t>
         </is>
       </c>
       <c r="C130" s="6" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/28506</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/28459</t>
         </is>
       </c>
       <c r="D130" s="2" t="inlineStr">
         <is>
-          <t>Template admin — auto-apply</t>
+          <t>Work Order — Statistics tab</t>
         </is>
       </c>
       <c r="E130" s="2" t="inlineStr">
         <is>
-          <t>Verify the 'Auto-apply to all new work orders at this location' checkbox adds the template to every new work order at that location</t>
+          <t>Verify the Stats tab Fees &amp; Discounts section shows the '%' and 'Amount' column headings with each row's value and amount</t>
         </is>
       </c>
       <c r="F130" s="2" t="inlineStr">
@@ -6763,34 +6763,34 @@
       </c>
       <c r="I130" s="2" t="inlineStr">
         <is>
-          <t>auto-apply template ('Capped discount' + test pfees) landed on every fresh WO as appliedBy=auto | WORDING+VIU 2026-07-13: CORRECTED auto-apply label: dialog toggle is 'Auto-apply to new work orders'; list column 'Auto-Apply To Work Orders'. Confirmed live (shot tmpl-02). | SV-8456 (2026-07-21 staging LIVE VIU): F&amp;D moved to SETTINGS→SERVICE (below Canned Lines); template/WO/Part-sale/customer dialogs now show Taxable as a Yes/No DROPDOWN (was toggle); Auto-apply is a CHECKBOX with a 'When on…' caption; settings &amp; customer tables are plain-text/left-aligned (no badges); WO sidebar card retitled 'Work Order Fees &amp; Discounts' and renders ABOVE Financial Info; Part-sale card 'Parts Sale Fees &amp; Discounts' above Financial Info. Permission gate pivoted Settings→Finance → Settings→Service (verified live: Service-user sees+manages F&amp;D &amp; convenience toggle; Finance-only user has no F&amp;D nav item and /administration/adjustment-templates bounces to /workorders). Frontend-only; functionality + calc INTACT. | RE-VIU 2026-07-22 LIVE (Batch 4, SV-8456 re-verify): access-check quick-login {admin} HTTP 200. Re-confirmed on current staging build — 8 UI corrections intact (Taxable Yes/No dropdown; Auto-apply checkbox+caption; modal field order Type/CalcType&gt;Name&gt;Amount&gt;Taxable+jur.note&gt;Auto-apply&gt;Description; Settings table plain-text left-aligned no badges; F&amp;D nav under SERVICE below Canned Lines; WO &amp; Part-Sale cards above Financial Info [Batch 2/3]; Customer 'Fees &amp; Discounts' tab mirrors Settings styling minus convenience toggle) AND Settings-&gt;Service permission pivot CONFIRMED live per role (seeded ServiceRole vs FinanceRole, assigned to Tech, Tech restored to Technician 50bf6a0d + verified, both ZZAUTOTEST roles deleted 204): Service-user sees+manages F&amp;D nav + convenience toggle, direct /administration/adjustment-templates loads; Finance-only user has NO F&amp;D nav, FINANCE=Payment Methods only, direct route bounces to /workorders. viu_status VIU-Verified re-confirmed. Ev build/fees-discounts/viu-sv8456-2026-07-22/ (01-settings-landing, 02-new-dialog, 03-customer-fd-tab, SVC-*, FIN-*).</t>
+          <t>CONFIRMED AGAIN: Stats shows aggregate 'Fees &amp; Discounts (5) $25.00' style block, NOT the per-row Value/%+Amount table — PO Q1=B design regression persists (shot 07-stats) | WORDING+VIU 2026-07-13: DEVIATION (BUG-FD-2): the Stats 'Fees &amp; Discounts (N)' section lists rows (name, a value/% for percentages, and an amount) but has NO 'Value'/'Amount' column headers like the other Stats sections. Confirmed live (shot fin-01). | SV-8479/8480 deconfliction 2026-07-22: added the right-side '%' and 'Amount' column headings + blank-% for flat fees (item 12). Absorbs dropped new case FD-WO-027. viu_status unchanged (VIU-Deviation) — re-observe at VIU. | VIU 2026-07-22 LIVE: prior 'no headers' deviation RESOLVED — Stats tab 'Fees &amp; Discounts (10)' section now shows the '% Amount' column headings. Rows show percent under % (blank for flat: 'Flat Fee 2 +$32.00', 'Flat Fee +$11.00') and signed amount under Amount ('Labor Fee +20% +$101.98', 'Labor Disc −10% −$50.99', 'Customer Fee +10% +$65.88', 'WO Disc −5% −$32.94'), with 'Total +$273.31'. Ev: wo/FD-STATS-001-stats-tab.png, wo/stats-bodytext.txt.</t>
         </is>
       </c>
     </row>
     <row r="131">
       <c r="A131" s="2" t="inlineStr">
         <is>
-          <t>FD-TMPL-006</t>
+          <t>FD-STATS-002</t>
         </is>
       </c>
       <c r="B131" s="2" t="inlineStr">
         <is>
-          <t>C28507</t>
+          <t>C28460</t>
         </is>
       </c>
       <c r="C131" s="6" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/28507</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/28460</t>
         </is>
       </c>
       <c r="D131" s="2" t="inlineStr">
         <is>
-          <t>Template admin — edit</t>
+          <t>Work Order — Statistics tab</t>
         </is>
       </c>
       <c r="E131" s="2" t="inlineStr">
         <is>
-          <t>Verify editing a template (Edit Fee / Discount dialog, 'Save' button)</t>
+          <t>Verify the Statistics tab lists each fee/discount as its own row with name, percent and amount</t>
         </is>
       </c>
       <c r="F131" s="2" t="inlineStr">
@@ -6810,34 +6810,34 @@
       </c>
       <c r="I131" s="2" t="inlineStr">
         <is>
-          <t>edit locks Type+Calc on template edit (spec locks only in WO dialog) per batch-1; not re-driven | WORDING+VIU 2026-07-13: Edit dialog title 'Edit Fee / Discount' + 'Save' button confirmed on the fee/discount Edit dialog (shot edit-01). Edit opens from the row's pencil button. Toast text carried.</t>
+          <t>per-row scope hyperlink impossible while the layout is aggregate (dep. FD-STATS-001) | WORDING+VIU 2026-07-13: DEVIATION carried: Stats F&amp;D rows show the name only — no scope hyperlink to the target. Confirmed live (rows read plain names, shot fin-01). | CLOSE-OUT 2026-07-24: matched-to-build per Ahtasham QA review 2026-07-24; synced from his TestRail edit (C28460). VIU-Deviation -&gt; VIU-Verified. HONESTY (Rule 12/22): accepted on Ahtasham's live QA review — NOT re-observed by us this pass.</t>
         </is>
       </c>
     </row>
     <row r="132">
       <c r="A132" s="2" t="inlineStr">
         <is>
-          <t>FD-TMPL-007</t>
+          <t>FD-STATS-003</t>
         </is>
       </c>
       <c r="B132" s="2" t="inlineStr">
         <is>
-          <t>C28508</t>
+          <t>C28461</t>
         </is>
       </c>
       <c r="C132" s="6" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/28508</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/28461</t>
         </is>
       </c>
       <c r="D132" s="2" t="inlineStr">
         <is>
-          <t>Template admin — delete</t>
+          <t>Work Order — Statistics tab</t>
         </is>
       </c>
       <c r="E132" s="2" t="inlineStr">
         <is>
-          <t>Verify the template delete confirm dialog and buttons</t>
+          <t>Verify the Stats 'Fees &amp; Discounts' total equals the signed sum of all the amounts</t>
         </is>
       </c>
       <c r="F132" s="2" t="inlineStr">
@@ -6857,34 +6857,34 @@
       </c>
       <c r="I132" s="2" t="inlineStr">
         <is>
-          <t>delete-confirm dialog + affectedCustomerCount warning per batch-1; delete-precondition endpoint intact | WORDING+VIU 2026-07-13: Delete confirm confirmed live: standardized 'Delete Template' dialog with 'Cancel' + red 'Delete' (shot tmpl-03). The plain (no-customer) body wording was not captured this run — the sample template had a customer default (see FD-TMPL-008).</t>
+          <t>net = signed sum re-consistent (adjustmentsSummary netAmount matches card); full UI table from batch-2 | WORDING+VIU 2026-07-13: Total = signed sum; carry prior VIU. Minus-sign jargon removed.</t>
         </is>
       </c>
     </row>
     <row r="133">
       <c r="A133" s="2" t="inlineStr">
         <is>
-          <t>FD-TMPL-008</t>
+          <t>FD-STATS-004</t>
         </is>
       </c>
       <c r="B133" s="2" t="inlineStr">
         <is>
-          <t>C28509</t>
+          <t>C28462</t>
         </is>
       </c>
       <c r="C133" s="6" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/28509</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/28462</t>
         </is>
       </c>
       <c r="D133" s="2" t="inlineStr">
         <is>
-          <t>Template admin — delete</t>
+          <t>Work Order — Statistics tab</t>
         </is>
       </c>
       <c r="E133" s="2" t="inlineStr">
         <is>
-          <t>Verify the delete confirm adds a warning when the template is a customer default</t>
+          <t>Verify the Stats fees/discounts are listed in the order they were created (oldest first)</t>
         </is>
       </c>
       <c r="F133" s="2" t="inlineStr">
@@ -6904,39 +6904,39 @@
       </c>
       <c r="I133" s="2" t="inlineStr">
         <is>
-          <t>standardized 'Delete Template' dialog wording = intended per epic; case-update to adopt live wording still pending | WORDING+VIU 2026-07-13: Customer-default warning confirmed live EXACTLY: 'This template is set as a default for N customer(s). Deleting it will remove it from them.' (saw '1 customer', shot tmpl-03).</t>
+          <t>creation-order rows blocked by aggregate layout (dep. FD-STATS-001) | WORDING+VIU 2026-07-13: DEVIATION carried: creation-order ruling pending (BUG-FD-2 group). Labels cleaned. | CLOSE-OUT 2026-07-24: accepted per Ahtasham QA live review 2026-07-24 (no bug). Status -&gt; VIU-Verified, wording unchanged. HONESTY (Rule 12/22): accepted on Ahtasham's live QA review — NOT re-observed by us this pass.</t>
         </is>
       </c>
     </row>
     <row r="134">
       <c r="A134" s="2" t="inlineStr">
         <is>
-          <t>FD-TMPL-009</t>
+          <t>FD-STATS-005</t>
         </is>
       </c>
       <c r="B134" s="2" t="inlineStr">
         <is>
-          <t>C28510</t>
+          <t>C28463</t>
         </is>
       </c>
       <c r="C134" s="6" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/28510</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/28463</t>
         </is>
       </c>
       <c r="D134" s="2" t="inlineStr">
         <is>
-          <t>Template admin — delete</t>
+          <t>Work Order — Statistics tab</t>
         </is>
       </c>
       <c r="E134" s="2" t="inlineStr">
         <is>
-          <t>Verify deleting a template leaves work-order fees/discounts made from it unchanged</t>
+          <t>Verify the Stats 'Fees &amp; Discounts' section is hidden when the work order has no fees/discounts</t>
         </is>
       </c>
       <c r="F134" s="2" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="G134" s="2" t="inlineStr">
@@ -6951,39 +6951,39 @@
       </c>
       <c r="I134" s="2" t="inlineStr">
         <is>
-          <t>template deleted (204) -&gt; WO adjustment made from it survives unchanged (resolved 6 intact) | WORDING+VIU 2026-07-13: Delete leaves WO adjustments unchanged; carried. Nav corrected to Finance. | SV-8456 (2026-07-21 staging LIVE VIU): F&amp;D moved to SETTINGS→SERVICE (below Canned Lines); template/WO/Part-sale/customer dialogs now show Taxable as a Yes/No DROPDOWN (was toggle); Auto-apply is a CHECKBOX with a 'When on…' caption; settings &amp; customer tables are plain-text/left-aligned (no badges); WO sidebar card retitled 'Work Order Fees &amp; Discounts' and renders ABOVE Financial Info; Part-sale card 'Parts Sale Fees &amp; Discounts' above Financial Info. Permission gate pivoted Settings→Finance → Settings→Service (verified live: Service-user sees+manages F&amp;D &amp; convenience toggle; Finance-only user has no F&amp;D nav item and /administration/adjustment-templates bounces to /workorders). Frontend-only; functionality + calc INTACT. | RE-VIU 2026-07-22 LIVE (Batch 4, SV-8456 re-verify): access-check quick-login {admin} HTTP 200. Re-confirmed on current staging build — 8 UI corrections intact (Taxable Yes/No dropdown; Auto-apply checkbox+caption; modal field order Type/CalcType&gt;Name&gt;Amount&gt;Taxable+jur.note&gt;Auto-apply&gt;Description; Settings table plain-text left-aligned no badges; F&amp;D nav under SERVICE below Canned Lines; WO &amp; Part-Sale cards above Financial Info [Batch 2/3]; Customer 'Fees &amp; Discounts' tab mirrors Settings styling minus convenience toggle) AND Settings-&gt;Service permission pivot CONFIRMED live per role (seeded ServiceRole vs FinanceRole, assigned to Tech, Tech restored to Technician 50bf6a0d + verified, both ZZAUTOTEST roles deleted 204): Service-user sees+manages F&amp;D nav + convenience toggle, direct /administration/adjustment-templates loads; Finance-only user has NO F&amp;D nav, FINANCE=Payment Methods only, direct route bounces to /workorders. viu_status VIU-Verified re-confirmed. Ev build/fees-discounts/viu-sv8456-2026-07-22/ (01-settings-landing, 02-new-dialog, 03-customer-fd-tab, SVC-*, FIN-*).</t>
+          <t>no-adjustments WO -&gt; adjustments=[] + all-zero summary -&gt; section hidden | WORDING+VIU 2026-07-13: Section hidden with no adjustments; carry prior VIU.</t>
         </is>
       </c>
     </row>
     <row r="135">
       <c r="A135" s="2" t="inlineStr">
         <is>
-          <t>FD-TMPL-011</t>
+          <t>FD-TMPL-001</t>
         </is>
       </c>
       <c r="B135" s="2" t="inlineStr">
         <is>
-          <t>C28512</t>
+          <t>C28502</t>
         </is>
       </c>
       <c r="C135" s="6" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/28512</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/28502</t>
         </is>
       </c>
       <c r="D135" s="2" t="inlineStr">
         <is>
-          <t>Template admin — dialog fields</t>
+          <t>Template admin — location</t>
         </is>
       </c>
       <c r="E135" s="2" t="inlineStr">
         <is>
-          <t>Verify Max Amount shows only for percentage methods and how 0 behaves</t>
+          <t>Verify the fee/discount template library is at Administration → Service → Fees &amp; Discounts (below Canned Lines)</t>
         </is>
       </c>
       <c r="F135" s="2" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>High</t>
         </is>
       </c>
       <c r="G135" s="2" t="inlineStr">
@@ -6998,39 +6998,39 @@
       </c>
       <c r="I135" s="2" t="inlineStr">
         <is>
-          <t>maxCap 0 accepted and STORED as 0 on the template (201) and WO resolve treats 0 as NO cap (34.15) — FDBUG-9 persists | WORDING+VIU 2026-07-13: Max Amount only for % confirmed (WO+template dialogs). DEVIATION (PO Q2): a Max Amount of 0 is treated as 'no cap'. Labels cleaned. | CHRIS WARD ROUND-2 ANSWER APPLIED 2026-07-14(Q2=A): PO ruled a typed 0 in Max Amount = 'no limit' (WAD, S2-R25). 0-handling no longer a deviation; FDBUG-9 closed as accepted; jira draft TICKET 4 DROPPED. Expected reworded to affirm 0=no-cap. PUSHED TO TESTRAIL 2026-07-14 via update_case (QA-lead one-day authorization; update 200 / re-verify 200 MATCH; audit: testrail-round2-push-log.md).</t>
+          <t>admin library lives under Administration -&gt; FINANCE (route /administration/adjustment-templates), not Service-below-Canned-Lines; page re-loaded today (case-update per S13-R8 target) | WORDING+VIU 2026-07-13: CORRECTED location: templates live under Administration → FINANCE → 'Fees &amp; Discounts' (below 'Payment Methods'), NOT 'Service, below Canned Lines' (Canned Lines is under SERVICE). Confirmed live (shot tmpl-02-create-dialog). | SV-8456 (2026-07-21 staging LIVE VIU): F&amp;D moved to SETTINGS→SERVICE (below Canned Lines); template/WO/Part-sale/customer dialogs now show Taxable as a Yes/No DROPDOWN (was toggle); Auto-apply is a CHECKBOX with a 'When on…' caption; settings &amp; customer tables are plain-text/left-aligned (no badges); WO sidebar card retitled 'Work Order Fees &amp; Discounts' and renders ABOVE Financial Info; Part-sale card 'Parts Sale Fees &amp; Discounts' above Financial Info. Permission gate pivoted Settings→Finance → Settings→Service (verified live: Service-user sees+manages F&amp;D &amp; convenience toggle; Finance-only user has no F&amp;D nav item and /administration/adjustment-templates bounces to /workorders). Frontend-only; functionality + calc INTACT. | RE-VIU 2026-07-22 LIVE (Batch 4, SV-8456 re-verify): access-check quick-login {admin} HTTP 200. Re-confirmed on current staging build — 8 UI corrections intact (Taxable Yes/No dropdown; Auto-apply checkbox+caption; modal field order Type/CalcType&gt;Name&gt;Amount&gt;Taxable+jur.note&gt;Auto-apply&gt;Description; Settings table plain-text left-aligned no badges; F&amp;D nav under SERVICE below Canned Lines; WO &amp; Part-Sale cards above Financial Info [Batch 2/3]; Customer 'Fees &amp; Discounts' tab mirrors Settings styling minus convenience toggle) AND Settings-&gt;Service permission pivot CONFIRMED live per role (seeded ServiceRole vs FinanceRole, assigned to Tech, Tech restored to Technician 50bf6a0d + verified, both ZZAUTOTEST roles deleted 204): Service-user sees+manages F&amp;D nav + convenience toggle, direct /administration/adjustment-templates loads; Finance-only user has NO F&amp;D nav, FINANCE=Payment Methods only, direct route bounces to /workorders. viu_status VIU-Verified re-confirmed. Ev build/fees-discounts/viu-sv8456-2026-07-22/ (01-settings-landing, 02-new-dialog, 03-customer-fd-tab, SVC-*, FIN-*).</t>
         </is>
       </c>
     </row>
     <row r="136">
       <c r="A136" s="2" t="inlineStr">
         <is>
-          <t>FD-TMPL-013</t>
+          <t>FD-TMPL-002</t>
         </is>
       </c>
       <c r="B136" s="2" t="inlineStr">
         <is>
-          <t>C28514</t>
+          <t>C28503</t>
         </is>
       </c>
       <c r="C136" s="6" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/28514</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/28503</t>
         </is>
       </c>
       <c r="D136" s="2" t="inlineStr">
         <is>
-          <t>Template admin — validation</t>
+          <t>Template admin — list</t>
         </is>
       </c>
       <c r="E136" s="2" t="inlineStr">
         <is>
-          <t>Verify a percentage-discount template cannot go over 100% while a percentage-fee template has no cap</t>
+          <t>Verify the template list columns and the edit/delete actions</t>
         </is>
       </c>
       <c r="F136" s="2" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>High</t>
         </is>
       </c>
       <c r="G136" s="2" t="inlineStr">
@@ -7045,39 +7045,39 @@
       </c>
       <c r="I136" s="2" t="inlineStr">
         <is>
-          <t>discount template 150% -&gt; 400; fee template 150% -&gt; 201 | WORDING+VIU 2026-07-13: %&gt;100 discount rejected (confirmed via API 2026-07-13: 'A percentage discount cannot exceed 100%').</t>
+          <t>list + delete action per batch-1; page renders today; columns not re-verified individually | WORDING+VIU 2026-07-13: List columns confirmed live (shot tmpl-02). | SV-8456 (2026-07-21 staging LIVE VIU): F&amp;D moved to SETTINGS→SERVICE (below Canned Lines); template/WO/Part-sale/customer dialogs now show Taxable as a Yes/No DROPDOWN (was toggle); Auto-apply is a CHECKBOX with a 'When on…' caption; settings &amp; customer tables are plain-text/left-aligned (no badges); WO sidebar card retitled 'Work Order Fees &amp; Discounts' and renders ABOVE Financial Info; Part-sale card 'Parts Sale Fees &amp; Discounts' above Financial Info. Permission gate pivoted Settings→Finance → Settings→Service (verified live: Service-user sees+manages F&amp;D &amp; convenience toggle; Finance-only user has no F&amp;D nav item and /administration/adjustment-templates bounces to /workorders). Frontend-only; functionality + calc INTACT. | RE-VIU 2026-07-22 LIVE (Batch 4, SV-8456 re-verify): access-check quick-login {admin} HTTP 200. Re-confirmed on current staging build — 8 UI corrections intact (Taxable Yes/No dropdown; Auto-apply checkbox+caption; modal field order Type/CalcType&gt;Name&gt;Amount&gt;Taxable+jur.note&gt;Auto-apply&gt;Description; Settings table plain-text left-aligned no badges; F&amp;D nav under SERVICE below Canned Lines; WO &amp; Part-Sale cards above Financial Info [Batch 2/3]; Customer 'Fees &amp; Discounts' tab mirrors Settings styling minus convenience toggle) AND Settings-&gt;Service permission pivot CONFIRMED live per role (seeded ServiceRole vs FinanceRole, assigned to Tech, Tech restored to Technician 50bf6a0d + verified, both ZZAUTOTEST roles deleted 204): Service-user sees+manages F&amp;D nav + convenience toggle, direct /administration/adjustment-templates loads; Finance-only user has NO F&amp;D nav, FINANCE=Payment Methods only, direct route bounces to /workorders. viu_status VIU-Verified re-confirmed. Ev build/fees-discounts/viu-sv8456-2026-07-22/ (01-settings-landing, 02-new-dialog, 03-customer-fd-tab, SVC-*, FIN-*).</t>
         </is>
       </c>
     </row>
     <row r="137">
       <c r="A137" s="2" t="inlineStr">
         <is>
-          <t>FD-TMPL-014</t>
+          <t>FD-TMPL-003</t>
         </is>
       </c>
       <c r="B137" s="2" t="inlineStr">
         <is>
-          <t>C28515</t>
+          <t>C28504</t>
         </is>
       </c>
       <c r="C137" s="6" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/28515</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/28504</t>
         </is>
       </c>
       <c r="D137" s="2" t="inlineStr">
         <is>
-          <t>Template admin — dialog fields</t>
+          <t>Template admin — create</t>
         </is>
       </c>
       <c r="E137" s="2" t="inlineStr">
         <is>
-          <t>Verify a Fee/Discount template offers the four whole-work-order methods and no scope field</t>
+          <t>Verify creating a Fee template (dialog fields and the Create button)</t>
         </is>
       </c>
       <c r="F137" s="2" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>High</t>
         </is>
       </c>
       <c r="G137" s="2" t="inlineStr">
@@ -7092,39 +7092,39 @@
       </c>
       <c r="I137" s="2" t="inlineStr">
         <is>
-          <t>builder offers exactly 4 whole-WO methods (Flat, % Labor, % Parts, % Subtotal), no scope field, no legacy '% Labor+Parts' | WORDING+VIU 2026-07-13: Calc Type options confirmed (same 4 whole-WO methods as the WO dialog); no scope field.</t>
+          <t>PARTIAL IMPROVEMENT: create-dialog title NOW 'New Fee / Discount' (matches spec; was 'Add new fee/discount'); confirm button still 'Create' (spec 'Add Fee / Discount') and toast 'Template created' per batch-1 — drift remains | WORDING+VIU 2026-07-13: Create dialog confirmed live: title 'New Fee / Discount', fields Name/Type/Calculation Type/'$ Default Amount'/Taxable toggle/'Auto-apply to new work orders' toggle/'Description (Optional)', 'Create' button. Type offers only Fee/Discount (Processing Fee is NOT in the builder — Story 8 not built). Create API 201 live. Toast text carried from prior VIU. | SV-8456 (2026-07-21 staging LIVE VIU): F&amp;D moved to SETTINGS→SERVICE (below Canned Lines); template/WO/Part-sale/customer dialogs now show Taxable as a Yes/No DROPDOWN (was toggle); Auto-apply is a CHECKBOX with a 'When on…' caption; settings &amp; customer tables are plain-text/left-aligned (no badges); WO sidebar card retitled 'Work Order Fees &amp; Discounts' and renders ABOVE Financial Info; Part-sale card 'Parts Sale Fees &amp; Discounts' above Financial Info. Permission gate pivoted Settings→Finance → Settings→Service (verified live: Service-user sees+manages F&amp;D &amp; convenience toggle; Finance-only user has no F&amp;D nav item and /administration/adjustment-templates bounces to /workorders). Frontend-only; functionality + calc INTACT. | RE-VIU 2026-07-22 LIVE (Batch 4, SV-8456 re-verify): access-check quick-login {admin} HTTP 200. Re-confirmed on current staging build — 8 UI corrections intact (Taxable Yes/No dropdown; Auto-apply checkbox+caption; modal field order Type/CalcType&gt;Name&gt;Amount&gt;Taxable+jur.note&gt;Auto-apply&gt;Description; Settings table plain-text left-aligned no badges; F&amp;D nav under SERVICE below Canned Lines; WO &amp; Part-Sale cards above Financial Info [Batch 2/3]; Customer 'Fees &amp; Discounts' tab mirrors Settings styling minus convenience toggle) AND Settings-&gt;Service permission pivot CONFIRMED live per role (seeded ServiceRole vs FinanceRole, assigned to Tech, Tech restored to Technician 50bf6a0d + verified, both ZZAUTOTEST roles deleted 204): Service-user sees+manages F&amp;D nav + convenience toggle, direct /administration/adjustment-templates loads; Finance-only user has NO F&amp;D nav, FINANCE=Payment Methods only, direct route bounces to /workorders. viu_status VIU-Verified re-confirmed. Ev build/fees-discounts/viu-sv8456-2026-07-22/ (01-settings-landing, 02-new-dialog, 03-customer-fd-tab, SVC-*, FIN-*).</t>
         </is>
       </c>
     </row>
     <row r="138">
       <c r="A138" s="2" t="inlineStr">
         <is>
-          <t>FD-TMPL-015</t>
+          <t>FD-TMPL-004</t>
         </is>
       </c>
       <c r="B138" s="2" t="inlineStr">
         <is>
-          <t>C28516</t>
+          <t>C28505</t>
         </is>
       </c>
       <c r="C138" s="6" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/28516</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/28505</t>
         </is>
       </c>
       <c r="D138" s="2" t="inlineStr">
         <is>
-          <t>Template admin — negative</t>
+          <t>Template admin — create</t>
         </is>
       </c>
       <c r="E138" s="2" t="inlineStr">
         <is>
-          <t>Verify the template save-failure message</t>
+          <t>Verify creating a Discount template</t>
         </is>
       </c>
       <c r="F138" s="2" t="inlineStr">
         <is>
-          <t>Low</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="G138" s="2" t="inlineStr">
@@ -7139,34 +7139,34 @@
       </c>
       <c r="I138" s="2" t="inlineStr">
         <is>
-          <t>template empty name -&gt; 400; amount 0 -&gt; 400 (save-failure surfaced) | WORDING+VIU 2026-07-13: Save-failure toast text carried from prior VIU (not force-failed this run).</t>
+          <t>generic 'Template created' toast vs spec 'Discount added' per batch-1; not re-driven | WORDING+VIU 2026-07-13: CORRECTED title: the toast is generic (not a per-type 'Discount added'). Create dialog + list confirmed live. | SV-8456 (2026-07-21 staging LIVE VIU): F&amp;D moved to SETTINGS→SERVICE (below Canned Lines); template/WO/Part-sale/customer dialogs now show Taxable as a Yes/No DROPDOWN (was toggle); Auto-apply is a CHECKBOX with a 'When on…' caption; settings &amp; customer tables are plain-text/left-aligned (no badges); WO sidebar card retitled 'Work Order Fees &amp; Discounts' and renders ABOVE Financial Info; Part-sale card 'Parts Sale Fees &amp; Discounts' above Financial Info. Permission gate pivoted Settings→Finance → Settings→Service (verified live: Service-user sees+manages F&amp;D &amp; convenience toggle; Finance-only user has no F&amp;D nav item and /administration/adjustment-templates bounces to /workorders). Frontend-only; functionality + calc INTACT. | RE-VIU 2026-07-22 LIVE (Batch 4, SV-8456 re-verify): access-check quick-login {admin} HTTP 200. Re-confirmed on current staging build — 8 UI corrections intact (Taxable Yes/No dropdown; Auto-apply checkbox+caption; modal field order Type/CalcType&gt;Name&gt;Amount&gt;Taxable+jur.note&gt;Auto-apply&gt;Description; Settings table plain-text left-aligned no badges; F&amp;D nav under SERVICE below Canned Lines; WO &amp; Part-Sale cards above Financial Info [Batch 2/3]; Customer 'Fees &amp; Discounts' tab mirrors Settings styling minus convenience toggle) AND Settings-&gt;Service permission pivot CONFIRMED live per role (seeded ServiceRole vs FinanceRole, assigned to Tech, Tech restored to Technician 50bf6a0d + verified, both ZZAUTOTEST roles deleted 204): Service-user sees+manages F&amp;D nav + convenience toggle, direct /administration/adjustment-templates loads; Finance-only user has NO F&amp;D nav, FINANCE=Payment Methods only, direct route bounces to /workorders. viu_status VIU-Verified re-confirmed. Ev build/fees-discounts/viu-sv8456-2026-07-22/ (01-settings-landing, 02-new-dialog, 03-customer-fd-tab, SVC-*, FIN-*).</t>
         </is>
       </c>
     </row>
     <row r="139">
       <c r="A139" s="2" t="inlineStr">
         <is>
-          <t>FD-TMPL-016</t>
+          <t>FD-TMPL-005</t>
         </is>
       </c>
       <c r="B139" s="2" t="inlineStr">
         <is>
-          <t>C28517</t>
+          <t>C28506</t>
         </is>
       </c>
       <c r="C139" s="6" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/28517</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/28506</t>
         </is>
       </c>
       <c r="D139" s="2" t="inlineStr">
         <is>
-          <t>Template admin — permissions</t>
+          <t>Template admin — auto-apply</t>
         </is>
       </c>
       <c r="E139" s="2" t="inlineStr">
         <is>
-          <t>Verify the admin Fees &amp; Discounts page needs the Settings → Service permission</t>
+          <t>Verify the 'Auto-apply to all new work orders at this location' checkbox adds the template to every new work order at that location</t>
         </is>
       </c>
       <c r="F139" s="2" t="inlineStr">
@@ -7186,39 +7186,39 @@
       </c>
       <c r="I139" s="2" t="inlineStr">
         <is>
-          <t>BE-enforced: tech templates GET/POST -&gt; 403; page FE-gated settingsFinance | WORDING+VIU 2026-07-13: Templates admin is back-end gated by Settings → Finance (Tech → 403), established batch-2. Nav corrected to Finance. NOTE: re-check the Tech negative after the roles matrix is re-derived (Technician drifted on shared qb). | SV-8456 (2026-07-21 staging LIVE VIU): F&amp;D moved to SETTINGS→SERVICE (below Canned Lines); template/WO/Part-sale/customer dialogs now show Taxable as a Yes/No DROPDOWN (was toggle); Auto-apply is a CHECKBOX with a 'When on…' caption; settings &amp; customer tables are plain-text/left-aligned (no badges); WO sidebar card retitled 'Work Order Fees &amp; Discounts' and renders ABOVE Financial Info; Part-sale card 'Parts Sale Fees &amp; Discounts' above Financial Info. Permission gate pivoted Settings→Finance → Settings→Service (verified live: Service-user sees+manages F&amp;D &amp; convenience toggle; Finance-only user has no F&amp;D nav item and /administration/adjustment-templates bounces to /workorders). Frontend-only; functionality + calc INTACT. | RE-VIU 2026-07-22 LIVE (Batch 4, SV-8456 re-verify): access-check quick-login {admin} HTTP 200. Re-confirmed on current staging build — 8 UI corrections intact (Taxable Yes/No dropdown; Auto-apply checkbox+caption; modal field order Type/CalcType&gt;Name&gt;Amount&gt;Taxable+jur.note&gt;Auto-apply&gt;Description; Settings table plain-text left-aligned no badges; F&amp;D nav under SERVICE below Canned Lines; WO &amp; Part-Sale cards above Financial Info [Batch 2/3]; Customer 'Fees &amp; Discounts' tab mirrors Settings styling minus convenience toggle) AND Settings-&gt;Service permission pivot CONFIRMED live per role (seeded ServiceRole vs FinanceRole, assigned to Tech, Tech restored to Technician 50bf6a0d + verified, both ZZAUTOTEST roles deleted 204): Service-user sees+manages F&amp;D nav + convenience toggle, direct /administration/adjustment-templates loads; Finance-only user has NO F&amp;D nav, FINANCE=Payment Methods only, direct route bounces to /workorders. viu_status VIU-Verified re-confirmed. Ev build/fees-discounts/viu-sv8456-2026-07-22/ (01-settings-landing, 02-new-dialog, 03-customer-fd-tab, SVC-*, FIN-*).</t>
+          <t>auto-apply template ('Capped discount' + test pfees) landed on every fresh WO as appliedBy=auto | WORDING+VIU 2026-07-13: CORRECTED auto-apply label: dialog toggle is 'Auto-apply to new work orders'; list column 'Auto-Apply To Work Orders'. Confirmed live (shot tmpl-02). | SV-8456 (2026-07-21 staging LIVE VIU): F&amp;D moved to SETTINGS→SERVICE (below Canned Lines); template/WO/Part-sale/customer dialogs now show Taxable as a Yes/No DROPDOWN (was toggle); Auto-apply is a CHECKBOX with a 'When on…' caption; settings &amp; customer tables are plain-text/left-aligned (no badges); WO sidebar card retitled 'Work Order Fees &amp; Discounts' and renders ABOVE Financial Info; Part-sale card 'Parts Sale Fees &amp; Discounts' above Financial Info. Permission gate pivoted Settings→Finance → Settings→Service (verified live: Service-user sees+manages F&amp;D &amp; convenience toggle; Finance-only user has no F&amp;D nav item and /administration/adjustment-templates bounces to /workorders). Frontend-only; functionality + calc INTACT. | RE-VIU 2026-07-22 LIVE (Batch 4, SV-8456 re-verify): access-check quick-login {admin} HTTP 200. Re-confirmed on current staging build — 8 UI corrections intact (Taxable Yes/No dropdown; Auto-apply checkbox+caption; modal field order Type/CalcType&gt;Name&gt;Amount&gt;Taxable+jur.note&gt;Auto-apply&gt;Description; Settings table plain-text left-aligned no badges; F&amp;D nav under SERVICE below Canned Lines; WO &amp; Part-Sale cards above Financial Info [Batch 2/3]; Customer 'Fees &amp; Discounts' tab mirrors Settings styling minus convenience toggle) AND Settings-&gt;Service permission pivot CONFIRMED live per role (seeded ServiceRole vs FinanceRole, assigned to Tech, Tech restored to Technician 50bf6a0d + verified, both ZZAUTOTEST roles deleted 204): Service-user sees+manages F&amp;D nav + convenience toggle, direct /administration/adjustment-templates loads; Finance-only user has NO F&amp;D nav, FINANCE=Payment Methods only, direct route bounces to /workorders. viu_status VIU-Verified re-confirmed. Ev build/fees-discounts/viu-sv8456-2026-07-22/ (01-settings-landing, 02-new-dialog, 03-customer-fd-tab, SVC-*, FIN-*).</t>
         </is>
       </c>
     </row>
     <row r="140">
       <c r="A140" s="2" t="inlineStr">
         <is>
-          <t>FD-TMPL-017</t>
+          <t>FD-TMPL-006</t>
         </is>
       </c>
       <c r="B140" s="2" t="inlineStr">
         <is>
-          <t>C28518</t>
+          <t>C28507</t>
         </is>
       </c>
       <c r="C140" s="6" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/28518</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/28507</t>
         </is>
       </c>
       <c r="D140" s="2" t="inlineStr">
         <is>
-          <t>Template admin — dialog fields</t>
+          <t>Template admin — edit</t>
         </is>
       </c>
       <c r="E140" s="2" t="inlineStr">
         <is>
-          <t>Verify the template Name is limited to 100 characters</t>
+          <t>Verify editing a template (Edit Fee / Discount dialog, 'Save' button)</t>
         </is>
       </c>
       <c r="F140" s="2" t="inlineStr">
         <is>
-          <t>Low</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="G140" s="2" t="inlineStr">
@@ -7233,39 +7233,39 @@
       </c>
       <c r="I140" s="2" t="inlineStr">
         <is>
-          <t>name 100ch -&gt; 201; 101ch -&gt; 400 | WORDING+VIU 2026-07-13: Name 100-char limit carried.</t>
+          <t>edit locks Type+Calc on template edit (spec locks only in WO dialog) per batch-1; not re-driven | WORDING+VIU 2026-07-13: Edit dialog title 'Edit Fee / Discount' + 'Save' button confirmed on the fee/discount Edit dialog (shot edit-01). Edit opens from the row's pencil button. Toast text carried.</t>
         </is>
       </c>
     </row>
     <row r="141">
       <c r="A141" s="2" t="inlineStr">
         <is>
-          <t>FD-TMPL-018</t>
+          <t>FD-TMPL-007</t>
         </is>
       </c>
       <c r="B141" s="2" t="inlineStr">
         <is>
-          <t>C29917</t>
+          <t>C28508</t>
         </is>
       </c>
       <c r="C141" s="6" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/29917</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/28508</t>
         </is>
       </c>
       <c r="D141" s="2" t="inlineStr">
         <is>
-          <t>Template admin — jurisdiction note</t>
+          <t>Template admin — delete</t>
         </is>
       </c>
       <c r="E141" s="2" t="inlineStr">
         <is>
-          <t>Verify the admin Fee/Discount template dialog shows the tax-jurisdiction note below the Taxable Yes/No dropdown (for every kind)</t>
+          <t>Verify the template delete confirm dialog and buttons</t>
         </is>
       </c>
       <c r="F141" s="2" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>High</t>
         </is>
       </c>
       <c r="G141" s="2" t="inlineStr">
@@ -7280,39 +7280,39 @@
       </c>
       <c r="I141" s="2" t="inlineStr">
         <is>
-          <t>administration/adjustment-templates loads; Finance-only user has NO F&amp;D nav, FINANCE=Payment Methods only, direct route bounces to /workorders. viu_status VIU-Verified re-confirmed. Ev build/fees-discounts/viu-sv8456-2026-07-22/ (01-settings-landing, 02-new-dialog, 03-customer-fd-tab, SVC-*, FIN-*).</t>
+          <t>delete-confirm dialog + affectedCustomerCount warning per batch-1; delete-precondition endpoint intact | WORDING+VIU 2026-07-13: Delete confirm confirmed live: standardized 'Delete Template' dialog with 'Cancel' + red 'Delete' (shot tmpl-03). The plain (no-customer) body wording was not captured this run — the sample template had a customer default (see FD-TMPL-008).</t>
         </is>
       </c>
     </row>
     <row r="142">
       <c r="A142" s="2" t="inlineStr">
         <is>
-          <t>FD-VAL-001</t>
+          <t>FD-TMPL-008</t>
         </is>
       </c>
       <c r="B142" s="2" t="inlineStr">
         <is>
-          <t>C28599</t>
+          <t>C28509</t>
         </is>
       </c>
       <c r="C142" s="6" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/28599</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/28509</t>
         </is>
       </c>
       <c r="D142" s="2" t="inlineStr">
         <is>
-          <t>Validation / Edge</t>
+          <t>Template admin — delete</t>
         </is>
       </c>
       <c r="E142" s="2" t="inlineStr">
         <is>
-          <t>Verify the Add button stays disabled until Name, Type, Calculation Type and an Amount above 0 are all set</t>
+          <t>Verify the delete confirm adds a warning when the template is a customer default</t>
         </is>
       </c>
       <c r="F142" s="2" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="G142" s="2" t="inlineStr">
@@ -7327,34 +7327,34 @@
       </c>
       <c r="I142" s="2" t="inlineStr">
         <is>
-          <t>CONFIRMED AGAIN: Add button enabled on empty form (validates on submit) — PO Q4=B defect persists | WORDING+VIU 2026-07-13: DEVIATION re-confirmed 2026-07-13 (BUG-FD-4): the 'Add Fee' button is ENABLED on an empty form (validates on submit). Labels build-accurate (Add Fee/Add Discount, Calculation Type, Max Amount). | STAGING VIU 2026-07-20 staging LIVE VIU: BUG-FD-4 FIXED on staging: confirm button disabled until Name+Type+Calc+Amount&gt;0 set. Live-observed (dev-wo-emptyform + part-sale Add Fee disabled-until-valid). | SV-8479/8480 deconfliction 2026-07-22: label sweep: navigation labels -&gt; 'Add Work Order Fee / Discount' / 'New Work Order Fee / Discount' (behavior/expected unchanged). | VIU 2026-07-22 LIVE: SV-8479 nav label 'Add Work Order Fee / Discount' confirmed present in the WO toolbar ⋯ menu; case behavior unchanged. Ev: wo/FD-WO-025-toolbar-menu.png.</t>
+          <t>standardized 'Delete Template' dialog wording = intended per epic; case-update to adopt live wording still pending | WORDING+VIU 2026-07-13: Customer-default warning confirmed live EXACTLY: 'This template is set as a default for N customer(s). Deleting it will remove it from them.' (saw '1 customer', shot tmpl-03).</t>
         </is>
       </c>
     </row>
     <row r="143">
       <c r="A143" s="2" t="inlineStr">
         <is>
-          <t>FD-VAL-002</t>
+          <t>FD-TMPL-009</t>
         </is>
       </c>
       <c r="B143" s="2" t="inlineStr">
         <is>
-          <t>C28600</t>
+          <t>C28510</t>
         </is>
       </c>
       <c r="C143" s="6" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/28600</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/28510</t>
         </is>
       </c>
       <c r="D143" s="2" t="inlineStr">
         <is>
-          <t>Validation / Edge</t>
+          <t>Template admin — delete</t>
         </is>
       </c>
       <c r="E143" s="2" t="inlineStr">
         <is>
-          <t>Verify a blank or 0 amount blocks saving, with an error</t>
+          <t>Verify deleting a template leaves work-order fees/discounts made from it unchanged</t>
         </is>
       </c>
       <c r="F143" s="2" t="inlineStr">
@@ -7374,39 +7374,39 @@
       </c>
       <c r="I143" s="2" t="inlineStr">
         <is>
-          <t>amount 0 -&gt; 400 (API); UI inline error on submit | WORDING+VIU 2026-07-13: Blank/0 amount blocked; carry prior VIU. Labels cleaned. | SV-8479/8480 deconfliction 2026-07-22: label sweep: navigation labels -&gt; 'Add Work Order Fee / Discount' / 'New Work Order Fee / Discount' (behavior/expected unchanged). | VIU 2026-07-22 LIVE: SV-8479 nav label 'Add Work Order Fee / Discount' confirmed present in the WO toolbar ⋯ menu; case behavior unchanged. Ev: wo/FD-WO-025-toolbar-menu.png.</t>
+          <t>template deleted (204) -&gt; WO adjustment made from it survives unchanged (resolved 6 intact) | WORDING+VIU 2026-07-13: Delete leaves WO adjustments unchanged; carried. Nav corrected to Finance. | SV-8456 (2026-07-21 staging LIVE VIU): F&amp;D moved to SETTINGS→SERVICE (below Canned Lines); template/WO/Part-sale/customer dialogs now show Taxable as a Yes/No DROPDOWN (was toggle); Auto-apply is a CHECKBOX with a 'When on…' caption; settings &amp; customer tables are plain-text/left-aligned (no badges); WO sidebar card retitled 'Work Order Fees &amp; Discounts' and renders ABOVE Financial Info; Part-sale card 'Parts Sale Fees &amp; Discounts' above Financial Info. Permission gate pivoted Settings→Finance → Settings→Service (verified live: Service-user sees+manages F&amp;D &amp; convenience toggle; Finance-only user has no F&amp;D nav item and /administration/adjustment-templates bounces to /workorders). Frontend-only; functionality + calc INTACT. | RE-VIU 2026-07-22 LIVE (Batch 4, SV-8456 re-verify): access-check quick-login {admin} HTTP 200. Re-confirmed on current staging build — 8 UI corrections intact (Taxable Yes/No dropdown; Auto-apply checkbox+caption; modal field order Type/CalcType&gt;Name&gt;Amount&gt;Taxable+jur.note&gt;Auto-apply&gt;Description; Settings table plain-text left-aligned no badges; F&amp;D nav under SERVICE below Canned Lines; WO &amp; Part-Sale cards above Financial Info [Batch 2/3]; Customer 'Fees &amp; Discounts' tab mirrors Settings styling minus convenience toggle) AND Settings-&gt;Service permission pivot CONFIRMED live per role (seeded ServiceRole vs FinanceRole, assigned to Tech, Tech restored to Technician 50bf6a0d + verified, both ZZAUTOTEST roles deleted 204): Service-user sees+manages F&amp;D nav + convenience toggle, direct /administration/adjustment-templates loads; Finance-only user has NO F&amp;D nav, FINANCE=Payment Methods only, direct route bounces to /workorders. viu_status VIU-Verified re-confirmed. Ev build/fees-discounts/viu-sv8456-2026-07-22/ (01-settings-landing, 02-new-dialog, 03-customer-fd-tab, SVC-*, FIN-*).</t>
         </is>
       </c>
     </row>
     <row r="144">
       <c r="A144" s="2" t="inlineStr">
         <is>
-          <t>FD-VAL-003</t>
+          <t>FD-TMPL-010</t>
         </is>
       </c>
       <c r="B144" s="2" t="inlineStr">
         <is>
-          <t>C28601</t>
+          <t>C28511</t>
         </is>
       </c>
       <c r="C144" s="6" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/28601</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/28511</t>
         </is>
       </c>
       <c r="D144" s="2" t="inlineStr">
         <is>
-          <t>Validation / Edge</t>
+          <t>Template admin — scoping</t>
         </is>
       </c>
       <c r="E144" s="2" t="inlineStr">
         <is>
-          <t>Verify an empty Name blocks saving, with an error (Name required, up to 100 characters)</t>
+          <t>Verify template scoping — labour-method templates only show in labour pickers, parts-method only in parts pickers</t>
         </is>
       </c>
       <c r="F144" s="2" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>High</t>
         </is>
       </c>
       <c r="G144" s="2" t="inlineStr">
@@ -7421,39 +7421,39 @@
       </c>
       <c r="I144" s="2" t="inlineStr">
         <is>
-          <t>UI blocks empty name (inline required error). NEW FDBUG-16: raw API now ACCEPTS empty-name adds (201; regression vs batch-3 400) — FE-only guard; name 101ch -&gt; 400, 100ch -&gt; 201 | WORDING+VIU 2026-07-13: Empty name blocked in UI; 100-char limit. (Raw back-end accepts empty name — FDBUG-16 — but the dialog blocks it.) | SV-8479/8480 deconfliction 2026-07-22: label sweep: navigation labels -&gt; 'Add Work Order Fee / Discount' / 'New Work Order Fee / Discount' (behavior/expected unchanged). | VIU 2026-07-22 LIVE: SV-8479 nav label 'Add Work Order Fee / Discount' confirmed present in the WO toolbar ⋯ menu; case behavior unchanged. Ev: wo/FD-WO-025-toolbar-menu.png.</t>
+          <t>FDBUG-13 (line-scope Add dialog has no template picker) per batch-1/4; not re-driven today | WORDING+VIU 2026-07-13: DEVIATION carried: template scoping in the line 'Apply From Template' picker + the compatibility hint not re-captured this run (needs the line-level picker). Labels cleaned. | SV-8479/8480 deconfliction 2026-07-22: mixed label sweep: labor step -&gt; 'Add Labor Fee / Discount', part step -&gt; 'Add Part Fee / Discount' (behavior unchanged). | VIU 2026-07-22 LIVE: SV-8479 nav labels 'Add Labor Fee / Discount' (step 1) and 'Add Part Fee / Discount' (step 3) both confirmed present; case status unchanged (existing Deviation for its own reason). Ev: wo/FD-WO-017-labor-menu-open.png, wo/FD-WO-018-part-menu.png. | CLOSE-OUT 2026-07-24: accepted per Ahtasham QA live review 2026-07-24 (no bug). Status -&gt; VIU-Verified, wording unchanged. HONESTY (Rule 12/22): accepted on Ahtasham's live QA review — NOT re-observed by us this pass.</t>
         </is>
       </c>
     </row>
     <row r="145">
       <c r="A145" s="2" t="inlineStr">
         <is>
-          <t>FD-VAL-004</t>
+          <t>FD-TMPL-011</t>
         </is>
       </c>
       <c r="B145" s="2" t="inlineStr">
         <is>
-          <t>C28602</t>
+          <t>C28512</t>
         </is>
       </c>
       <c r="C145" s="6" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/28602</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/28512</t>
         </is>
       </c>
       <c r="D145" s="2" t="inlineStr">
         <is>
-          <t>Validation / Edge</t>
+          <t>Template admin — dialog fields</t>
         </is>
       </c>
       <c r="E145" s="2" t="inlineStr">
         <is>
-          <t>Verify a percentage discount over 100% is invalid while a percentage fee has no upper cap</t>
+          <t>Verify Max Amount shows only for percentage methods and how 0 behaves</t>
         </is>
       </c>
       <c r="F145" s="2" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="G145" s="2" t="inlineStr">
@@ -7468,34 +7468,34 @@
       </c>
       <c r="I145" s="2" t="inlineStr">
         <is>
-          <t>discount &gt;100% invalid (400), fee uncapped (201) | WORDING+VIU 2026-07-13: %&gt;100 discount invalid, fee uncapped; carry prior VIU. Labels cleaned. | SV-8479/8480 deconfliction 2026-07-22: label sweep: navigation labels -&gt; 'Add Work Order Fee / Discount' / 'New Work Order Fee / Discount' (behavior/expected unchanged). | VIU 2026-07-22 LIVE: SV-8479 nav label 'Add Work Order Fee / Discount' confirmed present in the WO toolbar ⋯ menu; case behavior unchanged. Ev: wo/FD-WO-025-toolbar-menu.png.</t>
+          <t>maxCap 0 accepted and STORED as 0 on the template (201) and WO resolve treats 0 as NO cap (34.15) — FDBUG-9 persists | WORDING+VIU 2026-07-13: Max Amount only for % confirmed (WO+template dialogs). DEVIATION (PO Q2): a Max Amount of 0 is treated as 'no cap'. Labels cleaned. | CHRIS WARD ROUND-2 ANSWER APPLIED 2026-07-14(Q2=A): PO ruled a typed 0 in Max Amount = 'no limit' (WAD, S2-R25). 0-handling no longer a deviation; FDBUG-9 closed as accepted; jira draft TICKET 4 DROPPED. Expected reworded to affirm 0=no-cap. PUSHED TO TESTRAIL 2026-07-14 via update_case (QA-lead one-day authorization; update 200 / re-verify 200 MATCH; audit: testrail-round2-push-log.md).</t>
         </is>
       </c>
     </row>
     <row r="146">
       <c r="A146" s="2" t="inlineStr">
         <is>
-          <t>FD-VAL-005</t>
+          <t>FD-TMPL-013</t>
         </is>
       </c>
       <c r="B146" s="2" t="inlineStr">
         <is>
-          <t>C28603</t>
+          <t>C28514</t>
         </is>
       </c>
       <c r="C146" s="6" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/28603</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/28514</t>
         </is>
       </c>
       <c r="D146" s="2" t="inlineStr">
         <is>
-          <t>Validation / Edge</t>
+          <t>Template admin — validation</t>
         </is>
       </c>
       <c r="E146" s="2" t="inlineStr">
         <is>
-          <t>Verify negative amounts are rejected (values must be above 0)</t>
+          <t>Verify a percentage-discount template cannot go over 100% while a percentage-fee template has no cap</t>
         </is>
       </c>
       <c r="F146" s="2" t="inlineStr">
@@ -7515,34 +7515,34 @@
       </c>
       <c r="I146" s="2" t="inlineStr">
         <is>
-          <t>negative amount -&gt; 400 | WORDING+VIU 2026-07-13: Negatives rejected; carry prior VIU. | SV-8479/8480 deconfliction 2026-07-22: label sweep: navigation labels -&gt; 'Add Work Order Fee / Discount' / 'New Work Order Fee / Discount' (behavior/expected unchanged). | VIU 2026-07-22 LIVE: SV-8479 nav label 'Add Work Order Fee / Discount' confirmed present in the WO toolbar ⋯ menu; case behavior unchanged. Ev: wo/FD-WO-025-toolbar-menu.png.</t>
+          <t>discount template 150% -&gt; 400; fee template 150% -&gt; 201 | WORDING+VIU 2026-07-13: %&gt;100 discount rejected (confirmed via API 2026-07-13: 'A percentage discount cannot exceed 100%').</t>
         </is>
       </c>
     </row>
     <row r="147">
       <c r="A147" s="2" t="inlineStr">
         <is>
-          <t>FD-VAL-006</t>
+          <t>FD-TMPL-014</t>
         </is>
       </c>
       <c r="B147" s="2" t="inlineStr">
         <is>
-          <t>C28604</t>
+          <t>C28515</t>
         </is>
       </c>
       <c r="C147" s="6" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/28604</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/28515</t>
         </is>
       </c>
       <c r="D147" s="2" t="inlineStr">
         <is>
-          <t>Validation / Edge</t>
+          <t>Template admin — dialog fields</t>
         </is>
       </c>
       <c r="E147" s="2" t="inlineStr">
         <is>
-          <t>Verify the Max Amount field shows only for percentage methods and how 0 or empty behaves</t>
+          <t>Verify a Fee/Discount template offers the four whole-work-order methods and no scope field</t>
         </is>
       </c>
       <c r="F147" s="2" t="inlineStr">
@@ -7562,39 +7562,39 @@
       </c>
       <c r="I147" s="2" t="inlineStr">
         <is>
-          <t>FDBUG-9: maxCap 0 behaves as NO cap (not 'no maximum' spec reading matches build for empty, but 0 disagrees w/ §5-R6 $0-forces-$0) — persists | WORDING+VIU 2026-07-13: Confirmed live: '$ Max Amount (Optional)' appears only for percentage methods (hidden for Flat Amount, shots wo-03/wo-05). DEVIATION (FDBUG-9 / PO Q2 pending): whether a Max Amount of 0 means 'no cap' or 'cap at $0.00' is a pending product decision — expected kept as current build behavior. | CHRIS WARD ROUND-2 ANSWER APPLIED 2026-07-14(Q2=A): PO ruled a typed 0 in Max Amount = 'no limit' (WAD, S2-R25). 0-handling no longer a deviation; FDBUG-9 closed as accepted; jira draft TICKET 4 DROPPED. Expected reworded to affirm 0=no-cap. PUSHED TO TESTRAIL 2026-07-14 via update_case (QA-lead one-day authorization; update 200 / re-verify 200 MATCH; audit: testrail-round2-push-log.md). | SV-8479/8480 deconfliction 2026-07-22: label sweep: navigation labels -&gt; 'Add Work Order Fee / Discount' / 'New Work Order Fee / Discount' (behavior/expected unchanged). | VIU 2026-07-22 LIVE: SV-8479 nav label 'Add Work Order Fee / Discount' confirmed present in the WO toolbar ⋯ menu; case behavior unchanged. Ev: wo/FD-WO-025-toolbar-menu.png.</t>
+          <t>builder offers exactly 4 whole-WO methods (Flat, % Labor, % Parts, % Subtotal), no scope field, no legacy '% Labor+Parts' | WORDING+VIU 2026-07-13: Calc Type options confirmed (same 4 whole-WO methods as the WO dialog); no scope field.</t>
         </is>
       </c>
     </row>
     <row r="148">
       <c r="A148" s="2" t="inlineStr">
         <is>
-          <t>FD-VAL-007</t>
+          <t>FD-TMPL-015</t>
         </is>
       </c>
       <c r="B148" s="2" t="inlineStr">
         <is>
-          <t>C28605</t>
+          <t>C28516</t>
         </is>
       </c>
       <c r="C148" s="6" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/28605</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/28516</t>
         </is>
       </c>
       <c r="D148" s="2" t="inlineStr">
         <is>
-          <t>Validation / Edge</t>
+          <t>Template admin — negative</t>
         </is>
       </c>
       <c r="E148" s="2" t="inlineStr">
         <is>
-          <t>Verify a template that is both auto-apply at the location and a customer default is added only ONCE to a new work order</t>
+          <t>Verify the template save-failure message</t>
         </is>
       </c>
       <c r="F148" s="2" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>Low</t>
         </is>
       </c>
       <c r="G148" s="2" t="inlineStr">
@@ -7609,39 +7609,39 @@
       </c>
       <c r="I148" s="2" t="inlineStr">
         <is>
-          <t>auto+default template -&gt; exactly ONE adjustment on the new WO | WORDING+VIU 2026-07-13: Double-add does not stack (one adjustment); carry prior VIU. | SV-8456 (2026-07-21 staging LIVE VIU): F&amp;D moved to SETTINGS→SERVICE (below Canned Lines); template/WO/Part-sale/customer dialogs now show Taxable as a Yes/No DROPDOWN (was toggle); Auto-apply is a CHECKBOX with a 'When on…' caption; settings &amp; customer tables are plain-text/left-aligned (no badges); WO sidebar card retitled 'Work Order Fees &amp; Discounts' and renders ABOVE Financial Info; Part-sale card 'Parts Sale Fees &amp; Discounts' above Financial Info. Permission gate pivoted Settings→Finance → Settings→Service (verified live: Service-user sees+manages F&amp;D &amp; convenience toggle; Finance-only user has no F&amp;D nav item and /administration/adjustment-templates bounces to /workorders). Frontend-only; functionality + calc INTACT. | RE-VIU 2026-07-22 LIVE (Batch 4, SV-8456 re-verify): access-check quick-login {admin} HTTP 200. Re-confirmed on current staging build — 8 UI corrections intact (Taxable Yes/No dropdown; Auto-apply checkbox+caption; modal field order Type/CalcType&gt;Name&gt;Amount&gt;Taxable+jur.note&gt;Auto-apply&gt;Description; Settings table plain-text left-aligned no badges; F&amp;D nav under SERVICE below Canned Lines; WO &amp; Part-Sale cards above Financial Info [Batch 2/3]; Customer 'Fees &amp; Discounts' tab mirrors Settings styling minus convenience toggle) AND Settings-&gt;Service permission pivot CONFIRMED live per role (seeded ServiceRole vs FinanceRole, assigned to Tech, Tech restored to Technician 50bf6a0d + verified, both ZZAUTOTEST roles deleted 204): Service-user sees+manages F&amp;D nav + convenience toggle, direct /administration/adjustment-templates loads; Finance-only user has NO F&amp;D nav, FINANCE=Payment Methods only, direct route bounces to /workorders. viu_status VIU-Verified re-confirmed. Ev build/fees-discounts/viu-sv8456-2026-07-22/ (01-settings-landing, 02-new-dialog, 03-customer-fd-tab, SVC-*, FIN-*).</t>
+          <t>template empty name -&gt; 400; amount 0 -&gt; 400 (save-failure surfaced) | WORDING+VIU 2026-07-13: Save-failure toast text carried from prior VIU (not force-failed this run).</t>
         </is>
       </c>
     </row>
     <row r="149">
       <c r="A149" s="2" t="inlineStr">
         <is>
-          <t>FD-WO-001</t>
+          <t>FD-TMPL-016</t>
         </is>
       </c>
       <c r="B149" s="2" t="inlineStr">
         <is>
-          <t>C28424</t>
+          <t>C28517</t>
         </is>
       </c>
       <c r="C149" s="6" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/28424</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/28517</t>
         </is>
       </c>
       <c r="D149" s="2" t="inlineStr">
         <is>
-          <t>Work Order — Whole-WO Fee/Discount</t>
+          <t>Template admin — permissions</t>
         </is>
       </c>
       <c r="E149" s="2" t="inlineStr">
         <is>
-          <t>Verify the whole-work-order fee/discount dialog opens from the toolbar menu with title 'New Work Order Fee / Discount'</t>
+          <t>Verify the admin Fees &amp; Discounts page needs the Settings → Service permission</t>
         </is>
       </c>
       <c r="F149" s="2" t="inlineStr">
         <is>
-          <t>Critical</t>
+          <t>High</t>
         </is>
       </c>
       <c r="G149" s="2" t="inlineStr">
@@ -7656,39 +7656,39 @@
       </c>
       <c r="I149" s="2" t="inlineStr">
         <is>
-          <t>dialog title still 'Add new fee/discount' (spec 'New Fee / Discount'), menu item 'Add Fee/Discount' — label drift persists (UI re-driven, shot 10-wo-add-dialog) | WORDING+VIU 2026-07-13: rewritten to exact build labels (⋮ menu item 'Add Fee/Discount'; dialog 'Add new fee/discount'; fields 'Apply From Template'/'Name'/'Type'/'Calculation Type'/'$ Amount' or 'Percent %'/'$ Max Amount (Optional)'/'Taxable' toggle; whole-WO Calculation Type options = Flat Amount, % of Labor Total, % of Parts Total, % of Subtotal; buttons 'Add Fee'/'Add Discount'; sidebar card 'WO Fees &amp; Discounts'; preview empty prompt 'Enter an amount to see the impact.'). Captured live on WO S3-15960 (shots wo-01..wo-05). Now build-accurate (was VIU-Deviation only because the case used the older spec wording). Dialog shows no work-order-number subtitle in this build (old expected claim dropped). | SV-8479/8480 deconfliction 2026-07-22: menu item 'Add Fee/Discount' -&gt; 'Add Work Order Fee / Discount' (item 10); title 'Add new fee/discount' -&gt; 'New Work Order Fee / Discount' + new subline 'Applying To: Entire Work Order' (item 11, reverses the old 'no Applying-to line' claim). Absorbs dropped new case FD-WO-026. | VIU 2026-07-22 LIVE: whole-WO dialog opens from toolbar menu; title 'New Work Order Fee / Discount', subline 'Applying To: Entire Work Order', no scope dropdown. Ev: wo/FD-WO-001-wo-dialog.png, wo/wo-dialog-text.txt.</t>
+          <t>BE-enforced: tech templates GET/POST -&gt; 403; page FE-gated settingsFinance | WORDING+VIU 2026-07-13: Templates admin is back-end gated by Settings → Finance (Tech → 403), established batch-2. Nav corrected to Finance. NOTE: re-check the Tech negative after the roles matrix is re-derived (Technician drifted on shared qb). | SV-8456 (2026-07-21 staging LIVE VIU): F&amp;D moved to SETTINGS→SERVICE (below Canned Lines); template/WO/Part-sale/customer dialogs now show Taxable as a Yes/No DROPDOWN (was toggle); Auto-apply is a CHECKBOX with a 'When on…' caption; settings &amp; customer tables are plain-text/left-aligned (no badges); WO sidebar card retitled 'Work Order Fees &amp; Discounts' and renders ABOVE Financial Info; Part-sale card 'Parts Sale Fees &amp; Discounts' above Financial Info. Permission gate pivoted Settings→Finance → Settings→Service (verified live: Service-user sees+manages F&amp;D &amp; convenience toggle; Finance-only user has no F&amp;D nav item and /administration/adjustment-templates bounces to /workorders). Frontend-only; functionality + calc INTACT. | RE-VIU 2026-07-22 LIVE (Batch 4, SV-8456 re-verify): access-check quick-login {admin} HTTP 200. Re-confirmed on current staging build — 8 UI corrections intact (Taxable Yes/No dropdown; Auto-apply checkbox+caption; modal field order Type/CalcType&gt;Name&gt;Amount&gt;Taxable+jur.note&gt;Auto-apply&gt;Description; Settings table plain-text left-aligned no badges; F&amp;D nav under SERVICE below Canned Lines; WO &amp; Part-Sale cards above Financial Info [Batch 2/3]; Customer 'Fees &amp; Discounts' tab mirrors Settings styling minus convenience toggle) AND Settings-&gt;Service permission pivot CONFIRMED live per role (seeded ServiceRole vs FinanceRole, assigned to Tech, Tech restored to Technician 50bf6a0d + verified, both ZZAUTOTEST roles deleted 204): Service-user sees+manages F&amp;D nav + convenience toggle, direct /administration/adjustment-templates loads; Finance-only user has NO F&amp;D nav, FINANCE=Payment Methods only, direct route bounces to /workorders. viu_status VIU-Verified re-confirmed. Ev build/fees-discounts/viu-sv8456-2026-07-22/ (01-settings-landing, 02-new-dialog, 03-customer-fd-tab, SVC-*, FIN-*).</t>
         </is>
       </c>
     </row>
     <row r="150">
       <c r="A150" s="2" t="inlineStr">
         <is>
-          <t>FD-WO-002</t>
+          <t>FD-TMPL-017</t>
         </is>
       </c>
       <c r="B150" s="2" t="inlineStr">
         <is>
-          <t>C28425</t>
+          <t>C28518</t>
         </is>
       </c>
       <c r="C150" s="6" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/28425</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/28518</t>
         </is>
       </c>
       <c r="D150" s="2" t="inlineStr">
         <is>
-          <t>Work Order — Whole-WO Fee/Discount</t>
+          <t>Template admin — dialog fields</t>
         </is>
       </c>
       <c r="E150" s="2" t="inlineStr">
         <is>
-          <t>Verify adding a whole-work-order flat-amount fee saves and shows a success message</t>
+          <t>Verify the template Name is limited to 100 characters</t>
         </is>
       </c>
       <c r="F150" s="2" t="inlineStr">
         <is>
-          <t>Critical</t>
+          <t>Low</t>
         </is>
       </c>
       <c r="G150" s="2" t="inlineStr">
@@ -7703,39 +7703,39 @@
       </c>
       <c r="I150" s="2" t="inlineStr">
         <is>
-          <t>whole-WO flat fee add 201 + visible in WO view (flat 7.77 resolved exactly) | WORDING+VIU 2026-07-13: rewritten to exact build labels (⋮ menu item 'Add Fee/Discount'; dialog 'Add new fee/discount'; fields 'Apply From Template'/'Name'/'Type'/'Calculation Type'/'$ Amount' or 'Percent %'/'$ Max Amount (Optional)'/'Taxable' toggle; whole-WO Calculation Type options = Flat Amount, % of Labor Total, % of Parts Total, % of Subtotal; buttons 'Add Fee'/'Add Discount'; sidebar card 'WO Fees &amp; Discounts'; preview empty prompt 'Enter an amount to see the impact.'). Captured live on WO S3-15960 (shots wo-01..wo-05). Sidebar card is 'WO Fees &amp; Discounts' (was 'Work Order Fee / Discount'). Exact success-toast text not re-captured this pass (worded as 'a success message'). | SV-8456 (2026-07-21 staging LIVE VIU): F&amp;D moved to SETTINGS→SERVICE (below Canned Lines); template/WO/Part-sale/customer dialogs now show Taxable as a Yes/No DROPDOWN (was toggle); Auto-apply is a CHECKBOX with a 'When on…' caption; settings &amp; customer tables are plain-text/left-aligned (no badges); WO sidebar card retitled 'Work Order Fees &amp; Discounts' and renders ABOVE Financial Info; Part-sale card 'Parts Sale Fees &amp; Discounts' above Financial Info. Permission gate pivoted Settings→Finance → Settings→Service (verified live: Service-user sees+manages F&amp;D &amp; convenience toggle; Finance-only user has no F&amp;D nav item and /administration/adjustment-templates bounces to /workorders). Frontend-only; functionality + calc INTACT. | SV-8479/8480 deconfliction 2026-07-22: label sweep: navigation labels -&gt; 'Add Work Order Fee / Discount' / 'New Work Order Fee / Discount' (behavior/expected unchanged). | VIU 2026-07-22 LIVE: SV-8479 nav label 'Add Work Order Fee / Discount' confirmed present in the WO toolbar ⋯ menu; case behavior unchanged. Ev: wo/FD-WO-025-toolbar-menu.png. | RE-VIU 2026-07-22 LIVE (Batch 4, SV-8456 re-verify): access-check quick-login {admin} HTTP 200. Re-confirmed on current staging build — 8 UI corrections intact (Taxable Yes/No dropdown; Auto-apply checkbox+caption; modal field order Type/CalcType&gt;Name&gt;Amount&gt;Taxable+jur.note&gt;Auto-apply&gt;Description; Settings table plain-text left-aligned no badges; F&amp;D nav under SERVICE below Canned Lines; WO &amp; Part-Sale cards above Financial Info [Batch 2/3]; Customer 'Fees &amp; Discounts' tab mirrors Settings styling minus convenience toggle) AND Settings-&gt;Service permission pivot CONFIRMED live per role (seeded ServiceRole vs FinanceRole, assigned to Tech, Tech restored to Technician 50bf6a0d + verified, both ZZAUTOTEST roles deleted 204): Service-user sees+manages F&amp;D nav + convenience toggle, direct /administration/adjustment-templates loads; Finance-only user has NO F&amp;D nav, FINANCE=Payment Methods only, direct route bounces to /workorders. viu_status VIU-Verified re-confirmed. Ev build/fees-discounts/viu-sv8456-2026-07-22/ (01-settings-landing, 02-new-dialog, 03-customer-fd-tab, SVC-*, FIN-*).</t>
+          <t>name 100ch -&gt; 201; 101ch -&gt; 400 | WORDING+VIU 2026-07-13: Name 100-char limit carried.</t>
         </is>
       </c>
     </row>
     <row r="151">
       <c r="A151" s="2" t="inlineStr">
         <is>
-          <t>FD-WO-003</t>
+          <t>FD-TMPL-018</t>
         </is>
       </c>
       <c r="B151" s="2" t="inlineStr">
         <is>
-          <t>C28426</t>
+          <t>C29917</t>
         </is>
       </c>
       <c r="C151" s="6" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/28426</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/29917</t>
         </is>
       </c>
       <c r="D151" s="2" t="inlineStr">
         <is>
-          <t>Work Order — Whole-WO Fee/Discount</t>
+          <t>Template admin — jurisdiction note</t>
         </is>
       </c>
       <c r="E151" s="2" t="inlineStr">
         <is>
-          <t>Verify the live preview shows a whole-work-order percentage discount before you save</t>
+          <t>Verify the admin Fee/Discount template dialog shows the tax-jurisdiction note below the Taxable Yes/No dropdown (for every kind)</t>
         </is>
       </c>
       <c r="F151" s="2" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="G151" s="2" t="inlineStr">
@@ -7750,34 +7750,34 @@
       </c>
       <c r="I151" s="2" t="inlineStr">
         <is>
-          <t>dialog live preview re-driven ($5 flat -&gt; '+$5.00 / New work-order subtotal $187.76'); pct preview math not re-driven, API pct resolution re-proven (10%-&gt;17.08) | WORDING+VIU 2026-07-13: rewritten to exact build labels (⋮ menu item 'Add Fee/Discount'; dialog 'Add new fee/discount'; fields 'Apply From Template'/'Name'/'Type'/'Calculation Type'/'$ Amount' or 'Percent %'/'$ Max Amount (Optional)'/'Taxable' toggle; whole-WO Calculation Type options = Flat Amount, % of Labor Total, % of Parts Total, % of Subtotal; buttons 'Add Fee'/'Add Discount'; sidebar card 'WO Fees &amp; Discounts'; preview empty prompt 'Enter an amount to see the impact.'). Captured live on WO S3-15960 (shots wo-01..wo-05). Calc type corrected from generic 'Percentage' to the real whole-WO option '% of Subtotal'. Exact preview row labels not re-captured this pass (behavior verified 2026-07-10). | SV-8479/8480 deconfliction 2026-07-22: label sweep: navigation labels -&gt; 'Add Work Order Fee / Discount' / 'New Work Order Fee / Discount' (behavior/expected unchanged). | VIU 2026-07-22 LIVE: SV-8479 nav label 'Add Work Order Fee / Discount' confirmed present in the WO toolbar ⋯ menu; case behavior unchanged. Ev: wo/FD-WO-025-toolbar-menu.png.</t>
+          <t>administration/adjustment-templates loads; Finance-only user has NO F&amp;D nav, FINANCE=Payment Methods only, direct route bounces to /workorders. viu_status VIU-Verified re-confirmed. Ev build/fees-discounts/viu-sv8456-2026-07-22/ (01-settings-landing, 02-new-dialog, 03-customer-fd-tab, SVC-*, FIN-*).</t>
         </is>
       </c>
     </row>
     <row r="152">
       <c r="A152" s="2" t="inlineStr">
         <is>
-          <t>FD-WO-004</t>
+          <t>FD-VAL-001</t>
         </is>
       </c>
       <c r="B152" s="2" t="inlineStr">
         <is>
-          <t>C28427</t>
+          <t>C28599</t>
         </is>
       </c>
       <c r="C152" s="6" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/28427</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/28599</t>
         </is>
       </c>
       <c r="D152" s="2" t="inlineStr">
         <is>
-          <t>Work Order — Whole-WO Fee/Discount</t>
+          <t>Validation / Edge</t>
         </is>
       </c>
       <c r="E152" s="2" t="inlineStr">
         <is>
-          <t>Verify 'Apply From Template' fills the dialog with a template's values</t>
+          <t>Verify the Add button stays disabled until Name, Type, Calculation Type and an Amount above 0 are all set</t>
         </is>
       </c>
       <c r="F152" s="2" t="inlineStr">
@@ -7797,39 +7797,39 @@
       </c>
       <c r="I152" s="2" t="inlineStr">
         <is>
-          <t>not re-driven today (Apply-From-Template combobox present in dialog); templateId add path re-proven via API (FD-STACK-003) | WORDING+VIU 2026-07-13: rewritten to exact build labels (⋮ menu item 'Add Fee/Discount'; dialog 'Add new fee/discount'; fields 'Apply From Template'/'Name'/'Type'/'Calculation Type'/'$ Amount' or 'Percent %'/'$ Max Amount (Optional)'/'Taxable' toggle; whole-WO Calculation Type options = Flat Amount, % of Labor Total, % of Parts Total, % of Subtotal; buttons 'Add Fee'/'Add Discount'; sidebar card 'WO Fees &amp; Discounts'; preview empty prompt 'Enter an amount to see the impact.'). Captured live on WO S3-15960 (shots wo-01..wo-05). Dropdown label is exactly 'Apply From Template' (was 'Apply from template (optional)'). | SV-8479/8480 deconfliction 2026-07-22: label sweep: navigation labels -&gt; 'Add Work Order Fee / Discount' / 'New Work Order Fee / Discount' (behavior/expected unchanged). | VIU 2026-07-22 LIVE: SV-8479 nav label 'Add Work Order Fee / Discount' confirmed present in the WO toolbar ⋯ menu; case behavior unchanged. Ev: wo/FD-WO-025-toolbar-menu.png.</t>
+          <t>CONFIRMED AGAIN: Add button enabled on empty form (validates on submit) — PO Q4=B defect persists | WORDING+VIU 2026-07-13: DEVIATION re-confirmed 2026-07-13 (BUG-FD-4): the 'Add Fee' button is ENABLED on an empty form (validates on submit). Labels build-accurate (Add Fee/Add Discount, Calculation Type, Max Amount). | STAGING VIU 2026-07-20 staging LIVE VIU: BUG-FD-4 FIXED on staging: confirm button disabled until Name+Type+Calc+Amount&gt;0 set. Live-observed (dev-wo-emptyform + part-sale Add Fee disabled-until-valid). | SV-8479/8480 deconfliction 2026-07-22: label sweep: navigation labels -&gt; 'Add Work Order Fee / Discount' / 'New Work Order Fee / Discount' (behavior/expected unchanged). | VIU 2026-07-22 LIVE: SV-8479 nav label 'Add Work Order Fee / Discount' confirmed present in the WO toolbar ⋯ menu; case behavior unchanged. Ev: wo/FD-WO-025-toolbar-menu.png.</t>
         </is>
       </c>
     </row>
     <row r="153">
       <c r="A153" s="2" t="inlineStr">
         <is>
-          <t>FD-WO-005</t>
+          <t>FD-VAL-002</t>
         </is>
       </c>
       <c r="B153" s="2" t="inlineStr">
         <is>
-          <t>C28428</t>
+          <t>C28600</t>
         </is>
       </c>
       <c r="C153" s="6" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/28428</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/28600</t>
         </is>
       </c>
       <c r="D153" s="2" t="inlineStr">
         <is>
-          <t>Work Order — Whole-WO Fee/Discount</t>
+          <t>Validation / Edge</t>
         </is>
       </c>
       <c r="E153" s="2" t="inlineStr">
         <is>
-          <t>Verify the Add button stays disabled until Name, Type, Calculation Type and an Amount above 0 are all filled in</t>
+          <t>Verify a blank or 0 amount blocks saving, with an error</t>
         </is>
       </c>
       <c r="F153" s="2" t="inlineStr">
         <is>
-          <t>Critical</t>
+          <t>High</t>
         </is>
       </c>
       <c r="G153" s="2" t="inlineStr">
@@ -7844,34 +7844,34 @@
       </c>
       <c r="I153" s="2" t="inlineStr">
         <is>
-          <t>CONFIRMED AGAIN: 'Add Fee' button ENABLED on an empty form (disabled-on-empty=false) — PO Q4=B defect persists | WORDING+VIU 2026-07-13: rewritten to exact build labels (⋮ menu item 'Add Fee/Discount'; dialog 'Add new fee/discount'; fields 'Apply From Template'/'Name'/'Type'/'Calculation Type'/'$ Amount' or 'Percent %'/'$ Max Amount (Optional)'/'Taxable' toggle; whole-WO Calculation Type options = Flat Amount, % of Labor Total, % of Parts Total, % of Subtotal; buttons 'Add Fee'/'Add Discount'; sidebar card 'WO Fees &amp; Discounts'; preview empty prompt 'Enter an amount to see the impact.'). Captured live on WO S3-15960 (shots wo-01..wo-05). DEVIATION re-confirmed live 2026-07-13: the 'Add Fee' button is ENABLED on an empty form (validation happens on submit, not by disabling) — BUG-FD-4. Expected kept as the intended behavior; tester will see the button enabled. | STAGING VIU 2026-07-20 staging LIVE VIU: BUG-FD-4 FIXED on staging: Add Fee button is DISABLED on an empty form (was enabled on qb). Live-observed (dev-wo-emptyform, disabled=true). | SV-8479/8480 deconfliction 2026-07-22: label sweep: navigation labels -&gt; 'Add Work Order Fee / Discount' / 'New Work Order Fee / Discount' (behavior/expected unchanged). | VIU 2026-07-22 LIVE: SV-8479 nav label 'Add Work Order Fee / Discount' confirmed present in the WO toolbar ⋯ menu; case behavior unchanged. Ev: wo/FD-WO-025-toolbar-menu.png.</t>
+          <t>amount 0 -&gt; 400 (API); UI inline error on submit | WORDING+VIU 2026-07-13: Blank/0 amount blocked; carry prior VIU. Labels cleaned. | SV-8479/8480 deconfliction 2026-07-22: label sweep: navigation labels -&gt; 'Add Work Order Fee / Discount' / 'New Work Order Fee / Discount' (behavior/expected unchanged). | VIU 2026-07-22 LIVE: SV-8479 nav label 'Add Work Order Fee / Discount' confirmed present in the WO toolbar ⋯ menu; case behavior unchanged. Ev: wo/FD-WO-025-toolbar-menu.png.</t>
         </is>
       </c>
     </row>
     <row r="154">
       <c r="A154" s="2" t="inlineStr">
         <is>
-          <t>FD-WO-006</t>
+          <t>FD-VAL-003</t>
         </is>
       </c>
       <c r="B154" s="2" t="inlineStr">
         <is>
-          <t>C28429</t>
+          <t>C28601</t>
         </is>
       </c>
       <c r="C154" s="6" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/28429</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/28601</t>
         </is>
       </c>
       <c r="D154" s="2" t="inlineStr">
         <is>
-          <t>Work Order — Whole-WO Fee/Discount</t>
+          <t>Validation / Edge</t>
         </is>
       </c>
       <c r="E154" s="2" t="inlineStr">
         <is>
-          <t>Verify Max Amount caps a percentage fee (20% on a $100 base with Max Amount $15 → +$15.00)</t>
+          <t>Verify an empty Name blocks saving, with an error (Name required, up to 100 characters)</t>
         </is>
       </c>
       <c r="F154" s="2" t="inlineStr">
@@ -7891,39 +7891,39 @@
       </c>
       <c r="I154" s="2" t="inlineStr">
         <is>
-          <t>20% of 170.76 (=34.15) capped at Max 15 -&gt; resolved exactly 15 | WORDING+VIU 2026-07-13: rewritten to exact build labels (⋮ menu item 'Add Fee/Discount'; dialog 'Add new fee/discount'; fields 'Apply From Template'/'Name'/'Type'/'Calculation Type'/'$ Amount' or 'Percent %'/'$ Max Amount (Optional)'/'Taxable' toggle; whole-WO Calculation Type options = Flat Amount, % of Labor Total, % of Parts Total, % of Subtotal; buttons 'Add Fee'/'Add Discount'; sidebar card 'WO Fees &amp; Discounts'; preview empty prompt 'Enter an amount to see the impact.'). Captured live on WO S3-15960 (shots wo-01..wo-05). The '$ Max Amount (Optional)' field appears only after a percentage method is chosen (confirmed live). | SV-8479/8480 deconfliction 2026-07-22: label sweep: navigation labels -&gt; 'Add Work Order Fee / Discount' / 'New Work Order Fee / Discount' (behavior/expected unchanged). | VIU 2026-07-22 LIVE: SV-8479 nav label 'Add Work Order Fee / Discount' confirmed present in the WO toolbar ⋯ menu; case behavior unchanged. Ev: wo/FD-WO-025-toolbar-menu.png.</t>
+          <t>UI blocks empty name (inline required error). NEW FDBUG-16: raw API now ACCEPTS empty-name adds (201; regression vs batch-3 400) — FE-only guard; name 101ch -&gt; 400, 100ch -&gt; 201 | WORDING+VIU 2026-07-13: Empty name blocked in UI; 100-char limit. (Raw back-end accepts empty name — FDBUG-16 — but the dialog blocks it.) | SV-8479/8480 deconfliction 2026-07-22: label sweep: navigation labels -&gt; 'Add Work Order Fee / Discount' / 'New Work Order Fee / Discount' (behavior/expected unchanged). | VIU 2026-07-22 LIVE: SV-8479 nav label 'Add Work Order Fee / Discount' confirmed present in the WO toolbar ⋯ menu; case behavior unchanged. Ev: wo/FD-WO-025-toolbar-menu.png.</t>
         </is>
       </c>
     </row>
     <row r="155">
       <c r="A155" s="2" t="inlineStr">
         <is>
-          <t>FD-WO-007</t>
+          <t>FD-VAL-004</t>
         </is>
       </c>
       <c r="B155" s="2" t="inlineStr">
         <is>
-          <t>C28430</t>
+          <t>C28602</t>
         </is>
       </c>
       <c r="C155" s="6" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/28430</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/28602</t>
         </is>
       </c>
       <c r="D155" s="2" t="inlineStr">
         <is>
-          <t>Work Order — Whole-WO Fee/Discount</t>
+          <t>Validation / Edge</t>
         </is>
       </c>
       <c r="E155" s="2" t="inlineStr">
         <is>
-          <t>Verify the confirm button label follows the Type (Add Fee vs Add Discount)</t>
+          <t>Verify a percentage discount over 100% is invalid while a percentage fee has no upper cap</t>
         </is>
       </c>
       <c r="F155" s="2" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>High</t>
         </is>
       </c>
       <c r="G155" s="2" t="inlineStr">
@@ -7938,34 +7938,34 @@
       </c>
       <c r="I155" s="2" t="inlineStr">
         <is>
-          <t>confirm label 'Add Fee' observed; Type-flip re-observed in batch-1 (not re-driven) | WORDING+VIU 2026-07-13: rewritten to exact build labels (⋮ menu item 'Add Fee/Discount'; dialog 'Add new fee/discount'; fields 'Apply From Template'/'Name'/'Type'/'Calculation Type'/'$ Amount' or 'Percent %'/'$ Max Amount (Optional)'/'Taxable' toggle; whole-WO Calculation Type options = Flat Amount, % of Labor Total, % of Parts Total, % of Subtotal; buttons 'Add Fee'/'Add Discount'; sidebar card 'WO Fees &amp; Discounts'; preview empty prompt 'Enter an amount to see the impact.'). Captured live on WO S3-15960 (shots wo-01..wo-05). | SV-8479/8480 deconfliction 2026-07-22: label sweep: navigation labels -&gt; 'Add Work Order Fee / Discount' / 'New Work Order Fee / Discount' (behavior/expected unchanged). | VIU 2026-07-22 LIVE: SV-8479 nav label 'Add Work Order Fee / Discount' confirmed present in the WO toolbar ⋯ menu; case behavior unchanged. Ev: wo/FD-WO-025-toolbar-menu.png.</t>
+          <t>discount &gt;100% invalid (400), fee uncapped (201) | WORDING+VIU 2026-07-13: %&gt;100 discount invalid, fee uncapped; carry prior VIU. Labels cleaned. | SV-8479/8480 deconfliction 2026-07-22: label sweep: navigation labels -&gt; 'Add Work Order Fee / Discount' / 'New Work Order Fee / Discount' (behavior/expected unchanged). | VIU 2026-07-22 LIVE: SV-8479 nav label 'Add Work Order Fee / Discount' confirmed present in the WO toolbar ⋯ menu; case behavior unchanged. Ev: wo/FD-WO-025-toolbar-menu.png.</t>
         </is>
       </c>
     </row>
     <row r="156">
       <c r="A156" s="2" t="inlineStr">
         <is>
-          <t>FD-WO-008</t>
+          <t>FD-VAL-005</t>
         </is>
       </c>
       <c r="B156" s="2" t="inlineStr">
         <is>
-          <t>C28431</t>
+          <t>C28603</t>
         </is>
       </c>
       <c r="C156" s="6" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/28431</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/28603</t>
         </is>
       </c>
       <c r="D156" s="2" t="inlineStr">
         <is>
-          <t>Work Order — Whole-WO Fee/Discount</t>
+          <t>Validation / Edge</t>
         </is>
       </c>
       <c r="E156" s="2" t="inlineStr">
         <is>
-          <t>Verify an empty Name blocks saving a whole-work-order fee/discount</t>
+          <t>Verify negative amounts are rejected (values must be above 0)</t>
         </is>
       </c>
       <c r="F156" s="2" t="inlineStr">
@@ -7985,34 +7985,34 @@
       </c>
       <c r="I156" s="2" t="inlineStr">
         <is>
-          <t>UI BLOCKS empty name (inline 'Name' required, dialog stays open, nothing saved). NOTE NEW FDBUG-16: the RAW API now ACCEPTS an empty-name adjustment (201; was 400 in batch-3) — BE validation regression, FE still guards | WORDING+VIU 2026-07-13: rewritten to exact build labels (⋮ menu item 'Add Fee/Discount'; dialog 'Add new fee/discount'; fields 'Apply From Template'/'Name'/'Type'/'Calculation Type'/'$ Amount' or 'Percent %'/'$ Max Amount (Optional)'/'Taxable' toggle; whole-WO Calculation Type options = Flat Amount, % of Labor Total, % of Parts Total, % of Subtotal; buttons 'Add Fee'/'Add Discount'; sidebar card 'WO Fees &amp; Discounts'; preview empty prompt 'Enter an amount to see the impact.'). Captured live on WO S3-15960 (shots wo-01..wo-05). (Note: the raw back-end will accept an empty name — FDBUG-16 — but the on-screen dialog blocks it, which is what a manual tester sees.) | SV-8479/8480 deconfliction 2026-07-22: label sweep: navigation labels -&gt; 'Add Work Order Fee / Discount' / 'New Work Order Fee / Discount' (behavior/expected unchanged). | VIU 2026-07-22 LIVE: SV-8479 nav label 'Add Work Order Fee / Discount' confirmed present in the WO toolbar ⋯ menu; case behavior unchanged. Ev: wo/FD-WO-025-toolbar-menu.png.</t>
+          <t>negative amount -&gt; 400 | WORDING+VIU 2026-07-13: Negatives rejected; carry prior VIU. | SV-8479/8480 deconfliction 2026-07-22: label sweep: navigation labels -&gt; 'Add Work Order Fee / Discount' / 'New Work Order Fee / Discount' (behavior/expected unchanged). | VIU 2026-07-22 LIVE: SV-8479 nav label 'Add Work Order Fee / Discount' confirmed present in the WO toolbar ⋯ menu; case behavior unchanged. Ev: wo/FD-WO-025-toolbar-menu.png.</t>
         </is>
       </c>
     </row>
     <row r="157">
       <c r="A157" s="2" t="inlineStr">
         <is>
-          <t>FD-WO-009</t>
+          <t>FD-VAL-006</t>
         </is>
       </c>
       <c r="B157" s="2" t="inlineStr">
         <is>
-          <t>C28432</t>
+          <t>C28604</t>
         </is>
       </c>
       <c r="C157" s="6" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/28432</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/28604</t>
         </is>
       </c>
       <c r="D157" s="2" t="inlineStr">
         <is>
-          <t>Work Order — Whole-WO Fee/Discount</t>
+          <t>Validation / Edge</t>
         </is>
       </c>
       <c r="E157" s="2" t="inlineStr">
         <is>
-          <t>Verify an empty or zero amount blocks saving a whole-work-order fee/discount</t>
+          <t>Verify the Max Amount field shows only for percentage methods and how 0 or empty behaves</t>
         </is>
       </c>
       <c r="F157" s="2" t="inlineStr">
@@ -8032,34 +8032,34 @@
       </c>
       <c r="I157" s="2" t="inlineStr">
         <is>
-          <t>amount 0 -&gt; 400 at API; UI validates on submit | WORDING+VIU 2026-07-13: rewritten to exact build labels (⋮ menu item 'Add Fee/Discount'; dialog 'Add new fee/discount'; fields 'Apply From Template'/'Name'/'Type'/'Calculation Type'/'$ Amount' or 'Percent %'/'$ Max Amount (Optional)'/'Taxable' toggle; whole-WO Calculation Type options = Flat Amount, % of Labor Total, % of Parts Total, % of Subtotal; buttons 'Add Fee'/'Add Discount'; sidebar card 'WO Fees &amp; Discounts'; preview empty prompt 'Enter an amount to see the impact.'). Captured live on WO S3-15960 (shots wo-01..wo-05). | SV-8479/8480 deconfliction 2026-07-22: label sweep: navigation labels -&gt; 'Add Work Order Fee / Discount' / 'New Work Order Fee / Discount' (behavior/expected unchanged). | VIU 2026-07-22 LIVE: SV-8479 nav label 'Add Work Order Fee / Discount' confirmed present in the WO toolbar ⋯ menu; case behavior unchanged. Ev: wo/FD-WO-025-toolbar-menu.png.</t>
+          <t>FDBUG-9: maxCap 0 behaves as NO cap (not 'no maximum' spec reading matches build for empty, but 0 disagrees w/ §5-R6 $0-forces-$0) — persists | WORDING+VIU 2026-07-13: Confirmed live: '$ Max Amount (Optional)' appears only for percentage methods (hidden for Flat Amount, shots wo-03/wo-05). DEVIATION (FDBUG-9 / PO Q2 pending): whether a Max Amount of 0 means 'no cap' or 'cap at $0.00' is a pending product decision — expected kept as current build behavior. | CHRIS WARD ROUND-2 ANSWER APPLIED 2026-07-14(Q2=A): PO ruled a typed 0 in Max Amount = 'no limit' (WAD, S2-R25). 0-handling no longer a deviation; FDBUG-9 closed as accepted; jira draft TICKET 4 DROPPED. Expected reworded to affirm 0=no-cap. PUSHED TO TESTRAIL 2026-07-14 via update_case (QA-lead one-day authorization; update 200 / re-verify 200 MATCH; audit: testrail-round2-push-log.md). | SV-8479/8480 deconfliction 2026-07-22: label sweep: navigation labels -&gt; 'Add Work Order Fee / Discount' / 'New Work Order Fee / Discount' (behavior/expected unchanged). | VIU 2026-07-22 LIVE: SV-8479 nav label 'Add Work Order Fee / Discount' confirmed present in the WO toolbar ⋯ menu; case behavior unchanged. Ev: wo/FD-WO-025-toolbar-menu.png.</t>
         </is>
       </c>
     </row>
     <row r="158">
       <c r="A158" s="2" t="inlineStr">
         <is>
-          <t>FD-WO-010</t>
+          <t>FD-VAL-007</t>
         </is>
       </c>
       <c r="B158" s="2" t="inlineStr">
         <is>
-          <t>C28433</t>
+          <t>C28605</t>
         </is>
       </c>
       <c r="C158" s="6" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/28433</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/28605</t>
         </is>
       </c>
       <c r="D158" s="2" t="inlineStr">
         <is>
-          <t>Work Order — Whole-WO Fee/Discount</t>
+          <t>Validation / Edge</t>
         </is>
       </c>
       <c r="E158" s="2" t="inlineStr">
         <is>
-          <t>Verify a percentage discount over 100% is rejected while a percentage fee has no upper limit</t>
+          <t>Verify a template that is both auto-apply at the location and a customer default is added only ONCE to a new work order</t>
         </is>
       </c>
       <c r="F158" s="2" t="inlineStr">
@@ -8079,24 +8079,24 @@
       </c>
       <c r="I158" s="2" t="inlineStr">
         <is>
-          <t>discount 150% -&gt; 400 'A percentage discount cannot exceed 100%.'; fee 150% -&gt; 201 | WORDING+VIU 2026-07-13: rewritten to exact build labels (⋮ menu item 'Add Fee/Discount'; dialog 'Add new fee/discount'; fields 'Apply From Template'/'Name'/'Type'/'Calculation Type'/'$ Amount' or 'Percent %'/'$ Max Amount (Optional)'/'Taxable' toggle; whole-WO Calculation Type options = Flat Amount, % of Labor Total, % of Parts Total, % of Subtotal; buttons 'Add Fee'/'Add Discount'; sidebar card 'WO Fees &amp; Discounts'; preview empty prompt 'Enter an amount to see the impact.'). Captured live on WO S3-15960 (shots wo-01..wo-05). | SV-8479/8480 deconfliction 2026-07-22: label sweep: navigation labels -&gt; 'Add Work Order Fee / Discount' / 'New Work Order Fee / Discount' (behavior/expected unchanged). | VIU 2026-07-22 LIVE: SV-8479 nav label 'Add Work Order Fee / Discount' confirmed present in the WO toolbar ⋯ menu; case behavior unchanged. Ev: wo/FD-WO-025-toolbar-menu.png.</t>
+          <t>auto+default template -&gt; exactly ONE adjustment on the new WO | WORDING+VIU 2026-07-13: Double-add does not stack (one adjustment); carry prior VIU. | SV-8456 (2026-07-21 staging LIVE VIU): F&amp;D moved to SETTINGS→SERVICE (below Canned Lines); template/WO/Part-sale/customer dialogs now show Taxable as a Yes/No DROPDOWN (was toggle); Auto-apply is a CHECKBOX with a 'When on…' caption; settings &amp; customer tables are plain-text/left-aligned (no badges); WO sidebar card retitled 'Work Order Fees &amp; Discounts' and renders ABOVE Financial Info; Part-sale card 'Parts Sale Fees &amp; Discounts' above Financial Info. Permission gate pivoted Settings→Finance → Settings→Service (verified live: Service-user sees+manages F&amp;D &amp; convenience toggle; Finance-only user has no F&amp;D nav item and /administration/adjustment-templates bounces to /workorders). Frontend-only; functionality + calc INTACT. | RE-VIU 2026-07-22 LIVE (Batch 4, SV-8456 re-verify): access-check quick-login {admin} HTTP 200. Re-confirmed on current staging build — 8 UI corrections intact (Taxable Yes/No dropdown; Auto-apply checkbox+caption; modal field order Type/CalcType&gt;Name&gt;Amount&gt;Taxable+jur.note&gt;Auto-apply&gt;Description; Settings table plain-text left-aligned no badges; F&amp;D nav under SERVICE below Canned Lines; WO &amp; Part-Sale cards above Financial Info [Batch 2/3]; Customer 'Fees &amp; Discounts' tab mirrors Settings styling minus convenience toggle) AND Settings-&gt;Service permission pivot CONFIRMED live per role (seeded ServiceRole vs FinanceRole, assigned to Tech, Tech restored to Technician 50bf6a0d + verified, both ZZAUTOTEST roles deleted 204): Service-user sees+manages F&amp;D nav + convenience toggle, direct /administration/adjustment-templates loads; Finance-only user has NO F&amp;D nav, FINANCE=Payment Methods only, direct route bounces to /workorders. viu_status VIU-Verified re-confirmed. Ev build/fees-discounts/viu-sv8456-2026-07-22/ (01-settings-landing, 02-new-dialog, 03-customer-fd-tab, SVC-*, FIN-*).</t>
         </is>
       </c>
     </row>
     <row r="159">
       <c r="A159" s="2" t="inlineStr">
         <is>
-          <t>FD-WO-011</t>
+          <t>FD-WO-001</t>
         </is>
       </c>
       <c r="B159" s="2" t="inlineStr">
         <is>
-          <t>C28434</t>
+          <t>C28424</t>
         </is>
       </c>
       <c r="C159" s="6" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/28434</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/28424</t>
         </is>
       </c>
       <c r="D159" s="2" t="inlineStr">
@@ -8106,12 +8106,12 @@
       </c>
       <c r="E159" s="2" t="inlineStr">
         <is>
-          <t>Verify a whole-work-order percentage method uses the correct base (% of Subtotal example)</t>
+          <t>Verify the whole-work-order fee/discount dialog opens from the toolbar menu with title 'New Work Order Fee / Discount'</t>
         </is>
       </c>
       <c r="F159" s="2" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Critical</t>
         </is>
       </c>
       <c r="G159" s="2" t="inlineStr">
@@ -8126,24 +8126,24 @@
       </c>
       <c r="I159" s="2" t="inlineStr">
         <is>
-          <t>pct_subtotal resolves on the WO subtotal EXCLUDING whole-WO adjustments (10% of 182.76-sub -&gt; 17.08 = 10% of 170.76 line total) | WORDING+VIU 2026-07-13: rewritten to exact build labels (⋮ menu item 'Add Fee/Discount'; dialog 'Add new fee/discount'; fields 'Apply From Template'/'Name'/'Type'/'Calculation Type'/'$ Amount' or 'Percent %'/'$ Max Amount (Optional)'/'Taxable' toggle; whole-WO Calculation Type options = Flat Amount, % of Labor Total, % of Parts Total, % of Subtotal; buttons 'Add Fee'/'Add Discount'; sidebar card 'WO Fees &amp; Discounts'; preview empty prompt 'Enter an amount to see the impact.'). Captured live on WO S3-15960 (shots wo-01..wo-05). Calculation Type options confirmed live (exactly the 4 listed; no '% of Grand Total'). | SV-8479/8480 deconfliction 2026-07-22: label sweep: navigation labels -&gt; 'Add Work Order Fee / Discount' / 'New Work Order Fee / Discount' (behavior/expected unchanged). | VIU 2026-07-22 LIVE: SV-8479 nav label 'Add Work Order Fee / Discount' confirmed present in the WO toolbar ⋯ menu; case behavior unchanged. Ev: wo/FD-WO-025-toolbar-menu.png.</t>
+          <t>dialog title still 'Add new fee/discount' (spec 'New Fee / Discount'), menu item 'Add Fee/Discount' — label drift persists (UI re-driven, shot 10-wo-add-dialog) | WORDING+VIU 2026-07-13: rewritten to exact build labels (⋮ menu item 'Add Fee/Discount'; dialog 'Add new fee/discount'; fields 'Apply From Template'/'Name'/'Type'/'Calculation Type'/'$ Amount' or 'Percent %'/'$ Max Amount (Optional)'/'Taxable' toggle; whole-WO Calculation Type options = Flat Amount, % of Labor Total, % of Parts Total, % of Subtotal; buttons 'Add Fee'/'Add Discount'; sidebar card 'WO Fees &amp; Discounts'; preview empty prompt 'Enter an amount to see the impact.'). Captured live on WO S3-15960 (shots wo-01..wo-05). Now build-accurate (was VIU-Deviation only because the case used the older spec wording). Dialog shows no work-order-number subtitle in this build (old expected claim dropped). | SV-8479/8480 deconfliction 2026-07-22: menu item 'Add Fee/Discount' -&gt; 'Add Work Order Fee / Discount' (item 10); title 'Add new fee/discount' -&gt; 'New Work Order Fee / Discount' + new subline 'Applying To: Entire Work Order' (item 11, reverses the old 'no Applying-to line' claim). Absorbs dropped new case FD-WO-026. | VIU 2026-07-22 LIVE: whole-WO dialog opens from toolbar menu; title 'New Work Order Fee / Discount', subline 'Applying To: Entire Work Order', no scope dropdown. Ev: wo/FD-WO-001-wo-dialog.png, wo/wo-dialog-text.txt.</t>
         </is>
       </c>
     </row>
     <row r="160">
       <c r="A160" s="2" t="inlineStr">
         <is>
-          <t>FD-WO-012</t>
+          <t>FD-WO-002</t>
         </is>
       </c>
       <c r="B160" s="2" t="inlineStr">
         <is>
-          <t>C28435</t>
+          <t>C28425</t>
         </is>
       </c>
       <c r="C160" s="6" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/28435</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/28425</t>
         </is>
       </c>
       <c r="D160" s="2" t="inlineStr">
@@ -8153,12 +8153,12 @@
       </c>
       <c r="E160" s="2" t="inlineStr">
         <is>
-          <t>Verify Add Work Order Fee / Discount is hidden and blocked on an Invoiced or Paid work order</t>
+          <t>Verify adding a whole-work-order flat-amount fee saves and shows a success message</t>
         </is>
       </c>
       <c r="F160" s="2" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Critical</t>
         </is>
       </c>
       <c r="G160" s="2" t="inlineStr">
@@ -8173,24 +8173,24 @@
       </c>
       <c r="I160" s="2" t="inlineStr">
         <is>
-          <t>add on Invoiced WO -&gt; 409 'Adjustments cannot be changed on an invoiced or paid work order.'; edit also 409 | WORDING+VIU 2026-07-13: rewritten to exact build labels (⋮ menu item 'Add Fee/Discount'; dialog 'Add new fee/discount'; fields 'Apply From Template'/'Name'/'Type'/'Calculation Type'/'$ Amount' or 'Percent %'/'$ Max Amount (Optional)'/'Taxable' toggle; whole-WO Calculation Type options = Flat Amount, % of Labor Total, % of Parts Total, % of Subtotal; buttons 'Add Fee'/'Add Discount'; sidebar card 'WO Fees &amp; Discounts'; preview empty prompt 'Enter an amount to see the impact.'). Captured live on WO S3-15960 (shots wo-01..wo-05). | SV-8479/8480 deconfliction 2026-07-22: label sweep: navigation labels -&gt; 'Add Work Order Fee / Discount' / 'New Work Order Fee / Discount' (behavior/expected unchanged). | VIU 2026-07-22 LIVE: SV-8479 nav label 'Add Work Order Fee / Discount' confirmed present in the WO toolbar ⋯ menu; case behavior unchanged. Ev: wo/FD-WO-025-toolbar-menu.png.</t>
+          <t>whole-WO flat fee add 201 + visible in WO view (flat 7.77 resolved exactly) | WORDING+VIU 2026-07-13: rewritten to exact build labels (⋮ menu item 'Add Fee/Discount'; dialog 'Add new fee/discount'; fields 'Apply From Template'/'Name'/'Type'/'Calculation Type'/'$ Amount' or 'Percent %'/'$ Max Amount (Optional)'/'Taxable' toggle; whole-WO Calculation Type options = Flat Amount, % of Labor Total, % of Parts Total, % of Subtotal; buttons 'Add Fee'/'Add Discount'; sidebar card 'WO Fees &amp; Discounts'; preview empty prompt 'Enter an amount to see the impact.'). Captured live on WO S3-15960 (shots wo-01..wo-05). Sidebar card is 'WO Fees &amp; Discounts' (was 'Work Order Fee / Discount'). Exact success-toast text not re-captured this pass (worded as 'a success message'). | SV-8456 (2026-07-21 staging LIVE VIU): F&amp;D moved to SETTINGS→SERVICE (below Canned Lines); template/WO/Part-sale/customer dialogs now show Taxable as a Yes/No DROPDOWN (was toggle); Auto-apply is a CHECKBOX with a 'When on…' caption; settings &amp; customer tables are plain-text/left-aligned (no badges); WO sidebar card retitled 'Work Order Fees &amp; Discounts' and renders ABOVE Financial Info; Part-sale card 'Parts Sale Fees &amp; Discounts' above Financial Info. Permission gate pivoted Settings→Finance → Settings→Service (verified live: Service-user sees+manages F&amp;D &amp; convenience toggle; Finance-only user has no F&amp;D nav item and /administration/adjustment-templates bounces to /workorders). Frontend-only; functionality + calc INTACT. | SV-8479/8480 deconfliction 2026-07-22: label sweep: navigation labels -&gt; 'Add Work Order Fee / Discount' / 'New Work Order Fee / Discount' (behavior/expected unchanged). | VIU 2026-07-22 LIVE: SV-8479 nav label 'Add Work Order Fee / Discount' confirmed present in the WO toolbar ⋯ menu; case behavior unchanged. Ev: wo/FD-WO-025-toolbar-menu.png. | RE-VIU 2026-07-22 LIVE (Batch 4, SV-8456 re-verify): access-check quick-login {admin} HTTP 200. Re-confirmed on current staging build — 8 UI corrections intact (Taxable Yes/No dropdown; Auto-apply checkbox+caption; modal field order Type/CalcType&gt;Name&gt;Amount&gt;Taxable+jur.note&gt;Auto-apply&gt;Description; Settings table plain-text left-aligned no badges; F&amp;D nav under SERVICE below Canned Lines; WO &amp; Part-Sale cards above Financial Info [Batch 2/3]; Customer 'Fees &amp; Discounts' tab mirrors Settings styling minus convenience toggle) AND Settings-&gt;Service permission pivot CONFIRMED live per role (seeded ServiceRole vs FinanceRole, assigned to Tech, Tech restored to Technician 50bf6a0d + verified, both ZZAUTOTEST roles deleted 204): Service-user sees+manages F&amp;D nav + convenience toggle, direct /administration/adjustment-templates loads; Finance-only user has NO F&amp;D nav, FINANCE=Payment Methods only, direct route bounces to /workorders. viu_status VIU-Verified re-confirmed. Ev build/fees-discounts/viu-sv8456-2026-07-22/ (01-settings-landing, 02-new-dialog, 03-customer-fd-tab, SVC-*, FIN-*).</t>
         </is>
       </c>
     </row>
     <row r="161">
       <c r="A161" s="2" t="inlineStr">
         <is>
-          <t>FD-WO-013</t>
+          <t>FD-WO-003</t>
         </is>
       </c>
       <c r="B161" s="2" t="inlineStr">
         <is>
-          <t>C28436</t>
+          <t>C28426</t>
         </is>
       </c>
       <c r="C161" s="6" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/28436</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/28426</t>
         </is>
       </c>
       <c r="D161" s="2" t="inlineStr">
@@ -8200,12 +8200,12 @@
       </c>
       <c r="E161" s="2" t="inlineStr">
         <is>
-          <t>Verify the whole-work-order 'Add Work Order Fee / Discount' option is hidden without Work Orders: Create &amp; Edit</t>
+          <t>Verify the live preview shows a whole-work-order percentage discount before you save</t>
         </is>
       </c>
       <c r="F161" s="2" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>High</t>
         </is>
       </c>
       <c r="G161" s="2" t="inlineStr">
@@ -8220,24 +8220,24 @@
       </c>
       <c r="I161" s="2" t="inlineStr">
         <is>
-          <t>BUG-FD-3 stands on prior evidence; NOT re-testable today: the shared-env Technician role was CHANGED (now includes workOrdersCreateAndEdit+workOrdersDelete, 8 perms vs matrix 6) so tech's 201 is now legitimate; no login lacking the perm exists | WORDING+VIU 2026-07-13: rewritten to exact build labels (⋮ menu item 'Add Fee/Discount'; dialog 'Add new fee/discount'; fields 'Apply From Template'/'Name'/'Type'/'Calculation Type'/'$ Amount' or 'Percent %'/'$ Max Amount (Optional)'/'Taxable' toggle; whole-WO Calculation Type options = Flat Amount, % of Labor Total, % of Parts Total, % of Subtotal; buttons 'Add Fee'/'Add Discount'; sidebar card 'WO Fees &amp; Discounts'; preview empty prompt 'Enter an amount to see the impact.'). Captured live on WO S3-15960 (shots wo-01..wo-05). DEVIATION (BUG-FD-3: the hide is front-end only; the back-end does not block the write). NOT re-testable this run — the Technician role has drifted on the shared qb env; re-derive the roles matrix before re-checking. | SV-8479/8480 deconfliction 2026-07-22: label updated 'Add Fee/Discount' -&gt; 'Add Work Order Fee / Discount' (item 10); permission behavior unchanged. | VIU 2026-07-22 LIVE: toolbar label 'Add Work Order Fee / Discount' confirmed present (admin); permission-negative status unchanged — role-negative not re-driven this UI batch. | FE-BLOCK/BE-ALLOW PASS 2026-07-24 (user-authorized, Standing Rule 24): flipped VIU-Deviation -&gt; VIU-Verified (PASS). The whole-WO 'Add Work Order Fee / Discount' control being hidden for a role lacking Work Orders: Create &amp; Edit IS the tester-facing pass criterion; the FE-only enforcement (the back-end/API POST /api/work-orders/adjustments/add still returns 201 for such a role — pass-A evidence + impersonation) is ACCEPTED by product policy, not a bug. Added the plain tester line to Expected (Rule 7). This is FE-block/BE-allow = PASS (not the inverse FE-exposure defect).</t>
+          <t>dialog live preview re-driven ($5 flat -&gt; '+$5.00 / New work-order subtotal $187.76'); pct preview math not re-driven, API pct resolution re-proven (10%-&gt;17.08) | WORDING+VIU 2026-07-13: rewritten to exact build labels (⋮ menu item 'Add Fee/Discount'; dialog 'Add new fee/discount'; fields 'Apply From Template'/'Name'/'Type'/'Calculation Type'/'$ Amount' or 'Percent %'/'$ Max Amount (Optional)'/'Taxable' toggle; whole-WO Calculation Type options = Flat Amount, % of Labor Total, % of Parts Total, % of Subtotal; buttons 'Add Fee'/'Add Discount'; sidebar card 'WO Fees &amp; Discounts'; preview empty prompt 'Enter an amount to see the impact.'). Captured live on WO S3-15960 (shots wo-01..wo-05). Calc type corrected from generic 'Percentage' to the real whole-WO option '% of Subtotal'. Exact preview row labels not re-captured this pass (behavior verified 2026-07-10). | SV-8479/8480 deconfliction 2026-07-22: label sweep: navigation labels -&gt; 'Add Work Order Fee / Discount' / 'New Work Order Fee / Discount' (behavior/expected unchanged). | VIU 2026-07-22 LIVE: SV-8479 nav label 'Add Work Order Fee / Discount' confirmed present in the WO toolbar ⋯ menu; case behavior unchanged. Ev: wo/FD-WO-025-toolbar-menu.png.</t>
         </is>
       </c>
     </row>
     <row r="162">
       <c r="A162" s="2" t="inlineStr">
         <is>
-          <t>FD-WO-014</t>
+          <t>FD-WO-004</t>
         </is>
       </c>
       <c r="B162" s="2" t="inlineStr">
         <is>
-          <t>C28437</t>
+          <t>C28427</t>
         </is>
       </c>
       <c r="C162" s="6" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/28437</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/28427</t>
         </is>
       </c>
       <c r="D162" s="2" t="inlineStr">
@@ -8247,12 +8247,12 @@
       </c>
       <c r="E162" s="2" t="inlineStr">
         <is>
-          <t>Verify the preview shows the empty-amount prompt before an amount is entered</t>
+          <t>Verify 'Apply From Template' fills the dialog with a template's values</t>
         </is>
       </c>
       <c r="F162" s="2" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>High</t>
         </is>
       </c>
       <c r="G162" s="2" t="inlineStr">
@@ -8267,24 +8267,24 @@
       </c>
       <c r="I162" s="2" t="inlineStr">
         <is>
-          <t>'Enter an amount to see the impact.' prompt present in the re-driven dialog | WORDING+VIU 2026-07-13: rewritten to exact build labels (⋮ menu item 'Add Fee/Discount'; dialog 'Add new fee/discount'; fields 'Apply From Template'/'Name'/'Type'/'Calculation Type'/'$ Amount' or 'Percent %'/'$ Max Amount (Optional)'/'Taxable' toggle; whole-WO Calculation Type options = Flat Amount, % of Labor Total, % of Parts Total, % of Subtotal; buttons 'Add Fee'/'Add Discount'; sidebar card 'WO Fees &amp; Discounts'; preview empty prompt 'Enter an amount to see the impact.'). Captured live on WO S3-15960 (shots wo-01..wo-05). Exact prompt text 'Enter an amount to see the impact.' confirmed live (shot wo-03). | SV-8479/8480 deconfliction 2026-07-22: label sweep: navigation labels -&gt; 'Add Work Order Fee / Discount' / 'New Work Order Fee / Discount' (behavior/expected unchanged). | VIU 2026-07-22 LIVE: SV-8479 nav label 'Add Work Order Fee / Discount' confirmed present in the WO toolbar ⋯ menu; case behavior unchanged. Ev: wo/FD-WO-025-toolbar-menu.png.</t>
+          <t>not re-driven today (Apply-From-Template combobox present in dialog); templateId add path re-proven via API (FD-STACK-003) | WORDING+VIU 2026-07-13: rewritten to exact build labels (⋮ menu item 'Add Fee/Discount'; dialog 'Add new fee/discount'; fields 'Apply From Template'/'Name'/'Type'/'Calculation Type'/'$ Amount' or 'Percent %'/'$ Max Amount (Optional)'/'Taxable' toggle; whole-WO Calculation Type options = Flat Amount, % of Labor Total, % of Parts Total, % of Subtotal; buttons 'Add Fee'/'Add Discount'; sidebar card 'WO Fees &amp; Discounts'; preview empty prompt 'Enter an amount to see the impact.'). Captured live on WO S3-15960 (shots wo-01..wo-05). Dropdown label is exactly 'Apply From Template' (was 'Apply from template (optional)'). | SV-8479/8480 deconfliction 2026-07-22: label sweep: navigation labels -&gt; 'Add Work Order Fee / Discount' / 'New Work Order Fee / Discount' (behavior/expected unchanged). | VIU 2026-07-22 LIVE: SV-8479 nav label 'Add Work Order Fee / Discount' confirmed present in the WO toolbar ⋯ menu; case behavior unchanged. Ev: wo/FD-WO-025-toolbar-menu.png.</t>
         </is>
       </c>
     </row>
     <row r="163">
       <c r="A163" s="2" t="inlineStr">
         <is>
-          <t>FD-WO-015</t>
+          <t>FD-WO-005</t>
         </is>
       </c>
       <c r="B163" s="2" t="inlineStr">
         <is>
-          <t>C28438</t>
+          <t>C28428</t>
         </is>
       </c>
       <c r="C163" s="6" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/28438</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/28428</t>
         </is>
       </c>
       <c r="D163" s="2" t="inlineStr">
@@ -8294,12 +8294,12 @@
       </c>
       <c r="E163" s="2" t="inlineStr">
         <is>
-          <t>Verify the preview amount is signed for a fee (+) vs a discount (−)</t>
+          <t>Verify the Add button stays disabled until Name, Type, Calculation Type and an Amount above 0 are all filled in</t>
         </is>
       </c>
       <c r="F163" s="2" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>Critical</t>
         </is>
       </c>
       <c r="G163" s="2" t="inlineStr">
@@ -8314,24 +8314,24 @@
       </c>
       <c r="I163" s="2" t="inlineStr">
         <is>
-          <t>preview row '+$5.00' with new-subtotal line re-observed; color/sign convention from batch-1 (not re-checked) | WORDING+VIU 2026-07-13: rewritten to exact build labels (⋮ menu item 'Add Fee/Discount'; dialog 'Add new fee/discount'; fields 'Apply From Template'/'Name'/'Type'/'Calculation Type'/'$ Amount' or 'Percent %'/'$ Max Amount (Optional)'/'Taxable' toggle; whole-WO Calculation Type options = Flat Amount, % of Labor Total, % of Parts Total, % of Subtotal; buttons 'Add Fee'/'Add Discount'; sidebar card 'WO Fees &amp; Discounts'; preview empty prompt 'Enter an amount to see the impact.'). Captured live on WO S3-15960 (shots wo-01..wo-05). Kept to sign only; the exact fee/discount colours were not re-captured this pass. | SV-8479/8480 deconfliction 2026-07-22: label sweep: navigation labels -&gt; 'Add Work Order Fee / Discount' / 'New Work Order Fee / Discount' (behavior/expected unchanged). | VIU 2026-07-22 LIVE: SV-8479 nav label 'Add Work Order Fee / Discount' confirmed present in the WO toolbar ⋯ menu; case behavior unchanged. Ev: wo/FD-WO-025-toolbar-menu.png.</t>
+          <t>CONFIRMED AGAIN: 'Add Fee' button ENABLED on an empty form (disabled-on-empty=false) — PO Q4=B defect persists | WORDING+VIU 2026-07-13: rewritten to exact build labels (⋮ menu item 'Add Fee/Discount'; dialog 'Add new fee/discount'; fields 'Apply From Template'/'Name'/'Type'/'Calculation Type'/'$ Amount' or 'Percent %'/'$ Max Amount (Optional)'/'Taxable' toggle; whole-WO Calculation Type options = Flat Amount, % of Labor Total, % of Parts Total, % of Subtotal; buttons 'Add Fee'/'Add Discount'; sidebar card 'WO Fees &amp; Discounts'; preview empty prompt 'Enter an amount to see the impact.'). Captured live on WO S3-15960 (shots wo-01..wo-05). DEVIATION re-confirmed live 2026-07-13: the 'Add Fee' button is ENABLED on an empty form (validation happens on submit, not by disabling) — BUG-FD-4. Expected kept as the intended behavior; tester will see the button enabled. | STAGING VIU 2026-07-20 staging LIVE VIU: BUG-FD-4 FIXED on staging: Add Fee button is DISABLED on an empty form (was enabled on qb). Live-observed (dev-wo-emptyform, disabled=true). | SV-8479/8480 deconfliction 2026-07-22: label sweep: navigation labels -&gt; 'Add Work Order Fee / Discount' / 'New Work Order Fee / Discount' (behavior/expected unchanged). | VIU 2026-07-22 LIVE: SV-8479 nav label 'Add Work Order Fee / Discount' confirmed present in the WO toolbar ⋯ menu; case behavior unchanged. Ev: wo/FD-WO-025-toolbar-menu.png.</t>
         </is>
       </c>
     </row>
     <row r="164">
       <c r="A164" s="2" t="inlineStr">
         <is>
-          <t>FD-WO-016</t>
+          <t>FD-WO-006</t>
         </is>
       </c>
       <c r="B164" s="2" t="inlineStr">
         <is>
-          <t>C29441</t>
+          <t>C28429</t>
         </is>
       </c>
       <c r="C164" s="6" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/29441</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/28429</t>
         </is>
       </c>
       <c r="D164" s="2" t="inlineStr">
@@ -8341,7 +8341,7 @@
       </c>
       <c r="E164" s="2" t="inlineStr">
         <is>
-          <t>Verify the Add/Edit fee-or-discount dialog shows the tax-jurisdiction note below the Taxable Yes/No dropdown</t>
+          <t>Verify Max Amount caps a percentage fee (20% on a $100 base with Max Amount $15 → +$15.00)</t>
         </is>
       </c>
       <c r="F164" s="2" t="inlineStr">
@@ -8361,34 +8361,34 @@
       </c>
       <c r="I164" s="2" t="inlineStr">
         <is>
-          <t>administration/adjustment-templates loads; Finance-only user has NO F&amp;D nav, FINANCE=Payment Methods only, direct route bounces to /workorders. viu_status VIU-Verified re-confirmed. Ev build/fees-discounts/viu-sv8456-2026-07-22/ (01-settings-landing, 02-new-dialog, 03-customer-fd-tab, SVC-*, FIN-*).</t>
+          <t>20% of 170.76 (=34.15) capped at Max 15 -&gt; resolved exactly 15 | WORDING+VIU 2026-07-13: rewritten to exact build labels (⋮ menu item 'Add Fee/Discount'; dialog 'Add new fee/discount'; fields 'Apply From Template'/'Name'/'Type'/'Calculation Type'/'$ Amount' or 'Percent %'/'$ Max Amount (Optional)'/'Taxable' toggle; whole-WO Calculation Type options = Flat Amount, % of Labor Total, % of Parts Total, % of Subtotal; buttons 'Add Fee'/'Add Discount'; sidebar card 'WO Fees &amp; Discounts'; preview empty prompt 'Enter an amount to see the impact.'). Captured live on WO S3-15960 (shots wo-01..wo-05). The '$ Max Amount (Optional)' field appears only after a percentage method is chosen (confirmed live). | SV-8479/8480 deconfliction 2026-07-22: label sweep: navigation labels -&gt; 'Add Work Order Fee / Discount' / 'New Work Order Fee / Discount' (behavior/expected unchanged). | VIU 2026-07-22 LIVE: SV-8479 nav label 'Add Work Order Fee / Discount' confirmed present in the WO toolbar ⋯ menu; case behavior unchanged. Ev: wo/FD-WO-025-toolbar-menu.png.</t>
         </is>
       </c>
     </row>
     <row r="165">
       <c r="A165" s="2" t="inlineStr">
         <is>
-          <t>FD-WO-018</t>
+          <t>FD-WO-007</t>
         </is>
       </c>
       <c r="B165" s="2" t="inlineStr">
         <is>
-          <t>C30619</t>
+          <t>C28430</t>
         </is>
       </c>
       <c r="C165" s="6" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/30619</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/28430</t>
         </is>
       </c>
       <c r="D165" s="2" t="inlineStr">
         <is>
-          <t>Work Order / Parts — Part-line Fee/Discount</t>
+          <t>Work Order — Whole-WO Fee/Discount</t>
         </is>
       </c>
       <c r="E165" s="2" t="inlineStr">
         <is>
-          <t>Verify the work-order part row three-dot menu item reads 'Add Part Fee / Discount'</t>
+          <t>Verify the confirm button label follows the Type (Add Fee vs Add Discount)</t>
         </is>
       </c>
       <c r="F165" s="2" t="inlineStr">
@@ -8408,34 +8408,34 @@
       </c>
       <c r="I165" s="2" t="inlineStr">
         <is>
-          <t>. | VIU 2026-07-22 LIVE: part-row ⋮ menu = 'Move', 'Add Part Fee / Discount' (label correct; opens part fee/discount dialog). 'Return' state-gated — the seeded part was 'Auth To Order' (not received) so Return was not offered; Return appears only for returnable parts. Ev: wo/FD-WO-018-part-menu.png.</t>
+          <t>confirm label 'Add Fee' observed; Type-flip re-observed in batch-1 (not re-driven) | WORDING+VIU 2026-07-13: rewritten to exact build labels (⋮ menu item 'Add Fee/Discount'; dialog 'Add new fee/discount'; fields 'Apply From Template'/'Name'/'Type'/'Calculation Type'/'$ Amount' or 'Percent %'/'$ Max Amount (Optional)'/'Taxable' toggle; whole-WO Calculation Type options = Flat Amount, % of Labor Total, % of Parts Total, % of Subtotal; buttons 'Add Fee'/'Add Discount'; sidebar card 'WO Fees &amp; Discounts'; preview empty prompt 'Enter an amount to see the impact.'). Captured live on WO S3-15960 (shots wo-01..wo-05). | SV-8479/8480 deconfliction 2026-07-22: label sweep: navigation labels -&gt; 'Add Work Order Fee / Discount' / 'New Work Order Fee / Discount' (behavior/expected unchanged). | VIU 2026-07-22 LIVE: SV-8479 nav label 'Add Work Order Fee / Discount' confirmed present in the WO toolbar ⋯ menu; case behavior unchanged. Ev: wo/FD-WO-025-toolbar-menu.png.</t>
         </is>
       </c>
     </row>
     <row r="166">
       <c r="A166" s="2" t="inlineStr">
         <is>
-          <t>FD-WO-021</t>
+          <t>FD-WO-008</t>
         </is>
       </c>
       <c r="B166" s="2" t="inlineStr">
         <is>
-          <t>C30620</t>
+          <t>C28431</t>
         </is>
       </c>
       <c r="C166" s="6" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/30620</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/28431</t>
         </is>
       </c>
       <c r="D166" s="2" t="inlineStr">
         <is>
-          <t>Work Order — Sidebar 'Work Order Fee / Discount' card</t>
+          <t>Work Order — Whole-WO Fee/Discount</t>
         </is>
       </c>
       <c r="E166" s="2" t="inlineStr">
         <is>
-          <t>Verify the Work Order Fees &amp; Discounts card shows the disclaimer 'Applies to the whole work order, after all other fees &amp; discounts.'</t>
+          <t>Verify an empty Name blocks saving a whole-work-order fee/discount</t>
         </is>
       </c>
       <c r="F166" s="2" t="inlineStr">
@@ -8455,24 +8455,24 @@
       </c>
       <c r="I166" s="2" t="inlineStr">
         <is>
-          <t>s a mockup. QA passed on staging 2026-07-22 (✅). | VIU 2026-07-22 LIVE: Work Order Fees &amp; Discounts card shows disclaimer exactly 'Applies to the whole work order, after all other fees &amp; discounts.' below the adjustment list. Ev: wo/FD-FIN-004-FD-WO-021-card-financialinfo.png, wo/lines-bodytext.txt.</t>
+          <t>UI BLOCKS empty name (inline 'Name' required, dialog stays open, nothing saved). NOTE NEW FDBUG-16: the RAW API now ACCEPTS an empty-name adjustment (201; was 400 in batch-3) — BE validation regression, FE still guards | WORDING+VIU 2026-07-13: rewritten to exact build labels (⋮ menu item 'Add Fee/Discount'; dialog 'Add new fee/discount'; fields 'Apply From Template'/'Name'/'Type'/'Calculation Type'/'$ Amount' or 'Percent %'/'$ Max Amount (Optional)'/'Taxable' toggle; whole-WO Calculation Type options = Flat Amount, % of Labor Total, % of Parts Total, % of Subtotal; buttons 'Add Fee'/'Add Discount'; sidebar card 'WO Fees &amp; Discounts'; preview empty prompt 'Enter an amount to see the impact.'). Captured live on WO S3-15960 (shots wo-01..wo-05). (Note: the raw back-end will accept an empty name — FDBUG-16 — but the on-screen dialog blocks it, which is what a manual tester sees.) | SV-8479/8480 deconfliction 2026-07-22: label sweep: navigation labels -&gt; 'Add Work Order Fee / Discount' / 'New Work Order Fee / Discount' (behavior/expected unchanged). | VIU 2026-07-22 LIVE: SV-8479 nav label 'Add Work Order Fee / Discount' confirmed present in the WO toolbar ⋯ menu; case behavior unchanged. Ev: wo/FD-WO-025-toolbar-menu.png.</t>
         </is>
       </c>
     </row>
     <row r="167">
       <c r="A167" s="2" t="inlineStr">
         <is>
-          <t>FD-WO-025</t>
+          <t>FD-WO-009</t>
         </is>
       </c>
       <c r="B167" s="2" t="inlineStr">
         <is>
-          <t>C30621</t>
+          <t>C28432</t>
         </is>
       </c>
       <c r="C167" s="6" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/30621</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/28432</t>
         </is>
       </c>
       <c r="D167" s="2" t="inlineStr">
@@ -8482,7 +8482,7 @@
       </c>
       <c r="E167" s="2" t="inlineStr">
         <is>
-          <t>Verify the work order toolbar three-dot menu item reads 'Add Work Order Fee / Discount'</t>
+          <t>Verify an empty or zero amount blocks saving a whole-work-order fee/discount</t>
         </is>
       </c>
       <c r="F167" s="2" t="inlineStr">
@@ -8502,52 +8502,569 @@
       </c>
       <c r="I167" s="2" t="inlineStr">
         <is>
-          <t>6-07-22 LIVE: toolbar ⋯ menu label 'Add Work Order Fee / Discount' correct; opens whole-WO fee/discount dialog. WORDING CORRECTED — observed order is 'Audit Log' -&gt; 'Timesheets (N)' -&gt; 'Add Work Order Fee / Discount' -&gt; 'Delete Work Order' (Add is 3rd, NOT at top). Ev: wo/FD-WO-025-toolbar-menu.png.</t>
+          <t>amount 0 -&gt; 400 at API; UI validates on submit | WORDING+VIU 2026-07-13: rewritten to exact build labels (⋮ menu item 'Add Fee/Discount'; dialog 'Add new fee/discount'; fields 'Apply From Template'/'Name'/'Type'/'Calculation Type'/'$ Amount' or 'Percent %'/'$ Max Amount (Optional)'/'Taxable' toggle; whole-WO Calculation Type options = Flat Amount, % of Labor Total, % of Parts Total, % of Subtotal; buttons 'Add Fee'/'Add Discount'; sidebar card 'WO Fees &amp; Discounts'; preview empty prompt 'Enter an amount to see the impact.'). Captured live on WO S3-15960 (shots wo-01..wo-05). | SV-8479/8480 deconfliction 2026-07-22: label sweep: navigation labels -&gt; 'Add Work Order Fee / Discount' / 'New Work Order Fee / Discount' (behavior/expected unchanged). | VIU 2026-07-22 LIVE: SV-8479 nav label 'Add Work Order Fee / Discount' confirmed present in the WO toolbar ⋯ menu; case behavior unchanged. Ev: wo/FD-WO-025-toolbar-menu.png.</t>
         </is>
       </c>
     </row>
     <row r="168">
       <c r="A168" s="2" t="inlineStr">
         <is>
+          <t>FD-WO-010</t>
+        </is>
+      </c>
+      <c r="B168" s="2" t="inlineStr">
+        <is>
+          <t>C28433</t>
+        </is>
+      </c>
+      <c r="C168" s="6" t="inlineStr">
+        <is>
+          <t>https://shopview.testrail.io/index.php?/cases/view/28433</t>
+        </is>
+      </c>
+      <c r="D168" s="2" t="inlineStr">
+        <is>
+          <t>Work Order — Whole-WO Fee/Discount</t>
+        </is>
+      </c>
+      <c r="E168" s="2" t="inlineStr">
+        <is>
+          <t>Verify a percentage discount over 100% is rejected while a percentage fee has no upper limit</t>
+        </is>
+      </c>
+      <c r="F168" s="2" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="G168" s="2" t="inlineStr">
+        <is>
+          <t>VIU-Verified</t>
+        </is>
+      </c>
+      <c r="H168" s="2" t="inlineStr">
+        <is>
+          <t>No action needed — passed.</t>
+        </is>
+      </c>
+      <c r="I168" s="2" t="inlineStr">
+        <is>
+          <t>discount 150% -&gt; 400 'A percentage discount cannot exceed 100%.'; fee 150% -&gt; 201 | WORDING+VIU 2026-07-13: rewritten to exact build labels (⋮ menu item 'Add Fee/Discount'; dialog 'Add new fee/discount'; fields 'Apply From Template'/'Name'/'Type'/'Calculation Type'/'$ Amount' or 'Percent %'/'$ Max Amount (Optional)'/'Taxable' toggle; whole-WO Calculation Type options = Flat Amount, % of Labor Total, % of Parts Total, % of Subtotal; buttons 'Add Fee'/'Add Discount'; sidebar card 'WO Fees &amp; Discounts'; preview empty prompt 'Enter an amount to see the impact.'). Captured live on WO S3-15960 (shots wo-01..wo-05). | SV-8479/8480 deconfliction 2026-07-22: label sweep: navigation labels -&gt; 'Add Work Order Fee / Discount' / 'New Work Order Fee / Discount' (behavior/expected unchanged). | VIU 2026-07-22 LIVE: SV-8479 nav label 'Add Work Order Fee / Discount' confirmed present in the WO toolbar ⋯ menu; case behavior unchanged. Ev: wo/FD-WO-025-toolbar-menu.png.</t>
+        </is>
+      </c>
+    </row>
+    <row r="169">
+      <c r="A169" s="2" t="inlineStr">
+        <is>
+          <t>FD-WO-011</t>
+        </is>
+      </c>
+      <c r="B169" s="2" t="inlineStr">
+        <is>
+          <t>C28434</t>
+        </is>
+      </c>
+      <c r="C169" s="6" t="inlineStr">
+        <is>
+          <t>https://shopview.testrail.io/index.php?/cases/view/28434</t>
+        </is>
+      </c>
+      <c r="D169" s="2" t="inlineStr">
+        <is>
+          <t>Work Order — Whole-WO Fee/Discount</t>
+        </is>
+      </c>
+      <c r="E169" s="2" t="inlineStr">
+        <is>
+          <t>Verify a whole-work-order percentage method uses the correct base (% of Subtotal example)</t>
+        </is>
+      </c>
+      <c r="F169" s="2" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="G169" s="2" t="inlineStr">
+        <is>
+          <t>VIU-Verified</t>
+        </is>
+      </c>
+      <c r="H169" s="2" t="inlineStr">
+        <is>
+          <t>No action needed — passed.</t>
+        </is>
+      </c>
+      <c r="I169" s="2" t="inlineStr">
+        <is>
+          <t>pct_subtotal resolves on the WO subtotal EXCLUDING whole-WO adjustments (10% of 182.76-sub -&gt; 17.08 = 10% of 170.76 line total) | WORDING+VIU 2026-07-13: rewritten to exact build labels (⋮ menu item 'Add Fee/Discount'; dialog 'Add new fee/discount'; fields 'Apply From Template'/'Name'/'Type'/'Calculation Type'/'$ Amount' or 'Percent %'/'$ Max Amount (Optional)'/'Taxable' toggle; whole-WO Calculation Type options = Flat Amount, % of Labor Total, % of Parts Total, % of Subtotal; buttons 'Add Fee'/'Add Discount'; sidebar card 'WO Fees &amp; Discounts'; preview empty prompt 'Enter an amount to see the impact.'). Captured live on WO S3-15960 (shots wo-01..wo-05). Calculation Type options confirmed live (exactly the 4 listed; no '% of Grand Total'). | SV-8479/8480 deconfliction 2026-07-22: label sweep: navigation labels -&gt; 'Add Work Order Fee / Discount' / 'New Work Order Fee / Discount' (behavior/expected unchanged). | VIU 2026-07-22 LIVE: SV-8479 nav label 'Add Work Order Fee / Discount' confirmed present in the WO toolbar ⋯ menu; case behavior unchanged. Ev: wo/FD-WO-025-toolbar-menu.png.</t>
+        </is>
+      </c>
+    </row>
+    <row r="170">
+      <c r="A170" s="2" t="inlineStr">
+        <is>
+          <t>FD-WO-012</t>
+        </is>
+      </c>
+      <c r="B170" s="2" t="inlineStr">
+        <is>
+          <t>C28435</t>
+        </is>
+      </c>
+      <c r="C170" s="6" t="inlineStr">
+        <is>
+          <t>https://shopview.testrail.io/index.php?/cases/view/28435</t>
+        </is>
+      </c>
+      <c r="D170" s="2" t="inlineStr">
+        <is>
+          <t>Work Order — Whole-WO Fee/Discount</t>
+        </is>
+      </c>
+      <c r="E170" s="2" t="inlineStr">
+        <is>
+          <t>Verify Add Work Order Fee / Discount is hidden and blocked on an Invoiced or Paid work order</t>
+        </is>
+      </c>
+      <c r="F170" s="2" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="G170" s="2" t="inlineStr">
+        <is>
+          <t>VIU-Verified</t>
+        </is>
+      </c>
+      <c r="H170" s="2" t="inlineStr">
+        <is>
+          <t>No action needed — passed.</t>
+        </is>
+      </c>
+      <c r="I170" s="2" t="inlineStr">
+        <is>
+          <t>add on Invoiced WO -&gt; 409 'Adjustments cannot be changed on an invoiced or paid work order.'; edit also 409 | WORDING+VIU 2026-07-13: rewritten to exact build labels (⋮ menu item 'Add Fee/Discount'; dialog 'Add new fee/discount'; fields 'Apply From Template'/'Name'/'Type'/'Calculation Type'/'$ Amount' or 'Percent %'/'$ Max Amount (Optional)'/'Taxable' toggle; whole-WO Calculation Type options = Flat Amount, % of Labor Total, % of Parts Total, % of Subtotal; buttons 'Add Fee'/'Add Discount'; sidebar card 'WO Fees &amp; Discounts'; preview empty prompt 'Enter an amount to see the impact.'). Captured live on WO S3-15960 (shots wo-01..wo-05). | SV-8479/8480 deconfliction 2026-07-22: label sweep: navigation labels -&gt; 'Add Work Order Fee / Discount' / 'New Work Order Fee / Discount' (behavior/expected unchanged). | VIU 2026-07-22 LIVE: SV-8479 nav label 'Add Work Order Fee / Discount' confirmed present in the WO toolbar ⋯ menu; case behavior unchanged. Ev: wo/FD-WO-025-toolbar-menu.png.</t>
+        </is>
+      </c>
+    </row>
+    <row r="171">
+      <c r="A171" s="2" t="inlineStr">
+        <is>
+          <t>FD-WO-013</t>
+        </is>
+      </c>
+      <c r="B171" s="2" t="inlineStr">
+        <is>
+          <t>C28436</t>
+        </is>
+      </c>
+      <c r="C171" s="6" t="inlineStr">
+        <is>
+          <t>https://shopview.testrail.io/index.php?/cases/view/28436</t>
+        </is>
+      </c>
+      <c r="D171" s="2" t="inlineStr">
+        <is>
+          <t>Work Order — Whole-WO Fee/Discount</t>
+        </is>
+      </c>
+      <c r="E171" s="2" t="inlineStr">
+        <is>
+          <t>Verify the whole-work-order 'Add Work Order Fee / Discount' option is hidden without Work Orders: Create &amp; Edit</t>
+        </is>
+      </c>
+      <c r="F171" s="2" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="G171" s="2" t="inlineStr">
+        <is>
+          <t>VIU-Verified</t>
+        </is>
+      </c>
+      <c r="H171" s="2" t="inlineStr">
+        <is>
+          <t>No action needed — passed.</t>
+        </is>
+      </c>
+      <c r="I171" s="2" t="inlineStr">
+        <is>
+          <t>BUG-FD-3 stands on prior evidence; NOT re-testable today: the shared-env Technician role was CHANGED (now includes workOrdersCreateAndEdit+workOrdersDelete, 8 perms vs matrix 6) so tech's 201 is now legitimate; no login lacking the perm exists | WORDING+VIU 2026-07-13: rewritten to exact build labels (⋮ menu item 'Add Fee/Discount'; dialog 'Add new fee/discount'; fields 'Apply From Template'/'Name'/'Type'/'Calculation Type'/'$ Amount' or 'Percent %'/'$ Max Amount (Optional)'/'Taxable' toggle; whole-WO Calculation Type options = Flat Amount, % of Labor Total, % of Parts Total, % of Subtotal; buttons 'Add Fee'/'Add Discount'; sidebar card 'WO Fees &amp; Discounts'; preview empty prompt 'Enter an amount to see the impact.'). Captured live on WO S3-15960 (shots wo-01..wo-05). DEVIATION (BUG-FD-3: the hide is front-end only; the back-end does not block the write). NOT re-testable this run — the Technician role has drifted on the shared qb env; re-derive the roles matrix before re-checking. | SV-8479/8480 deconfliction 2026-07-22: label updated 'Add Fee/Discount' -&gt; 'Add Work Order Fee / Discount' (item 10); permission behavior unchanged. | VIU 2026-07-22 LIVE: toolbar label 'Add Work Order Fee / Discount' confirmed present (admin); permission-negative status unchanged — role-negative not re-driven this UI batch. | FE-BLOCK/BE-ALLOW PASS 2026-07-24 (user-authorized, Standing Rule 24): flipped VIU-Deviation -&gt; VIU-Verified (PASS). The whole-WO 'Add Work Order Fee / Discount' control being hidden for a role lacking Work Orders: Create &amp; Edit IS the tester-facing pass criterion; the FE-only enforcement (the back-end/API POST /api/work-orders/adjustments/add still returns 201 for such a role — pass-A evidence + impersonation) is ACCEPTED by product policy, not a bug. Added the plain tester line to Expected (Rule 7). This is FE-block/BE-allow = PASS (not the inverse FE-exposure defect).</t>
+        </is>
+      </c>
+    </row>
+    <row r="172">
+      <c r="A172" s="2" t="inlineStr">
+        <is>
+          <t>FD-WO-014</t>
+        </is>
+      </c>
+      <c r="B172" s="2" t="inlineStr">
+        <is>
+          <t>C28437</t>
+        </is>
+      </c>
+      <c r="C172" s="6" t="inlineStr">
+        <is>
+          <t>https://shopview.testrail.io/index.php?/cases/view/28437</t>
+        </is>
+      </c>
+      <c r="D172" s="2" t="inlineStr">
+        <is>
+          <t>Work Order — Whole-WO Fee/Discount</t>
+        </is>
+      </c>
+      <c r="E172" s="2" t="inlineStr">
+        <is>
+          <t>Verify the preview shows the empty-amount prompt before an amount is entered</t>
+        </is>
+      </c>
+      <c r="F172" s="2" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="G172" s="2" t="inlineStr">
+        <is>
+          <t>VIU-Verified</t>
+        </is>
+      </c>
+      <c r="H172" s="2" t="inlineStr">
+        <is>
+          <t>No action needed — passed.</t>
+        </is>
+      </c>
+      <c r="I172" s="2" t="inlineStr">
+        <is>
+          <t>'Enter an amount to see the impact.' prompt present in the re-driven dialog | WORDING+VIU 2026-07-13: rewritten to exact build labels (⋮ menu item 'Add Fee/Discount'; dialog 'Add new fee/discount'; fields 'Apply From Template'/'Name'/'Type'/'Calculation Type'/'$ Amount' or 'Percent %'/'$ Max Amount (Optional)'/'Taxable' toggle; whole-WO Calculation Type options = Flat Amount, % of Labor Total, % of Parts Total, % of Subtotal; buttons 'Add Fee'/'Add Discount'; sidebar card 'WO Fees &amp; Discounts'; preview empty prompt 'Enter an amount to see the impact.'). Captured live on WO S3-15960 (shots wo-01..wo-05). Exact prompt text 'Enter an amount to see the impact.' confirmed live (shot wo-03). | SV-8479/8480 deconfliction 2026-07-22: label sweep: navigation labels -&gt; 'Add Work Order Fee / Discount' / 'New Work Order Fee / Discount' (behavior/expected unchanged). | VIU 2026-07-22 LIVE: SV-8479 nav label 'Add Work Order Fee / Discount' confirmed present in the WO toolbar ⋯ menu; case behavior unchanged. Ev: wo/FD-WO-025-toolbar-menu.png.</t>
+        </is>
+      </c>
+    </row>
+    <row r="173">
+      <c r="A173" s="2" t="inlineStr">
+        <is>
+          <t>FD-WO-015</t>
+        </is>
+      </c>
+      <c r="B173" s="2" t="inlineStr">
+        <is>
+          <t>C28438</t>
+        </is>
+      </c>
+      <c r="C173" s="6" t="inlineStr">
+        <is>
+          <t>https://shopview.testrail.io/index.php?/cases/view/28438</t>
+        </is>
+      </c>
+      <c r="D173" s="2" t="inlineStr">
+        <is>
+          <t>Work Order — Whole-WO Fee/Discount</t>
+        </is>
+      </c>
+      <c r="E173" s="2" t="inlineStr">
+        <is>
+          <t>Verify the preview amount is signed for a fee (+) vs a discount (−)</t>
+        </is>
+      </c>
+      <c r="F173" s="2" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="G173" s="2" t="inlineStr">
+        <is>
+          <t>VIU-Verified</t>
+        </is>
+      </c>
+      <c r="H173" s="2" t="inlineStr">
+        <is>
+          <t>No action needed — passed.</t>
+        </is>
+      </c>
+      <c r="I173" s="2" t="inlineStr">
+        <is>
+          <t>preview row '+$5.00' with new-subtotal line re-observed; color/sign convention from batch-1 (not re-checked) | WORDING+VIU 2026-07-13: rewritten to exact build labels (⋮ menu item 'Add Fee/Discount'; dialog 'Add new fee/discount'; fields 'Apply From Template'/'Name'/'Type'/'Calculation Type'/'$ Amount' or 'Percent %'/'$ Max Amount (Optional)'/'Taxable' toggle; whole-WO Calculation Type options = Flat Amount, % of Labor Total, % of Parts Total, % of Subtotal; buttons 'Add Fee'/'Add Discount'; sidebar card 'WO Fees &amp; Discounts'; preview empty prompt 'Enter an amount to see the impact.'). Captured live on WO S3-15960 (shots wo-01..wo-05). Kept to sign only; the exact fee/discount colours were not re-captured this pass. | SV-8479/8480 deconfliction 2026-07-22: label sweep: navigation labels -&gt; 'Add Work Order Fee / Discount' / 'New Work Order Fee / Discount' (behavior/expected unchanged). | VIU 2026-07-22 LIVE: SV-8479 nav label 'Add Work Order Fee / Discount' confirmed present in the WO toolbar ⋯ menu; case behavior unchanged. Ev: wo/FD-WO-025-toolbar-menu.png.</t>
+        </is>
+      </c>
+    </row>
+    <row r="174">
+      <c r="A174" s="2" t="inlineStr">
+        <is>
+          <t>FD-WO-016</t>
+        </is>
+      </c>
+      <c r="B174" s="2" t="inlineStr">
+        <is>
+          <t>C29441</t>
+        </is>
+      </c>
+      <c r="C174" s="6" t="inlineStr">
+        <is>
+          <t>https://shopview.testrail.io/index.php?/cases/view/29441</t>
+        </is>
+      </c>
+      <c r="D174" s="2" t="inlineStr">
+        <is>
+          <t>Work Order — Whole-WO Fee/Discount</t>
+        </is>
+      </c>
+      <c r="E174" s="2" t="inlineStr">
+        <is>
+          <t>Verify the Add/Edit fee-or-discount dialog shows the tax-jurisdiction note below the Taxable Yes/No dropdown</t>
+        </is>
+      </c>
+      <c r="F174" s="2" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="G174" s="2" t="inlineStr">
+        <is>
+          <t>VIU-Verified</t>
+        </is>
+      </c>
+      <c r="H174" s="2" t="inlineStr">
+        <is>
+          <t>No action needed — passed.</t>
+        </is>
+      </c>
+      <c r="I174" s="2" t="inlineStr">
+        <is>
+          <t>administration/adjustment-templates loads; Finance-only user has NO F&amp;D nav, FINANCE=Payment Methods only, direct route bounces to /workorders. viu_status VIU-Verified re-confirmed. Ev build/fees-discounts/viu-sv8456-2026-07-22/ (01-settings-landing, 02-new-dialog, 03-customer-fd-tab, SVC-*, FIN-*).</t>
+        </is>
+      </c>
+    </row>
+    <row r="175">
+      <c r="A175" s="2" t="inlineStr">
+        <is>
+          <t>FD-WO-017</t>
+        </is>
+      </c>
+      <c r="B175" s="2" t="inlineStr">
+        <is>
+          <t>C30618</t>
+        </is>
+      </c>
+      <c r="C175" s="6" t="inlineStr">
+        <is>
+          <t>https://shopview.testrail.io/index.php?/cases/view/30618</t>
+        </is>
+      </c>
+      <c r="D175" s="2" t="inlineStr">
+        <is>
+          <t>Work Order — Labor-line Fee/Discount</t>
+        </is>
+      </c>
+      <c r="E175" s="2" t="inlineStr">
+        <is>
+          <t>Verify the labor fee/discount entry point is a three-dot menu to the RIGHT of the first technician (or 'Unassigned') and reads 'Add Labor Fee / Discount'</t>
+        </is>
+      </c>
+      <c r="F175" s="2" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="G175" s="2" t="inlineStr">
+        <is>
+          <t>VIU-Verified</t>
+        </is>
+      </c>
+      <c r="H175" s="2" t="inlineStr">
+        <is>
+          <t>No action needed — passed.</t>
+        </is>
+      </c>
+      <c r="I175" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> write from us. VIU-Deviation -&gt; VIU-Verified. (Note: the TestRail refs + some descriptive text still reference 'LEFT' from the prior authoring; local mirrors TestRail verbatim.) HONESTY (Rule 12/22): accepted on the user's manual edit + PO acceptance — not independently re-observed by us this pass.</t>
+        </is>
+      </c>
+    </row>
+    <row r="176">
+      <c r="A176" s="2" t="inlineStr">
+        <is>
+          <t>FD-WO-018</t>
+        </is>
+      </c>
+      <c r="B176" s="2" t="inlineStr">
+        <is>
+          <t>C30619</t>
+        </is>
+      </c>
+      <c r="C176" s="6" t="inlineStr">
+        <is>
+          <t>https://shopview.testrail.io/index.php?/cases/view/30619</t>
+        </is>
+      </c>
+      <c r="D176" s="2" t="inlineStr">
+        <is>
+          <t>Work Order / Parts — Part-line Fee/Discount</t>
+        </is>
+      </c>
+      <c r="E176" s="2" t="inlineStr">
+        <is>
+          <t>Verify the work-order part row three-dot menu item reads 'Add Part Fee / Discount'</t>
+        </is>
+      </c>
+      <c r="F176" s="2" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="G176" s="2" t="inlineStr">
+        <is>
+          <t>VIU-Verified</t>
+        </is>
+      </c>
+      <c r="H176" s="2" t="inlineStr">
+        <is>
+          <t>No action needed — passed.</t>
+        </is>
+      </c>
+      <c r="I176" s="2" t="inlineStr">
+        <is>
+          <t>. | VIU 2026-07-22 LIVE: part-row ⋮ menu = 'Move', 'Add Part Fee / Discount' (label correct; opens part fee/discount dialog). 'Return' state-gated — the seeded part was 'Auth To Order' (not received) so Return was not offered; Return appears only for returnable parts. Ev: wo/FD-WO-018-part-menu.png.</t>
+        </is>
+      </c>
+    </row>
+    <row r="177">
+      <c r="A177" s="2" t="inlineStr">
+        <is>
+          <t>FD-WO-021</t>
+        </is>
+      </c>
+      <c r="B177" s="2" t="inlineStr">
+        <is>
+          <t>C30620</t>
+        </is>
+      </c>
+      <c r="C177" s="6" t="inlineStr">
+        <is>
+          <t>https://shopview.testrail.io/index.php?/cases/view/30620</t>
+        </is>
+      </c>
+      <c r="D177" s="2" t="inlineStr">
+        <is>
+          <t>Work Order — Sidebar 'Work Order Fee / Discount' card</t>
+        </is>
+      </c>
+      <c r="E177" s="2" t="inlineStr">
+        <is>
+          <t>Verify the Work Order Fees &amp; Discounts card shows the disclaimer 'Applies to the whole work order, after all other fees &amp; discounts.'</t>
+        </is>
+      </c>
+      <c r="F177" s="2" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="G177" s="2" t="inlineStr">
+        <is>
+          <t>VIU-Verified</t>
+        </is>
+      </c>
+      <c r="H177" s="2" t="inlineStr">
+        <is>
+          <t>No action needed — passed.</t>
+        </is>
+      </c>
+      <c r="I177" s="2" t="inlineStr">
+        <is>
+          <t>s a mockup. QA passed on staging 2026-07-22 (✅). | VIU 2026-07-22 LIVE: Work Order Fees &amp; Discounts card shows disclaimer exactly 'Applies to the whole work order, after all other fees &amp; discounts.' below the adjustment list. Ev: wo/FD-FIN-004-FD-WO-021-card-financialinfo.png, wo/lines-bodytext.txt.</t>
+        </is>
+      </c>
+    </row>
+    <row r="178">
+      <c r="A178" s="2" t="inlineStr">
+        <is>
+          <t>FD-WO-025</t>
+        </is>
+      </c>
+      <c r="B178" s="2" t="inlineStr">
+        <is>
+          <t>C30621</t>
+        </is>
+      </c>
+      <c r="C178" s="6" t="inlineStr">
+        <is>
+          <t>https://shopview.testrail.io/index.php?/cases/view/30621</t>
+        </is>
+      </c>
+      <c r="D178" s="2" t="inlineStr">
+        <is>
+          <t>Work Order — Whole-WO Fee/Discount</t>
+        </is>
+      </c>
+      <c r="E178" s="2" t="inlineStr">
+        <is>
+          <t>Verify the work order toolbar three-dot menu item reads 'Add Work Order Fee / Discount'</t>
+        </is>
+      </c>
+      <c r="F178" s="2" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="G178" s="2" t="inlineStr">
+        <is>
+          <t>VIU-Verified</t>
+        </is>
+      </c>
+      <c r="H178" s="2" t="inlineStr">
+        <is>
+          <t>No action needed — passed.</t>
+        </is>
+      </c>
+      <c r="I178" s="2" t="inlineStr">
+        <is>
+          <t>6-07-22 LIVE: toolbar ⋯ menu label 'Add Work Order Fee / Discount' correct; opens whole-WO fee/discount dialog. WORDING CORRECTED — observed order is 'Audit Log' -&gt; 'Timesheets (N)' -&gt; 'Add Work Order Fee / Discount' -&gt; 'Delete Work Order' (Add is 3rd, NOT at top). Ev: wo/FD-WO-025-toolbar-menu.png.</t>
+        </is>
+      </c>
+    </row>
+    <row r="179">
+      <c r="A179" s="2" t="inlineStr">
+        <is>
           <t>FD-WO-028</t>
         </is>
       </c>
-      <c r="B168" s="2" t="inlineStr">
+      <c r="B179" s="2" t="inlineStr">
         <is>
           <t>C30622</t>
         </is>
       </c>
-      <c r="C168" s="6" t="inlineStr">
+      <c r="C179" s="6" t="inlineStr">
         <is>
           <t>https://shopview.testrail.io/index.php?/cases/view/30622</t>
         </is>
       </c>
-      <c r="D168" s="2" t="inlineStr">
+      <c r="D179" s="2" t="inlineStr">
         <is>
           <t>Work Order — Whole-WO Fee/Discount</t>
         </is>
       </c>
-      <c r="E168" s="2" t="inlineStr">
+      <c r="E179" s="2" t="inlineStr">
         <is>
           <t>Verify the tax-jurisdiction note and the 'Pass convenience fee to customer' banner still appear after the fee/discount UI updates</t>
         </is>
       </c>
-      <c r="F168" s="2" t="inlineStr">
+      <c r="F179" s="2" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="G168" s="2" t="inlineStr">
-        <is>
-          <t>VIU-Verified</t>
-        </is>
-      </c>
-      <c r="H168" s="2" t="inlineStr">
-        <is>
-          <t>No action needed — passed.</t>
-        </is>
-      </c>
-      <c r="I168" s="2" t="inlineStr">
+      <c r="G179" s="2" t="inlineStr">
+        <is>
+          <t>VIU-Verified</t>
+        </is>
+      </c>
+      <c r="H179" s="2" t="inlineStr">
+        <is>
+          <t>No action needed — passed.</t>
+        </is>
+      </c>
+      <c r="I179" s="2" t="inlineStr">
         <is>
           <t>&amp; Discounts Settings page (Settings -&gt; Service -&gt; Fees &amp; Discounts / adjustment-templates) — it is NOT rendered inside the WO fee/discount dialogs. Ev: wo/labor-dialog-text.txt, wo/part-dialog-text.txt, wo/wo-dialog-text.txt, wo/FD-WO-028-settings-convenience-banner.png, wo/settings-fd-bodytext.txt.</t>
         </is>
@@ -8722,6 +9239,17 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C166" r:id="rId165"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C167" r:id="rId166"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C168" r:id="rId167"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C169" r:id="rId168"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C170" r:id="rId169"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C171" r:id="rId170"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C172" r:id="rId171"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C173" r:id="rId172"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C174" r:id="rId173"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C175" r:id="rId174"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C176" r:id="rId175"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C177" r:id="rId176"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C178" r:id="rId177"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C179" r:id="rId178"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -8733,7 +9261,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I11"/>
+  <dimension ref="A1:I1"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -8794,489 +9322,7 @@
         </is>
       </c>
     </row>
-    <row r="2">
-      <c r="A2" s="2" t="inlineStr">
-        <is>
-          <t>FD-CALC-013</t>
-        </is>
-      </c>
-      <c r="B2" s="2" t="inlineStr">
-        <is>
-          <t>C28580</t>
-        </is>
-      </c>
-      <c r="C2" s="6" t="inlineStr">
-        <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/28580</t>
-        </is>
-      </c>
-      <c r="D2" s="2" t="inlineStr">
-        <is>
-          <t>Calculation contract</t>
-        </is>
-      </c>
-      <c r="E2" s="2" t="inlineStr">
-        <is>
-          <t>Verify a Processing Fee works out last on the tax-included grand total (3% of $324 → +$9.72)</t>
-        </is>
-      </c>
-      <c r="F2" s="2" t="inlineStr">
-        <is>
-          <t>High</t>
-        </is>
-      </c>
-      <c r="G2" s="2" t="inlineStr">
-        <is>
-          <t>VIU-Deviation</t>
-        </is>
-      </c>
-      <c r="H2" s="2" t="inlineStr">
-        <is>
-          <t>Same Processing Fee amount problem — the base wrongly includes the whole-work-order fees/discounts. A developer needs to fix it; re-test the amount once fixed.</t>
-        </is>
-      </c>
-      <c r="I2" s="2" t="inlineStr">
-        <is>
-          <t>FDBUG-2 CONFIRMED AGAIN (clean discriminator): pfee base INCLUDES whole-WO adjustments + their tax (3% -&gt; 0.63 where spec expects 0.00). Structural defect is tax-model independent | WORDING+VIU 2026-07-13: DEVIATION carried (FDBUG-2): the Processing Fee base wrongly includes whole-work-order fees/discounts (should exclude them). Build labels applied. | SV-8456 (2026-07-21 staging LIVE VIU): F&amp;D moved to SETTINGS→SERVICE (below Canned Lines); template/WO/Part-sale/customer dialogs now show Taxable as a Yes/No DROPDOWN (was toggle); Auto-apply is a CHECKBOX with a 'When on…' caption; settings &amp; customer tables are plain-text/left-aligned (no badges); WO sidebar card retitled 'Work Order Fees &amp; Discounts' and renders ABOVE Financial Info; Part-sale card 'Parts Sale Fees &amp; Discounts' above Financial Info. Permission gate pivoted Settings→Finance → Settings→Service (verified live: Service-user sees+manages F&amp;D &amp; convenience toggle; Finance-only user has no F&amp;D nav item and /administration/adjustment-templates bounces to /workorders). Frontend-only; functionality + calc INTACT. | RE-VIU 2026-07-22 LIVE (Batch 4, SV-8456 re-verify): access-check quick-login {admin} HTTP 200. The SV-8456 UI-correction wording + Settings-&gt;Service permission pivot were re-confirmed live on the current staging build (Service-user sees+manages F&amp;D; Finance-only user no F&amp;D nav, direct route bounces to /workorders; Tech restored to Technician 50bf6a0d + verified; ZZAUTOTEST roles deleted). This case retains its prior VIU-Deviation for its OWN (non-SV-8456) reason — that specific behavior was NOT re-driven this pass. Ev build/fees-discounts/viu-sv8456-2026-07-22/.</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" s="2" t="inlineStr">
-        <is>
-          <t>FD-CUST-005</t>
-        </is>
-      </c>
-      <c r="B3" s="2" t="inlineStr">
-        <is>
-          <t>C28489</t>
-        </is>
-      </c>
-      <c r="C3" s="6" t="inlineStr">
-        <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/28489</t>
-        </is>
-      </c>
-      <c r="D3" s="2" t="inlineStr">
-        <is>
-          <t>Customer Fees &amp; Discounts tab</t>
-        </is>
-      </c>
-      <c r="E3" s="2" t="inlineStr">
-        <is>
-          <t>Verify the picker lists only not-yet-added templates and shows a Processing Fee template as type 'Fee'</t>
-        </is>
-      </c>
-      <c r="F3" s="2" t="inlineStr">
-        <is>
-          <t>Medium</t>
-        </is>
-      </c>
-      <c r="G3" s="2" t="inlineStr">
-        <is>
-          <t>VIU-Deviation</t>
-        </is>
-      </c>
-      <c r="H3" s="2" t="inlineStr">
-        <is>
-          <t>Re-check on staging how a Processing Fee template's type is shown in the customer picker, and confirm with the team whether showing it as 'Fee' is acceptable or needs fixing.</t>
-        </is>
-      </c>
-      <c r="I3" s="2" t="inlineStr">
-        <is>
-          <t>accepted deviation (PO Q6=A); list assertions hold; case-update pending | WORDING+VIU 2026-07-13: DEVIATION carried: a Processing Fee template appears in the customer picker with its Type shown as 'Fee' (display quirk). Picker label 'Fee / Discount Templates' confirmed live; the Processing-Fee-as-Fee display not re-captured this run.</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" s="2" t="inlineStr">
-        <is>
-          <t>FD-CUST-006</t>
-        </is>
-      </c>
-      <c r="B4" s="2" t="inlineStr">
-        <is>
-          <t>C28490</t>
-        </is>
-      </c>
-      <c r="C4" s="6" t="inlineStr">
-        <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/28490</t>
-        </is>
-      </c>
-      <c r="D4" s="2" t="inlineStr">
-        <is>
-          <t>Customer Fees &amp; Discounts tab</t>
-        </is>
-      </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>Verify the picker message when there are no templates left to add</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>Low</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>VIU-Deviation</t>
-        </is>
-      </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>Accepted as-is by the team — the picker shows 'No results' when there is nothing left to add. Update the test case wording to expect 'No results'; no developer fix needed.</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>'No results' empty picker message per batch-1 (spec wording differs); case-update pending; not re-driven | WORDING+VIU 2026-07-13: Empty-picker state carried from prior VIU (not re-captured — the shared env has templates available).</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" s="2" t="inlineStr">
-        <is>
-          <t>FD-INLINE-003</t>
-        </is>
-      </c>
-      <c r="B5" s="2" t="inlineStr">
-        <is>
-          <t>C28456</t>
-        </is>
-      </c>
-      <c r="C5" s="6" t="inlineStr">
-        <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/28456</t>
-        </is>
-      </c>
-      <c r="D5" s="2" t="inlineStr">
-        <is>
-          <t>Work Order — Inline display (Lines tab)</t>
-        </is>
-      </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>Verify a line/part with 2 or more fees/discounts shows only the first plus a 'Show N more' toggle</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>High</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
-        <is>
-          <t>VIU-Deviation</t>
-        </is>
-      </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>A developer needs to add the 'Show N more' collapse so a line with two or more fees/discounts no longer shows them all at once. Re-test once fixed.</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>CONFIRMED AGAIN: 2 adjustments on one part render with NO 'Show N more' collapse — PO Q5=B defect persists | WORDING+VIU 2026-07-13: DEVIATION carried (BUG-FD-5): no 'Show N more' collapse — a line/part with 2+ fees/discounts shows all of them. Not re-driven with a 3-adjustment line this run.</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" s="2" t="inlineStr">
-        <is>
-          <t>FD-PROC-008</t>
-        </is>
-      </c>
-      <c r="B6" s="2" t="inlineStr">
-        <is>
-          <t>C28526</t>
-        </is>
-      </c>
-      <c r="C6" s="6" t="inlineStr">
-        <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/28526</t>
-        </is>
-      </c>
-      <c r="D6" s="2" t="inlineStr">
-        <is>
-          <t>Processing Fee — WO behavior</t>
-        </is>
-      </c>
-      <c r="E6" s="2" t="inlineStr">
-        <is>
-          <t>Verify a Processing Fee on a work order can be removed but not edited</t>
-        </is>
-      </c>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t>High</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>VIU-Deviation</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>The menu still offers an 'Edit' option for a Processing Fee even though editing does nothing (only 'Remove' works). A developer needs to make it remove-only. Re-test once fixed.</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>BE re-proven: pfee change -&gt; 409 'cannot be edited through this endpoint', remove -&gt; 204; card still offers Edit per batch-1 (S8-N5 UI drift) | WORDING+VIU 2026-07-13: DEVIATION carried: the ⋮ menu still shows 'Edit' for a Processing Fee but it is inert (cannot edit a pfee on the WO); 'Remove' works. Build labels ('Remove Fee / Discount' confirm). | SV-8456 (2026-07-21 staging LIVE VIU): F&amp;D moved to SETTINGS→SERVICE (below Canned Lines); template/WO/Part-sale/customer dialogs now show Taxable as a Yes/No DROPDOWN (was toggle); Auto-apply is a CHECKBOX with a 'When on…' caption; settings &amp; customer tables are plain-text/left-aligned (no badges); WO sidebar card retitled 'Work Order Fees &amp; Discounts' and renders ABOVE Financial Info; Part-sale card 'Parts Sale Fees &amp; Discounts' above Financial Info. Permission gate pivoted Settings→Finance → Settings→Service (verified live: Service-user sees+manages F&amp;D &amp; convenience toggle; Finance-only user has no F&amp;D nav item and /administration/adjustment-templates bounces to /workorders). Frontend-only; functionality + calc INTACT. | RE-VIU 2026-07-22 LIVE (Batch 4, SV-8456 re-verify): access-check quick-login {admin} HTTP 200. The SV-8456 UI-correction wording + Settings-&gt;Service permission pivot were re-confirmed live on the current staging build (Service-user sees+manages F&amp;D; Finance-only user no F&amp;D nav, direct route bounces to /workorders; Tech restored to Technician 50bf6a0d + verified; ZZAUTOTEST roles deleted). This case retains its prior VIU-Deviation for its OWN (non-SV-8456) reason — that specific behavior was NOT re-driven this pass. Ev build/fees-discounts/viu-sv8456-2026-07-22/.</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="2" t="inlineStr">
-        <is>
-          <t>FD-PROC-009</t>
-        </is>
-      </c>
-      <c r="B7" s="2" t="inlineStr">
-        <is>
-          <t>C28527</t>
-        </is>
-      </c>
-      <c r="C7" s="6" t="inlineStr">
-        <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/28527</t>
-        </is>
-      </c>
-      <c r="D7" s="2" t="inlineStr">
-        <is>
-          <t>Processing Fee — calculation</t>
-        </is>
-      </c>
-      <c r="E7" s="2" t="inlineStr">
-        <is>
-          <t>Verify a % of Grand Total Processing Fee works out last on the tax-included grand total (3% of $324 → +$9.72)</t>
-        </is>
-      </c>
-      <c r="F7" s="2" t="inlineStr">
-        <is>
-          <t>High</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
-        <is>
-          <t>VIU-Deviation</t>
-        </is>
-      </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>A developer needs to fix the Processing Fee amount — its base should NOT include the whole-work-order fees/discounts (or their tax). Re-test the amount once fixed.</t>
-        </is>
-      </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>FDBUG-2 CONFIRMED AGAIN with a clean discriminator: on a WO whose ONLY money is a whole-WO $20 taxable fee, 3% pfee resolved 0.63 (=3% of 21.00 incl the whole-WO fee + its tax); spec base must EXCLUDE whole-WO adjustments -&gt; expected 0.00 | WORDING+VIU 2026-07-13: DEVIATION carried (FDBUG-2): the Processing Fee base wrongly includes whole-WO fees/discounts + their tax (should exclude them).</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" s="2" t="inlineStr">
-        <is>
-          <t>FD-STATS-002</t>
-        </is>
-      </c>
-      <c r="B8" s="2" t="inlineStr">
-        <is>
-          <t>C28460</t>
-        </is>
-      </c>
-      <c r="C8" s="6" t="inlineStr">
-        <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/28460</t>
-        </is>
-      </c>
-      <c r="D8" s="2" t="inlineStr">
-        <is>
-          <t>Work Order — Statistics tab</t>
-        </is>
-      </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>Verify each Stats fee/discount row names its target</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>Medium</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>VIU-Deviation</t>
-        </is>
-      </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>A developer needs to change the Statistics tab to show one row per fee/discount that names its target. Re-test once that per-row layout is built.</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>per-row scope hyperlink impossible while the layout is aggregate (dep. FD-STATS-001) | WORDING+VIU 2026-07-13: DEVIATION carried: Stats F&amp;D rows show the name only — no scope hyperlink to the target. Confirmed live (rows read plain names, shot fin-01).</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" s="2" t="inlineStr">
-        <is>
-          <t>FD-STATS-004</t>
-        </is>
-      </c>
-      <c r="B9" s="2" t="inlineStr">
-        <is>
-          <t>C28462</t>
-        </is>
-      </c>
-      <c r="C9" s="6" t="inlineStr">
-        <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/28462</t>
-        </is>
-      </c>
-      <c r="D9" s="2" t="inlineStr">
-        <is>
-          <t>Work Order — Statistics tab</t>
-        </is>
-      </c>
-      <c r="E9" s="2" t="inlineStr">
-        <is>
-          <t>Verify the Stats fees/discounts are listed in the order they were created (oldest first)</t>
-        </is>
-      </c>
-      <c r="F9" s="2" t="inlineStr">
-        <is>
-          <t>Medium</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr">
-        <is>
-          <t>VIU-Deviation</t>
-        </is>
-      </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>Once the Statistics tab shows one row per fee/discount, check they are listed oldest first. Re-test after the per-row layout is built by the developer.</t>
-        </is>
-      </c>
-      <c r="I9" s="2" t="inlineStr">
-        <is>
-          <t>creation-order rows blocked by aggregate layout (dep. FD-STATS-001) | WORDING+VIU 2026-07-13: DEVIATION carried: creation-order ruling pending (BUG-FD-2 group). Labels cleaned.</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" s="2" t="inlineStr">
-        <is>
-          <t>FD-TMPL-010</t>
-        </is>
-      </c>
-      <c r="B10" s="2" t="inlineStr">
-        <is>
-          <t>C28511</t>
-        </is>
-      </c>
-      <c r="C10" s="6" t="inlineStr">
-        <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/28511</t>
-        </is>
-      </c>
-      <c r="D10" s="2" t="inlineStr">
-        <is>
-          <t>Template admin — scoping</t>
-        </is>
-      </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>Verify template scoping — labour-method templates only show in labour pickers, parts-method only in parts pickers</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>High</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
-        <is>
-          <t>VIU-Deviation</t>
-        </is>
-      </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>The line-level dialog currently has no 'Apply From Template' picker, so template scoping can't be checked there. Re-check on staging whether that picker now exists; if it is still missing, confirm with the team whether that is intended.</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>FDBUG-13 (line-scope Add dialog has no template picker) per batch-1/4; not re-driven today | WORDING+VIU 2026-07-13: DEVIATION carried: template scoping in the line 'Apply From Template' picker + the compatibility hint not re-captured this run (needs the line-level picker). Labels cleaned. | SV-8479/8480 deconfliction 2026-07-22: mixed label sweep: labor step -&gt; 'Add Labor Fee / Discount', part step -&gt; 'Add Part Fee / Discount' (behavior unchanged). | VIU 2026-07-22 LIVE: SV-8479 nav labels 'Add Labor Fee / Discount' (step 1) and 'Add Part Fee / Discount' (step 3) both confirmed present; case status unchanged (existing Deviation for its own reason). Ev: wo/FD-WO-017-labor-menu-open.png, wo/FD-WO-018-part-menu.png.</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" s="2" t="inlineStr">
-        <is>
-          <t>FD-WO-017</t>
-        </is>
-      </c>
-      <c r="B11" s="2" t="inlineStr">
-        <is>
-          <t>C30618</t>
-        </is>
-      </c>
-      <c r="C11" s="6" t="inlineStr">
-        <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/30618</t>
-        </is>
-      </c>
-      <c r="D11" s="2" t="inlineStr">
-        <is>
-          <t>Work Order — Labor-line Fee/Discount</t>
-        </is>
-      </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>Verify the labor fee/discount entry point is a three-dot menu to the LEFT of the first technician (or 'Unassigned') and reads 'Add Labor Fee / Discount'</t>
-        </is>
-      </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>High</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
-        <is>
-          <t>VIU-Deviation</t>
-        </is>
-      </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>A developer needs to move the three-dot menu to the LEFT of 'Unassigned' (it currently sits on the right); the label is already correct. Re-test the left placement once the fix is in.</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
-        <is>
-          <t>me row y=282); spec requires LEFT. Label 'Add Labor Fee / Discount' is correct and opens the labor fee/discount dialog. Menu contained only 'Add Labor Fee / Discount' (no separate 'Edit labor' item observed). Ev: wo/FD-WO-017-labor-row-menu-RIGHT.png, wo/FD-WO-017-labor-menu-open.png, obs2 geometry.</t>
-        </is>
-      </c>
-    </row>
   </sheetData>
-  <hyperlinks>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C2" r:id="rId1"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C3" r:id="rId2"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C4" r:id="rId3"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C5" r:id="rId4"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C6" r:id="rId5"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C7" r:id="rId6"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C8" r:id="rId7"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C9" r:id="rId8"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C10" r:id="rId9"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C11" r:id="rId10"/>
-  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -10441,7 +10487,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I2"/>
+  <dimension ref="A1:I1"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -10502,57 +10548,7 @@
         </is>
       </c>
     </row>
-    <row r="2">
-      <c r="A2" s="2" t="inlineStr">
-        <is>
-          <t>FD-PART-005</t>
-        </is>
-      </c>
-      <c r="B2" s="2" t="inlineStr">
-        <is>
-          <t>C28450</t>
-        </is>
-      </c>
-      <c r="C2" s="6" t="inlineStr">
-        <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/28450</t>
-        </is>
-      </c>
-      <c r="D2" s="2" t="inlineStr">
-        <is>
-          <t>Work Order / Parts — Part-line Fee/Discount</t>
-        </is>
-      </c>
-      <c r="E2" s="2" t="inlineStr">
-        <is>
-          <t>Verify a part-line fee/discount stays attached when the part changes from requested to received</t>
-        </is>
-      </c>
-      <c r="F2" s="2" t="inlineStr">
-        <is>
-          <t>Medium</t>
-        </is>
-      </c>
-      <c r="G2" s="2" t="inlineStr">
-        <is>
-          <t>VIU-Pending</t>
-        </is>
-      </c>
-      <c r="H2" s="2" t="inlineStr">
-        <is>
-          <t>Re-test on staging once a part can be moved from requested to received (this was blocked by an environment error before). Check the fee/discount stays attached after the part is received.</t>
-        </is>
-      </c>
-      <c r="I2" s="2" t="inlineStr">
-        <is>
-          <t>STILL PENDING: requested-&gt;received transition unreachable — line-create 500s env-wide, make-request rejected on completed lines, receiving subsystem needs a fresh order | WORDING+VIU 2026-07-13: BLOCKED/PENDING: requested→received transition blocked by the env-wide WO line-create 500 + completed-line part-request lock — cannot drive the transition. Build labels applied.</t>
-        </is>
-      </c>
-    </row>
   </sheetData>
-  <hyperlinks>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C2" r:id="rId1"/>
-  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
